--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI433"/>
+  <dimension ref="A1:AI449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52011,6 +52011,1910 @@
       </c>
       <c r="AI433" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>28</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>200</v>
+      </c>
+      <c r="F434" t="n">
+        <v>76</v>
+      </c>
+      <c r="G434" t="n">
+        <v>19</v>
+      </c>
+      <c r="H434" t="n">
+        <v>36</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>28</v>
+      </c>
+      <c r="K434" t="n">
+        <v>17</v>
+      </c>
+      <c r="L434" t="n">
+        <v>20</v>
+      </c>
+      <c r="M434" t="n">
+        <v>14</v>
+      </c>
+      <c r="N434" t="n">
+        <v>27</v>
+      </c>
+      <c r="O434" t="n">
+        <v>9</v>
+      </c>
+      <c r="P434" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>16</v>
+      </c>
+      <c r="R434" t="n">
+        <v>19</v>
+      </c>
+      <c r="S434" t="n">
+        <v>19</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V434" t="n">
+        <v>74</v>
+      </c>
+      <c r="W434" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="X434" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>5.848584493085781</v>
+      </c>
+      <c r="AG434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI434" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>28</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>200</v>
+      </c>
+      <c r="F435" t="n">
+        <v>80</v>
+      </c>
+      <c r="G435" t="n">
+        <v>22</v>
+      </c>
+      <c r="H435" t="n">
+        <v>43</v>
+      </c>
+      <c r="I435" t="n">
+        <v>6</v>
+      </c>
+      <c r="J435" t="n">
+        <v>18</v>
+      </c>
+      <c r="K435" t="n">
+        <v>18</v>
+      </c>
+      <c r="L435" t="n">
+        <v>26</v>
+      </c>
+      <c r="M435" t="n">
+        <v>7</v>
+      </c>
+      <c r="N435" t="n">
+        <v>25</v>
+      </c>
+      <c r="O435" t="n">
+        <v>17</v>
+      </c>
+      <c r="P435" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>13</v>
+      </c>
+      <c r="R435" t="n">
+        <v>21</v>
+      </c>
+      <c r="S435" t="n">
+        <v>22</v>
+      </c>
+      <c r="T435" t="n">
+        <v>1</v>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V435" t="n">
+        <v>79</v>
+      </c>
+      <c r="W435" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X435" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>0.5079365079365079</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>2.190903518046071</v>
+      </c>
+      <c r="AG435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI435" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>28</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>200</v>
+      </c>
+      <c r="F436" t="n">
+        <v>56</v>
+      </c>
+      <c r="G436" t="n">
+        <v>12</v>
+      </c>
+      <c r="H436" t="n">
+        <v>47</v>
+      </c>
+      <c r="I436" t="n">
+        <v>5</v>
+      </c>
+      <c r="J436" t="n">
+        <v>17</v>
+      </c>
+      <c r="K436" t="n">
+        <v>17</v>
+      </c>
+      <c r="L436" t="n">
+        <v>27</v>
+      </c>
+      <c r="M436" t="n">
+        <v>15</v>
+      </c>
+      <c r="N436" t="n">
+        <v>26</v>
+      </c>
+      <c r="O436" t="n">
+        <v>10</v>
+      </c>
+      <c r="P436" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>11</v>
+      </c>
+      <c r="R436" t="n">
+        <v>25</v>
+      </c>
+      <c r="S436" t="n">
+        <v>24</v>
+      </c>
+      <c r="T436" t="n">
+        <v>3</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V436" t="n">
+        <v>72</v>
+      </c>
+      <c r="W436" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="X436" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0.3061224489795918</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0.4939759036144578</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>-19.86532566650253</v>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI436" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>28</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>200</v>
+      </c>
+      <c r="F437" t="n">
+        <v>79</v>
+      </c>
+      <c r="G437" t="n">
+        <v>21</v>
+      </c>
+      <c r="H437" t="n">
+        <v>35</v>
+      </c>
+      <c r="I437" t="n">
+        <v>8</v>
+      </c>
+      <c r="J437" t="n">
+        <v>31</v>
+      </c>
+      <c r="K437" t="n">
+        <v>13</v>
+      </c>
+      <c r="L437" t="n">
+        <v>14</v>
+      </c>
+      <c r="M437" t="n">
+        <v>7</v>
+      </c>
+      <c r="N437" t="n">
+        <v>24</v>
+      </c>
+      <c r="O437" t="n">
+        <v>19</v>
+      </c>
+      <c r="P437" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>14</v>
+      </c>
+      <c r="R437" t="n">
+        <v>22</v>
+      </c>
+      <c r="S437" t="n">
+        <v>21</v>
+      </c>
+      <c r="T437" t="n">
+        <v>6</v>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V437" t="n">
+        <v>80</v>
+      </c>
+      <c r="W437" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="X437" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>79.16</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>0.492063492063492</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>-2.190903518046071</v>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI437" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>28</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>200</v>
+      </c>
+      <c r="F438" t="n">
+        <v>79</v>
+      </c>
+      <c r="G438" t="n">
+        <v>18</v>
+      </c>
+      <c r="H438" t="n">
+        <v>38</v>
+      </c>
+      <c r="I438" t="n">
+        <v>6</v>
+      </c>
+      <c r="J438" t="n">
+        <v>23</v>
+      </c>
+      <c r="K438" t="n">
+        <v>25</v>
+      </c>
+      <c r="L438" t="n">
+        <v>29</v>
+      </c>
+      <c r="M438" t="n">
+        <v>7</v>
+      </c>
+      <c r="N438" t="n">
+        <v>22</v>
+      </c>
+      <c r="O438" t="n">
+        <v>18</v>
+      </c>
+      <c r="P438" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" t="n">
+        <v>20</v>
+      </c>
+      <c r="S438" t="n">
+        <v>23</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V438" t="n">
+        <v>88</v>
+      </c>
+      <c r="W438" t="n">
+        <v>83.75999999999999</v>
+      </c>
+      <c r="X438" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>0.4202898550724637</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>-15.23433761206408</v>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI438" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>28</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>200</v>
+      </c>
+      <c r="F439" t="n">
+        <v>84</v>
+      </c>
+      <c r="G439" t="n">
+        <v>17</v>
+      </c>
+      <c r="H439" t="n">
+        <v>35</v>
+      </c>
+      <c r="I439" t="n">
+        <v>12</v>
+      </c>
+      <c r="J439" t="n">
+        <v>26</v>
+      </c>
+      <c r="K439" t="n">
+        <v>14</v>
+      </c>
+      <c r="L439" t="n">
+        <v>17</v>
+      </c>
+      <c r="M439" t="n">
+        <v>8</v>
+      </c>
+      <c r="N439" t="n">
+        <v>17</v>
+      </c>
+      <c r="O439" t="n">
+        <v>21</v>
+      </c>
+      <c r="P439" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>12</v>
+      </c>
+      <c r="R439" t="n">
+        <v>24</v>
+      </c>
+      <c r="S439" t="n">
+        <v>18</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>90</v>
+      </c>
+      <c r="W439" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="X439" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>-7.191299433390824</v>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI439" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>28</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>200</v>
+      </c>
+      <c r="F440" t="n">
+        <v>70</v>
+      </c>
+      <c r="G440" t="n">
+        <v>19</v>
+      </c>
+      <c r="H440" t="n">
+        <v>34</v>
+      </c>
+      <c r="I440" t="n">
+        <v>7</v>
+      </c>
+      <c r="J440" t="n">
+        <v>28</v>
+      </c>
+      <c r="K440" t="n">
+        <v>11</v>
+      </c>
+      <c r="L440" t="n">
+        <v>17</v>
+      </c>
+      <c r="M440" t="n">
+        <v>14</v>
+      </c>
+      <c r="N440" t="n">
+        <v>15</v>
+      </c>
+      <c r="O440" t="n">
+        <v>15</v>
+      </c>
+      <c r="P440" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>13</v>
+      </c>
+      <c r="R440" t="n">
+        <v>23</v>
+      </c>
+      <c r="S440" t="n">
+        <v>21</v>
+      </c>
+      <c r="T440" t="n">
+        <v>3</v>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V440" t="n">
+        <v>88</v>
+      </c>
+      <c r="W440" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="X440" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>-30.47036176904953</v>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI440" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>28</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>200</v>
+      </c>
+      <c r="F441" t="n">
+        <v>88</v>
+      </c>
+      <c r="G441" t="n">
+        <v>18</v>
+      </c>
+      <c r="H441" t="n">
+        <v>29</v>
+      </c>
+      <c r="I441" t="n">
+        <v>9</v>
+      </c>
+      <c r="J441" t="n">
+        <v>22</v>
+      </c>
+      <c r="K441" t="n">
+        <v>25</v>
+      </c>
+      <c r="L441" t="n">
+        <v>28</v>
+      </c>
+      <c r="M441" t="n">
+        <v>8</v>
+      </c>
+      <c r="N441" t="n">
+        <v>22</v>
+      </c>
+      <c r="O441" t="n">
+        <v>27</v>
+      </c>
+      <c r="P441" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>11</v>
+      </c>
+      <c r="R441" t="n">
+        <v>21</v>
+      </c>
+      <c r="S441" t="n">
+        <v>23</v>
+      </c>
+      <c r="T441" t="n">
+        <v>1</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V441" t="n">
+        <v>70</v>
+      </c>
+      <c r="W441" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="X441" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>66.31999999999999</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0.5084745762711864</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>30.47036176904953</v>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI441" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>28</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>200</v>
+      </c>
+      <c r="F442" t="n">
+        <v>74</v>
+      </c>
+      <c r="G442" t="n">
+        <v>17</v>
+      </c>
+      <c r="H442" t="n">
+        <v>44</v>
+      </c>
+      <c r="I442" t="n">
+        <v>10</v>
+      </c>
+      <c r="J442" t="n">
+        <v>23</v>
+      </c>
+      <c r="K442" t="n">
+        <v>10</v>
+      </c>
+      <c r="L442" t="n">
+        <v>12</v>
+      </c>
+      <c r="M442" t="n">
+        <v>8</v>
+      </c>
+      <c r="N442" t="n">
+        <v>24</v>
+      </c>
+      <c r="O442" t="n">
+        <v>10</v>
+      </c>
+      <c r="P442" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>13</v>
+      </c>
+      <c r="R442" t="n">
+        <v>20</v>
+      </c>
+      <c r="S442" t="n">
+        <v>19</v>
+      </c>
+      <c r="T442" t="n">
+        <v>2</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>76</v>
+      </c>
+      <c r="W442" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="X442" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>0.4383561643835616</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>-5.848584493085781</v>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI442" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>28</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>200</v>
+      </c>
+      <c r="F443" t="n">
+        <v>54</v>
+      </c>
+      <c r="G443" t="n">
+        <v>22</v>
+      </c>
+      <c r="H443" t="n">
+        <v>39</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
+        <v>28</v>
+      </c>
+      <c r="K443" t="n">
+        <v>7</v>
+      </c>
+      <c r="L443" t="n">
+        <v>13</v>
+      </c>
+      <c r="M443" t="n">
+        <v>12</v>
+      </c>
+      <c r="N443" t="n">
+        <v>29</v>
+      </c>
+      <c r="O443" t="n">
+        <v>16</v>
+      </c>
+      <c r="P443" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>14</v>
+      </c>
+      <c r="R443" t="n">
+        <v>17</v>
+      </c>
+      <c r="S443" t="n">
+        <v>18</v>
+      </c>
+      <c r="T443" t="n">
+        <v>5</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V443" t="n">
+        <v>73</v>
+      </c>
+      <c r="W443" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="X443" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>-32.91751260421231</v>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI443" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>28</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>200</v>
+      </c>
+      <c r="F444" t="n">
+        <v>88</v>
+      </c>
+      <c r="G444" t="n">
+        <v>24</v>
+      </c>
+      <c r="H444" t="n">
+        <v>48</v>
+      </c>
+      <c r="I444" t="n">
+        <v>9</v>
+      </c>
+      <c r="J444" t="n">
+        <v>26</v>
+      </c>
+      <c r="K444" t="n">
+        <v>13</v>
+      </c>
+      <c r="L444" t="n">
+        <v>17</v>
+      </c>
+      <c r="M444" t="n">
+        <v>14</v>
+      </c>
+      <c r="N444" t="n">
+        <v>26</v>
+      </c>
+      <c r="O444" t="n">
+        <v>14</v>
+      </c>
+      <c r="P444" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>7</v>
+      </c>
+      <c r="R444" t="n">
+        <v>23</v>
+      </c>
+      <c r="S444" t="n">
+        <v>20</v>
+      </c>
+      <c r="T444" t="n">
+        <v>2</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>79</v>
+      </c>
+      <c r="W444" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="X444" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>0.5797101449275363</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>15.23433761206408</v>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI444" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>28</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>200</v>
+      </c>
+      <c r="F445" t="n">
+        <v>73</v>
+      </c>
+      <c r="G445" t="n">
+        <v>13</v>
+      </c>
+      <c r="H445" t="n">
+        <v>28</v>
+      </c>
+      <c r="I445" t="n">
+        <v>13</v>
+      </c>
+      <c r="J445" t="n">
+        <v>38</v>
+      </c>
+      <c r="K445" t="n">
+        <v>8</v>
+      </c>
+      <c r="L445" t="n">
+        <v>10</v>
+      </c>
+      <c r="M445" t="n">
+        <v>11</v>
+      </c>
+      <c r="N445" t="n">
+        <v>26</v>
+      </c>
+      <c r="O445" t="n">
+        <v>18</v>
+      </c>
+      <c r="P445" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>10</v>
+      </c>
+      <c r="R445" t="n">
+        <v>18</v>
+      </c>
+      <c r="S445" t="n">
+        <v>17</v>
+      </c>
+      <c r="T445" t="n">
+        <v>1</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>54</v>
+      </c>
+      <c r="W445" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="X445" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>32.91751260421231</v>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI445" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>28</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>200</v>
+      </c>
+      <c r="F446" t="n">
+        <v>81</v>
+      </c>
+      <c r="G446" t="n">
+        <v>20</v>
+      </c>
+      <c r="H446" t="n">
+        <v>30</v>
+      </c>
+      <c r="I446" t="n">
+        <v>10</v>
+      </c>
+      <c r="J446" t="n">
+        <v>34</v>
+      </c>
+      <c r="K446" t="n">
+        <v>11</v>
+      </c>
+      <c r="L446" t="n">
+        <v>19</v>
+      </c>
+      <c r="M446" t="n">
+        <v>13</v>
+      </c>
+      <c r="N446" t="n">
+        <v>26</v>
+      </c>
+      <c r="O446" t="n">
+        <v>18</v>
+      </c>
+      <c r="P446" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>10</v>
+      </c>
+      <c r="R446" t="n">
+        <v>23</v>
+      </c>
+      <c r="S446" t="n">
+        <v>21</v>
+      </c>
+      <c r="T446" t="n">
+        <v>5</v>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>53</v>
+      </c>
+      <c r="W446" t="n">
+        <v>82.36</v>
+      </c>
+      <c r="X446" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>47.48284374049891</v>
+      </c>
+      <c r="AG446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI446" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>28</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>200</v>
+      </c>
+      <c r="F447" t="n">
+        <v>90</v>
+      </c>
+      <c r="G447" t="n">
+        <v>19</v>
+      </c>
+      <c r="H447" t="n">
+        <v>27</v>
+      </c>
+      <c r="I447" t="n">
+        <v>11</v>
+      </c>
+      <c r="J447" t="n">
+        <v>32</v>
+      </c>
+      <c r="K447" t="n">
+        <v>19</v>
+      </c>
+      <c r="L447" t="n">
+        <v>23</v>
+      </c>
+      <c r="M447" t="n">
+        <v>8</v>
+      </c>
+      <c r="N447" t="n">
+        <v>22</v>
+      </c>
+      <c r="O447" t="n">
+        <v>16</v>
+      </c>
+      <c r="P447" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>12</v>
+      </c>
+      <c r="R447" t="n">
+        <v>18</v>
+      </c>
+      <c r="S447" t="n">
+        <v>24</v>
+      </c>
+      <c r="T447" t="n">
+        <v>1</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>84</v>
+      </c>
+      <c r="W447" t="n">
+        <v>81.12</v>
+      </c>
+      <c r="X447" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>7.191299433390824</v>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI447" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>28</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>200</v>
+      </c>
+      <c r="F448" t="n">
+        <v>72</v>
+      </c>
+      <c r="G448" t="n">
+        <v>16</v>
+      </c>
+      <c r="H448" t="n">
+        <v>33</v>
+      </c>
+      <c r="I448" t="n">
+        <v>6</v>
+      </c>
+      <c r="J448" t="n">
+        <v>24</v>
+      </c>
+      <c r="K448" t="n">
+        <v>22</v>
+      </c>
+      <c r="L448" t="n">
+        <v>31</v>
+      </c>
+      <c r="M448" t="n">
+        <v>8</v>
+      </c>
+      <c r="N448" t="n">
+        <v>34</v>
+      </c>
+      <c r="O448" t="n">
+        <v>15</v>
+      </c>
+      <c r="P448" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>11</v>
+      </c>
+      <c r="R448" t="n">
+        <v>24</v>
+      </c>
+      <c r="S448" t="n">
+        <v>25</v>
+      </c>
+      <c r="T448" t="n">
+        <v>7</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>56</v>
+      </c>
+      <c r="W448" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="X448" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>19.86532566650253</v>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI448" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>28</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>200</v>
+      </c>
+      <c r="F449" t="n">
+        <v>53</v>
+      </c>
+      <c r="G449" t="n">
+        <v>15</v>
+      </c>
+      <c r="H449" t="n">
+        <v>41</v>
+      </c>
+      <c r="I449" t="n">
+        <v>4</v>
+      </c>
+      <c r="J449" t="n">
+        <v>23</v>
+      </c>
+      <c r="K449" t="n">
+        <v>11</v>
+      </c>
+      <c r="L449" t="n">
+        <v>17</v>
+      </c>
+      <c r="M449" t="n">
+        <v>10</v>
+      </c>
+      <c r="N449" t="n">
+        <v>20</v>
+      </c>
+      <c r="O449" t="n">
+        <v>8</v>
+      </c>
+      <c r="P449" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>15</v>
+      </c>
+      <c r="R449" t="n">
+        <v>21</v>
+      </c>
+      <c r="S449" t="n">
+        <v>23</v>
+      </c>
+      <c r="T449" t="n">
+        <v>1</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>81</v>
+      </c>
+      <c r="W449" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="X449" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>-47.48284374049891</v>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI449" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI433"/>
+  <dimension ref="A1:AI465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52010,6 +52010,3814 @@
         </is>
       </c>
       <c r="AI433" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>28</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>200</v>
+      </c>
+      <c r="F434" t="n">
+        <v>76</v>
+      </c>
+      <c r="G434" t="n">
+        <v>19</v>
+      </c>
+      <c r="H434" t="n">
+        <v>36</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>28</v>
+      </c>
+      <c r="K434" t="n">
+        <v>17</v>
+      </c>
+      <c r="L434" t="n">
+        <v>20</v>
+      </c>
+      <c r="M434" t="n">
+        <v>14</v>
+      </c>
+      <c r="N434" t="n">
+        <v>27</v>
+      </c>
+      <c r="O434" t="n">
+        <v>9</v>
+      </c>
+      <c r="P434" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>16</v>
+      </c>
+      <c r="R434" t="n">
+        <v>19</v>
+      </c>
+      <c r="S434" t="n">
+        <v>19</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V434" t="n">
+        <v>74</v>
+      </c>
+      <c r="W434" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="X434" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>5.848584493085781</v>
+      </c>
+      <c r="AG434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI434" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>28</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>200</v>
+      </c>
+      <c r="F435" t="n">
+        <v>80</v>
+      </c>
+      <c r="G435" t="n">
+        <v>22</v>
+      </c>
+      <c r="H435" t="n">
+        <v>43</v>
+      </c>
+      <c r="I435" t="n">
+        <v>6</v>
+      </c>
+      <c r="J435" t="n">
+        <v>18</v>
+      </c>
+      <c r="K435" t="n">
+        <v>18</v>
+      </c>
+      <c r="L435" t="n">
+        <v>26</v>
+      </c>
+      <c r="M435" t="n">
+        <v>7</v>
+      </c>
+      <c r="N435" t="n">
+        <v>25</v>
+      </c>
+      <c r="O435" t="n">
+        <v>17</v>
+      </c>
+      <c r="P435" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>13</v>
+      </c>
+      <c r="R435" t="n">
+        <v>21</v>
+      </c>
+      <c r="S435" t="n">
+        <v>22</v>
+      </c>
+      <c r="T435" t="n">
+        <v>1</v>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V435" t="n">
+        <v>79</v>
+      </c>
+      <c r="W435" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X435" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>0.5079365079365079</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>2.190903518046071</v>
+      </c>
+      <c r="AG435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI435" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>28</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>200</v>
+      </c>
+      <c r="F436" t="n">
+        <v>56</v>
+      </c>
+      <c r="G436" t="n">
+        <v>12</v>
+      </c>
+      <c r="H436" t="n">
+        <v>47</v>
+      </c>
+      <c r="I436" t="n">
+        <v>5</v>
+      </c>
+      <c r="J436" t="n">
+        <v>17</v>
+      </c>
+      <c r="K436" t="n">
+        <v>17</v>
+      </c>
+      <c r="L436" t="n">
+        <v>27</v>
+      </c>
+      <c r="M436" t="n">
+        <v>15</v>
+      </c>
+      <c r="N436" t="n">
+        <v>26</v>
+      </c>
+      <c r="O436" t="n">
+        <v>10</v>
+      </c>
+      <c r="P436" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>11</v>
+      </c>
+      <c r="R436" t="n">
+        <v>25</v>
+      </c>
+      <c r="S436" t="n">
+        <v>24</v>
+      </c>
+      <c r="T436" t="n">
+        <v>3</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V436" t="n">
+        <v>72</v>
+      </c>
+      <c r="W436" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="X436" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0.3061224489795918</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0.4939759036144578</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>-19.86532566650253</v>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI436" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>28</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>200</v>
+      </c>
+      <c r="F437" t="n">
+        <v>79</v>
+      </c>
+      <c r="G437" t="n">
+        <v>21</v>
+      </c>
+      <c r="H437" t="n">
+        <v>35</v>
+      </c>
+      <c r="I437" t="n">
+        <v>8</v>
+      </c>
+      <c r="J437" t="n">
+        <v>31</v>
+      </c>
+      <c r="K437" t="n">
+        <v>13</v>
+      </c>
+      <c r="L437" t="n">
+        <v>14</v>
+      </c>
+      <c r="M437" t="n">
+        <v>7</v>
+      </c>
+      <c r="N437" t="n">
+        <v>24</v>
+      </c>
+      <c r="O437" t="n">
+        <v>19</v>
+      </c>
+      <c r="P437" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>14</v>
+      </c>
+      <c r="R437" t="n">
+        <v>22</v>
+      </c>
+      <c r="S437" t="n">
+        <v>21</v>
+      </c>
+      <c r="T437" t="n">
+        <v>6</v>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V437" t="n">
+        <v>80</v>
+      </c>
+      <c r="W437" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="X437" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>79.16</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>0.492063492063492</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>-2.190903518046071</v>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI437" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>28</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>200</v>
+      </c>
+      <c r="F438" t="n">
+        <v>79</v>
+      </c>
+      <c r="G438" t="n">
+        <v>18</v>
+      </c>
+      <c r="H438" t="n">
+        <v>38</v>
+      </c>
+      <c r="I438" t="n">
+        <v>6</v>
+      </c>
+      <c r="J438" t="n">
+        <v>23</v>
+      </c>
+      <c r="K438" t="n">
+        <v>25</v>
+      </c>
+      <c r="L438" t="n">
+        <v>29</v>
+      </c>
+      <c r="M438" t="n">
+        <v>7</v>
+      </c>
+      <c r="N438" t="n">
+        <v>22</v>
+      </c>
+      <c r="O438" t="n">
+        <v>18</v>
+      </c>
+      <c r="P438" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" t="n">
+        <v>20</v>
+      </c>
+      <c r="S438" t="n">
+        <v>23</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V438" t="n">
+        <v>88</v>
+      </c>
+      <c r="W438" t="n">
+        <v>83.75999999999999</v>
+      </c>
+      <c r="X438" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>0.4202898550724637</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>-15.23433761206408</v>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI438" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>28</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>200</v>
+      </c>
+      <c r="F439" t="n">
+        <v>84</v>
+      </c>
+      <c r="G439" t="n">
+        <v>17</v>
+      </c>
+      <c r="H439" t="n">
+        <v>35</v>
+      </c>
+      <c r="I439" t="n">
+        <v>12</v>
+      </c>
+      <c r="J439" t="n">
+        <v>26</v>
+      </c>
+      <c r="K439" t="n">
+        <v>14</v>
+      </c>
+      <c r="L439" t="n">
+        <v>17</v>
+      </c>
+      <c r="M439" t="n">
+        <v>8</v>
+      </c>
+      <c r="N439" t="n">
+        <v>17</v>
+      </c>
+      <c r="O439" t="n">
+        <v>21</v>
+      </c>
+      <c r="P439" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>12</v>
+      </c>
+      <c r="R439" t="n">
+        <v>24</v>
+      </c>
+      <c r="S439" t="n">
+        <v>18</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>90</v>
+      </c>
+      <c r="W439" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="X439" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>-7.191299433390824</v>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI439" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>28</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>200</v>
+      </c>
+      <c r="F440" t="n">
+        <v>70</v>
+      </c>
+      <c r="G440" t="n">
+        <v>19</v>
+      </c>
+      <c r="H440" t="n">
+        <v>34</v>
+      </c>
+      <c r="I440" t="n">
+        <v>7</v>
+      </c>
+      <c r="J440" t="n">
+        <v>28</v>
+      </c>
+      <c r="K440" t="n">
+        <v>11</v>
+      </c>
+      <c r="L440" t="n">
+        <v>17</v>
+      </c>
+      <c r="M440" t="n">
+        <v>14</v>
+      </c>
+      <c r="N440" t="n">
+        <v>15</v>
+      </c>
+      <c r="O440" t="n">
+        <v>15</v>
+      </c>
+      <c r="P440" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>13</v>
+      </c>
+      <c r="R440" t="n">
+        <v>23</v>
+      </c>
+      <c r="S440" t="n">
+        <v>21</v>
+      </c>
+      <c r="T440" t="n">
+        <v>3</v>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V440" t="n">
+        <v>88</v>
+      </c>
+      <c r="W440" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="X440" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>-30.47036176904953</v>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI440" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>28</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>200</v>
+      </c>
+      <c r="F441" t="n">
+        <v>88</v>
+      </c>
+      <c r="G441" t="n">
+        <v>18</v>
+      </c>
+      <c r="H441" t="n">
+        <v>29</v>
+      </c>
+      <c r="I441" t="n">
+        <v>9</v>
+      </c>
+      <c r="J441" t="n">
+        <v>22</v>
+      </c>
+      <c r="K441" t="n">
+        <v>25</v>
+      </c>
+      <c r="L441" t="n">
+        <v>28</v>
+      </c>
+      <c r="M441" t="n">
+        <v>8</v>
+      </c>
+      <c r="N441" t="n">
+        <v>22</v>
+      </c>
+      <c r="O441" t="n">
+        <v>27</v>
+      </c>
+      <c r="P441" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>11</v>
+      </c>
+      <c r="R441" t="n">
+        <v>21</v>
+      </c>
+      <c r="S441" t="n">
+        <v>23</v>
+      </c>
+      <c r="T441" t="n">
+        <v>1</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V441" t="n">
+        <v>70</v>
+      </c>
+      <c r="W441" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="X441" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>66.31999999999999</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0.5084745762711864</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>30.47036176904953</v>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI441" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>28</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>200</v>
+      </c>
+      <c r="F442" t="n">
+        <v>74</v>
+      </c>
+      <c r="G442" t="n">
+        <v>17</v>
+      </c>
+      <c r="H442" t="n">
+        <v>44</v>
+      </c>
+      <c r="I442" t="n">
+        <v>10</v>
+      </c>
+      <c r="J442" t="n">
+        <v>23</v>
+      </c>
+      <c r="K442" t="n">
+        <v>10</v>
+      </c>
+      <c r="L442" t="n">
+        <v>12</v>
+      </c>
+      <c r="M442" t="n">
+        <v>8</v>
+      </c>
+      <c r="N442" t="n">
+        <v>24</v>
+      </c>
+      <c r="O442" t="n">
+        <v>10</v>
+      </c>
+      <c r="P442" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>13</v>
+      </c>
+      <c r="R442" t="n">
+        <v>20</v>
+      </c>
+      <c r="S442" t="n">
+        <v>19</v>
+      </c>
+      <c r="T442" t="n">
+        <v>2</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>76</v>
+      </c>
+      <c r="W442" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="X442" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>0.4383561643835616</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>-5.848584493085781</v>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI442" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>28</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>200</v>
+      </c>
+      <c r="F443" t="n">
+        <v>54</v>
+      </c>
+      <c r="G443" t="n">
+        <v>22</v>
+      </c>
+      <c r="H443" t="n">
+        <v>39</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
+        <v>28</v>
+      </c>
+      <c r="K443" t="n">
+        <v>7</v>
+      </c>
+      <c r="L443" t="n">
+        <v>13</v>
+      </c>
+      <c r="M443" t="n">
+        <v>12</v>
+      </c>
+      <c r="N443" t="n">
+        <v>29</v>
+      </c>
+      <c r="O443" t="n">
+        <v>16</v>
+      </c>
+      <c r="P443" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>14</v>
+      </c>
+      <c r="R443" t="n">
+        <v>17</v>
+      </c>
+      <c r="S443" t="n">
+        <v>18</v>
+      </c>
+      <c r="T443" t="n">
+        <v>5</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V443" t="n">
+        <v>73</v>
+      </c>
+      <c r="W443" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="X443" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>-32.91751260421231</v>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI443" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>28</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>200</v>
+      </c>
+      <c r="F444" t="n">
+        <v>88</v>
+      </c>
+      <c r="G444" t="n">
+        <v>24</v>
+      </c>
+      <c r="H444" t="n">
+        <v>48</v>
+      </c>
+      <c r="I444" t="n">
+        <v>9</v>
+      </c>
+      <c r="J444" t="n">
+        <v>26</v>
+      </c>
+      <c r="K444" t="n">
+        <v>13</v>
+      </c>
+      <c r="L444" t="n">
+        <v>17</v>
+      </c>
+      <c r="M444" t="n">
+        <v>14</v>
+      </c>
+      <c r="N444" t="n">
+        <v>26</v>
+      </c>
+      <c r="O444" t="n">
+        <v>14</v>
+      </c>
+      <c r="P444" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>7</v>
+      </c>
+      <c r="R444" t="n">
+        <v>23</v>
+      </c>
+      <c r="S444" t="n">
+        <v>20</v>
+      </c>
+      <c r="T444" t="n">
+        <v>2</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>79</v>
+      </c>
+      <c r="W444" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="X444" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>0.5797101449275363</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>15.23433761206408</v>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI444" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>28</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>200</v>
+      </c>
+      <c r="F445" t="n">
+        <v>73</v>
+      </c>
+      <c r="G445" t="n">
+        <v>13</v>
+      </c>
+      <c r="H445" t="n">
+        <v>28</v>
+      </c>
+      <c r="I445" t="n">
+        <v>13</v>
+      </c>
+      <c r="J445" t="n">
+        <v>38</v>
+      </c>
+      <c r="K445" t="n">
+        <v>8</v>
+      </c>
+      <c r="L445" t="n">
+        <v>10</v>
+      </c>
+      <c r="M445" t="n">
+        <v>11</v>
+      </c>
+      <c r="N445" t="n">
+        <v>26</v>
+      </c>
+      <c r="O445" t="n">
+        <v>18</v>
+      </c>
+      <c r="P445" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>10</v>
+      </c>
+      <c r="R445" t="n">
+        <v>18</v>
+      </c>
+      <c r="S445" t="n">
+        <v>17</v>
+      </c>
+      <c r="T445" t="n">
+        <v>1</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>54</v>
+      </c>
+      <c r="W445" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="X445" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>32.91751260421231</v>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI445" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>28</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>200</v>
+      </c>
+      <c r="F446" t="n">
+        <v>81</v>
+      </c>
+      <c r="G446" t="n">
+        <v>20</v>
+      </c>
+      <c r="H446" t="n">
+        <v>30</v>
+      </c>
+      <c r="I446" t="n">
+        <v>10</v>
+      </c>
+      <c r="J446" t="n">
+        <v>34</v>
+      </c>
+      <c r="K446" t="n">
+        <v>11</v>
+      </c>
+      <c r="L446" t="n">
+        <v>19</v>
+      </c>
+      <c r="M446" t="n">
+        <v>13</v>
+      </c>
+      <c r="N446" t="n">
+        <v>26</v>
+      </c>
+      <c r="O446" t="n">
+        <v>18</v>
+      </c>
+      <c r="P446" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>10</v>
+      </c>
+      <c r="R446" t="n">
+        <v>23</v>
+      </c>
+      <c r="S446" t="n">
+        <v>21</v>
+      </c>
+      <c r="T446" t="n">
+        <v>5</v>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>53</v>
+      </c>
+      <c r="W446" t="n">
+        <v>82.36</v>
+      </c>
+      <c r="X446" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>47.48284374049891</v>
+      </c>
+      <c r="AG446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI446" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>28</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>200</v>
+      </c>
+      <c r="F447" t="n">
+        <v>90</v>
+      </c>
+      <c r="G447" t="n">
+        <v>19</v>
+      </c>
+      <c r="H447" t="n">
+        <v>27</v>
+      </c>
+      <c r="I447" t="n">
+        <v>11</v>
+      </c>
+      <c r="J447" t="n">
+        <v>32</v>
+      </c>
+      <c r="K447" t="n">
+        <v>19</v>
+      </c>
+      <c r="L447" t="n">
+        <v>23</v>
+      </c>
+      <c r="M447" t="n">
+        <v>8</v>
+      </c>
+      <c r="N447" t="n">
+        <v>22</v>
+      </c>
+      <c r="O447" t="n">
+        <v>16</v>
+      </c>
+      <c r="P447" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>12</v>
+      </c>
+      <c r="R447" t="n">
+        <v>18</v>
+      </c>
+      <c r="S447" t="n">
+        <v>24</v>
+      </c>
+      <c r="T447" t="n">
+        <v>1</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>84</v>
+      </c>
+      <c r="W447" t="n">
+        <v>81.12</v>
+      </c>
+      <c r="X447" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>7.191299433390824</v>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI447" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>28</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>200</v>
+      </c>
+      <c r="F448" t="n">
+        <v>72</v>
+      </c>
+      <c r="G448" t="n">
+        <v>16</v>
+      </c>
+      <c r="H448" t="n">
+        <v>33</v>
+      </c>
+      <c r="I448" t="n">
+        <v>6</v>
+      </c>
+      <c r="J448" t="n">
+        <v>24</v>
+      </c>
+      <c r="K448" t="n">
+        <v>22</v>
+      </c>
+      <c r="L448" t="n">
+        <v>31</v>
+      </c>
+      <c r="M448" t="n">
+        <v>8</v>
+      </c>
+      <c r="N448" t="n">
+        <v>34</v>
+      </c>
+      <c r="O448" t="n">
+        <v>15</v>
+      </c>
+      <c r="P448" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>11</v>
+      </c>
+      <c r="R448" t="n">
+        <v>24</v>
+      </c>
+      <c r="S448" t="n">
+        <v>25</v>
+      </c>
+      <c r="T448" t="n">
+        <v>7</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>56</v>
+      </c>
+      <c r="W448" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="X448" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>19.86532566650253</v>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI448" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>28</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>200</v>
+      </c>
+      <c r="F449" t="n">
+        <v>53</v>
+      </c>
+      <c r="G449" t="n">
+        <v>15</v>
+      </c>
+      <c r="H449" t="n">
+        <v>41</v>
+      </c>
+      <c r="I449" t="n">
+        <v>4</v>
+      </c>
+      <c r="J449" t="n">
+        <v>23</v>
+      </c>
+      <c r="K449" t="n">
+        <v>11</v>
+      </c>
+      <c r="L449" t="n">
+        <v>17</v>
+      </c>
+      <c r="M449" t="n">
+        <v>10</v>
+      </c>
+      <c r="N449" t="n">
+        <v>20</v>
+      </c>
+      <c r="O449" t="n">
+        <v>8</v>
+      </c>
+      <c r="P449" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>15</v>
+      </c>
+      <c r="R449" t="n">
+        <v>21</v>
+      </c>
+      <c r="S449" t="n">
+        <v>23</v>
+      </c>
+      <c r="T449" t="n">
+        <v>1</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>81</v>
+      </c>
+      <c r="W449" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="X449" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>-47.48284374049891</v>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI449" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>29</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>200</v>
+      </c>
+      <c r="F450" t="n">
+        <v>65</v>
+      </c>
+      <c r="G450" t="n">
+        <v>12</v>
+      </c>
+      <c r="H450" t="n">
+        <v>25</v>
+      </c>
+      <c r="I450" t="n">
+        <v>11</v>
+      </c>
+      <c r="J450" t="n">
+        <v>32</v>
+      </c>
+      <c r="K450" t="n">
+        <v>8</v>
+      </c>
+      <c r="L450" t="n">
+        <v>12</v>
+      </c>
+      <c r="M450" t="n">
+        <v>10</v>
+      </c>
+      <c r="N450" t="n">
+        <v>22</v>
+      </c>
+      <c r="O450" t="n">
+        <v>11</v>
+      </c>
+      <c r="P450" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>17</v>
+      </c>
+      <c r="R450" t="n">
+        <v>22</v>
+      </c>
+      <c r="S450" t="n">
+        <v>18</v>
+      </c>
+      <c r="T450" t="n">
+        <v>2</v>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="V450" t="n">
+        <v>73</v>
+      </c>
+      <c r="W450" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="X450" t="n">
+        <v>0.8198789101917255</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>93.82217090069284</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>0.9292260692464358</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>100.606394707828</v>
+      </c>
+      <c r="AC450" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AD450" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>0.5245901639344263</v>
+      </c>
+      <c r="AF450" t="n">
+        <v>-6.784223807135163</v>
+      </c>
+      <c r="AG450" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI450" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>29</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>200</v>
+      </c>
+      <c r="F451" t="n">
+        <v>81</v>
+      </c>
+      <c r="G451" t="n">
+        <v>15</v>
+      </c>
+      <c r="H451" t="n">
+        <v>32</v>
+      </c>
+      <c r="I451" t="n">
+        <v>8</v>
+      </c>
+      <c r="J451" t="n">
+        <v>31</v>
+      </c>
+      <c r="K451" t="n">
+        <v>27</v>
+      </c>
+      <c r="L451" t="n">
+        <v>30</v>
+      </c>
+      <c r="M451" t="n">
+        <v>14</v>
+      </c>
+      <c r="N451" t="n">
+        <v>15</v>
+      </c>
+      <c r="O451" t="n">
+        <v>19</v>
+      </c>
+      <c r="P451" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>12</v>
+      </c>
+      <c r="R451" t="n">
+        <v>19</v>
+      </c>
+      <c r="S451" t="n">
+        <v>22</v>
+      </c>
+      <c r="T451" t="n">
+        <v>3</v>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="V451" t="n">
+        <v>79</v>
+      </c>
+      <c r="W451" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="X451" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>109.1644204851752</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>0.9748272458045411</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>108.1599123767799</v>
+      </c>
+      <c r="AC451" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="AD451" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF451" t="n">
+        <v>1.004508108395342</v>
+      </c>
+      <c r="AG451" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI451" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>29</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>200</v>
+      </c>
+      <c r="F452" t="n">
+        <v>67</v>
+      </c>
+      <c r="G452" t="n">
+        <v>17</v>
+      </c>
+      <c r="H452" t="n">
+        <v>41</v>
+      </c>
+      <c r="I452" t="n">
+        <v>7</v>
+      </c>
+      <c r="J452" t="n">
+        <v>27</v>
+      </c>
+      <c r="K452" t="n">
+        <v>12</v>
+      </c>
+      <c r="L452" t="n">
+        <v>20</v>
+      </c>
+      <c r="M452" t="n">
+        <v>19</v>
+      </c>
+      <c r="N452" t="n">
+        <v>21</v>
+      </c>
+      <c r="O452" t="n">
+        <v>13</v>
+      </c>
+      <c r="P452" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>13</v>
+      </c>
+      <c r="R452" t="n">
+        <v>27</v>
+      </c>
+      <c r="S452" t="n">
+        <v>19</v>
+      </c>
+      <c r="T452" t="n">
+        <v>1</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="V452" t="n">
+        <v>72</v>
+      </c>
+      <c r="W452" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="X452" t="n">
+        <v>0.7461024498886415</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>94.63276836158192</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>0.9370119729307652</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>104.5903544450901</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="AD452" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF452" t="n">
+        <v>-9.957586083508133</v>
+      </c>
+      <c r="AG452" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI452" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>29</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>200</v>
+      </c>
+      <c r="F453" t="n">
+        <v>79</v>
+      </c>
+      <c r="G453" t="n">
+        <v>16</v>
+      </c>
+      <c r="H453" t="n">
+        <v>26</v>
+      </c>
+      <c r="I453" t="n">
+        <v>12</v>
+      </c>
+      <c r="J453" t="n">
+        <v>32</v>
+      </c>
+      <c r="K453" t="n">
+        <v>11</v>
+      </c>
+      <c r="L453" t="n">
+        <v>16</v>
+      </c>
+      <c r="M453" t="n">
+        <v>8</v>
+      </c>
+      <c r="N453" t="n">
+        <v>20</v>
+      </c>
+      <c r="O453" t="n">
+        <v>22</v>
+      </c>
+      <c r="P453" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>16</v>
+      </c>
+      <c r="R453" t="n">
+        <v>22</v>
+      </c>
+      <c r="S453" t="n">
+        <v>19</v>
+      </c>
+      <c r="T453" t="n">
+        <v>1</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="V453" t="n">
+        <v>81</v>
+      </c>
+      <c r="W453" t="n">
+        <v>81.03999999999999</v>
+      </c>
+      <c r="X453" t="n">
+        <v>0.9748272458045411</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>73.03999999999999</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>108.1599123767799</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>109.1644204851752</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="AE453" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF453" t="n">
+        <v>-1.004508108395342</v>
+      </c>
+      <c r="AG453" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI453" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>29</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>200</v>
+      </c>
+      <c r="F454" t="n">
+        <v>73</v>
+      </c>
+      <c r="G454" t="n">
+        <v>21</v>
+      </c>
+      <c r="H454" t="n">
+        <v>38</v>
+      </c>
+      <c r="I454" t="n">
+        <v>4</v>
+      </c>
+      <c r="J454" t="n">
+        <v>17</v>
+      </c>
+      <c r="K454" t="n">
+        <v>19</v>
+      </c>
+      <c r="L454" t="n">
+        <v>24</v>
+      </c>
+      <c r="M454" t="n">
+        <v>6</v>
+      </c>
+      <c r="N454" t="n">
+        <v>23</v>
+      </c>
+      <c r="O454" t="n">
+        <v>14</v>
+      </c>
+      <c r="P454" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>13</v>
+      </c>
+      <c r="R454" t="n">
+        <v>19</v>
+      </c>
+      <c r="S454" t="n">
+        <v>22</v>
+      </c>
+      <c r="T454" t="n">
+        <v>4</v>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="V454" t="n">
+        <v>65</v>
+      </c>
+      <c r="W454" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="X454" t="n">
+        <v>0.9292260692464358</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>100.606394707828</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>0.8198789101917255</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>93.82217090069284</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>0.4754098360655737</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>6.784223807135163</v>
+      </c>
+      <c r="AG454" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH454" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI454" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>29</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>200</v>
+      </c>
+      <c r="F455" t="n">
+        <v>72</v>
+      </c>
+      <c r="G455" t="n">
+        <v>10</v>
+      </c>
+      <c r="H455" t="n">
+        <v>24</v>
+      </c>
+      <c r="I455" t="n">
+        <v>7</v>
+      </c>
+      <c r="J455" t="n">
+        <v>24</v>
+      </c>
+      <c r="K455" t="n">
+        <v>31</v>
+      </c>
+      <c r="L455" t="n">
+        <v>36</v>
+      </c>
+      <c r="M455" t="n">
+        <v>8</v>
+      </c>
+      <c r="N455" t="n">
+        <v>25</v>
+      </c>
+      <c r="O455" t="n">
+        <v>16</v>
+      </c>
+      <c r="P455" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>13</v>
+      </c>
+      <c r="R455" t="n">
+        <v>19</v>
+      </c>
+      <c r="S455" t="n">
+        <v>27</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="V455" t="n">
+        <v>67</v>
+      </c>
+      <c r="W455" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="X455" t="n">
+        <v>0.9370119729307652</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>104.5903544450901</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>0.7461024498886415</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>94.63276836158192</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>0.5681818181818182</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>0.4520547945205479</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>9.957586083508133</v>
+      </c>
+      <c r="AG455" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI455" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>29</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>200</v>
+      </c>
+      <c r="F456" t="n">
+        <v>79</v>
+      </c>
+      <c r="G456" t="n">
+        <v>20</v>
+      </c>
+      <c r="H456" t="n">
+        <v>34</v>
+      </c>
+      <c r="I456" t="n">
+        <v>9</v>
+      </c>
+      <c r="J456" t="n">
+        <v>25</v>
+      </c>
+      <c r="K456" t="n">
+        <v>12</v>
+      </c>
+      <c r="L456" t="n">
+        <v>21</v>
+      </c>
+      <c r="M456" t="n">
+        <v>10</v>
+      </c>
+      <c r="N456" t="n">
+        <v>16</v>
+      </c>
+      <c r="O456" t="n">
+        <v>18</v>
+      </c>
+      <c r="P456" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>11</v>
+      </c>
+      <c r="R456" t="n">
+        <v>19</v>
+      </c>
+      <c r="S456" t="n">
+        <v>21</v>
+      </c>
+      <c r="T456" t="n">
+        <v>1</v>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="V456" t="n">
+        <v>83</v>
+      </c>
+      <c r="W456" t="n">
+        <v>79.24000000000001</v>
+      </c>
+      <c r="X456" t="n">
+        <v>0.9969712266532054</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>69.24000000000001</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>114.0958983246678</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>1.014669926650367</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>117.2316384180791</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>0.456140350877193</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>-3.1357400934113</v>
+      </c>
+      <c r="AG456" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH456" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI456" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>29</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>200</v>
+      </c>
+      <c r="F457" t="n">
+        <v>76</v>
+      </c>
+      <c r="G457" t="n">
+        <v>13</v>
+      </c>
+      <c r="H457" t="n">
+        <v>30</v>
+      </c>
+      <c r="I457" t="n">
+        <v>9</v>
+      </c>
+      <c r="J457" t="n">
+        <v>35</v>
+      </c>
+      <c r="K457" t="n">
+        <v>23</v>
+      </c>
+      <c r="L457" t="n">
+        <v>26</v>
+      </c>
+      <c r="M457" t="n">
+        <v>13</v>
+      </c>
+      <c r="N457" t="n">
+        <v>12</v>
+      </c>
+      <c r="O457" t="n">
+        <v>12</v>
+      </c>
+      <c r="P457" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>12</v>
+      </c>
+      <c r="R457" t="n">
+        <v>22</v>
+      </c>
+      <c r="S457" t="n">
+        <v>23</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>2486512</t>
+        </is>
+      </c>
+      <c r="V457" t="n">
+        <v>96</v>
+      </c>
+      <c r="W457" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="X457" t="n">
+        <v>0.8593396653098145</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>100.7423117709438</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>1.170731707317073</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>126.3157894736842</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>0.462962962962963</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>-25.5734777027404</v>
+      </c>
+      <c r="AG457" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI457" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>29</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>200</v>
+      </c>
+      <c r="F458" t="n">
+        <v>83</v>
+      </c>
+      <c r="G458" t="n">
+        <v>19</v>
+      </c>
+      <c r="H458" t="n">
+        <v>32</v>
+      </c>
+      <c r="I458" t="n">
+        <v>9</v>
+      </c>
+      <c r="J458" t="n">
+        <v>31</v>
+      </c>
+      <c r="K458" t="n">
+        <v>18</v>
+      </c>
+      <c r="L458" t="n">
+        <v>20</v>
+      </c>
+      <c r="M458" t="n">
+        <v>11</v>
+      </c>
+      <c r="N458" t="n">
+        <v>20</v>
+      </c>
+      <c r="O458" t="n">
+        <v>19</v>
+      </c>
+      <c r="P458" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>10</v>
+      </c>
+      <c r="R458" t="n">
+        <v>21</v>
+      </c>
+      <c r="S458" t="n">
+        <v>19</v>
+      </c>
+      <c r="T458" t="n">
+        <v>3</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="V458" t="n">
+        <v>79</v>
+      </c>
+      <c r="W458" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="X458" t="n">
+        <v>1.014669926650367</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>117.2316384180791</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>0.9969712266532054</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>114.0958983246678</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>0.543859649122807</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>3.1357400934113</v>
+      </c>
+      <c r="AG458" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI458" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>29</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>200</v>
+      </c>
+      <c r="F459" t="n">
+        <v>74</v>
+      </c>
+      <c r="G459" t="n">
+        <v>15</v>
+      </c>
+      <c r="H459" t="n">
+        <v>42</v>
+      </c>
+      <c r="I459" t="n">
+        <v>10</v>
+      </c>
+      <c r="J459" t="n">
+        <v>35</v>
+      </c>
+      <c r="K459" t="n">
+        <v>14</v>
+      </c>
+      <c r="L459" t="n">
+        <v>19</v>
+      </c>
+      <c r="M459" t="n">
+        <v>11</v>
+      </c>
+      <c r="N459" t="n">
+        <v>17</v>
+      </c>
+      <c r="O459" t="n">
+        <v>13</v>
+      </c>
+      <c r="P459" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>7</v>
+      </c>
+      <c r="R459" t="n">
+        <v>18</v>
+      </c>
+      <c r="S459" t="n">
+        <v>21</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>2486510</t>
+        </is>
+      </c>
+      <c r="V459" t="n">
+        <v>87</v>
+      </c>
+      <c r="W459" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="X459" t="n">
+        <v>0.8012126461671719</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>90.95378564405114</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>1.028368794326241</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>115.0793650793651</v>
+      </c>
+      <c r="AC459" t="n">
+        <v>0.2244897959183673</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AE459" t="n">
+        <v>0.3733333333333334</v>
+      </c>
+      <c r="AF459" t="n">
+        <v>-24.12557943531395</v>
+      </c>
+      <c r="AG459" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AI459" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>29</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>200</v>
+      </c>
+      <c r="F460" t="n">
+        <v>87</v>
+      </c>
+      <c r="G460" t="n">
+        <v>25</v>
+      </c>
+      <c r="H460" t="n">
+        <v>34</v>
+      </c>
+      <c r="I460" t="n">
+        <v>8</v>
+      </c>
+      <c r="J460" t="n">
+        <v>28</v>
+      </c>
+      <c r="K460" t="n">
+        <v>13</v>
+      </c>
+      <c r="L460" t="n">
+        <v>15</v>
+      </c>
+      <c r="M460" t="n">
+        <v>9</v>
+      </c>
+      <c r="N460" t="n">
+        <v>38</v>
+      </c>
+      <c r="O460" t="n">
+        <v>17</v>
+      </c>
+      <c r="P460" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>16</v>
+      </c>
+      <c r="R460" t="n">
+        <v>21</v>
+      </c>
+      <c r="S460" t="n">
+        <v>18</v>
+      </c>
+      <c r="T460" t="n">
+        <v>3</v>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>2486510</t>
+        </is>
+      </c>
+      <c r="V460" t="n">
+        <v>74</v>
+      </c>
+      <c r="W460" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="X460" t="n">
+        <v>1.028368794326241</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>115.0793650793651</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>0.8012126461671719</v>
+      </c>
+      <c r="AB460" t="n">
+        <v>90.95378564405114</v>
+      </c>
+      <c r="AC460" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="AD460" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="AE460" t="n">
+        <v>0.6266666666666667</v>
+      </c>
+      <c r="AF460" t="n">
+        <v>24.12557943531395</v>
+      </c>
+      <c r="AG460" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AI460" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>29</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>200</v>
+      </c>
+      <c r="F461" t="n">
+        <v>84</v>
+      </c>
+      <c r="G461" t="n">
+        <v>14</v>
+      </c>
+      <c r="H461" t="n">
+        <v>25</v>
+      </c>
+      <c r="I461" t="n">
+        <v>11</v>
+      </c>
+      <c r="J461" t="n">
+        <v>33</v>
+      </c>
+      <c r="K461" t="n">
+        <v>23</v>
+      </c>
+      <c r="L461" t="n">
+        <v>28</v>
+      </c>
+      <c r="M461" t="n">
+        <v>11</v>
+      </c>
+      <c r="N461" t="n">
+        <v>16</v>
+      </c>
+      <c r="O461" t="n">
+        <v>12</v>
+      </c>
+      <c r="P461" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>13</v>
+      </c>
+      <c r="R461" t="n">
+        <v>29</v>
+      </c>
+      <c r="S461" t="n">
+        <v>24</v>
+      </c>
+      <c r="T461" t="n">
+        <v>0</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="V461" t="n">
+        <v>92</v>
+      </c>
+      <c r="W461" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="X461" t="n">
+        <v>1.00816130580893</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>116.1504424778761</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>1.147704590818363</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>127.4944567627495</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>0.3793103448275862</v>
+      </c>
+      <c r="AD461" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE461" t="n">
+        <v>0.5094339622641509</v>
+      </c>
+      <c r="AF461" t="n">
+        <v>-11.34401428487334</v>
+      </c>
+      <c r="AG461" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI461" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>29</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>200</v>
+      </c>
+      <c r="F462" t="n">
+        <v>82</v>
+      </c>
+      <c r="G462" t="n">
+        <v>12</v>
+      </c>
+      <c r="H462" t="n">
+        <v>27</v>
+      </c>
+      <c r="I462" t="n">
+        <v>14</v>
+      </c>
+      <c r="J462" t="n">
+        <v>37</v>
+      </c>
+      <c r="K462" t="n">
+        <v>16</v>
+      </c>
+      <c r="L462" t="n">
+        <v>19</v>
+      </c>
+      <c r="M462" t="n">
+        <v>9</v>
+      </c>
+      <c r="N462" t="n">
+        <v>30</v>
+      </c>
+      <c r="O462" t="n">
+        <v>21</v>
+      </c>
+      <c r="P462" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>14</v>
+      </c>
+      <c r="R462" t="n">
+        <v>18</v>
+      </c>
+      <c r="S462" t="n">
+        <v>19</v>
+      </c>
+      <c r="T462" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="V462" t="n">
+        <v>75</v>
+      </c>
+      <c r="W462" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="X462" t="n">
+        <v>0.9495136637332098</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>105.9979317476732</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>0.8628624022089277</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>96.25256673511294</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>0.5064935064935064</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>9.745365012560285</v>
+      </c>
+      <c r="AG462" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH462" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI462" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>29</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>200</v>
+      </c>
+      <c r="F463" t="n">
+        <v>92</v>
+      </c>
+      <c r="G463" t="n">
+        <v>18</v>
+      </c>
+      <c r="H463" t="n">
+        <v>26</v>
+      </c>
+      <c r="I463" t="n">
+        <v>10</v>
+      </c>
+      <c r="J463" t="n">
+        <v>26</v>
+      </c>
+      <c r="K463" t="n">
+        <v>26</v>
+      </c>
+      <c r="L463" t="n">
+        <v>39</v>
+      </c>
+      <c r="M463" t="n">
+        <v>8</v>
+      </c>
+      <c r="N463" t="n">
+        <v>18</v>
+      </c>
+      <c r="O463" t="n">
+        <v>15</v>
+      </c>
+      <c r="P463" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>11</v>
+      </c>
+      <c r="R463" t="n">
+        <v>24</v>
+      </c>
+      <c r="S463" t="n">
+        <v>29</v>
+      </c>
+      <c r="T463" t="n">
+        <v>1</v>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="V463" t="n">
+        <v>84</v>
+      </c>
+      <c r="W463" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X463" t="n">
+        <v>1.147704590818363</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>127.4944567627495</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>1.00816130580893</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>116.1504424778761</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD463" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="AE463" t="n">
+        <v>0.4905660377358491</v>
+      </c>
+      <c r="AF463" t="n">
+        <v>11.34401428487334</v>
+      </c>
+      <c r="AG463" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH463" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI463" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>29</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>200</v>
+      </c>
+      <c r="F464" t="n">
+        <v>96</v>
+      </c>
+      <c r="G464" t="n">
+        <v>17</v>
+      </c>
+      <c r="H464" t="n">
+        <v>24</v>
+      </c>
+      <c r="I464" t="n">
+        <v>14</v>
+      </c>
+      <c r="J464" t="n">
+        <v>28</v>
+      </c>
+      <c r="K464" t="n">
+        <v>20</v>
+      </c>
+      <c r="L464" t="n">
+        <v>25</v>
+      </c>
+      <c r="M464" t="n">
+        <v>6</v>
+      </c>
+      <c r="N464" t="n">
+        <v>23</v>
+      </c>
+      <c r="O464" t="n">
+        <v>13</v>
+      </c>
+      <c r="P464" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>19</v>
+      </c>
+      <c r="R464" t="n">
+        <v>23</v>
+      </c>
+      <c r="S464" t="n">
+        <v>22</v>
+      </c>
+      <c r="T464" t="n">
+        <v>2</v>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>2486512</t>
+        </is>
+      </c>
+      <c r="V464" t="n">
+        <v>76</v>
+      </c>
+      <c r="W464" t="n">
+        <v>82</v>
+      </c>
+      <c r="X464" t="n">
+        <v>1.170731707317073</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>126.3157894736842</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>0.8593396653098145</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>100.7423117709438</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD464" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AE464" t="n">
+        <v>0.5370370370370371</v>
+      </c>
+      <c r="AF464" t="n">
+        <v>25.5734777027404</v>
+      </c>
+      <c r="AG464" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH464" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI464" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>29</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>200</v>
+      </c>
+      <c r="F465" t="n">
+        <v>75</v>
+      </c>
+      <c r="G465" t="n">
+        <v>20</v>
+      </c>
+      <c r="H465" t="n">
+        <v>47</v>
+      </c>
+      <c r="I465" t="n">
+        <v>7</v>
+      </c>
+      <c r="J465" t="n">
+        <v>23</v>
+      </c>
+      <c r="K465" t="n">
+        <v>14</v>
+      </c>
+      <c r="L465" t="n">
+        <v>18</v>
+      </c>
+      <c r="M465" t="n">
+        <v>9</v>
+      </c>
+      <c r="N465" t="n">
+        <v>29</v>
+      </c>
+      <c r="O465" t="n">
+        <v>14</v>
+      </c>
+      <c r="P465" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>9</v>
+      </c>
+      <c r="R465" t="n">
+        <v>20</v>
+      </c>
+      <c r="S465" t="n">
+        <v>17</v>
+      </c>
+      <c r="T465" t="n">
+        <v>3</v>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="V465" t="n">
+        <v>82</v>
+      </c>
+      <c r="W465" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="X465" t="n">
+        <v>0.8628624022089277</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>96.25256673511294</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>0.9495136637332098</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>105.9979317476732</v>
+      </c>
+      <c r="AC465" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AD465" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="AE465" t="n">
+        <v>0.4935064935064935</v>
+      </c>
+      <c r="AF465" t="n">
+        <v>-9.745365012560285</v>
+      </c>
+      <c r="AG465" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH465" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI465" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI465"/>
+  <dimension ref="A1:AI481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55819,6 +55819,1910 @@
       </c>
       <c r="AI465" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>30</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>200</v>
+      </c>
+      <c r="F466" t="n">
+        <v>69</v>
+      </c>
+      <c r="G466" t="n">
+        <v>11</v>
+      </c>
+      <c r="H466" t="n">
+        <v>28</v>
+      </c>
+      <c r="I466" t="n">
+        <v>9</v>
+      </c>
+      <c r="J466" t="n">
+        <v>32</v>
+      </c>
+      <c r="K466" t="n">
+        <v>20</v>
+      </c>
+      <c r="L466" t="n">
+        <v>24</v>
+      </c>
+      <c r="M466" t="n">
+        <v>10</v>
+      </c>
+      <c r="N466" t="n">
+        <v>16</v>
+      </c>
+      <c r="O466" t="n">
+        <v>16</v>
+      </c>
+      <c r="P466" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>16</v>
+      </c>
+      <c r="R466" t="n">
+        <v>20</v>
+      </c>
+      <c r="S466" t="n">
+        <v>20</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="V466" t="n">
+        <v>75</v>
+      </c>
+      <c r="W466" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="X466" t="n">
+        <v>0.7971349353049907</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>90.12539184952978</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>0.8733115975780159</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>98.84027411702689</v>
+      </c>
+      <c r="AC466" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD466" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="AE466" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="AF466" t="n">
+        <v>-8.714882267497117</v>
+      </c>
+      <c r="AG466" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH466" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI466" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>30</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>225</v>
+      </c>
+      <c r="F467" t="n">
+        <v>87</v>
+      </c>
+      <c r="G467" t="n">
+        <v>21</v>
+      </c>
+      <c r="H467" t="n">
+        <v>42</v>
+      </c>
+      <c r="I467" t="n">
+        <v>10</v>
+      </c>
+      <c r="J467" t="n">
+        <v>37</v>
+      </c>
+      <c r="K467" t="n">
+        <v>15</v>
+      </c>
+      <c r="L467" t="n">
+        <v>21</v>
+      </c>
+      <c r="M467" t="n">
+        <v>9</v>
+      </c>
+      <c r="N467" t="n">
+        <v>33</v>
+      </c>
+      <c r="O467" t="n">
+        <v>10</v>
+      </c>
+      <c r="P467" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>10</v>
+      </c>
+      <c r="R467" t="n">
+        <v>24</v>
+      </c>
+      <c r="S467" t="n">
+        <v>21</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="V467" t="n">
+        <v>94</v>
+      </c>
+      <c r="W467" t="n">
+        <v>98.24000000000001</v>
+      </c>
+      <c r="X467" t="n">
+        <v>0.8855863192182409</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>89.24000000000001</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>97.48991483639622</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>0.9418837675350702</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>105.8558558558559</v>
+      </c>
+      <c r="AC467" t="n">
+        <v>0.2093023255813954</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE467" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="AF467" t="n">
+        <v>-8.36594101945964</v>
+      </c>
+      <c r="AG467" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH467" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI467" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>30</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>200</v>
+      </c>
+      <c r="F468" t="n">
+        <v>57</v>
+      </c>
+      <c r="G468" t="n">
+        <v>16</v>
+      </c>
+      <c r="H468" t="n">
+        <v>43</v>
+      </c>
+      <c r="I468" t="n">
+        <v>4</v>
+      </c>
+      <c r="J468" t="n">
+        <v>22</v>
+      </c>
+      <c r="K468" t="n">
+        <v>13</v>
+      </c>
+      <c r="L468" t="n">
+        <v>16</v>
+      </c>
+      <c r="M468" t="n">
+        <v>13</v>
+      </c>
+      <c r="N468" t="n">
+        <v>16</v>
+      </c>
+      <c r="O468" t="n">
+        <v>14</v>
+      </c>
+      <c r="P468" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>13</v>
+      </c>
+      <c r="R468" t="n">
+        <v>24</v>
+      </c>
+      <c r="S468" t="n">
+        <v>16</v>
+      </c>
+      <c r="T468" t="n">
+        <v>2</v>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>2486521</t>
+        </is>
+      </c>
+      <c r="V468" t="n">
+        <v>94</v>
+      </c>
+      <c r="W468" t="n">
+        <v>85.03999999999999</v>
+      </c>
+      <c r="X468" t="n">
+        <v>0.6702728127939793</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>72.03999999999999</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>79.12270960577457</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>1.160493827160494</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>130.5555555555555</v>
+      </c>
+      <c r="AC468" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE468" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="AF468" t="n">
+        <v>-51.43284594978097</v>
+      </c>
+      <c r="AG468" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH468" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI468" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>30</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>200</v>
+      </c>
+      <c r="F469" t="n">
+        <v>77</v>
+      </c>
+      <c r="G469" t="n">
+        <v>22</v>
+      </c>
+      <c r="H469" t="n">
+        <v>34</v>
+      </c>
+      <c r="I469" t="n">
+        <v>6</v>
+      </c>
+      <c r="J469" t="n">
+        <v>17</v>
+      </c>
+      <c r="K469" t="n">
+        <v>15</v>
+      </c>
+      <c r="L469" t="n">
+        <v>23</v>
+      </c>
+      <c r="M469" t="n">
+        <v>6</v>
+      </c>
+      <c r="N469" t="n">
+        <v>24</v>
+      </c>
+      <c r="O469" t="n">
+        <v>11</v>
+      </c>
+      <c r="P469" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>17</v>
+      </c>
+      <c r="R469" t="n">
+        <v>18</v>
+      </c>
+      <c r="S469" t="n">
+        <v>18</v>
+      </c>
+      <c r="T469" t="n">
+        <v>2</v>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="V469" t="n">
+        <v>80</v>
+      </c>
+      <c r="W469" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="X469" t="n">
+        <v>0.985663082437276</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>106.7665002773156</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>0.964785335262904</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>108.2251082251082</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE469" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF469" t="n">
+        <v>-1.458607947792657</v>
+      </c>
+      <c r="AG469" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH469" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI469" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>30</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>200</v>
+      </c>
+      <c r="F470" t="n">
+        <v>75</v>
+      </c>
+      <c r="G470" t="n">
+        <v>20</v>
+      </c>
+      <c r="H470" t="n">
+        <v>38</v>
+      </c>
+      <c r="I470" t="n">
+        <v>10</v>
+      </c>
+      <c r="J470" t="n">
+        <v>29</v>
+      </c>
+      <c r="K470" t="n">
+        <v>5</v>
+      </c>
+      <c r="L470" t="n">
+        <v>16</v>
+      </c>
+      <c r="M470" t="n">
+        <v>10</v>
+      </c>
+      <c r="N470" t="n">
+        <v>26</v>
+      </c>
+      <c r="O470" t="n">
+        <v>15</v>
+      </c>
+      <c r="P470" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>12</v>
+      </c>
+      <c r="R470" t="n">
+        <v>15</v>
+      </c>
+      <c r="S470" t="n">
+        <v>20</v>
+      </c>
+      <c r="T470" t="n">
+        <v>0</v>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="V470" t="n">
+        <v>74</v>
+      </c>
+      <c r="W470" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X470" t="n">
+        <v>0.8716875871687588</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>98.63229879011048</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>0.828853046594982</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>97.01101206082852</v>
+      </c>
+      <c r="AC470" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE470" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF470" t="n">
+        <v>1.621286729281962</v>
+      </c>
+      <c r="AG470" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH470" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI470" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>30</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>200</v>
+      </c>
+      <c r="F471" t="n">
+        <v>74</v>
+      </c>
+      <c r="G471" t="n">
+        <v>9</v>
+      </c>
+      <c r="H471" t="n">
+        <v>23</v>
+      </c>
+      <c r="I471" t="n">
+        <v>13</v>
+      </c>
+      <c r="J471" t="n">
+        <v>39</v>
+      </c>
+      <c r="K471" t="n">
+        <v>17</v>
+      </c>
+      <c r="L471" t="n">
+        <v>22</v>
+      </c>
+      <c r="M471" t="n">
+        <v>8</v>
+      </c>
+      <c r="N471" t="n">
+        <v>25</v>
+      </c>
+      <c r="O471" t="n">
+        <v>12</v>
+      </c>
+      <c r="P471" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>9</v>
+      </c>
+      <c r="R471" t="n">
+        <v>23</v>
+      </c>
+      <c r="S471" t="n">
+        <v>21</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1</v>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="V471" t="n">
+        <v>82</v>
+      </c>
+      <c r="W471" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="X471" t="n">
+        <v>0.9172037679722359</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>101.8161805173363</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>0.9597378277153559</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AC471" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE471" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="AF471" t="n">
+        <v>-6.879471656576783</v>
+      </c>
+      <c r="AG471" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH471" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI471" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>30</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>200</v>
+      </c>
+      <c r="F472" t="n">
+        <v>80</v>
+      </c>
+      <c r="G472" t="n">
+        <v>11</v>
+      </c>
+      <c r="H472" t="n">
+        <v>26</v>
+      </c>
+      <c r="I472" t="n">
+        <v>16</v>
+      </c>
+      <c r="J472" t="n">
+        <v>33</v>
+      </c>
+      <c r="K472" t="n">
+        <v>10</v>
+      </c>
+      <c r="L472" t="n">
+        <v>18</v>
+      </c>
+      <c r="M472" t="n">
+        <v>9</v>
+      </c>
+      <c r="N472" t="n">
+        <v>16</v>
+      </c>
+      <c r="O472" t="n">
+        <v>18</v>
+      </c>
+      <c r="P472" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>16</v>
+      </c>
+      <c r="R472" t="n">
+        <v>18</v>
+      </c>
+      <c r="S472" t="n">
+        <v>18</v>
+      </c>
+      <c r="T472" t="n">
+        <v>2</v>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="V472" t="n">
+        <v>77</v>
+      </c>
+      <c r="W472" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="X472" t="n">
+        <v>0.964785335262904</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>108.2251082251082</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>0.985663082437276</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>106.7665002773156</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE472" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF472" t="n">
+        <v>1.458607947792657</v>
+      </c>
+      <c r="AG472" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH472" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI472" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>30</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>200</v>
+      </c>
+      <c r="F473" t="n">
+        <v>67</v>
+      </c>
+      <c r="G473" t="n">
+        <v>15</v>
+      </c>
+      <c r="H473" t="n">
+        <v>28</v>
+      </c>
+      <c r="I473" t="n">
+        <v>8</v>
+      </c>
+      <c r="J473" t="n">
+        <v>36</v>
+      </c>
+      <c r="K473" t="n">
+        <v>13</v>
+      </c>
+      <c r="L473" t="n">
+        <v>22</v>
+      </c>
+      <c r="M473" t="n">
+        <v>11</v>
+      </c>
+      <c r="N473" t="n">
+        <v>22</v>
+      </c>
+      <c r="O473" t="n">
+        <v>12</v>
+      </c>
+      <c r="P473" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>15</v>
+      </c>
+      <c r="R473" t="n">
+        <v>26</v>
+      </c>
+      <c r="S473" t="n">
+        <v>24</v>
+      </c>
+      <c r="T473" t="n">
+        <v>2</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="V473" t="n">
+        <v>72</v>
+      </c>
+      <c r="W473" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="X473" t="n">
+        <v>0.7555254848894902</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>86.25128733264675</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AB473" t="n">
+        <v>98.36065573770492</v>
+      </c>
+      <c r="AC473" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AD473" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE473" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AF473" t="n">
+        <v>-12.10936840505816</v>
+      </c>
+      <c r="AG473" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI473" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>30</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>200</v>
+      </c>
+      <c r="F474" t="n">
+        <v>82</v>
+      </c>
+      <c r="G474" t="n">
+        <v>18</v>
+      </c>
+      <c r="H474" t="n">
+        <v>36</v>
+      </c>
+      <c r="I474" t="n">
+        <v>9</v>
+      </c>
+      <c r="J474" t="n">
+        <v>25</v>
+      </c>
+      <c r="K474" t="n">
+        <v>19</v>
+      </c>
+      <c r="L474" t="n">
+        <v>26</v>
+      </c>
+      <c r="M474" t="n">
+        <v>10</v>
+      </c>
+      <c r="N474" t="n">
+        <v>29</v>
+      </c>
+      <c r="O474" t="n">
+        <v>16</v>
+      </c>
+      <c r="P474" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>13</v>
+      </c>
+      <c r="R474" t="n">
+        <v>21</v>
+      </c>
+      <c r="S474" t="n">
+        <v>23</v>
+      </c>
+      <c r="T474" t="n">
+        <v>2</v>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="V474" t="n">
+        <v>74</v>
+      </c>
+      <c r="W474" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X474" t="n">
+        <v>0.9597378277153559</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>0.9172037679722359</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>101.8161805173363</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="AE474" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="AF474" t="n">
+        <v>6.879471656576783</v>
+      </c>
+      <c r="AG474" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH474" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI474" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>30</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>200</v>
+      </c>
+      <c r="F475" t="n">
+        <v>82</v>
+      </c>
+      <c r="G475" t="n">
+        <v>18</v>
+      </c>
+      <c r="H475" t="n">
+        <v>34</v>
+      </c>
+      <c r="I475" t="n">
+        <v>8</v>
+      </c>
+      <c r="J475" t="n">
+        <v>30</v>
+      </c>
+      <c r="K475" t="n">
+        <v>22</v>
+      </c>
+      <c r="L475" t="n">
+        <v>36</v>
+      </c>
+      <c r="M475" t="n">
+        <v>19</v>
+      </c>
+      <c r="N475" t="n">
+        <v>34</v>
+      </c>
+      <c r="O475" t="n">
+        <v>17</v>
+      </c>
+      <c r="P475" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>18</v>
+      </c>
+      <c r="R475" t="n">
+        <v>21</v>
+      </c>
+      <c r="S475" t="n">
+        <v>26</v>
+      </c>
+      <c r="T475" t="n">
+        <v>2</v>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>2486522</t>
+        </is>
+      </c>
+      <c r="V475" t="n">
+        <v>65</v>
+      </c>
+      <c r="W475" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="X475" t="n">
+        <v>0.8381030253475061</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>104.0081177067478</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>0.7705073494547179</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>80.88601294176208</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>0.5135135135135135</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AE475" t="n">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="AF475" t="n">
+        <v>23.12210476498576</v>
+      </c>
+      <c r="AG475" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH475" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AI475" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>30</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>200</v>
+      </c>
+      <c r="F476" t="n">
+        <v>74</v>
+      </c>
+      <c r="G476" t="n">
+        <v>16</v>
+      </c>
+      <c r="H476" t="n">
+        <v>32</v>
+      </c>
+      <c r="I476" t="n">
+        <v>11</v>
+      </c>
+      <c r="J476" t="n">
+        <v>39</v>
+      </c>
+      <c r="K476" t="n">
+        <v>9</v>
+      </c>
+      <c r="L476" t="n">
+        <v>12</v>
+      </c>
+      <c r="M476" t="n">
+        <v>13</v>
+      </c>
+      <c r="N476" t="n">
+        <v>28</v>
+      </c>
+      <c r="O476" t="n">
+        <v>14</v>
+      </c>
+      <c r="P476" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>13</v>
+      </c>
+      <c r="R476" t="n">
+        <v>20</v>
+      </c>
+      <c r="S476" t="n">
+        <v>15</v>
+      </c>
+      <c r="T476" t="n">
+        <v>3</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="V476" t="n">
+        <v>75</v>
+      </c>
+      <c r="W476" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="X476" t="n">
+        <v>0.828853046594982</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>97.01101206082852</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>0.8716875871687588</v>
+      </c>
+      <c r="AB476" t="n">
+        <v>98.63229879011048</v>
+      </c>
+      <c r="AC476" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD476" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="AE476" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF476" t="n">
+        <v>-1.621286729281962</v>
+      </c>
+      <c r="AG476" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI476" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>30</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>225</v>
+      </c>
+      <c r="F477" t="n">
+        <v>94</v>
+      </c>
+      <c r="G477" t="n">
+        <v>17</v>
+      </c>
+      <c r="H477" t="n">
+        <v>30</v>
+      </c>
+      <c r="I477" t="n">
+        <v>15</v>
+      </c>
+      <c r="J477" t="n">
+        <v>49</v>
+      </c>
+      <c r="K477" t="n">
+        <v>15</v>
+      </c>
+      <c r="L477" t="n">
+        <v>20</v>
+      </c>
+      <c r="M477" t="n">
+        <v>11</v>
+      </c>
+      <c r="N477" t="n">
+        <v>34</v>
+      </c>
+      <c r="O477" t="n">
+        <v>20</v>
+      </c>
+      <c r="P477" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>12</v>
+      </c>
+      <c r="R477" t="n">
+        <v>22</v>
+      </c>
+      <c r="S477" t="n">
+        <v>24</v>
+      </c>
+      <c r="T477" t="n">
+        <v>1</v>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="V477" t="n">
+        <v>87</v>
+      </c>
+      <c r="W477" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="X477" t="n">
+        <v>0.9418837675350702</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>105.8558558558559</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>0.8855863192182409</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>97.48991483639622</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="AE477" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="AF477" t="n">
+        <v>8.36594101945964</v>
+      </c>
+      <c r="AG477" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH477" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI477" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>30</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>200</v>
+      </c>
+      <c r="F478" t="n">
+        <v>94</v>
+      </c>
+      <c r="G478" t="n">
+        <v>27</v>
+      </c>
+      <c r="H478" t="n">
+        <v>41</v>
+      </c>
+      <c r="I478" t="n">
+        <v>8</v>
+      </c>
+      <c r="J478" t="n">
+        <v>19</v>
+      </c>
+      <c r="K478" t="n">
+        <v>16</v>
+      </c>
+      <c r="L478" t="n">
+        <v>25</v>
+      </c>
+      <c r="M478" t="n">
+        <v>9</v>
+      </c>
+      <c r="N478" t="n">
+        <v>26</v>
+      </c>
+      <c r="O478" t="n">
+        <v>21</v>
+      </c>
+      <c r="P478" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>10</v>
+      </c>
+      <c r="R478" t="n">
+        <v>16</v>
+      </c>
+      <c r="S478" t="n">
+        <v>23</v>
+      </c>
+      <c r="T478" t="n">
+        <v>1</v>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>2486521</t>
+        </is>
+      </c>
+      <c r="V478" t="n">
+        <v>57</v>
+      </c>
+      <c r="W478" t="n">
+        <v>81</v>
+      </c>
+      <c r="X478" t="n">
+        <v>1.160493827160494</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>130.5555555555555</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>0.6702728127939793</v>
+      </c>
+      <c r="AB478" t="n">
+        <v>79.12270960577457</v>
+      </c>
+      <c r="AC478" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AD478" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE478" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="AF478" t="n">
+        <v>51.43284594978097</v>
+      </c>
+      <c r="AG478" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH478" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI478" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>30</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>200</v>
+      </c>
+      <c r="F479" t="n">
+        <v>75</v>
+      </c>
+      <c r="G479" t="n">
+        <v>23</v>
+      </c>
+      <c r="H479" t="n">
+        <v>37</v>
+      </c>
+      <c r="I479" t="n">
+        <v>4</v>
+      </c>
+      <c r="J479" t="n">
+        <v>20</v>
+      </c>
+      <c r="K479" t="n">
+        <v>17</v>
+      </c>
+      <c r="L479" t="n">
+        <v>27</v>
+      </c>
+      <c r="M479" t="n">
+        <v>10</v>
+      </c>
+      <c r="N479" t="n">
+        <v>25</v>
+      </c>
+      <c r="O479" t="n">
+        <v>17</v>
+      </c>
+      <c r="P479" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>17</v>
+      </c>
+      <c r="R479" t="n">
+        <v>21</v>
+      </c>
+      <c r="S479" t="n">
+        <v>20</v>
+      </c>
+      <c r="T479" t="n">
+        <v>2</v>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="V479" t="n">
+        <v>69</v>
+      </c>
+      <c r="W479" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="X479" t="n">
+        <v>0.8733115975780159</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>98.84027411702689</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>0.7971349353049907</v>
+      </c>
+      <c r="AB479" t="n">
+        <v>90.12539184952978</v>
+      </c>
+      <c r="AC479" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE479" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="AF479" t="n">
+        <v>8.714882267497117</v>
+      </c>
+      <c r="AG479" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH479" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI479" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>30</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>200</v>
+      </c>
+      <c r="F480" t="n">
+        <v>65</v>
+      </c>
+      <c r="G480" t="n">
+        <v>22</v>
+      </c>
+      <c r="H480" t="n">
+        <v>45</v>
+      </c>
+      <c r="I480" t="n">
+        <v>3</v>
+      </c>
+      <c r="J480" t="n">
+        <v>17</v>
+      </c>
+      <c r="K480" t="n">
+        <v>12</v>
+      </c>
+      <c r="L480" t="n">
+        <v>19</v>
+      </c>
+      <c r="M480" t="n">
+        <v>4</v>
+      </c>
+      <c r="N480" t="n">
+        <v>18</v>
+      </c>
+      <c r="O480" t="n">
+        <v>6</v>
+      </c>
+      <c r="P480" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>14</v>
+      </c>
+      <c r="R480" t="n">
+        <v>27</v>
+      </c>
+      <c r="S480" t="n">
+        <v>21</v>
+      </c>
+      <c r="T480" t="n">
+        <v>2</v>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>2486522</t>
+        </is>
+      </c>
+      <c r="V480" t="n">
+        <v>82</v>
+      </c>
+      <c r="W480" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="X480" t="n">
+        <v>0.7705073494547179</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>80.88601294176208</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>0.8381030253475061</v>
+      </c>
+      <c r="AB480" t="n">
+        <v>104.0081177067478</v>
+      </c>
+      <c r="AC480" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="AE480" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="AF480" t="n">
+        <v>-23.12210476498576</v>
+      </c>
+      <c r="AG480" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH480" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AI480" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>30</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>200</v>
+      </c>
+      <c r="F481" t="n">
+        <v>72</v>
+      </c>
+      <c r="G481" t="n">
+        <v>15</v>
+      </c>
+      <c r="H481" t="n">
+        <v>24</v>
+      </c>
+      <c r="I481" t="n">
+        <v>7</v>
+      </c>
+      <c r="J481" t="n">
+        <v>28</v>
+      </c>
+      <c r="K481" t="n">
+        <v>21</v>
+      </c>
+      <c r="L481" t="n">
+        <v>30</v>
+      </c>
+      <c r="M481" t="n">
+        <v>6</v>
+      </c>
+      <c r="N481" t="n">
+        <v>21</v>
+      </c>
+      <c r="O481" t="n">
+        <v>11</v>
+      </c>
+      <c r="P481" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>14</v>
+      </c>
+      <c r="R481" t="n">
+        <v>24</v>
+      </c>
+      <c r="S481" t="n">
+        <v>26</v>
+      </c>
+      <c r="T481" t="n">
+        <v>2</v>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="V481" t="n">
+        <v>67</v>
+      </c>
+      <c r="W481" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="X481" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>98.36065573770492</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>0.7555254848894902</v>
+      </c>
+      <c r="AB481" t="n">
+        <v>86.25128733264675</v>
+      </c>
+      <c r="AC481" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AE481" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AF481" t="n">
+        <v>12.10936840505816</v>
+      </c>
+      <c r="AG481" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH481" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI481" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI481"/>
+  <dimension ref="A1:AI513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57723,6 +57723,3814 @@
       </c>
       <c r="AI481" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>31</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>200</v>
+      </c>
+      <c r="F482" t="n">
+        <v>89</v>
+      </c>
+      <c r="G482" t="n">
+        <v>20</v>
+      </c>
+      <c r="H482" t="n">
+        <v>34</v>
+      </c>
+      <c r="I482" t="n">
+        <v>14</v>
+      </c>
+      <c r="J482" t="n">
+        <v>36</v>
+      </c>
+      <c r="K482" t="n">
+        <v>7</v>
+      </c>
+      <c r="L482" t="n">
+        <v>14</v>
+      </c>
+      <c r="M482" t="n">
+        <v>15</v>
+      </c>
+      <c r="N482" t="n">
+        <v>24</v>
+      </c>
+      <c r="O482" t="n">
+        <v>23</v>
+      </c>
+      <c r="P482" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>9</v>
+      </c>
+      <c r="R482" t="n">
+        <v>18</v>
+      </c>
+      <c r="S482" t="n">
+        <v>19</v>
+      </c>
+      <c r="T482" t="n">
+        <v>0</v>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>2486535</t>
+        </is>
+      </c>
+      <c r="V482" t="n">
+        <v>74</v>
+      </c>
+      <c r="W482" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="X482" t="n">
+        <v>1.045091592296853</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>126.8529076396807</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>0.9245377311344328</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>99.94597514856835</v>
+      </c>
+      <c r="AC482" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE482" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AF482" t="n">
+        <v>26.90693249111239</v>
+      </c>
+      <c r="AG482" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH482" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI482" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>31</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>200</v>
+      </c>
+      <c r="F483" t="n">
+        <v>78</v>
+      </c>
+      <c r="G483" t="n">
+        <v>19</v>
+      </c>
+      <c r="H483" t="n">
+        <v>45</v>
+      </c>
+      <c r="I483" t="n">
+        <v>8</v>
+      </c>
+      <c r="J483" t="n">
+        <v>22</v>
+      </c>
+      <c r="K483" t="n">
+        <v>16</v>
+      </c>
+      <c r="L483" t="n">
+        <v>19</v>
+      </c>
+      <c r="M483" t="n">
+        <v>12</v>
+      </c>
+      <c r="N483" t="n">
+        <v>29</v>
+      </c>
+      <c r="O483" t="n">
+        <v>15</v>
+      </c>
+      <c r="P483" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>16</v>
+      </c>
+      <c r="R483" t="n">
+        <v>21</v>
+      </c>
+      <c r="S483" t="n">
+        <v>20</v>
+      </c>
+      <c r="T483" t="n">
+        <v>2</v>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>2486533</t>
+        </is>
+      </c>
+      <c r="V483" t="n">
+        <v>64</v>
+      </c>
+      <c r="W483" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="X483" t="n">
+        <v>0.8537653239929948</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>98.28629032258064</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>0.7191011235955056</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>81.01265822784811</v>
+      </c>
+      <c r="AC483" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE483" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF483" t="n">
+        <v>17.27363209473253</v>
+      </c>
+      <c r="AG483" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH483" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI483" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>31</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>200</v>
+      </c>
+      <c r="F484" t="n">
+        <v>90</v>
+      </c>
+      <c r="G484" t="n">
+        <v>22</v>
+      </c>
+      <c r="H484" t="n">
+        <v>36</v>
+      </c>
+      <c r="I484" t="n">
+        <v>10</v>
+      </c>
+      <c r="J484" t="n">
+        <v>25</v>
+      </c>
+      <c r="K484" t="n">
+        <v>16</v>
+      </c>
+      <c r="L484" t="n">
+        <v>26</v>
+      </c>
+      <c r="M484" t="n">
+        <v>13</v>
+      </c>
+      <c r="N484" t="n">
+        <v>24</v>
+      </c>
+      <c r="O484" t="n">
+        <v>20</v>
+      </c>
+      <c r="P484" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>14</v>
+      </c>
+      <c r="R484" t="n">
+        <v>24</v>
+      </c>
+      <c r="S484" t="n">
+        <v>25</v>
+      </c>
+      <c r="T484" t="n">
+        <v>2</v>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="V484" t="n">
+        <v>93</v>
+      </c>
+      <c r="W484" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="X484" t="n">
+        <v>1.041184636742249</v>
+      </c>
+      <c r="Y484" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>122.5490196078431</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>1.085941148995796</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>118.2604272634791</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AE484" t="n">
+        <v>0.5967741935483871</v>
+      </c>
+      <c r="AF484" t="n">
+        <v>4.288592344363991</v>
+      </c>
+      <c r="AG484" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH484" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI484" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>31</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>200</v>
+      </c>
+      <c r="F485" t="n">
+        <v>63</v>
+      </c>
+      <c r="G485" t="n">
+        <v>15</v>
+      </c>
+      <c r="H485" t="n">
+        <v>42</v>
+      </c>
+      <c r="I485" t="n">
+        <v>8</v>
+      </c>
+      <c r="J485" t="n">
+        <v>23</v>
+      </c>
+      <c r="K485" t="n">
+        <v>9</v>
+      </c>
+      <c r="L485" t="n">
+        <v>14</v>
+      </c>
+      <c r="M485" t="n">
+        <v>10</v>
+      </c>
+      <c r="N485" t="n">
+        <v>19</v>
+      </c>
+      <c r="O485" t="n">
+        <v>15</v>
+      </c>
+      <c r="P485" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>9</v>
+      </c>
+      <c r="R485" t="n">
+        <v>18</v>
+      </c>
+      <c r="S485" t="n">
+        <v>17</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="V485" t="n">
+        <v>73</v>
+      </c>
+      <c r="W485" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X485" t="n">
+        <v>0.7859281437125749</v>
+      </c>
+      <c r="Y485" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="Z485" t="n">
+        <v>89.79475484606614</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>0.9843581445523194</v>
+      </c>
+      <c r="AB485" t="n">
+        <v>110.3385731559855</v>
+      </c>
+      <c r="AC485" t="n">
+        <v>0.2702702702702703</v>
+      </c>
+      <c r="AD485" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="AE485" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="AF485" t="n">
+        <v>-20.54381830991936</v>
+      </c>
+      <c r="AG485" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH485" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI485" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>31</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>200</v>
+      </c>
+      <c r="F486" t="n">
+        <v>89</v>
+      </c>
+      <c r="G486" t="n">
+        <v>24</v>
+      </c>
+      <c r="H486" t="n">
+        <v>44</v>
+      </c>
+      <c r="I486" t="n">
+        <v>7</v>
+      </c>
+      <c r="J486" t="n">
+        <v>20</v>
+      </c>
+      <c r="K486" t="n">
+        <v>20</v>
+      </c>
+      <c r="L486" t="n">
+        <v>21</v>
+      </c>
+      <c r="M486" t="n">
+        <v>4</v>
+      </c>
+      <c r="N486" t="n">
+        <v>26</v>
+      </c>
+      <c r="O486" t="n">
+        <v>20</v>
+      </c>
+      <c r="P486" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>9</v>
+      </c>
+      <c r="R486" t="n">
+        <v>18</v>
+      </c>
+      <c r="S486" t="n">
+        <v>21</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="V486" t="n">
+        <v>80</v>
+      </c>
+      <c r="W486" t="n">
+        <v>82.24000000000001</v>
+      </c>
+      <c r="X486" t="n">
+        <v>1.082198443579766</v>
+      </c>
+      <c r="Y486" t="n">
+        <v>78.24000000000001</v>
+      </c>
+      <c r="Z486" t="n">
+        <v>113.7525562372188</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>0.9737098344693281</v>
+      </c>
+      <c r="AB486" t="n">
+        <v>103.6806635562468</v>
+      </c>
+      <c r="AC486" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AD486" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AE486" t="n">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="AF486" t="n">
+        <v>10.07189268097203</v>
+      </c>
+      <c r="AG486" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH486" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI486" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>31</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>200</v>
+      </c>
+      <c r="F487" t="n">
+        <v>80</v>
+      </c>
+      <c r="G487" t="n">
+        <v>16</v>
+      </c>
+      <c r="H487" t="n">
+        <v>30</v>
+      </c>
+      <c r="I487" t="n">
+        <v>13</v>
+      </c>
+      <c r="J487" t="n">
+        <v>32</v>
+      </c>
+      <c r="K487" t="n">
+        <v>9</v>
+      </c>
+      <c r="L487" t="n">
+        <v>14</v>
+      </c>
+      <c r="M487" t="n">
+        <v>5</v>
+      </c>
+      <c r="N487" t="n">
+        <v>26</v>
+      </c>
+      <c r="O487" t="n">
+        <v>20</v>
+      </c>
+      <c r="P487" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>14</v>
+      </c>
+      <c r="R487" t="n">
+        <v>21</v>
+      </c>
+      <c r="S487" t="n">
+        <v>16</v>
+      </c>
+      <c r="T487" t="n">
+        <v>2</v>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="V487" t="n">
+        <v>89</v>
+      </c>
+      <c r="W487" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="X487" t="n">
+        <v>0.9737098344693281</v>
+      </c>
+      <c r="Y487" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="Z487" t="n">
+        <v>103.6806635562468</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>1.082198443579766</v>
+      </c>
+      <c r="AB487" t="n">
+        <v>113.7525562372188</v>
+      </c>
+      <c r="AC487" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AD487" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AE487" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="AF487" t="n">
+        <v>-10.07189268097203</v>
+      </c>
+      <c r="AG487" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH487" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI487" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>31</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>200</v>
+      </c>
+      <c r="F488" t="n">
+        <v>64</v>
+      </c>
+      <c r="G488" t="n">
+        <v>14</v>
+      </c>
+      <c r="H488" t="n">
+        <v>26</v>
+      </c>
+      <c r="I488" t="n">
+        <v>7</v>
+      </c>
+      <c r="J488" t="n">
+        <v>35</v>
+      </c>
+      <c r="K488" t="n">
+        <v>15</v>
+      </c>
+      <c r="L488" t="n">
+        <v>25</v>
+      </c>
+      <c r="M488" t="n">
+        <v>10</v>
+      </c>
+      <c r="N488" t="n">
+        <v>26</v>
+      </c>
+      <c r="O488" t="n">
+        <v>17</v>
+      </c>
+      <c r="P488" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>17</v>
+      </c>
+      <c r="R488" t="n">
+        <v>20</v>
+      </c>
+      <c r="S488" t="n">
+        <v>21</v>
+      </c>
+      <c r="T488" t="n">
+        <v>4</v>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>2486533</t>
+        </is>
+      </c>
+      <c r="V488" t="n">
+        <v>78</v>
+      </c>
+      <c r="W488" t="n">
+        <v>89</v>
+      </c>
+      <c r="X488" t="n">
+        <v>0.7191011235955056</v>
+      </c>
+      <c r="Y488" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z488" t="n">
+        <v>81.01265822784811</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>0.8537653239929948</v>
+      </c>
+      <c r="AB488" t="n">
+        <v>98.28629032258064</v>
+      </c>
+      <c r="AC488" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD488" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AE488" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF488" t="n">
+        <v>-17.27363209473253</v>
+      </c>
+      <c r="AG488" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH488" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI488" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>31</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>225</v>
+      </c>
+      <c r="F489" t="n">
+        <v>99</v>
+      </c>
+      <c r="G489" t="n">
+        <v>18</v>
+      </c>
+      <c r="H489" t="n">
+        <v>36</v>
+      </c>
+      <c r="I489" t="n">
+        <v>16</v>
+      </c>
+      <c r="J489" t="n">
+        <v>35</v>
+      </c>
+      <c r="K489" t="n">
+        <v>15</v>
+      </c>
+      <c r="L489" t="n">
+        <v>20</v>
+      </c>
+      <c r="M489" t="n">
+        <v>3</v>
+      </c>
+      <c r="N489" t="n">
+        <v>24</v>
+      </c>
+      <c r="O489" t="n">
+        <v>15</v>
+      </c>
+      <c r="P489" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>12</v>
+      </c>
+      <c r="R489" t="n">
+        <v>21</v>
+      </c>
+      <c r="S489" t="n">
+        <v>19</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="V489" t="n">
+        <v>96</v>
+      </c>
+      <c r="W489" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="X489" t="n">
+        <v>1.07843137254902</v>
+      </c>
+      <c r="Y489" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z489" t="n">
+        <v>111.4864864864865</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>109.0909090909091</v>
+      </c>
+      <c r="AC489" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AE489" t="n">
+        <v>0.4029850746268657</v>
+      </c>
+      <c r="AF489" t="n">
+        <v>2.395577395577391</v>
+      </c>
+      <c r="AG489" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH489" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI489" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>31</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>200</v>
+      </c>
+      <c r="F490" t="n">
+        <v>72</v>
+      </c>
+      <c r="G490" t="n">
+        <v>15</v>
+      </c>
+      <c r="H490" t="n">
+        <v>35</v>
+      </c>
+      <c r="I490" t="n">
+        <v>10</v>
+      </c>
+      <c r="J490" t="n">
+        <v>27</v>
+      </c>
+      <c r="K490" t="n">
+        <v>12</v>
+      </c>
+      <c r="L490" t="n">
+        <v>17</v>
+      </c>
+      <c r="M490" t="n">
+        <v>8</v>
+      </c>
+      <c r="N490" t="n">
+        <v>20</v>
+      </c>
+      <c r="O490" t="n">
+        <v>13</v>
+      </c>
+      <c r="P490" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>9</v>
+      </c>
+      <c r="R490" t="n">
+        <v>27</v>
+      </c>
+      <c r="S490" t="n">
+        <v>22</v>
+      </c>
+      <c r="T490" t="n">
+        <v>2</v>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>2486531</t>
+        </is>
+      </c>
+      <c r="V490" t="n">
+        <v>81</v>
+      </c>
+      <c r="W490" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="X490" t="n">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="Y490" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="Z490" t="n">
+        <v>102.1566401816118</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>0.9839650145772596</v>
+      </c>
+      <c r="AB490" t="n">
+        <v>113.5726303982053</v>
+      </c>
+      <c r="AC490" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD490" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AE490" t="n">
+        <v>0.4307692307692308</v>
+      </c>
+      <c r="AF490" t="n">
+        <v>-11.41599021659347</v>
+      </c>
+      <c r="AG490" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH490" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI490" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>31</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>200</v>
+      </c>
+      <c r="F491" t="n">
+        <v>73</v>
+      </c>
+      <c r="G491" t="n">
+        <v>26</v>
+      </c>
+      <c r="H491" t="n">
+        <v>42</v>
+      </c>
+      <c r="I491" t="n">
+        <v>4</v>
+      </c>
+      <c r="J491" t="n">
+        <v>18</v>
+      </c>
+      <c r="K491" t="n">
+        <v>9</v>
+      </c>
+      <c r="L491" t="n">
+        <v>14</v>
+      </c>
+      <c r="M491" t="n">
+        <v>8</v>
+      </c>
+      <c r="N491" t="n">
+        <v>27</v>
+      </c>
+      <c r="O491" t="n">
+        <v>23</v>
+      </c>
+      <c r="P491" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>8</v>
+      </c>
+      <c r="R491" t="n">
+        <v>18</v>
+      </c>
+      <c r="S491" t="n">
+        <v>18</v>
+      </c>
+      <c r="T491" t="n">
+        <v>6</v>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="V491" t="n">
+        <v>63</v>
+      </c>
+      <c r="W491" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="X491" t="n">
+        <v>0.9843581445523194</v>
+      </c>
+      <c r="Y491" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="Z491" t="n">
+        <v>110.3385731559855</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>0.7859281437125749</v>
+      </c>
+      <c r="AB491" t="n">
+        <v>89.79475484606614</v>
+      </c>
+      <c r="AC491" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="AD491" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="AE491" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="AF491" t="n">
+        <v>20.54381830991936</v>
+      </c>
+      <c r="AG491" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH491" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI491" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>31</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>200</v>
+      </c>
+      <c r="F492" t="n">
+        <v>81</v>
+      </c>
+      <c r="G492" t="n">
+        <v>12</v>
+      </c>
+      <c r="H492" t="n">
+        <v>31</v>
+      </c>
+      <c r="I492" t="n">
+        <v>12</v>
+      </c>
+      <c r="J492" t="n">
+        <v>31</v>
+      </c>
+      <c r="K492" t="n">
+        <v>21</v>
+      </c>
+      <c r="L492" t="n">
+        <v>28</v>
+      </c>
+      <c r="M492" t="n">
+        <v>11</v>
+      </c>
+      <c r="N492" t="n">
+        <v>26</v>
+      </c>
+      <c r="O492" t="n">
+        <v>21</v>
+      </c>
+      <c r="P492" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>8</v>
+      </c>
+      <c r="R492" t="n">
+        <v>22</v>
+      </c>
+      <c r="S492" t="n">
+        <v>27</v>
+      </c>
+      <c r="T492" t="n">
+        <v>3</v>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>2486531</t>
+        </is>
+      </c>
+      <c r="V492" t="n">
+        <v>72</v>
+      </c>
+      <c r="W492" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="X492" t="n">
+        <v>0.9839650145772596</v>
+      </c>
+      <c r="Y492" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="Z492" t="n">
+        <v>113.5726303982053</v>
+      </c>
+      <c r="AA492" t="n">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="AB492" t="n">
+        <v>102.1566401816118</v>
+      </c>
+      <c r="AC492" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="AD492" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE492" t="n">
+        <v>0.5692307692307692</v>
+      </c>
+      <c r="AF492" t="n">
+        <v>11.41599021659347</v>
+      </c>
+      <c r="AG492" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH492" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI492" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>31</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>200</v>
+      </c>
+      <c r="F493" t="n">
+        <v>73</v>
+      </c>
+      <c r="G493" t="n">
+        <v>14</v>
+      </c>
+      <c r="H493" t="n">
+        <v>26</v>
+      </c>
+      <c r="I493" t="n">
+        <v>10</v>
+      </c>
+      <c r="J493" t="n">
+        <v>34</v>
+      </c>
+      <c r="K493" t="n">
+        <v>15</v>
+      </c>
+      <c r="L493" t="n">
+        <v>20</v>
+      </c>
+      <c r="M493" t="n">
+        <v>11</v>
+      </c>
+      <c r="N493" t="n">
+        <v>26</v>
+      </c>
+      <c r="O493" t="n">
+        <v>10</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>15</v>
+      </c>
+      <c r="R493" t="n">
+        <v>17</v>
+      </c>
+      <c r="S493" t="n">
+        <v>21</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>2486532</t>
+        </is>
+      </c>
+      <c r="V493" t="n">
+        <v>86</v>
+      </c>
+      <c r="W493" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X493" t="n">
+        <v>0.8711217183770883</v>
+      </c>
+      <c r="Y493" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z493" t="n">
+        <v>100.2747252747253</v>
+      </c>
+      <c r="AA493" t="n">
+        <v>1.072854291417166</v>
+      </c>
+      <c r="AB493" t="n">
+        <v>117.550574084199</v>
+      </c>
+      <c r="AC493" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD493" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AE493" t="n">
+        <v>0.5362318840579711</v>
+      </c>
+      <c r="AF493" t="n">
+        <v>-17.27584880947374</v>
+      </c>
+      <c r="AG493" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH493" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI493" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>31</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>225</v>
+      </c>
+      <c r="F494" t="n">
+        <v>96</v>
+      </c>
+      <c r="G494" t="n">
+        <v>19</v>
+      </c>
+      <c r="H494" t="n">
+        <v>35</v>
+      </c>
+      <c r="I494" t="n">
+        <v>13</v>
+      </c>
+      <c r="J494" t="n">
+        <v>37</v>
+      </c>
+      <c r="K494" t="n">
+        <v>19</v>
+      </c>
+      <c r="L494" t="n">
+        <v>25</v>
+      </c>
+      <c r="M494" t="n">
+        <v>11</v>
+      </c>
+      <c r="N494" t="n">
+        <v>29</v>
+      </c>
+      <c r="O494" t="n">
+        <v>13</v>
+      </c>
+      <c r="P494" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>16</v>
+      </c>
+      <c r="R494" t="n">
+        <v>19</v>
+      </c>
+      <c r="S494" t="n">
+        <v>21</v>
+      </c>
+      <c r="T494" t="n">
+        <v>2</v>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="V494" t="n">
+        <v>99</v>
+      </c>
+      <c r="W494" t="n">
+        <v>99</v>
+      </c>
+      <c r="X494" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="Y494" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z494" t="n">
+        <v>109.0909090909091</v>
+      </c>
+      <c r="AA494" t="n">
+        <v>1.07843137254902</v>
+      </c>
+      <c r="AB494" t="n">
+        <v>111.4864864864865</v>
+      </c>
+      <c r="AC494" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="AD494" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="AE494" t="n">
+        <v>0.5970149253731343</v>
+      </c>
+      <c r="AF494" t="n">
+        <v>-2.395577395577391</v>
+      </c>
+      <c r="AG494" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH494" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI494" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>31</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>200</v>
+      </c>
+      <c r="F495" t="n">
+        <v>86</v>
+      </c>
+      <c r="G495" t="n">
+        <v>18</v>
+      </c>
+      <c r="H495" t="n">
+        <v>33</v>
+      </c>
+      <c r="I495" t="n">
+        <v>13</v>
+      </c>
+      <c r="J495" t="n">
+        <v>33</v>
+      </c>
+      <c r="K495" t="n">
+        <v>11</v>
+      </c>
+      <c r="L495" t="n">
+        <v>14</v>
+      </c>
+      <c r="M495" t="n">
+        <v>7</v>
+      </c>
+      <c r="N495" t="n">
+        <v>25</v>
+      </c>
+      <c r="O495" t="n">
+        <v>20</v>
+      </c>
+      <c r="P495" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>8</v>
+      </c>
+      <c r="R495" t="n">
+        <v>21</v>
+      </c>
+      <c r="S495" t="n">
+        <v>17</v>
+      </c>
+      <c r="T495" t="n">
+        <v>2</v>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>2486532</t>
+        </is>
+      </c>
+      <c r="V495" t="n">
+        <v>73</v>
+      </c>
+      <c r="W495" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X495" t="n">
+        <v>1.072854291417166</v>
+      </c>
+      <c r="Y495" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="Z495" t="n">
+        <v>117.550574084199</v>
+      </c>
+      <c r="AA495" t="n">
+        <v>0.8711217183770883</v>
+      </c>
+      <c r="AB495" t="n">
+        <v>100.2747252747253</v>
+      </c>
+      <c r="AC495" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="AD495" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE495" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="AF495" t="n">
+        <v>17.27584880947374</v>
+      </c>
+      <c r="AG495" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH495" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI495" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>31</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>200</v>
+      </c>
+      <c r="F496" t="n">
+        <v>74</v>
+      </c>
+      <c r="G496" t="n">
+        <v>24</v>
+      </c>
+      <c r="H496" t="n">
+        <v>43</v>
+      </c>
+      <c r="I496" t="n">
+        <v>5</v>
+      </c>
+      <c r="J496" t="n">
+        <v>18</v>
+      </c>
+      <c r="K496" t="n">
+        <v>11</v>
+      </c>
+      <c r="L496" t="n">
+        <v>16</v>
+      </c>
+      <c r="M496" t="n">
+        <v>6</v>
+      </c>
+      <c r="N496" t="n">
+        <v>21</v>
+      </c>
+      <c r="O496" t="n">
+        <v>16</v>
+      </c>
+      <c r="P496" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>12</v>
+      </c>
+      <c r="R496" t="n">
+        <v>19</v>
+      </c>
+      <c r="S496" t="n">
+        <v>18</v>
+      </c>
+      <c r="T496" t="n">
+        <v>4</v>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>2486535</t>
+        </is>
+      </c>
+      <c r="V496" t="n">
+        <v>89</v>
+      </c>
+      <c r="W496" t="n">
+        <v>80.03999999999999</v>
+      </c>
+      <c r="X496" t="n">
+        <v>0.9245377311344328</v>
+      </c>
+      <c r="Y496" t="n">
+        <v>74.03999999999999</v>
+      </c>
+      <c r="Z496" t="n">
+        <v>99.94597514856835</v>
+      </c>
+      <c r="AA496" t="n">
+        <v>1.045091592296853</v>
+      </c>
+      <c r="AB496" t="n">
+        <v>126.8529076396807</v>
+      </c>
+      <c r="AC496" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD496" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AE496" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="AF496" t="n">
+        <v>-26.90693249111239</v>
+      </c>
+      <c r="AG496" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH496" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI496" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>31</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>200</v>
+      </c>
+      <c r="F497" t="n">
+        <v>93</v>
+      </c>
+      <c r="G497" t="n">
+        <v>13</v>
+      </c>
+      <c r="H497" t="n">
+        <v>35</v>
+      </c>
+      <c r="I497" t="n">
+        <v>13</v>
+      </c>
+      <c r="J497" t="n">
+        <v>25</v>
+      </c>
+      <c r="K497" t="n">
+        <v>28</v>
+      </c>
+      <c r="L497" t="n">
+        <v>31</v>
+      </c>
+      <c r="M497" t="n">
+        <v>7</v>
+      </c>
+      <c r="N497" t="n">
+        <v>18</v>
+      </c>
+      <c r="O497" t="n">
+        <v>21</v>
+      </c>
+      <c r="P497" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>12</v>
+      </c>
+      <c r="R497" t="n">
+        <v>25</v>
+      </c>
+      <c r="S497" t="n">
+        <v>24</v>
+      </c>
+      <c r="T497" t="n">
+        <v>3</v>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="V497" t="n">
+        <v>90</v>
+      </c>
+      <c r="W497" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="X497" t="n">
+        <v>1.085941148995796</v>
+      </c>
+      <c r="Y497" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="Z497" t="n">
+        <v>118.2604272634791</v>
+      </c>
+      <c r="AA497" t="n">
+        <v>1.041184636742249</v>
+      </c>
+      <c r="AB497" t="n">
+        <v>122.5490196078431</v>
+      </c>
+      <c r="AC497" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="AD497" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="AE497" t="n">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="AF497" t="n">
+        <v>-4.288592344363991</v>
+      </c>
+      <c r="AG497" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH497" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI497" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>32</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>200</v>
+      </c>
+      <c r="F498" t="n">
+        <v>86</v>
+      </c>
+      <c r="G498" t="n">
+        <v>21</v>
+      </c>
+      <c r="H498" t="n">
+        <v>40</v>
+      </c>
+      <c r="I498" t="n">
+        <v>9</v>
+      </c>
+      <c r="J498" t="n">
+        <v>28</v>
+      </c>
+      <c r="K498" t="n">
+        <v>17</v>
+      </c>
+      <c r="L498" t="n">
+        <v>26</v>
+      </c>
+      <c r="M498" t="n">
+        <v>11</v>
+      </c>
+      <c r="N498" t="n">
+        <v>18</v>
+      </c>
+      <c r="O498" t="n">
+        <v>18</v>
+      </c>
+      <c r="P498" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>4</v>
+      </c>
+      <c r="R498" t="n">
+        <v>19</v>
+      </c>
+      <c r="S498" t="n">
+        <v>26</v>
+      </c>
+      <c r="T498" t="n">
+        <v>2</v>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="V498" t="n">
+        <v>89</v>
+      </c>
+      <c r="W498" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="X498" t="n">
+        <v>1.030680728667306</v>
+      </c>
+      <c r="Y498" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="Z498" t="n">
+        <v>118.7189398122584</v>
+      </c>
+      <c r="AA498" t="n">
+        <v>1.155244029075805</v>
+      </c>
+      <c r="AB498" t="n">
+        <v>123.5424764019989</v>
+      </c>
+      <c r="AC498" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD498" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="AE498" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF498" t="n">
+        <v>-4.823536589740471</v>
+      </c>
+      <c r="AG498" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH498" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI498" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>32</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>200</v>
+      </c>
+      <c r="F499" t="n">
+        <v>70</v>
+      </c>
+      <c r="G499" t="n">
+        <v>18</v>
+      </c>
+      <c r="H499" t="n">
+        <v>34</v>
+      </c>
+      <c r="I499" t="n">
+        <v>5</v>
+      </c>
+      <c r="J499" t="n">
+        <v>23</v>
+      </c>
+      <c r="K499" t="n">
+        <v>19</v>
+      </c>
+      <c r="L499" t="n">
+        <v>30</v>
+      </c>
+      <c r="M499" t="n">
+        <v>10</v>
+      </c>
+      <c r="N499" t="n">
+        <v>23</v>
+      </c>
+      <c r="O499" t="n">
+        <v>11</v>
+      </c>
+      <c r="P499" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>9</v>
+      </c>
+      <c r="R499" t="n">
+        <v>27</v>
+      </c>
+      <c r="S499" t="n">
+        <v>28</v>
+      </c>
+      <c r="T499" t="n">
+        <v>2</v>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="V499" t="n">
+        <v>73</v>
+      </c>
+      <c r="W499" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="X499" t="n">
+        <v>0.8838383838383838</v>
+      </c>
+      <c r="Y499" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z499" t="n">
+        <v>101.1560693641619</v>
+      </c>
+      <c r="AA499" t="n">
+        <v>0.9554973821989529</v>
+      </c>
+      <c r="AB499" t="n">
+        <v>106.7251461988304</v>
+      </c>
+      <c r="AC499" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD499" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="AE499" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF499" t="n">
+        <v>-5.56907683466855</v>
+      </c>
+      <c r="AG499" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH499" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI499" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>32</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>200</v>
+      </c>
+      <c r="F500" t="n">
+        <v>70</v>
+      </c>
+      <c r="G500" t="n">
+        <v>13</v>
+      </c>
+      <c r="H500" t="n">
+        <v>34</v>
+      </c>
+      <c r="I500" t="n">
+        <v>11</v>
+      </c>
+      <c r="J500" t="n">
+        <v>30</v>
+      </c>
+      <c r="K500" t="n">
+        <v>11</v>
+      </c>
+      <c r="L500" t="n">
+        <v>21</v>
+      </c>
+      <c r="M500" t="n">
+        <v>11</v>
+      </c>
+      <c r="N500" t="n">
+        <v>25</v>
+      </c>
+      <c r="O500" t="n">
+        <v>15</v>
+      </c>
+      <c r="P500" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>10</v>
+      </c>
+      <c r="R500" t="n">
+        <v>16</v>
+      </c>
+      <c r="S500" t="n">
+        <v>20</v>
+      </c>
+      <c r="T500" t="n">
+        <v>1</v>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>2486542</t>
+        </is>
+      </c>
+      <c r="V500" t="n">
+        <v>92</v>
+      </c>
+      <c r="W500" t="n">
+        <v>83.24000000000001</v>
+      </c>
+      <c r="X500" t="n">
+        <v>0.8409418548774626</v>
+      </c>
+      <c r="Y500" t="n">
+        <v>72.24000000000001</v>
+      </c>
+      <c r="Z500" t="n">
+        <v>96.89922480620154</v>
+      </c>
+      <c r="AA500" t="n">
+        <v>1.108968177434908</v>
+      </c>
+      <c r="AB500" t="n">
+        <v>127.8488048916064</v>
+      </c>
+      <c r="AC500" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="AD500" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE500" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF500" t="n">
+        <v>-30.94958008540489</v>
+      </c>
+      <c r="AG500" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH500" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI500" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>32</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>200</v>
+      </c>
+      <c r="F501" t="n">
+        <v>91</v>
+      </c>
+      <c r="G501" t="n">
+        <v>24</v>
+      </c>
+      <c r="H501" t="n">
+        <v>37</v>
+      </c>
+      <c r="I501" t="n">
+        <v>10</v>
+      </c>
+      <c r="J501" t="n">
+        <v>26</v>
+      </c>
+      <c r="K501" t="n">
+        <v>13</v>
+      </c>
+      <c r="L501" t="n">
+        <v>19</v>
+      </c>
+      <c r="M501" t="n">
+        <v>8</v>
+      </c>
+      <c r="N501" t="n">
+        <v>33</v>
+      </c>
+      <c r="O501" t="n">
+        <v>19</v>
+      </c>
+      <c r="P501" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>17</v>
+      </c>
+      <c r="R501" t="n">
+        <v>15</v>
+      </c>
+      <c r="S501" t="n">
+        <v>19</v>
+      </c>
+      <c r="T501" t="n">
+        <v>1</v>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="V501" t="n">
+        <v>82</v>
+      </c>
+      <c r="W501" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="X501" t="n">
+        <v>1.02987777274785</v>
+      </c>
+      <c r="Y501" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="Z501" t="n">
+        <v>113.2404181184669</v>
+      </c>
+      <c r="AA501" t="n">
+        <v>0.9860509860509861</v>
+      </c>
+      <c r="AB501" t="n">
+        <v>104.9129989764586</v>
+      </c>
+      <c r="AC501" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="AD501" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="AE501" t="n">
+        <v>0.6307692307692307</v>
+      </c>
+      <c r="AF501" t="n">
+        <v>8.327419142008353</v>
+      </c>
+      <c r="AG501" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH501" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI501" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>32</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>200</v>
+      </c>
+      <c r="F502" t="n">
+        <v>89</v>
+      </c>
+      <c r="G502" t="n">
+        <v>18</v>
+      </c>
+      <c r="H502" t="n">
+        <v>27</v>
+      </c>
+      <c r="I502" t="n">
+        <v>13</v>
+      </c>
+      <c r="J502" t="n">
+        <v>29</v>
+      </c>
+      <c r="K502" t="n">
+        <v>14</v>
+      </c>
+      <c r="L502" t="n">
+        <v>16</v>
+      </c>
+      <c r="M502" t="n">
+        <v>5</v>
+      </c>
+      <c r="N502" t="n">
+        <v>23</v>
+      </c>
+      <c r="O502" t="n">
+        <v>12</v>
+      </c>
+      <c r="P502" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>14</v>
+      </c>
+      <c r="R502" t="n">
+        <v>27</v>
+      </c>
+      <c r="S502" t="n">
+        <v>19</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="V502" t="n">
+        <v>86</v>
+      </c>
+      <c r="W502" t="n">
+        <v>77.03999999999999</v>
+      </c>
+      <c r="X502" t="n">
+        <v>1.155244029075805</v>
+      </c>
+      <c r="Y502" t="n">
+        <v>72.03999999999999</v>
+      </c>
+      <c r="Z502" t="n">
+        <v>123.5424764019989</v>
+      </c>
+      <c r="AA502" t="n">
+        <v>1.030680728667306</v>
+      </c>
+      <c r="AB502" t="n">
+        <v>118.7189398122584</v>
+      </c>
+      <c r="AC502" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="AD502" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE502" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF502" t="n">
+        <v>4.823536589740471</v>
+      </c>
+      <c r="AG502" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH502" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI502" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>32</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>200</v>
+      </c>
+      <c r="F503" t="n">
+        <v>82</v>
+      </c>
+      <c r="G503" t="n">
+        <v>18</v>
+      </c>
+      <c r="H503" t="n">
+        <v>40</v>
+      </c>
+      <c r="I503" t="n">
+        <v>12</v>
+      </c>
+      <c r="J503" t="n">
+        <v>29</v>
+      </c>
+      <c r="K503" t="n">
+        <v>10</v>
+      </c>
+      <c r="L503" t="n">
+        <v>14</v>
+      </c>
+      <c r="M503" t="n">
+        <v>5</v>
+      </c>
+      <c r="N503" t="n">
+        <v>19</v>
+      </c>
+      <c r="O503" t="n">
+        <v>18</v>
+      </c>
+      <c r="P503" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>8</v>
+      </c>
+      <c r="R503" t="n">
+        <v>19</v>
+      </c>
+      <c r="S503" t="n">
+        <v>15</v>
+      </c>
+      <c r="T503" t="n">
+        <v>4</v>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="V503" t="n">
+        <v>91</v>
+      </c>
+      <c r="W503" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="X503" t="n">
+        <v>0.9860509860509861</v>
+      </c>
+      <c r="Y503" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="Z503" t="n">
+        <v>104.9129989764586</v>
+      </c>
+      <c r="AA503" t="n">
+        <v>1.02987777274785</v>
+      </c>
+      <c r="AB503" t="n">
+        <v>113.2404181184669</v>
+      </c>
+      <c r="AC503" t="n">
+        <v>0.131578947368421</v>
+      </c>
+      <c r="AD503" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="AE503" t="n">
+        <v>0.3692307692307693</v>
+      </c>
+      <c r="AF503" t="n">
+        <v>-8.327419142008353</v>
+      </c>
+      <c r="AG503" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH503" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI503" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>32</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>200</v>
+      </c>
+      <c r="F504" t="n">
+        <v>96</v>
+      </c>
+      <c r="G504" t="n">
+        <v>23</v>
+      </c>
+      <c r="H504" t="n">
+        <v>33</v>
+      </c>
+      <c r="I504" t="n">
+        <v>10</v>
+      </c>
+      <c r="J504" t="n">
+        <v>23</v>
+      </c>
+      <c r="K504" t="n">
+        <v>20</v>
+      </c>
+      <c r="L504" t="n">
+        <v>32</v>
+      </c>
+      <c r="M504" t="n">
+        <v>6</v>
+      </c>
+      <c r="N504" t="n">
+        <v>25</v>
+      </c>
+      <c r="O504" t="n">
+        <v>21</v>
+      </c>
+      <c r="P504" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>16</v>
+      </c>
+      <c r="R504" t="n">
+        <v>27</v>
+      </c>
+      <c r="S504" t="n">
+        <v>29</v>
+      </c>
+      <c r="T504" t="n">
+        <v>3</v>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="V504" t="n">
+        <v>81</v>
+      </c>
+      <c r="W504" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="X504" t="n">
+        <v>1.115241635687732</v>
+      </c>
+      <c r="Y504" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="Z504" t="n">
+        <v>119.8801198801199</v>
+      </c>
+      <c r="AA504" t="n">
+        <v>0.8587786259541985</v>
+      </c>
+      <c r="AB504" t="n">
+        <v>99.60649286768323</v>
+      </c>
+      <c r="AC504" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AD504" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AE504" t="n">
+        <v>0.4769230769230769</v>
+      </c>
+      <c r="AF504" t="n">
+        <v>20.27362701243665</v>
+      </c>
+      <c r="AG504" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH504" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI504" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>32</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>200</v>
+      </c>
+      <c r="F505" t="n">
+        <v>73</v>
+      </c>
+      <c r="G505" t="n">
+        <v>12</v>
+      </c>
+      <c r="H505" t="n">
+        <v>27</v>
+      </c>
+      <c r="I505" t="n">
+        <v>7</v>
+      </c>
+      <c r="J505" t="n">
+        <v>26</v>
+      </c>
+      <c r="K505" t="n">
+        <v>28</v>
+      </c>
+      <c r="L505" t="n">
+        <v>35</v>
+      </c>
+      <c r="M505" t="n">
+        <v>8</v>
+      </c>
+      <c r="N505" t="n">
+        <v>25</v>
+      </c>
+      <c r="O505" t="n">
+        <v>13</v>
+      </c>
+      <c r="P505" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>8</v>
+      </c>
+      <c r="R505" t="n">
+        <v>29</v>
+      </c>
+      <c r="S505" t="n">
+        <v>27</v>
+      </c>
+      <c r="T505" t="n">
+        <v>3</v>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="V505" t="n">
+        <v>70</v>
+      </c>
+      <c r="W505" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="X505" t="n">
+        <v>0.9554973821989529</v>
+      </c>
+      <c r="Y505" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Z505" t="n">
+        <v>106.7251461988304</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>0.8838383838383838</v>
+      </c>
+      <c r="AB505" t="n">
+        <v>101.1560693641619</v>
+      </c>
+      <c r="AC505" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="AD505" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE505" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF505" t="n">
+        <v>5.56907683466855</v>
+      </c>
+      <c r="AG505" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH505" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI505" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>32</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>200</v>
+      </c>
+      <c r="F506" t="n">
+        <v>68</v>
+      </c>
+      <c r="G506" t="n">
+        <v>11</v>
+      </c>
+      <c r="H506" t="n">
+        <v>35</v>
+      </c>
+      <c r="I506" t="n">
+        <v>11</v>
+      </c>
+      <c r="J506" t="n">
+        <v>33</v>
+      </c>
+      <c r="K506" t="n">
+        <v>13</v>
+      </c>
+      <c r="L506" t="n">
+        <v>20</v>
+      </c>
+      <c r="M506" t="n">
+        <v>15</v>
+      </c>
+      <c r="N506" t="n">
+        <v>29</v>
+      </c>
+      <c r="O506" t="n">
+        <v>16</v>
+      </c>
+      <c r="P506" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>11</v>
+      </c>
+      <c r="R506" t="n">
+        <v>22</v>
+      </c>
+      <c r="S506" t="n">
+        <v>21</v>
+      </c>
+      <c r="T506" t="n">
+        <v>2</v>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="V506" t="n">
+        <v>77</v>
+      </c>
+      <c r="W506" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="X506" t="n">
+        <v>0.7744874715261959</v>
+      </c>
+      <c r="Y506" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z506" t="n">
+        <v>93.40659340659342</v>
+      </c>
+      <c r="AA506" t="n">
+        <v>0.918854415274463</v>
+      </c>
+      <c r="AB506" t="n">
+        <v>104.3360433604336</v>
+      </c>
+      <c r="AC506" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="AD506" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE506" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+      <c r="AF506" t="n">
+        <v>-10.92944995384019</v>
+      </c>
+      <c r="AG506" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH506" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI506" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>32</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>200</v>
+      </c>
+      <c r="F507" t="n">
+        <v>81</v>
+      </c>
+      <c r="G507" t="n">
+        <v>20</v>
+      </c>
+      <c r="H507" t="n">
+        <v>35</v>
+      </c>
+      <c r="I507" t="n">
+        <v>10</v>
+      </c>
+      <c r="J507" t="n">
+        <v>25</v>
+      </c>
+      <c r="K507" t="n">
+        <v>11</v>
+      </c>
+      <c r="L507" t="n">
+        <v>17</v>
+      </c>
+      <c r="M507" t="n">
+        <v>4</v>
+      </c>
+      <c r="N507" t="n">
+        <v>24</v>
+      </c>
+      <c r="O507" t="n">
+        <v>29</v>
+      </c>
+      <c r="P507" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>11</v>
+      </c>
+      <c r="R507" t="n">
+        <v>17</v>
+      </c>
+      <c r="S507" t="n">
+        <v>20</v>
+      </c>
+      <c r="T507" t="n">
+        <v>3</v>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>2486539</t>
+        </is>
+      </c>
+      <c r="V507" t="n">
+        <v>92</v>
+      </c>
+      <c r="W507" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="X507" t="n">
+        <v>1.032110091743119</v>
+      </c>
+      <c r="Y507" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="Z507" t="n">
+        <v>108.7540279269602</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>0.9603340292275574</v>
+      </c>
+      <c r="AB507" t="n">
+        <v>113.8613861386139</v>
+      </c>
+      <c r="AC507" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="AD507" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="AE507" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="AF507" t="n">
+        <v>-5.107358211653619</v>
+      </c>
+      <c r="AG507" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH507" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI507" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>32</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>200</v>
+      </c>
+      <c r="F508" t="n">
+        <v>92</v>
+      </c>
+      <c r="G508" t="n">
+        <v>24</v>
+      </c>
+      <c r="H508" t="n">
+        <v>51</v>
+      </c>
+      <c r="I508" t="n">
+        <v>10</v>
+      </c>
+      <c r="J508" t="n">
+        <v>27</v>
+      </c>
+      <c r="K508" t="n">
+        <v>14</v>
+      </c>
+      <c r="L508" t="n">
+        <v>20</v>
+      </c>
+      <c r="M508" t="n">
+        <v>15</v>
+      </c>
+      <c r="N508" t="n">
+        <v>25</v>
+      </c>
+      <c r="O508" t="n">
+        <v>22</v>
+      </c>
+      <c r="P508" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>9</v>
+      </c>
+      <c r="R508" t="n">
+        <v>20</v>
+      </c>
+      <c r="S508" t="n">
+        <v>17</v>
+      </c>
+      <c r="T508" t="n">
+        <v>1</v>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>2486539</t>
+        </is>
+      </c>
+      <c r="V508" t="n">
+        <v>81</v>
+      </c>
+      <c r="W508" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="X508" t="n">
+        <v>0.9603340292275574</v>
+      </c>
+      <c r="Y508" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="Z508" t="n">
+        <v>113.8613861386139</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>1.032110091743119</v>
+      </c>
+      <c r="AB508" t="n">
+        <v>108.7540279269602</v>
+      </c>
+      <c r="AC508" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="AD508" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="AE508" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="AF508" t="n">
+        <v>5.107358211653619</v>
+      </c>
+      <c r="AG508" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH508" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI508" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>32</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>200</v>
+      </c>
+      <c r="F509" t="n">
+        <v>81</v>
+      </c>
+      <c r="G509" t="n">
+        <v>13</v>
+      </c>
+      <c r="H509" t="n">
+        <v>30</v>
+      </c>
+      <c r="I509" t="n">
+        <v>11</v>
+      </c>
+      <c r="J509" t="n">
+        <v>37</v>
+      </c>
+      <c r="K509" t="n">
+        <v>22</v>
+      </c>
+      <c r="L509" t="n">
+        <v>28</v>
+      </c>
+      <c r="M509" t="n">
+        <v>13</v>
+      </c>
+      <c r="N509" t="n">
+        <v>21</v>
+      </c>
+      <c r="O509" t="n">
+        <v>12</v>
+      </c>
+      <c r="P509" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>15</v>
+      </c>
+      <c r="R509" t="n">
+        <v>29</v>
+      </c>
+      <c r="S509" t="n">
+        <v>26</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="V509" t="n">
+        <v>96</v>
+      </c>
+      <c r="W509" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="X509" t="n">
+        <v>0.8587786259541985</v>
+      </c>
+      <c r="Y509" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="Z509" t="n">
+        <v>99.60649286768323</v>
+      </c>
+      <c r="AA509" t="n">
+        <v>1.115241635687732</v>
+      </c>
+      <c r="AB509" t="n">
+        <v>119.8801198801199</v>
+      </c>
+      <c r="AC509" t="n">
+        <v>0.3421052631578947</v>
+      </c>
+      <c r="AD509" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AE509" t="n">
+        <v>0.5230769230769231</v>
+      </c>
+      <c r="AF509" t="n">
+        <v>-20.27362701243665</v>
+      </c>
+      <c r="AG509" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH509" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI509" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>32</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>200</v>
+      </c>
+      <c r="F510" t="n">
+        <v>89</v>
+      </c>
+      <c r="G510" t="n">
+        <v>17</v>
+      </c>
+      <c r="H510" t="n">
+        <v>30</v>
+      </c>
+      <c r="I510" t="n">
+        <v>13</v>
+      </c>
+      <c r="J510" t="n">
+        <v>35</v>
+      </c>
+      <c r="K510" t="n">
+        <v>16</v>
+      </c>
+      <c r="L510" t="n">
+        <v>20</v>
+      </c>
+      <c r="M510" t="n">
+        <v>14</v>
+      </c>
+      <c r="N510" t="n">
+        <v>20</v>
+      </c>
+      <c r="O510" t="n">
+        <v>14</v>
+      </c>
+      <c r="P510" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>9</v>
+      </c>
+      <c r="R510" t="n">
+        <v>23</v>
+      </c>
+      <c r="S510" t="n">
+        <v>22</v>
+      </c>
+      <c r="T510" t="n">
+        <v>2</v>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="V510" t="n">
+        <v>79</v>
+      </c>
+      <c r="W510" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X510" t="n">
+        <v>1.07487922705314</v>
+      </c>
+      <c r="Y510" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="Z510" t="n">
+        <v>129.3604651162791</v>
+      </c>
+      <c r="AA510" t="n">
+        <v>1.004067107269954</v>
+      </c>
+      <c r="AB510" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AC510" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AD510" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AE510" t="n">
+        <v>0.576271186440678</v>
+      </c>
+      <c r="AF510" t="n">
+        <v>20.66481294236604</v>
+      </c>
+      <c r="AG510" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH510" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI510" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>32</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>200</v>
+      </c>
+      <c r="F511" t="n">
+        <v>79</v>
+      </c>
+      <c r="G511" t="n">
+        <v>15</v>
+      </c>
+      <c r="H511" t="n">
+        <v>23</v>
+      </c>
+      <c r="I511" t="n">
+        <v>11</v>
+      </c>
+      <c r="J511" t="n">
+        <v>30</v>
+      </c>
+      <c r="K511" t="n">
+        <v>16</v>
+      </c>
+      <c r="L511" t="n">
+        <v>22</v>
+      </c>
+      <c r="M511" t="n">
+        <v>6</v>
+      </c>
+      <c r="N511" t="n">
+        <v>19</v>
+      </c>
+      <c r="O511" t="n">
+        <v>23</v>
+      </c>
+      <c r="P511" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>16</v>
+      </c>
+      <c r="R511" t="n">
+        <v>22</v>
+      </c>
+      <c r="S511" t="n">
+        <v>22</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="V511" t="n">
+        <v>89</v>
+      </c>
+      <c r="W511" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="X511" t="n">
+        <v>1.004067107269954</v>
+      </c>
+      <c r="Y511" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z511" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AA511" t="n">
+        <v>1.07487922705314</v>
+      </c>
+      <c r="AB511" t="n">
+        <v>129.3604651162791</v>
+      </c>
+      <c r="AC511" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AD511" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="AE511" t="n">
+        <v>0.423728813559322</v>
+      </c>
+      <c r="AF511" t="n">
+        <v>-20.66481294236604</v>
+      </c>
+      <c r="AG511" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH511" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI511" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>32</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>200</v>
+      </c>
+      <c r="F512" t="n">
+        <v>77</v>
+      </c>
+      <c r="G512" t="n">
+        <v>16</v>
+      </c>
+      <c r="H512" t="n">
+        <v>34</v>
+      </c>
+      <c r="I512" t="n">
+        <v>9</v>
+      </c>
+      <c r="J512" t="n">
+        <v>32</v>
+      </c>
+      <c r="K512" t="n">
+        <v>18</v>
+      </c>
+      <c r="L512" t="n">
+        <v>20</v>
+      </c>
+      <c r="M512" t="n">
+        <v>10</v>
+      </c>
+      <c r="N512" t="n">
+        <v>28</v>
+      </c>
+      <c r="O512" t="n">
+        <v>12</v>
+      </c>
+      <c r="P512" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>9</v>
+      </c>
+      <c r="R512" t="n">
+        <v>21</v>
+      </c>
+      <c r="S512" t="n">
+        <v>20</v>
+      </c>
+      <c r="T512" t="n">
+        <v>5</v>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="V512" t="n">
+        <v>68</v>
+      </c>
+      <c r="W512" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X512" t="n">
+        <v>0.918854415274463</v>
+      </c>
+      <c r="Y512" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="Z512" t="n">
+        <v>104.3360433604336</v>
+      </c>
+      <c r="AA512" t="n">
+        <v>0.7744874715261959</v>
+      </c>
+      <c r="AB512" t="n">
+        <v>93.40659340659342</v>
+      </c>
+      <c r="AC512" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD512" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="AE512" t="n">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="AF512" t="n">
+        <v>10.92944995384019</v>
+      </c>
+      <c r="AG512" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH512" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI512" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>32</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>200</v>
+      </c>
+      <c r="F513" t="n">
+        <v>92</v>
+      </c>
+      <c r="G513" t="n">
+        <v>26</v>
+      </c>
+      <c r="H513" t="n">
+        <v>43</v>
+      </c>
+      <c r="I513" t="n">
+        <v>12</v>
+      </c>
+      <c r="J513" t="n">
+        <v>29</v>
+      </c>
+      <c r="K513" t="n">
+        <v>4</v>
+      </c>
+      <c r="L513" t="n">
+        <v>9</v>
+      </c>
+      <c r="M513" t="n">
+        <v>11</v>
+      </c>
+      <c r="N513" t="n">
+        <v>30</v>
+      </c>
+      <c r="O513" t="n">
+        <v>24</v>
+      </c>
+      <c r="P513" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>7</v>
+      </c>
+      <c r="R513" t="n">
+        <v>20</v>
+      </c>
+      <c r="S513" t="n">
+        <v>16</v>
+      </c>
+      <c r="T513" t="n">
+        <v>1</v>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>2486542</t>
+        </is>
+      </c>
+      <c r="V513" t="n">
+        <v>70</v>
+      </c>
+      <c r="W513" t="n">
+        <v>82.96000000000001</v>
+      </c>
+      <c r="X513" t="n">
+        <v>1.108968177434908</v>
+      </c>
+      <c r="Y513" t="n">
+        <v>71.96000000000001</v>
+      </c>
+      <c r="Z513" t="n">
+        <v>127.8488048916064</v>
+      </c>
+      <c r="AA513" t="n">
+        <v>0.8409418548774626</v>
+      </c>
+      <c r="AB513" t="n">
+        <v>96.89922480620154</v>
+      </c>
+      <c r="AC513" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD513" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="AE513" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF513" t="n">
+        <v>30.94958008540489</v>
+      </c>
+      <c r="AG513" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH513" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI513" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI513"/>
+  <dimension ref="A1:AI433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52010,9526 +52010,6 @@
         </is>
       </c>
       <c r="AI433" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B434" t="n">
-        <v>28</v>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="E434" t="n">
-        <v>200</v>
-      </c>
-      <c r="F434" t="n">
-        <v>76</v>
-      </c>
-      <c r="G434" t="n">
-        <v>19</v>
-      </c>
-      <c r="H434" t="n">
-        <v>36</v>
-      </c>
-      <c r="I434" t="n">
-        <v>7</v>
-      </c>
-      <c r="J434" t="n">
-        <v>28</v>
-      </c>
-      <c r="K434" t="n">
-        <v>17</v>
-      </c>
-      <c r="L434" t="n">
-        <v>20</v>
-      </c>
-      <c r="M434" t="n">
-        <v>14</v>
-      </c>
-      <c r="N434" t="n">
-        <v>27</v>
-      </c>
-      <c r="O434" t="n">
-        <v>9</v>
-      </c>
-      <c r="P434" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q434" t="n">
-        <v>16</v>
-      </c>
-      <c r="R434" t="n">
-        <v>19</v>
-      </c>
-      <c r="S434" t="n">
-        <v>19</v>
-      </c>
-      <c r="T434" t="n">
-        <v>2</v>
-      </c>
-      <c r="U434" t="inlineStr">
-        <is>
-          <t>2486505</t>
-        </is>
-      </c>
-      <c r="V434" t="n">
-        <v>74</v>
-      </c>
-      <c r="W434" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="X434" t="n">
-        <v>0.8558558558558559</v>
-      </c>
-      <c r="Y434" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="Z434" t="n">
-        <v>101.6042780748663</v>
-      </c>
-      <c r="AA434" t="n">
-        <v>0.8677298311444652</v>
-      </c>
-      <c r="AB434" t="n">
-        <v>95.75569358178053</v>
-      </c>
-      <c r="AC434" t="n">
-        <v>0.3684210526315789</v>
-      </c>
-      <c r="AD434" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="AE434" t="n">
-        <v>0.5616438356164384</v>
-      </c>
-      <c r="AF434" t="n">
-        <v>5.848584493085781</v>
-      </c>
-      <c r="AG434" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH434" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI434" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B435" t="n">
-        <v>28</v>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="E435" t="n">
-        <v>200</v>
-      </c>
-      <c r="F435" t="n">
-        <v>80</v>
-      </c>
-      <c r="G435" t="n">
-        <v>22</v>
-      </c>
-      <c r="H435" t="n">
-        <v>43</v>
-      </c>
-      <c r="I435" t="n">
-        <v>6</v>
-      </c>
-      <c r="J435" t="n">
-        <v>18</v>
-      </c>
-      <c r="K435" t="n">
-        <v>18</v>
-      </c>
-      <c r="L435" t="n">
-        <v>26</v>
-      </c>
-      <c r="M435" t="n">
-        <v>7</v>
-      </c>
-      <c r="N435" t="n">
-        <v>25</v>
-      </c>
-      <c r="O435" t="n">
-        <v>17</v>
-      </c>
-      <c r="P435" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q435" t="n">
-        <v>13</v>
-      </c>
-      <c r="R435" t="n">
-        <v>21</v>
-      </c>
-      <c r="S435" t="n">
-        <v>22</v>
-      </c>
-      <c r="T435" t="n">
-        <v>1</v>
-      </c>
-      <c r="U435" t="inlineStr">
-        <is>
-          <t>2486507</t>
-        </is>
-      </c>
-      <c r="V435" t="n">
-        <v>79</v>
-      </c>
-      <c r="W435" t="n">
-        <v>85.44</v>
-      </c>
-      <c r="X435" t="n">
-        <v>0.9363295880149813</v>
-      </c>
-      <c r="Y435" t="n">
-        <v>78.44</v>
-      </c>
-      <c r="Z435" t="n">
-        <v>101.9887812340643</v>
-      </c>
-      <c r="AA435" t="n">
-        <v>0.9168987929433612</v>
-      </c>
-      <c r="AB435" t="n">
-        <v>99.79787771601819</v>
-      </c>
-      <c r="AC435" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="AD435" t="n">
-        <v>0.78125</v>
-      </c>
-      <c r="AE435" t="n">
-        <v>0.5079365079365079</v>
-      </c>
-      <c r="AF435" t="n">
-        <v>2.190903518046071</v>
-      </c>
-      <c r="AG435" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH435" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI435" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B436" t="n">
-        <v>28</v>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="E436" t="n">
-        <v>200</v>
-      </c>
-      <c r="F436" t="n">
-        <v>56</v>
-      </c>
-      <c r="G436" t="n">
-        <v>12</v>
-      </c>
-      <c r="H436" t="n">
-        <v>47</v>
-      </c>
-      <c r="I436" t="n">
-        <v>5</v>
-      </c>
-      <c r="J436" t="n">
-        <v>17</v>
-      </c>
-      <c r="K436" t="n">
-        <v>17</v>
-      </c>
-      <c r="L436" t="n">
-        <v>27</v>
-      </c>
-      <c r="M436" t="n">
-        <v>15</v>
-      </c>
-      <c r="N436" t="n">
-        <v>26</v>
-      </c>
-      <c r="O436" t="n">
-        <v>10</v>
-      </c>
-      <c r="P436" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q436" t="n">
-        <v>11</v>
-      </c>
-      <c r="R436" t="n">
-        <v>25</v>
-      </c>
-      <c r="S436" t="n">
-        <v>24</v>
-      </c>
-      <c r="T436" t="n">
-        <v>3</v>
-      </c>
-      <c r="U436" t="inlineStr">
-        <is>
-          <t>2486502</t>
-        </is>
-      </c>
-      <c r="V436" t="n">
-        <v>72</v>
-      </c>
-      <c r="W436" t="n">
-        <v>86.88</v>
-      </c>
-      <c r="X436" t="n">
-        <v>0.6445672191528545</v>
-      </c>
-      <c r="Y436" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="Z436" t="n">
-        <v>77.90762381747358</v>
-      </c>
-      <c r="AA436" t="n">
-        <v>0.8819206271435571</v>
-      </c>
-      <c r="AB436" t="n">
-        <v>97.77294948397611</v>
-      </c>
-      <c r="AC436" t="n">
-        <v>0.3061224489795918</v>
-      </c>
-      <c r="AD436" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="AE436" t="n">
-        <v>0.4939759036144578</v>
-      </c>
-      <c r="AF436" t="n">
-        <v>-19.86532566650253</v>
-      </c>
-      <c r="AG436" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH436" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI436" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B437" t="n">
-        <v>28</v>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="E437" t="n">
-        <v>200</v>
-      </c>
-      <c r="F437" t="n">
-        <v>79</v>
-      </c>
-      <c r="G437" t="n">
-        <v>21</v>
-      </c>
-      <c r="H437" t="n">
-        <v>35</v>
-      </c>
-      <c r="I437" t="n">
-        <v>8</v>
-      </c>
-      <c r="J437" t="n">
-        <v>31</v>
-      </c>
-      <c r="K437" t="n">
-        <v>13</v>
-      </c>
-      <c r="L437" t="n">
-        <v>14</v>
-      </c>
-      <c r="M437" t="n">
-        <v>7</v>
-      </c>
-      <c r="N437" t="n">
-        <v>24</v>
-      </c>
-      <c r="O437" t="n">
-        <v>19</v>
-      </c>
-      <c r="P437" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q437" t="n">
-        <v>14</v>
-      </c>
-      <c r="R437" t="n">
-        <v>22</v>
-      </c>
-      <c r="S437" t="n">
-        <v>21</v>
-      </c>
-      <c r="T437" t="n">
-        <v>6</v>
-      </c>
-      <c r="U437" t="inlineStr">
-        <is>
-          <t>2486507</t>
-        </is>
-      </c>
-      <c r="V437" t="n">
-        <v>80</v>
-      </c>
-      <c r="W437" t="n">
-        <v>86.16</v>
-      </c>
-      <c r="X437" t="n">
-        <v>0.9168987929433612</v>
-      </c>
-      <c r="Y437" t="n">
-        <v>79.16</v>
-      </c>
-      <c r="Z437" t="n">
-        <v>99.79787771601819</v>
-      </c>
-      <c r="AA437" t="n">
-        <v>0.9363295880149813</v>
-      </c>
-      <c r="AB437" t="n">
-        <v>101.9887812340643</v>
-      </c>
-      <c r="AC437" t="n">
-        <v>0.21875</v>
-      </c>
-      <c r="AD437" t="n">
-        <v>0.7741935483870968</v>
-      </c>
-      <c r="AE437" t="n">
-        <v>0.492063492063492</v>
-      </c>
-      <c r="AF437" t="n">
-        <v>-2.190903518046071</v>
-      </c>
-      <c r="AG437" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH437" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI437" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B438" t="n">
-        <v>28</v>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="E438" t="n">
-        <v>200</v>
-      </c>
-      <c r="F438" t="n">
-        <v>79</v>
-      </c>
-      <c r="G438" t="n">
-        <v>18</v>
-      </c>
-      <c r="H438" t="n">
-        <v>38</v>
-      </c>
-      <c r="I438" t="n">
-        <v>6</v>
-      </c>
-      <c r="J438" t="n">
-        <v>23</v>
-      </c>
-      <c r="K438" t="n">
-        <v>25</v>
-      </c>
-      <c r="L438" t="n">
-        <v>29</v>
-      </c>
-      <c r="M438" t="n">
-        <v>7</v>
-      </c>
-      <c r="N438" t="n">
-        <v>22</v>
-      </c>
-      <c r="O438" t="n">
-        <v>18</v>
-      </c>
-      <c r="P438" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q438" t="n">
-        <v>10</v>
-      </c>
-      <c r="R438" t="n">
-        <v>20</v>
-      </c>
-      <c r="S438" t="n">
-        <v>23</v>
-      </c>
-      <c r="T438" t="n">
-        <v>1</v>
-      </c>
-      <c r="U438" t="inlineStr">
-        <is>
-          <t>2486506</t>
-        </is>
-      </c>
-      <c r="V438" t="n">
-        <v>88</v>
-      </c>
-      <c r="W438" t="n">
-        <v>83.75999999999999</v>
-      </c>
-      <c r="X438" t="n">
-        <v>0.9431709646609361</v>
-      </c>
-      <c r="Y438" t="n">
-        <v>76.75999999999999</v>
-      </c>
-      <c r="Z438" t="n">
-        <v>102.9181865554977</v>
-      </c>
-      <c r="AA438" t="n">
-        <v>0.9945750452079566</v>
-      </c>
-      <c r="AB438" t="n">
-        <v>118.1525241675618</v>
-      </c>
-      <c r="AC438" t="n">
-        <v>0.2121212121212121</v>
-      </c>
-      <c r="AD438" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="AE438" t="n">
-        <v>0.4202898550724637</v>
-      </c>
-      <c r="AF438" t="n">
-        <v>-15.23433761206408</v>
-      </c>
-      <c r="AG438" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AH438" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI438" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B439" t="n">
-        <v>28</v>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="E439" t="n">
-        <v>200</v>
-      </c>
-      <c r="F439" t="n">
-        <v>84</v>
-      </c>
-      <c r="G439" t="n">
-        <v>17</v>
-      </c>
-      <c r="H439" t="n">
-        <v>35</v>
-      </c>
-      <c r="I439" t="n">
-        <v>12</v>
-      </c>
-      <c r="J439" t="n">
-        <v>26</v>
-      </c>
-      <c r="K439" t="n">
-        <v>14</v>
-      </c>
-      <c r="L439" t="n">
-        <v>17</v>
-      </c>
-      <c r="M439" t="n">
-        <v>8</v>
-      </c>
-      <c r="N439" t="n">
-        <v>17</v>
-      </c>
-      <c r="O439" t="n">
-        <v>21</v>
-      </c>
-      <c r="P439" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q439" t="n">
-        <v>12</v>
-      </c>
-      <c r="R439" t="n">
-        <v>24</v>
-      </c>
-      <c r="S439" t="n">
-        <v>18</v>
-      </c>
-      <c r="T439" t="n">
-        <v>0</v>
-      </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>2486504</t>
-        </is>
-      </c>
-      <c r="V439" t="n">
-        <v>90</v>
-      </c>
-      <c r="W439" t="n">
-        <v>80.48</v>
-      </c>
-      <c r="X439" t="n">
-        <v>1.043737574552684</v>
-      </c>
-      <c r="Y439" t="n">
-        <v>72.48</v>
-      </c>
-      <c r="Z439" t="n">
-        <v>115.8940397350993</v>
-      </c>
-      <c r="AA439" t="n">
-        <v>1.109467455621302</v>
-      </c>
-      <c r="AB439" t="n">
-        <v>123.0853391684902</v>
-      </c>
-      <c r="AC439" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="AD439" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AE439" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="AF439" t="n">
-        <v>-7.191299433390824</v>
-      </c>
-      <c r="AG439" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH439" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI439" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B440" t="n">
-        <v>28</v>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="E440" t="n">
-        <v>200</v>
-      </c>
-      <c r="F440" t="n">
-        <v>70</v>
-      </c>
-      <c r="G440" t="n">
-        <v>19</v>
-      </c>
-      <c r="H440" t="n">
-        <v>34</v>
-      </c>
-      <c r="I440" t="n">
-        <v>7</v>
-      </c>
-      <c r="J440" t="n">
-        <v>28</v>
-      </c>
-      <c r="K440" t="n">
-        <v>11</v>
-      </c>
-      <c r="L440" t="n">
-        <v>17</v>
-      </c>
-      <c r="M440" t="n">
-        <v>14</v>
-      </c>
-      <c r="N440" t="n">
-        <v>15</v>
-      </c>
-      <c r="O440" t="n">
-        <v>15</v>
-      </c>
-      <c r="P440" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q440" t="n">
-        <v>13</v>
-      </c>
-      <c r="R440" t="n">
-        <v>23</v>
-      </c>
-      <c r="S440" t="n">
-        <v>21</v>
-      </c>
-      <c r="T440" t="n">
-        <v>3</v>
-      </c>
-      <c r="U440" t="inlineStr">
-        <is>
-          <t>2486501</t>
-        </is>
-      </c>
-      <c r="V440" t="n">
-        <v>88</v>
-      </c>
-      <c r="W440" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="X440" t="n">
-        <v>0.8486905916585838</v>
-      </c>
-      <c r="Y440" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="Z440" t="n">
-        <v>102.2196261682243</v>
-      </c>
-      <c r="AA440" t="n">
-        <v>1.184068891280947</v>
-      </c>
-      <c r="AB440" t="n">
-        <v>132.6899879372738</v>
-      </c>
-      <c r="AC440" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="AD440" t="n">
-        <v>0.6521739130434783</v>
-      </c>
-      <c r="AE440" t="n">
-        <v>0.4915254237288136</v>
-      </c>
-      <c r="AF440" t="n">
-        <v>-30.47036176904953</v>
-      </c>
-      <c r="AG440" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AH440" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI440" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B441" t="n">
-        <v>28</v>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="E441" t="n">
-        <v>200</v>
-      </c>
-      <c r="F441" t="n">
-        <v>88</v>
-      </c>
-      <c r="G441" t="n">
-        <v>18</v>
-      </c>
-      <c r="H441" t="n">
-        <v>29</v>
-      </c>
-      <c r="I441" t="n">
-        <v>9</v>
-      </c>
-      <c r="J441" t="n">
-        <v>22</v>
-      </c>
-      <c r="K441" t="n">
-        <v>25</v>
-      </c>
-      <c r="L441" t="n">
-        <v>28</v>
-      </c>
-      <c r="M441" t="n">
-        <v>8</v>
-      </c>
-      <c r="N441" t="n">
-        <v>22</v>
-      </c>
-      <c r="O441" t="n">
-        <v>27</v>
-      </c>
-      <c r="P441" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>11</v>
-      </c>
-      <c r="R441" t="n">
-        <v>21</v>
-      </c>
-      <c r="S441" t="n">
-        <v>23</v>
-      </c>
-      <c r="T441" t="n">
-        <v>1</v>
-      </c>
-      <c r="U441" t="inlineStr">
-        <is>
-          <t>2486501</t>
-        </is>
-      </c>
-      <c r="V441" t="n">
-        <v>70</v>
-      </c>
-      <c r="W441" t="n">
-        <v>74.31999999999999</v>
-      </c>
-      <c r="X441" t="n">
-        <v>1.184068891280947</v>
-      </c>
-      <c r="Y441" t="n">
-        <v>66.31999999999999</v>
-      </c>
-      <c r="Z441" t="n">
-        <v>132.6899879372738</v>
-      </c>
-      <c r="AA441" t="n">
-        <v>0.8486905916585838</v>
-      </c>
-      <c r="AB441" t="n">
-        <v>102.2196261682243</v>
-      </c>
-      <c r="AC441" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="AD441" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="AE441" t="n">
-        <v>0.5084745762711864</v>
-      </c>
-      <c r="AF441" t="n">
-        <v>30.47036176904953</v>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI441" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B442" t="n">
-        <v>28</v>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E442" t="n">
-        <v>200</v>
-      </c>
-      <c r="F442" t="n">
-        <v>74</v>
-      </c>
-      <c r="G442" t="n">
-        <v>17</v>
-      </c>
-      <c r="H442" t="n">
-        <v>44</v>
-      </c>
-      <c r="I442" t="n">
-        <v>10</v>
-      </c>
-      <c r="J442" t="n">
-        <v>23</v>
-      </c>
-      <c r="K442" t="n">
-        <v>10</v>
-      </c>
-      <c r="L442" t="n">
-        <v>12</v>
-      </c>
-      <c r="M442" t="n">
-        <v>8</v>
-      </c>
-      <c r="N442" t="n">
-        <v>24</v>
-      </c>
-      <c r="O442" t="n">
-        <v>10</v>
-      </c>
-      <c r="P442" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>13</v>
-      </c>
-      <c r="R442" t="n">
-        <v>20</v>
-      </c>
-      <c r="S442" t="n">
-        <v>19</v>
-      </c>
-      <c r="T442" t="n">
-        <v>2</v>
-      </c>
-      <c r="U442" t="inlineStr">
-        <is>
-          <t>2486505</t>
-        </is>
-      </c>
-      <c r="V442" t="n">
-        <v>76</v>
-      </c>
-      <c r="W442" t="n">
-        <v>85.28</v>
-      </c>
-      <c r="X442" t="n">
-        <v>0.8677298311444652</v>
-      </c>
-      <c r="Y442" t="n">
-        <v>77.28</v>
-      </c>
-      <c r="Z442" t="n">
-        <v>95.75569358178053</v>
-      </c>
-      <c r="AA442" t="n">
-        <v>0.8558558558558559</v>
-      </c>
-      <c r="AB442" t="n">
-        <v>101.6042780748663</v>
-      </c>
-      <c r="AC442" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AD442" t="n">
-        <v>0.631578947368421</v>
-      </c>
-      <c r="AE442" t="n">
-        <v>0.4383561643835616</v>
-      </c>
-      <c r="AF442" t="n">
-        <v>-5.848584493085781</v>
-      </c>
-      <c r="AG442" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH442" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI442" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B443" t="n">
-        <v>28</v>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="E443" t="n">
-        <v>200</v>
-      </c>
-      <c r="F443" t="n">
-        <v>54</v>
-      </c>
-      <c r="G443" t="n">
-        <v>22</v>
-      </c>
-      <c r="H443" t="n">
-        <v>39</v>
-      </c>
-      <c r="I443" t="n">
-        <v>1</v>
-      </c>
-      <c r="J443" t="n">
-        <v>28</v>
-      </c>
-      <c r="K443" t="n">
-        <v>7</v>
-      </c>
-      <c r="L443" t="n">
-        <v>13</v>
-      </c>
-      <c r="M443" t="n">
-        <v>12</v>
-      </c>
-      <c r="N443" t="n">
-        <v>29</v>
-      </c>
-      <c r="O443" t="n">
-        <v>16</v>
-      </c>
-      <c r="P443" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q443" t="n">
-        <v>14</v>
-      </c>
-      <c r="R443" t="n">
-        <v>17</v>
-      </c>
-      <c r="S443" t="n">
-        <v>18</v>
-      </c>
-      <c r="T443" t="n">
-        <v>5</v>
-      </c>
-      <c r="U443" t="inlineStr">
-        <is>
-          <t>2486508</t>
-        </is>
-      </c>
-      <c r="V443" t="n">
-        <v>73</v>
-      </c>
-      <c r="W443" t="n">
-        <v>86.72</v>
-      </c>
-      <c r="X443" t="n">
-        <v>0.6226937269372694</v>
-      </c>
-      <c r="Y443" t="n">
-        <v>74.72</v>
-      </c>
-      <c r="Z443" t="n">
-        <v>72.26980728051392</v>
-      </c>
-      <c r="AA443" t="n">
-        <v>0.907960199004975</v>
-      </c>
-      <c r="AB443" t="n">
-        <v>105.1873198847262</v>
-      </c>
-      <c r="AC443" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="AD443" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="AE443" t="n">
-        <v>0.5256410256410257</v>
-      </c>
-      <c r="AF443" t="n">
-        <v>-32.91751260421231</v>
-      </c>
-      <c r="AG443" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH443" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI443" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B444" t="n">
-        <v>28</v>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="E444" t="n">
-        <v>200</v>
-      </c>
-      <c r="F444" t="n">
-        <v>88</v>
-      </c>
-      <c r="G444" t="n">
-        <v>24</v>
-      </c>
-      <c r="H444" t="n">
-        <v>48</v>
-      </c>
-      <c r="I444" t="n">
-        <v>9</v>
-      </c>
-      <c r="J444" t="n">
-        <v>26</v>
-      </c>
-      <c r="K444" t="n">
-        <v>13</v>
-      </c>
-      <c r="L444" t="n">
-        <v>17</v>
-      </c>
-      <c r="M444" t="n">
-        <v>14</v>
-      </c>
-      <c r="N444" t="n">
-        <v>26</v>
-      </c>
-      <c r="O444" t="n">
-        <v>14</v>
-      </c>
-      <c r="P444" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q444" t="n">
-        <v>7</v>
-      </c>
-      <c r="R444" t="n">
-        <v>23</v>
-      </c>
-      <c r="S444" t="n">
-        <v>20</v>
-      </c>
-      <c r="T444" t="n">
-        <v>2</v>
-      </c>
-      <c r="U444" t="inlineStr">
-        <is>
-          <t>2486506</t>
-        </is>
-      </c>
-      <c r="V444" t="n">
-        <v>79</v>
-      </c>
-      <c r="W444" t="n">
-        <v>88.48</v>
-      </c>
-      <c r="X444" t="n">
-        <v>0.9945750452079566</v>
-      </c>
-      <c r="Y444" t="n">
-        <v>74.48</v>
-      </c>
-      <c r="Z444" t="n">
-        <v>118.1525241675618</v>
-      </c>
-      <c r="AA444" t="n">
-        <v>0.9431709646609361</v>
-      </c>
-      <c r="AB444" t="n">
-        <v>102.9181865554977</v>
-      </c>
-      <c r="AC444" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="AD444" t="n">
-        <v>0.7878787878787878</v>
-      </c>
-      <c r="AE444" t="n">
-        <v>0.5797101449275363</v>
-      </c>
-      <c r="AF444" t="n">
-        <v>15.23433761206408</v>
-      </c>
-      <c r="AG444" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AH444" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI444" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B445" t="n">
-        <v>28</v>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="E445" t="n">
-        <v>200</v>
-      </c>
-      <c r="F445" t="n">
-        <v>73</v>
-      </c>
-      <c r="G445" t="n">
-        <v>13</v>
-      </c>
-      <c r="H445" t="n">
-        <v>28</v>
-      </c>
-      <c r="I445" t="n">
-        <v>13</v>
-      </c>
-      <c r="J445" t="n">
-        <v>38</v>
-      </c>
-      <c r="K445" t="n">
-        <v>8</v>
-      </c>
-      <c r="L445" t="n">
-        <v>10</v>
-      </c>
-      <c r="M445" t="n">
-        <v>11</v>
-      </c>
-      <c r="N445" t="n">
-        <v>26</v>
-      </c>
-      <c r="O445" t="n">
-        <v>18</v>
-      </c>
-      <c r="P445" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q445" t="n">
-        <v>10</v>
-      </c>
-      <c r="R445" t="n">
-        <v>18</v>
-      </c>
-      <c r="S445" t="n">
-        <v>17</v>
-      </c>
-      <c r="T445" t="n">
-        <v>1</v>
-      </c>
-      <c r="U445" t="inlineStr">
-        <is>
-          <t>2486508</t>
-        </is>
-      </c>
-      <c r="V445" t="n">
-        <v>54</v>
-      </c>
-      <c r="W445" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="X445" t="n">
-        <v>0.907960199004975</v>
-      </c>
-      <c r="Y445" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="Z445" t="n">
-        <v>105.1873198847262</v>
-      </c>
-      <c r="AA445" t="n">
-        <v>0.6226937269372694</v>
-      </c>
-      <c r="AB445" t="n">
-        <v>72.26980728051392</v>
-      </c>
-      <c r="AC445" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="AD445" t="n">
-        <v>0.6842105263157895</v>
-      </c>
-      <c r="AE445" t="n">
-        <v>0.4743589743589743</v>
-      </c>
-      <c r="AF445" t="n">
-        <v>32.91751260421231</v>
-      </c>
-      <c r="AG445" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH445" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI445" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B446" t="n">
-        <v>28</v>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="E446" t="n">
-        <v>200</v>
-      </c>
-      <c r="F446" t="n">
-        <v>81</v>
-      </c>
-      <c r="G446" t="n">
-        <v>20</v>
-      </c>
-      <c r="H446" t="n">
-        <v>30</v>
-      </c>
-      <c r="I446" t="n">
-        <v>10</v>
-      </c>
-      <c r="J446" t="n">
-        <v>34</v>
-      </c>
-      <c r="K446" t="n">
-        <v>11</v>
-      </c>
-      <c r="L446" t="n">
-        <v>19</v>
-      </c>
-      <c r="M446" t="n">
-        <v>13</v>
-      </c>
-      <c r="N446" t="n">
-        <v>26</v>
-      </c>
-      <c r="O446" t="n">
-        <v>18</v>
-      </c>
-      <c r="P446" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q446" t="n">
-        <v>10</v>
-      </c>
-      <c r="R446" t="n">
-        <v>23</v>
-      </c>
-      <c r="S446" t="n">
-        <v>21</v>
-      </c>
-      <c r="T446" t="n">
-        <v>5</v>
-      </c>
-      <c r="U446" t="inlineStr">
-        <is>
-          <t>2486503</t>
-        </is>
-      </c>
-      <c r="V446" t="n">
-        <v>53</v>
-      </c>
-      <c r="W446" t="n">
-        <v>82.36</v>
-      </c>
-      <c r="X446" t="n">
-        <v>0.9834871296745993</v>
-      </c>
-      <c r="Y446" t="n">
-        <v>69.36</v>
-      </c>
-      <c r="Z446" t="n">
-        <v>116.7820069204152</v>
-      </c>
-      <c r="AA446" t="n">
-        <v>0.6128584643848288</v>
-      </c>
-      <c r="AB446" t="n">
-        <v>69.29916317991632</v>
-      </c>
-      <c r="AC446" t="n">
-        <v>0.3939393939393939</v>
-      </c>
-      <c r="AD446" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="AE446" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="AF446" t="n">
-        <v>47.48284374049891</v>
-      </c>
-      <c r="AG446" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH446" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI446" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B447" t="n">
-        <v>28</v>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="E447" t="n">
-        <v>200</v>
-      </c>
-      <c r="F447" t="n">
-        <v>90</v>
-      </c>
-      <c r="G447" t="n">
-        <v>19</v>
-      </c>
-      <c r="H447" t="n">
-        <v>27</v>
-      </c>
-      <c r="I447" t="n">
-        <v>11</v>
-      </c>
-      <c r="J447" t="n">
-        <v>32</v>
-      </c>
-      <c r="K447" t="n">
-        <v>19</v>
-      </c>
-      <c r="L447" t="n">
-        <v>23</v>
-      </c>
-      <c r="M447" t="n">
-        <v>8</v>
-      </c>
-      <c r="N447" t="n">
-        <v>22</v>
-      </c>
-      <c r="O447" t="n">
-        <v>16</v>
-      </c>
-      <c r="P447" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q447" t="n">
-        <v>12</v>
-      </c>
-      <c r="R447" t="n">
-        <v>18</v>
-      </c>
-      <c r="S447" t="n">
-        <v>24</v>
-      </c>
-      <c r="T447" t="n">
-        <v>1</v>
-      </c>
-      <c r="U447" t="inlineStr">
-        <is>
-          <t>2486504</t>
-        </is>
-      </c>
-      <c r="V447" t="n">
-        <v>84</v>
-      </c>
-      <c r="W447" t="n">
-        <v>81.12</v>
-      </c>
-      <c r="X447" t="n">
-        <v>1.109467455621302</v>
-      </c>
-      <c r="Y447" t="n">
-        <v>73.12</v>
-      </c>
-      <c r="Z447" t="n">
-        <v>123.0853391684902</v>
-      </c>
-      <c r="AA447" t="n">
-        <v>1.043737574552684</v>
-      </c>
-      <c r="AB447" t="n">
-        <v>115.8940397350993</v>
-      </c>
-      <c r="AC447" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AD447" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="AE447" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="AF447" t="n">
-        <v>7.191299433390824</v>
-      </c>
-      <c r="AG447" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH447" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI447" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B448" t="n">
-        <v>28</v>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E448" t="n">
-        <v>200</v>
-      </c>
-      <c r="F448" t="n">
-        <v>72</v>
-      </c>
-      <c r="G448" t="n">
-        <v>16</v>
-      </c>
-      <c r="H448" t="n">
-        <v>33</v>
-      </c>
-      <c r="I448" t="n">
-        <v>6</v>
-      </c>
-      <c r="J448" t="n">
-        <v>24</v>
-      </c>
-      <c r="K448" t="n">
-        <v>22</v>
-      </c>
-      <c r="L448" t="n">
-        <v>31</v>
-      </c>
-      <c r="M448" t="n">
-        <v>8</v>
-      </c>
-      <c r="N448" t="n">
-        <v>34</v>
-      </c>
-      <c r="O448" t="n">
-        <v>15</v>
-      </c>
-      <c r="P448" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q448" t="n">
-        <v>11</v>
-      </c>
-      <c r="R448" t="n">
-        <v>24</v>
-      </c>
-      <c r="S448" t="n">
-        <v>25</v>
-      </c>
-      <c r="T448" t="n">
-        <v>7</v>
-      </c>
-      <c r="U448" t="inlineStr">
-        <is>
-          <t>2486502</t>
-        </is>
-      </c>
-      <c r="V448" t="n">
-        <v>56</v>
-      </c>
-      <c r="W448" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="X448" t="n">
-        <v>0.8819206271435571</v>
-      </c>
-      <c r="Y448" t="n">
-        <v>73.64</v>
-      </c>
-      <c r="Z448" t="n">
-        <v>97.77294948397611</v>
-      </c>
-      <c r="AA448" t="n">
-        <v>0.6445672191528545</v>
-      </c>
-      <c r="AB448" t="n">
-        <v>77.90762381747358</v>
-      </c>
-      <c r="AC448" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="AD448" t="n">
-        <v>0.6938775510204082</v>
-      </c>
-      <c r="AE448" t="n">
-        <v>0.5060240963855421</v>
-      </c>
-      <c r="AF448" t="n">
-        <v>19.86532566650253</v>
-      </c>
-      <c r="AG448" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH448" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI448" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B449" t="n">
-        <v>28</v>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="E449" t="n">
-        <v>200</v>
-      </c>
-      <c r="F449" t="n">
-        <v>53</v>
-      </c>
-      <c r="G449" t="n">
-        <v>15</v>
-      </c>
-      <c r="H449" t="n">
-        <v>41</v>
-      </c>
-      <c r="I449" t="n">
-        <v>4</v>
-      </c>
-      <c r="J449" t="n">
-        <v>23</v>
-      </c>
-      <c r="K449" t="n">
-        <v>11</v>
-      </c>
-      <c r="L449" t="n">
-        <v>17</v>
-      </c>
-      <c r="M449" t="n">
-        <v>10</v>
-      </c>
-      <c r="N449" t="n">
-        <v>20</v>
-      </c>
-      <c r="O449" t="n">
-        <v>8</v>
-      </c>
-      <c r="P449" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q449" t="n">
-        <v>15</v>
-      </c>
-      <c r="R449" t="n">
-        <v>21</v>
-      </c>
-      <c r="S449" t="n">
-        <v>23</v>
-      </c>
-      <c r="T449" t="n">
-        <v>1</v>
-      </c>
-      <c r="U449" t="inlineStr">
-        <is>
-          <t>2486503</t>
-        </is>
-      </c>
-      <c r="V449" t="n">
-        <v>81</v>
-      </c>
-      <c r="W449" t="n">
-        <v>86.48</v>
-      </c>
-      <c r="X449" t="n">
-        <v>0.6128584643848288</v>
-      </c>
-      <c r="Y449" t="n">
-        <v>76.48</v>
-      </c>
-      <c r="Z449" t="n">
-        <v>69.29916317991632</v>
-      </c>
-      <c r="AA449" t="n">
-        <v>0.9834871296745993</v>
-      </c>
-      <c r="AB449" t="n">
-        <v>116.7820069204152</v>
-      </c>
-      <c r="AC449" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="AD449" t="n">
-        <v>0.6060606060606061</v>
-      </c>
-      <c r="AE449" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="AF449" t="n">
-        <v>-47.48284374049891</v>
-      </c>
-      <c r="AG449" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH449" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI449" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B450" t="n">
-        <v>29</v>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="E450" t="n">
-        <v>200</v>
-      </c>
-      <c r="F450" t="n">
-        <v>65</v>
-      </c>
-      <c r="G450" t="n">
-        <v>12</v>
-      </c>
-      <c r="H450" t="n">
-        <v>25</v>
-      </c>
-      <c r="I450" t="n">
-        <v>11</v>
-      </c>
-      <c r="J450" t="n">
-        <v>32</v>
-      </c>
-      <c r="K450" t="n">
-        <v>8</v>
-      </c>
-      <c r="L450" t="n">
-        <v>12</v>
-      </c>
-      <c r="M450" t="n">
-        <v>10</v>
-      </c>
-      <c r="N450" t="n">
-        <v>22</v>
-      </c>
-      <c r="O450" t="n">
-        <v>11</v>
-      </c>
-      <c r="P450" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q450" t="n">
-        <v>17</v>
-      </c>
-      <c r="R450" t="n">
-        <v>22</v>
-      </c>
-      <c r="S450" t="n">
-        <v>18</v>
-      </c>
-      <c r="T450" t="n">
-        <v>2</v>
-      </c>
-      <c r="U450" t="inlineStr">
-        <is>
-          <t>2486516</t>
-        </is>
-      </c>
-      <c r="V450" t="n">
-        <v>73</v>
-      </c>
-      <c r="W450" t="n">
-        <v>79.28</v>
-      </c>
-      <c r="X450" t="n">
-        <v>0.8198789101917255</v>
-      </c>
-      <c r="Y450" t="n">
-        <v>69.28</v>
-      </c>
-      <c r="Z450" t="n">
-        <v>93.82217090069284</v>
-      </c>
-      <c r="AA450" t="n">
-        <v>0.9292260692464358</v>
-      </c>
-      <c r="AB450" t="n">
-        <v>100.606394707828</v>
-      </c>
-      <c r="AC450" t="n">
-        <v>0.303030303030303</v>
-      </c>
-      <c r="AD450" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AE450" t="n">
-        <v>0.5245901639344263</v>
-      </c>
-      <c r="AF450" t="n">
-        <v>-6.784223807135163</v>
-      </c>
-      <c r="AG450" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH450" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI450" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B451" t="n">
-        <v>29</v>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>200</v>
-      </c>
-      <c r="F451" t="n">
-        <v>81</v>
-      </c>
-      <c r="G451" t="n">
-        <v>15</v>
-      </c>
-      <c r="H451" t="n">
-        <v>32</v>
-      </c>
-      <c r="I451" t="n">
-        <v>8</v>
-      </c>
-      <c r="J451" t="n">
-        <v>31</v>
-      </c>
-      <c r="K451" t="n">
-        <v>27</v>
-      </c>
-      <c r="L451" t="n">
-        <v>30</v>
-      </c>
-      <c r="M451" t="n">
-        <v>14</v>
-      </c>
-      <c r="N451" t="n">
-        <v>15</v>
-      </c>
-      <c r="O451" t="n">
-        <v>19</v>
-      </c>
-      <c r="P451" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q451" t="n">
-        <v>12</v>
-      </c>
-      <c r="R451" t="n">
-        <v>19</v>
-      </c>
-      <c r="S451" t="n">
-        <v>22</v>
-      </c>
-      <c r="T451" t="n">
-        <v>3</v>
-      </c>
-      <c r="U451" t="inlineStr">
-        <is>
-          <t>2486518</t>
-        </is>
-      </c>
-      <c r="V451" t="n">
-        <v>79</v>
-      </c>
-      <c r="W451" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="X451" t="n">
-        <v>0.9183673469387755</v>
-      </c>
-      <c r="Y451" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="Z451" t="n">
-        <v>109.1644204851752</v>
-      </c>
-      <c r="AA451" t="n">
-        <v>0.9748272458045411</v>
-      </c>
-      <c r="AB451" t="n">
-        <v>108.1599123767799</v>
-      </c>
-      <c r="AC451" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="AD451" t="n">
-        <v>0.6521739130434783</v>
-      </c>
-      <c r="AE451" t="n">
-        <v>0.5087719298245614</v>
-      </c>
-      <c r="AF451" t="n">
-        <v>1.004508108395342</v>
-      </c>
-      <c r="AG451" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AH451" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI451" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B452" t="n">
-        <v>29</v>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="E452" t="n">
-        <v>200</v>
-      </c>
-      <c r="F452" t="n">
-        <v>67</v>
-      </c>
-      <c r="G452" t="n">
-        <v>17</v>
-      </c>
-      <c r="H452" t="n">
-        <v>41</v>
-      </c>
-      <c r="I452" t="n">
-        <v>7</v>
-      </c>
-      <c r="J452" t="n">
-        <v>27</v>
-      </c>
-      <c r="K452" t="n">
-        <v>12</v>
-      </c>
-      <c r="L452" t="n">
-        <v>20</v>
-      </c>
-      <c r="M452" t="n">
-        <v>19</v>
-      </c>
-      <c r="N452" t="n">
-        <v>21</v>
-      </c>
-      <c r="O452" t="n">
-        <v>13</v>
-      </c>
-      <c r="P452" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q452" t="n">
-        <v>13</v>
-      </c>
-      <c r="R452" t="n">
-        <v>27</v>
-      </c>
-      <c r="S452" t="n">
-        <v>19</v>
-      </c>
-      <c r="T452" t="n">
-        <v>1</v>
-      </c>
-      <c r="U452" t="inlineStr">
-        <is>
-          <t>2486515</t>
-        </is>
-      </c>
-      <c r="V452" t="n">
-        <v>72</v>
-      </c>
-      <c r="W452" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X452" t="n">
-        <v>0.7461024498886415</v>
-      </c>
-      <c r="Y452" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="Z452" t="n">
-        <v>94.63276836158192</v>
-      </c>
-      <c r="AA452" t="n">
-        <v>0.9370119729307652</v>
-      </c>
-      <c r="AB452" t="n">
-        <v>104.5903544450901</v>
-      </c>
-      <c r="AC452" t="n">
-        <v>0.4318181818181818</v>
-      </c>
-      <c r="AD452" t="n">
-        <v>0.7241379310344828</v>
-      </c>
-      <c r="AE452" t="n">
-        <v>0.547945205479452</v>
-      </c>
-      <c r="AF452" t="n">
-        <v>-9.957586083508133</v>
-      </c>
-      <c r="AG452" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AH452" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI452" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B453" t="n">
-        <v>29</v>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="E453" t="n">
-        <v>200</v>
-      </c>
-      <c r="F453" t="n">
-        <v>79</v>
-      </c>
-      <c r="G453" t="n">
-        <v>16</v>
-      </c>
-      <c r="H453" t="n">
-        <v>26</v>
-      </c>
-      <c r="I453" t="n">
-        <v>12</v>
-      </c>
-      <c r="J453" t="n">
-        <v>32</v>
-      </c>
-      <c r="K453" t="n">
-        <v>11</v>
-      </c>
-      <c r="L453" t="n">
-        <v>16</v>
-      </c>
-      <c r="M453" t="n">
-        <v>8</v>
-      </c>
-      <c r="N453" t="n">
-        <v>20</v>
-      </c>
-      <c r="O453" t="n">
-        <v>22</v>
-      </c>
-      <c r="P453" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q453" t="n">
-        <v>16</v>
-      </c>
-      <c r="R453" t="n">
-        <v>22</v>
-      </c>
-      <c r="S453" t="n">
-        <v>19</v>
-      </c>
-      <c r="T453" t="n">
-        <v>1</v>
-      </c>
-      <c r="U453" t="inlineStr">
-        <is>
-          <t>2486518</t>
-        </is>
-      </c>
-      <c r="V453" t="n">
-        <v>81</v>
-      </c>
-      <c r="W453" t="n">
-        <v>81.03999999999999</v>
-      </c>
-      <c r="X453" t="n">
-        <v>0.9748272458045411</v>
-      </c>
-      <c r="Y453" t="n">
-        <v>73.03999999999999</v>
-      </c>
-      <c r="Z453" t="n">
-        <v>108.1599123767799</v>
-      </c>
-      <c r="AA453" t="n">
-        <v>0.9183673469387755</v>
-      </c>
-      <c r="AB453" t="n">
-        <v>109.1644204851752</v>
-      </c>
-      <c r="AC453" t="n">
-        <v>0.3478260869565217</v>
-      </c>
-      <c r="AD453" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="AE453" t="n">
-        <v>0.4912280701754386</v>
-      </c>
-      <c r="AF453" t="n">
-        <v>-1.004508108395342</v>
-      </c>
-      <c r="AG453" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AH453" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI453" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B454" t="n">
-        <v>29</v>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E454" t="n">
-        <v>200</v>
-      </c>
-      <c r="F454" t="n">
-        <v>73</v>
-      </c>
-      <c r="G454" t="n">
-        <v>21</v>
-      </c>
-      <c r="H454" t="n">
-        <v>38</v>
-      </c>
-      <c r="I454" t="n">
-        <v>4</v>
-      </c>
-      <c r="J454" t="n">
-        <v>17</v>
-      </c>
-      <c r="K454" t="n">
-        <v>19</v>
-      </c>
-      <c r="L454" t="n">
-        <v>24</v>
-      </c>
-      <c r="M454" t="n">
-        <v>6</v>
-      </c>
-      <c r="N454" t="n">
-        <v>23</v>
-      </c>
-      <c r="O454" t="n">
-        <v>14</v>
-      </c>
-      <c r="P454" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q454" t="n">
-        <v>13</v>
-      </c>
-      <c r="R454" t="n">
-        <v>19</v>
-      </c>
-      <c r="S454" t="n">
-        <v>22</v>
-      </c>
-      <c r="T454" t="n">
-        <v>4</v>
-      </c>
-      <c r="U454" t="inlineStr">
-        <is>
-          <t>2486516</t>
-        </is>
-      </c>
-      <c r="V454" t="n">
-        <v>65</v>
-      </c>
-      <c r="W454" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="X454" t="n">
-        <v>0.9292260692464358</v>
-      </c>
-      <c r="Y454" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="Z454" t="n">
-        <v>100.606394707828</v>
-      </c>
-      <c r="AA454" t="n">
-        <v>0.8198789101917255</v>
-      </c>
-      <c r="AB454" t="n">
-        <v>93.82217090069284</v>
-      </c>
-      <c r="AC454" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="AD454" t="n">
-        <v>0.696969696969697</v>
-      </c>
-      <c r="AE454" t="n">
-        <v>0.4754098360655737</v>
-      </c>
-      <c r="AF454" t="n">
-        <v>6.784223807135163</v>
-      </c>
-      <c r="AG454" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH454" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI454" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B455" t="n">
-        <v>29</v>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E455" t="n">
-        <v>200</v>
-      </c>
-      <c r="F455" t="n">
-        <v>72</v>
-      </c>
-      <c r="G455" t="n">
-        <v>10</v>
-      </c>
-      <c r="H455" t="n">
-        <v>24</v>
-      </c>
-      <c r="I455" t="n">
-        <v>7</v>
-      </c>
-      <c r="J455" t="n">
-        <v>24</v>
-      </c>
-      <c r="K455" t="n">
-        <v>31</v>
-      </c>
-      <c r="L455" t="n">
-        <v>36</v>
-      </c>
-      <c r="M455" t="n">
-        <v>8</v>
-      </c>
-      <c r="N455" t="n">
-        <v>25</v>
-      </c>
-      <c r="O455" t="n">
-        <v>16</v>
-      </c>
-      <c r="P455" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q455" t="n">
-        <v>13</v>
-      </c>
-      <c r="R455" t="n">
-        <v>19</v>
-      </c>
-      <c r="S455" t="n">
-        <v>27</v>
-      </c>
-      <c r="T455" t="n">
-        <v>0</v>
-      </c>
-      <c r="U455" t="inlineStr">
-        <is>
-          <t>2486515</t>
-        </is>
-      </c>
-      <c r="V455" t="n">
-        <v>67</v>
-      </c>
-      <c r="W455" t="n">
-        <v>76.84</v>
-      </c>
-      <c r="X455" t="n">
-        <v>0.9370119729307652</v>
-      </c>
-      <c r="Y455" t="n">
-        <v>68.84</v>
-      </c>
-      <c r="Z455" t="n">
-        <v>104.5903544450901</v>
-      </c>
-      <c r="AA455" t="n">
-        <v>0.7461024498886415</v>
-      </c>
-      <c r="AB455" t="n">
-        <v>94.63276836158192</v>
-      </c>
-      <c r="AC455" t="n">
-        <v>0.2758620689655172</v>
-      </c>
-      <c r="AD455" t="n">
-        <v>0.5681818181818182</v>
-      </c>
-      <c r="AE455" t="n">
-        <v>0.4520547945205479</v>
-      </c>
-      <c r="AF455" t="n">
-        <v>9.957586083508133</v>
-      </c>
-      <c r="AG455" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AH455" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI455" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B456" t="n">
-        <v>29</v>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="E456" t="n">
-        <v>200</v>
-      </c>
-      <c r="F456" t="n">
-        <v>79</v>
-      </c>
-      <c r="G456" t="n">
-        <v>20</v>
-      </c>
-      <c r="H456" t="n">
-        <v>34</v>
-      </c>
-      <c r="I456" t="n">
-        <v>9</v>
-      </c>
-      <c r="J456" t="n">
-        <v>25</v>
-      </c>
-      <c r="K456" t="n">
-        <v>12</v>
-      </c>
-      <c r="L456" t="n">
-        <v>21</v>
-      </c>
-      <c r="M456" t="n">
-        <v>10</v>
-      </c>
-      <c r="N456" t="n">
-        <v>16</v>
-      </c>
-      <c r="O456" t="n">
-        <v>18</v>
-      </c>
-      <c r="P456" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q456" t="n">
-        <v>11</v>
-      </c>
-      <c r="R456" t="n">
-        <v>19</v>
-      </c>
-      <c r="S456" t="n">
-        <v>21</v>
-      </c>
-      <c r="T456" t="n">
-        <v>1</v>
-      </c>
-      <c r="U456" t="inlineStr">
-        <is>
-          <t>2486514</t>
-        </is>
-      </c>
-      <c r="V456" t="n">
-        <v>83</v>
-      </c>
-      <c r="W456" t="n">
-        <v>79.24000000000001</v>
-      </c>
-      <c r="X456" t="n">
-        <v>0.9969712266532054</v>
-      </c>
-      <c r="Y456" t="n">
-        <v>69.24000000000001</v>
-      </c>
-      <c r="Z456" t="n">
-        <v>114.0958983246678</v>
-      </c>
-      <c r="AA456" t="n">
-        <v>1.014669926650367</v>
-      </c>
-      <c r="AB456" t="n">
-        <v>117.2316384180791</v>
-      </c>
-      <c r="AC456" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD456" t="n">
-        <v>0.5925925925925926</v>
-      </c>
-      <c r="AE456" t="n">
-        <v>0.456140350877193</v>
-      </c>
-      <c r="AF456" t="n">
-        <v>-3.1357400934113</v>
-      </c>
-      <c r="AG456" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AH456" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AI456" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B457" t="n">
-        <v>29</v>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="E457" t="n">
-        <v>200</v>
-      </c>
-      <c r="F457" t="n">
-        <v>76</v>
-      </c>
-      <c r="G457" t="n">
-        <v>13</v>
-      </c>
-      <c r="H457" t="n">
-        <v>30</v>
-      </c>
-      <c r="I457" t="n">
-        <v>9</v>
-      </c>
-      <c r="J457" t="n">
-        <v>35</v>
-      </c>
-      <c r="K457" t="n">
-        <v>23</v>
-      </c>
-      <c r="L457" t="n">
-        <v>26</v>
-      </c>
-      <c r="M457" t="n">
-        <v>13</v>
-      </c>
-      <c r="N457" t="n">
-        <v>12</v>
-      </c>
-      <c r="O457" t="n">
-        <v>12</v>
-      </c>
-      <c r="P457" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q457" t="n">
-        <v>12</v>
-      </c>
-      <c r="R457" t="n">
-        <v>22</v>
-      </c>
-      <c r="S457" t="n">
-        <v>23</v>
-      </c>
-      <c r="T457" t="n">
-        <v>1</v>
-      </c>
-      <c r="U457" t="inlineStr">
-        <is>
-          <t>2486512</t>
-        </is>
-      </c>
-      <c r="V457" t="n">
-        <v>96</v>
-      </c>
-      <c r="W457" t="n">
-        <v>88.44</v>
-      </c>
-      <c r="X457" t="n">
-        <v>0.8593396653098145</v>
-      </c>
-      <c r="Y457" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="Z457" t="n">
-        <v>100.7423117709438</v>
-      </c>
-      <c r="AA457" t="n">
-        <v>1.170731707317073</v>
-      </c>
-      <c r="AB457" t="n">
-        <v>126.3157894736842</v>
-      </c>
-      <c r="AC457" t="n">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="AD457" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE457" t="n">
-        <v>0.462962962962963</v>
-      </c>
-      <c r="AF457" t="n">
-        <v>-25.5734777027404</v>
-      </c>
-      <c r="AG457" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AH457" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AI457" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B458" t="n">
-        <v>29</v>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="E458" t="n">
-        <v>200</v>
-      </c>
-      <c r="F458" t="n">
-        <v>83</v>
-      </c>
-      <c r="G458" t="n">
-        <v>19</v>
-      </c>
-      <c r="H458" t="n">
-        <v>32</v>
-      </c>
-      <c r="I458" t="n">
-        <v>9</v>
-      </c>
-      <c r="J458" t="n">
-        <v>31</v>
-      </c>
-      <c r="K458" t="n">
-        <v>18</v>
-      </c>
-      <c r="L458" t="n">
-        <v>20</v>
-      </c>
-      <c r="M458" t="n">
-        <v>11</v>
-      </c>
-      <c r="N458" t="n">
-        <v>20</v>
-      </c>
-      <c r="O458" t="n">
-        <v>19</v>
-      </c>
-      <c r="P458" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q458" t="n">
-        <v>10</v>
-      </c>
-      <c r="R458" t="n">
-        <v>21</v>
-      </c>
-      <c r="S458" t="n">
-        <v>19</v>
-      </c>
-      <c r="T458" t="n">
-        <v>3</v>
-      </c>
-      <c r="U458" t="inlineStr">
-        <is>
-          <t>2486514</t>
-        </is>
-      </c>
-      <c r="V458" t="n">
-        <v>79</v>
-      </c>
-      <c r="W458" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="X458" t="n">
-        <v>1.014669926650367</v>
-      </c>
-      <c r="Y458" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="Z458" t="n">
-        <v>117.2316384180791</v>
-      </c>
-      <c r="AA458" t="n">
-        <v>0.9969712266532054</v>
-      </c>
-      <c r="AB458" t="n">
-        <v>114.0958983246678</v>
-      </c>
-      <c r="AC458" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="AD458" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE458" t="n">
-        <v>0.543859649122807</v>
-      </c>
-      <c r="AF458" t="n">
-        <v>3.1357400934113</v>
-      </c>
-      <c r="AG458" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AH458" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AI458" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B459" t="n">
-        <v>29</v>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="E459" t="n">
-        <v>200</v>
-      </c>
-      <c r="F459" t="n">
-        <v>74</v>
-      </c>
-      <c r="G459" t="n">
-        <v>15</v>
-      </c>
-      <c r="H459" t="n">
-        <v>42</v>
-      </c>
-      <c r="I459" t="n">
-        <v>10</v>
-      </c>
-      <c r="J459" t="n">
-        <v>35</v>
-      </c>
-      <c r="K459" t="n">
-        <v>14</v>
-      </c>
-      <c r="L459" t="n">
-        <v>19</v>
-      </c>
-      <c r="M459" t="n">
-        <v>11</v>
-      </c>
-      <c r="N459" t="n">
-        <v>17</v>
-      </c>
-      <c r="O459" t="n">
-        <v>13</v>
-      </c>
-      <c r="P459" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q459" t="n">
-        <v>7</v>
-      </c>
-      <c r="R459" t="n">
-        <v>18</v>
-      </c>
-      <c r="S459" t="n">
-        <v>21</v>
-      </c>
-      <c r="T459" t="n">
-        <v>0</v>
-      </c>
-      <c r="U459" t="inlineStr">
-        <is>
-          <t>2486510</t>
-        </is>
-      </c>
-      <c r="V459" t="n">
-        <v>87</v>
-      </c>
-      <c r="W459" t="n">
-        <v>92.36</v>
-      </c>
-      <c r="X459" t="n">
-        <v>0.8012126461671719</v>
-      </c>
-      <c r="Y459" t="n">
-        <v>81.36</v>
-      </c>
-      <c r="Z459" t="n">
-        <v>90.95378564405114</v>
-      </c>
-      <c r="AA459" t="n">
-        <v>1.028368794326241</v>
-      </c>
-      <c r="AB459" t="n">
-        <v>115.0793650793651</v>
-      </c>
-      <c r="AC459" t="n">
-        <v>0.2244897959183673</v>
-      </c>
-      <c r="AD459" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="AE459" t="n">
-        <v>0.3733333333333334</v>
-      </c>
-      <c r="AF459" t="n">
-        <v>-24.12557943531395</v>
-      </c>
-      <c r="AG459" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH459" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AI459" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B460" t="n">
-        <v>29</v>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="E460" t="n">
-        <v>200</v>
-      </c>
-      <c r="F460" t="n">
-        <v>87</v>
-      </c>
-      <c r="G460" t="n">
-        <v>25</v>
-      </c>
-      <c r="H460" t="n">
-        <v>34</v>
-      </c>
-      <c r="I460" t="n">
-        <v>8</v>
-      </c>
-      <c r="J460" t="n">
-        <v>28</v>
-      </c>
-      <c r="K460" t="n">
-        <v>13</v>
-      </c>
-      <c r="L460" t="n">
-        <v>15</v>
-      </c>
-      <c r="M460" t="n">
-        <v>9</v>
-      </c>
-      <c r="N460" t="n">
-        <v>38</v>
-      </c>
-      <c r="O460" t="n">
-        <v>17</v>
-      </c>
-      <c r="P460" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q460" t="n">
-        <v>16</v>
-      </c>
-      <c r="R460" t="n">
-        <v>21</v>
-      </c>
-      <c r="S460" t="n">
-        <v>18</v>
-      </c>
-      <c r="T460" t="n">
-        <v>3</v>
-      </c>
-      <c r="U460" t="inlineStr">
-        <is>
-          <t>2486510</t>
-        </is>
-      </c>
-      <c r="V460" t="n">
-        <v>74</v>
-      </c>
-      <c r="W460" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="X460" t="n">
-        <v>1.028368794326241</v>
-      </c>
-      <c r="Y460" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="Z460" t="n">
-        <v>115.0793650793651</v>
-      </c>
-      <c r="AA460" t="n">
-        <v>0.8012126461671719</v>
-      </c>
-      <c r="AB460" t="n">
-        <v>90.95378564405114</v>
-      </c>
-      <c r="AC460" t="n">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="AD460" t="n">
-        <v>0.7755102040816326</v>
-      </c>
-      <c r="AE460" t="n">
-        <v>0.6266666666666667</v>
-      </c>
-      <c r="AF460" t="n">
-        <v>24.12557943531395</v>
-      </c>
-      <c r="AG460" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH460" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AI460" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B461" t="n">
-        <v>29</v>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="E461" t="n">
-        <v>200</v>
-      </c>
-      <c r="F461" t="n">
-        <v>84</v>
-      </c>
-      <c r="G461" t="n">
-        <v>14</v>
-      </c>
-      <c r="H461" t="n">
-        <v>25</v>
-      </c>
-      <c r="I461" t="n">
-        <v>11</v>
-      </c>
-      <c r="J461" t="n">
-        <v>33</v>
-      </c>
-      <c r="K461" t="n">
-        <v>23</v>
-      </c>
-      <c r="L461" t="n">
-        <v>28</v>
-      </c>
-      <c r="M461" t="n">
-        <v>11</v>
-      </c>
-      <c r="N461" t="n">
-        <v>16</v>
-      </c>
-      <c r="O461" t="n">
-        <v>12</v>
-      </c>
-      <c r="P461" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q461" t="n">
-        <v>13</v>
-      </c>
-      <c r="R461" t="n">
-        <v>29</v>
-      </c>
-      <c r="S461" t="n">
-        <v>24</v>
-      </c>
-      <c r="T461" t="n">
-        <v>0</v>
-      </c>
-      <c r="U461" t="inlineStr">
-        <is>
-          <t>2486513</t>
-        </is>
-      </c>
-      <c r="V461" t="n">
-        <v>92</v>
-      </c>
-      <c r="W461" t="n">
-        <v>83.31999999999999</v>
-      </c>
-      <c r="X461" t="n">
-        <v>1.00816130580893</v>
-      </c>
-      <c r="Y461" t="n">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="Z461" t="n">
-        <v>116.1504424778761</v>
-      </c>
-      <c r="AA461" t="n">
-        <v>1.147704590818363</v>
-      </c>
-      <c r="AB461" t="n">
-        <v>127.4944567627495</v>
-      </c>
-      <c r="AC461" t="n">
-        <v>0.3793103448275862</v>
-      </c>
-      <c r="AD461" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE461" t="n">
-        <v>0.5094339622641509</v>
-      </c>
-      <c r="AF461" t="n">
-        <v>-11.34401428487334</v>
-      </c>
-      <c r="AG461" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AH461" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI461" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B462" t="n">
-        <v>29</v>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="E462" t="n">
-        <v>200</v>
-      </c>
-      <c r="F462" t="n">
-        <v>82</v>
-      </c>
-      <c r="G462" t="n">
-        <v>12</v>
-      </c>
-      <c r="H462" t="n">
-        <v>27</v>
-      </c>
-      <c r="I462" t="n">
-        <v>14</v>
-      </c>
-      <c r="J462" t="n">
-        <v>37</v>
-      </c>
-      <c r="K462" t="n">
-        <v>16</v>
-      </c>
-      <c r="L462" t="n">
-        <v>19</v>
-      </c>
-      <c r="M462" t="n">
-        <v>9</v>
-      </c>
-      <c r="N462" t="n">
-        <v>30</v>
-      </c>
-      <c r="O462" t="n">
-        <v>21</v>
-      </c>
-      <c r="P462" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q462" t="n">
-        <v>14</v>
-      </c>
-      <c r="R462" t="n">
-        <v>18</v>
-      </c>
-      <c r="S462" t="n">
-        <v>19</v>
-      </c>
-      <c r="T462" t="n">
-        <v>1</v>
-      </c>
-      <c r="U462" t="inlineStr">
-        <is>
-          <t>2486511</t>
-        </is>
-      </c>
-      <c r="V462" t="n">
-        <v>75</v>
-      </c>
-      <c r="W462" t="n">
-        <v>86.36</v>
-      </c>
-      <c r="X462" t="n">
-        <v>0.9495136637332098</v>
-      </c>
-      <c r="Y462" t="n">
-        <v>77.36</v>
-      </c>
-      <c r="Z462" t="n">
-        <v>105.9979317476732</v>
-      </c>
-      <c r="AA462" t="n">
-        <v>0.8628624022089277</v>
-      </c>
-      <c r="AB462" t="n">
-        <v>96.25256673511294</v>
-      </c>
-      <c r="AC462" t="n">
-        <v>0.2368421052631579</v>
-      </c>
-      <c r="AD462" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="AE462" t="n">
-        <v>0.5064935064935064</v>
-      </c>
-      <c r="AF462" t="n">
-        <v>9.745365012560285</v>
-      </c>
-      <c r="AG462" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AH462" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI462" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B463" t="n">
-        <v>29</v>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="E463" t="n">
-        <v>200</v>
-      </c>
-      <c r="F463" t="n">
-        <v>92</v>
-      </c>
-      <c r="G463" t="n">
-        <v>18</v>
-      </c>
-      <c r="H463" t="n">
-        <v>26</v>
-      </c>
-      <c r="I463" t="n">
-        <v>10</v>
-      </c>
-      <c r="J463" t="n">
-        <v>26</v>
-      </c>
-      <c r="K463" t="n">
-        <v>26</v>
-      </c>
-      <c r="L463" t="n">
-        <v>39</v>
-      </c>
-      <c r="M463" t="n">
-        <v>8</v>
-      </c>
-      <c r="N463" t="n">
-        <v>18</v>
-      </c>
-      <c r="O463" t="n">
-        <v>15</v>
-      </c>
-      <c r="P463" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q463" t="n">
-        <v>11</v>
-      </c>
-      <c r="R463" t="n">
-        <v>24</v>
-      </c>
-      <c r="S463" t="n">
-        <v>29</v>
-      </c>
-      <c r="T463" t="n">
-        <v>1</v>
-      </c>
-      <c r="U463" t="inlineStr">
-        <is>
-          <t>2486513</t>
-        </is>
-      </c>
-      <c r="V463" t="n">
-        <v>84</v>
-      </c>
-      <c r="W463" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="X463" t="n">
-        <v>1.147704590818363</v>
-      </c>
-      <c r="Y463" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="Z463" t="n">
-        <v>127.4944567627495</v>
-      </c>
-      <c r="AA463" t="n">
-        <v>1.00816130580893</v>
-      </c>
-      <c r="AB463" t="n">
-        <v>116.1504424778761</v>
-      </c>
-      <c r="AC463" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD463" t="n">
-        <v>0.6206896551724138</v>
-      </c>
-      <c r="AE463" t="n">
-        <v>0.4905660377358491</v>
-      </c>
-      <c r="AF463" t="n">
-        <v>11.34401428487334</v>
-      </c>
-      <c r="AG463" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AH463" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI463" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B464" t="n">
-        <v>29</v>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="E464" t="n">
-        <v>200</v>
-      </c>
-      <c r="F464" t="n">
-        <v>96</v>
-      </c>
-      <c r="G464" t="n">
-        <v>17</v>
-      </c>
-      <c r="H464" t="n">
-        <v>24</v>
-      </c>
-      <c r="I464" t="n">
-        <v>14</v>
-      </c>
-      <c r="J464" t="n">
-        <v>28</v>
-      </c>
-      <c r="K464" t="n">
-        <v>20</v>
-      </c>
-      <c r="L464" t="n">
-        <v>25</v>
-      </c>
-      <c r="M464" t="n">
-        <v>6</v>
-      </c>
-      <c r="N464" t="n">
-        <v>23</v>
-      </c>
-      <c r="O464" t="n">
-        <v>13</v>
-      </c>
-      <c r="P464" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q464" t="n">
-        <v>19</v>
-      </c>
-      <c r="R464" t="n">
-        <v>23</v>
-      </c>
-      <c r="S464" t="n">
-        <v>22</v>
-      </c>
-      <c r="T464" t="n">
-        <v>2</v>
-      </c>
-      <c r="U464" t="inlineStr">
-        <is>
-          <t>2486512</t>
-        </is>
-      </c>
-      <c r="V464" t="n">
-        <v>76</v>
-      </c>
-      <c r="W464" t="n">
-        <v>82</v>
-      </c>
-      <c r="X464" t="n">
-        <v>1.170731707317073</v>
-      </c>
-      <c r="Y464" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z464" t="n">
-        <v>126.3157894736842</v>
-      </c>
-      <c r="AA464" t="n">
-        <v>0.8593396653098145</v>
-      </c>
-      <c r="AB464" t="n">
-        <v>100.7423117709438</v>
-      </c>
-      <c r="AC464" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD464" t="n">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="AE464" t="n">
-        <v>0.5370370370370371</v>
-      </c>
-      <c r="AF464" t="n">
-        <v>25.5734777027404</v>
-      </c>
-      <c r="AG464" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AH464" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AI464" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B465" t="n">
-        <v>29</v>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="E465" t="n">
-        <v>200</v>
-      </c>
-      <c r="F465" t="n">
-        <v>75</v>
-      </c>
-      <c r="G465" t="n">
-        <v>20</v>
-      </c>
-      <c r="H465" t="n">
-        <v>47</v>
-      </c>
-      <c r="I465" t="n">
-        <v>7</v>
-      </c>
-      <c r="J465" t="n">
-        <v>23</v>
-      </c>
-      <c r="K465" t="n">
-        <v>14</v>
-      </c>
-      <c r="L465" t="n">
-        <v>18</v>
-      </c>
-      <c r="M465" t="n">
-        <v>9</v>
-      </c>
-      <c r="N465" t="n">
-        <v>29</v>
-      </c>
-      <c r="O465" t="n">
-        <v>14</v>
-      </c>
-      <c r="P465" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q465" t="n">
-        <v>9</v>
-      </c>
-      <c r="R465" t="n">
-        <v>20</v>
-      </c>
-      <c r="S465" t="n">
-        <v>17</v>
-      </c>
-      <c r="T465" t="n">
-        <v>3</v>
-      </c>
-      <c r="U465" t="inlineStr">
-        <is>
-          <t>2486511</t>
-        </is>
-      </c>
-      <c r="V465" t="n">
-        <v>82</v>
-      </c>
-      <c r="W465" t="n">
-        <v>86.92</v>
-      </c>
-      <c r="X465" t="n">
-        <v>0.8628624022089277</v>
-      </c>
-      <c r="Y465" t="n">
-        <v>77.92</v>
-      </c>
-      <c r="Z465" t="n">
-        <v>96.25256673511294</v>
-      </c>
-      <c r="AA465" t="n">
-        <v>0.9495136637332098</v>
-      </c>
-      <c r="AB465" t="n">
-        <v>105.9979317476732</v>
-      </c>
-      <c r="AC465" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="AD465" t="n">
-        <v>0.7631578947368421</v>
-      </c>
-      <c r="AE465" t="n">
-        <v>0.4935064935064935</v>
-      </c>
-      <c r="AF465" t="n">
-        <v>-9.745365012560285</v>
-      </c>
-      <c r="AG465" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AH465" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI465" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B466" t="n">
-        <v>30</v>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="E466" t="n">
-        <v>200</v>
-      </c>
-      <c r="F466" t="n">
-        <v>69</v>
-      </c>
-      <c r="G466" t="n">
-        <v>11</v>
-      </c>
-      <c r="H466" t="n">
-        <v>28</v>
-      </c>
-      <c r="I466" t="n">
-        <v>9</v>
-      </c>
-      <c r="J466" t="n">
-        <v>32</v>
-      </c>
-      <c r="K466" t="n">
-        <v>20</v>
-      </c>
-      <c r="L466" t="n">
-        <v>24</v>
-      </c>
-      <c r="M466" t="n">
-        <v>10</v>
-      </c>
-      <c r="N466" t="n">
-        <v>16</v>
-      </c>
-      <c r="O466" t="n">
-        <v>16</v>
-      </c>
-      <c r="P466" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q466" t="n">
-        <v>16</v>
-      </c>
-      <c r="R466" t="n">
-        <v>20</v>
-      </c>
-      <c r="S466" t="n">
-        <v>20</v>
-      </c>
-      <c r="T466" t="n">
-        <v>0</v>
-      </c>
-      <c r="U466" t="inlineStr">
-        <is>
-          <t>2486523</t>
-        </is>
-      </c>
-      <c r="V466" t="n">
-        <v>75</v>
-      </c>
-      <c r="W466" t="n">
-        <v>86.56</v>
-      </c>
-      <c r="X466" t="n">
-        <v>0.7971349353049907</v>
-      </c>
-      <c r="Y466" t="n">
-        <v>76.56</v>
-      </c>
-      <c r="Z466" t="n">
-        <v>90.12539184952978</v>
-      </c>
-      <c r="AA466" t="n">
-        <v>0.8733115975780159</v>
-      </c>
-      <c r="AB466" t="n">
-        <v>98.84027411702689</v>
-      </c>
-      <c r="AC466" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="AD466" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="AE466" t="n">
-        <v>0.4262295081967213</v>
-      </c>
-      <c r="AF466" t="n">
-        <v>-8.714882267497117</v>
-      </c>
-      <c r="AG466" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH466" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI466" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B467" t="n">
-        <v>30</v>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="E467" t="n">
-        <v>225</v>
-      </c>
-      <c r="F467" t="n">
-        <v>87</v>
-      </c>
-      <c r="G467" t="n">
-        <v>21</v>
-      </c>
-      <c r="H467" t="n">
-        <v>42</v>
-      </c>
-      <c r="I467" t="n">
-        <v>10</v>
-      </c>
-      <c r="J467" t="n">
-        <v>37</v>
-      </c>
-      <c r="K467" t="n">
-        <v>15</v>
-      </c>
-      <c r="L467" t="n">
-        <v>21</v>
-      </c>
-      <c r="M467" t="n">
-        <v>9</v>
-      </c>
-      <c r="N467" t="n">
-        <v>33</v>
-      </c>
-      <c r="O467" t="n">
-        <v>10</v>
-      </c>
-      <c r="P467" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q467" t="n">
-        <v>10</v>
-      </c>
-      <c r="R467" t="n">
-        <v>24</v>
-      </c>
-      <c r="S467" t="n">
-        <v>21</v>
-      </c>
-      <c r="T467" t="n">
-        <v>0</v>
-      </c>
-      <c r="U467" t="inlineStr">
-        <is>
-          <t>2486526</t>
-        </is>
-      </c>
-      <c r="V467" t="n">
-        <v>94</v>
-      </c>
-      <c r="W467" t="n">
-        <v>98.24000000000001</v>
-      </c>
-      <c r="X467" t="n">
-        <v>0.8855863192182409</v>
-      </c>
-      <c r="Y467" t="n">
-        <v>89.24000000000001</v>
-      </c>
-      <c r="Z467" t="n">
-        <v>97.48991483639622</v>
-      </c>
-      <c r="AA467" t="n">
-        <v>0.9418837675350702</v>
-      </c>
-      <c r="AB467" t="n">
-        <v>105.8558558558559</v>
-      </c>
-      <c r="AC467" t="n">
-        <v>0.2093023255813954</v>
-      </c>
-      <c r="AD467" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE467" t="n">
-        <v>0.4827586206896552</v>
-      </c>
-      <c r="AF467" t="n">
-        <v>-8.36594101945964</v>
-      </c>
-      <c r="AG467" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AH467" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI467" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B468" t="n">
-        <v>30</v>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="E468" t="n">
-        <v>200</v>
-      </c>
-      <c r="F468" t="n">
-        <v>57</v>
-      </c>
-      <c r="G468" t="n">
-        <v>16</v>
-      </c>
-      <c r="H468" t="n">
-        <v>43</v>
-      </c>
-      <c r="I468" t="n">
-        <v>4</v>
-      </c>
-      <c r="J468" t="n">
-        <v>22</v>
-      </c>
-      <c r="K468" t="n">
-        <v>13</v>
-      </c>
-      <c r="L468" t="n">
-        <v>16</v>
-      </c>
-      <c r="M468" t="n">
-        <v>13</v>
-      </c>
-      <c r="N468" t="n">
-        <v>16</v>
-      </c>
-      <c r="O468" t="n">
-        <v>14</v>
-      </c>
-      <c r="P468" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q468" t="n">
-        <v>13</v>
-      </c>
-      <c r="R468" t="n">
-        <v>24</v>
-      </c>
-      <c r="S468" t="n">
-        <v>16</v>
-      </c>
-      <c r="T468" t="n">
-        <v>2</v>
-      </c>
-      <c r="U468" t="inlineStr">
-        <is>
-          <t>2486521</t>
-        </is>
-      </c>
-      <c r="V468" t="n">
-        <v>94</v>
-      </c>
-      <c r="W468" t="n">
-        <v>85.03999999999999</v>
-      </c>
-      <c r="X468" t="n">
-        <v>0.6702728127939793</v>
-      </c>
-      <c r="Y468" t="n">
-        <v>72.03999999999999</v>
-      </c>
-      <c r="Z468" t="n">
-        <v>79.12270960577457</v>
-      </c>
-      <c r="AA468" t="n">
-        <v>1.160493827160494</v>
-      </c>
-      <c r="AB468" t="n">
-        <v>130.5555555555555</v>
-      </c>
-      <c r="AC468" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD468" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AE468" t="n">
-        <v>0.453125</v>
-      </c>
-      <c r="AF468" t="n">
-        <v>-51.43284594978097</v>
-      </c>
-      <c r="AG468" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH468" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI468" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B469" t="n">
-        <v>30</v>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="E469" t="n">
-        <v>200</v>
-      </c>
-      <c r="F469" t="n">
-        <v>77</v>
-      </c>
-      <c r="G469" t="n">
-        <v>22</v>
-      </c>
-      <c r="H469" t="n">
-        <v>34</v>
-      </c>
-      <c r="I469" t="n">
-        <v>6</v>
-      </c>
-      <c r="J469" t="n">
-        <v>17</v>
-      </c>
-      <c r="K469" t="n">
-        <v>15</v>
-      </c>
-      <c r="L469" t="n">
-        <v>23</v>
-      </c>
-      <c r="M469" t="n">
-        <v>6</v>
-      </c>
-      <c r="N469" t="n">
-        <v>24</v>
-      </c>
-      <c r="O469" t="n">
-        <v>11</v>
-      </c>
-      <c r="P469" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q469" t="n">
-        <v>17</v>
-      </c>
-      <c r="R469" t="n">
-        <v>18</v>
-      </c>
-      <c r="S469" t="n">
-        <v>18</v>
-      </c>
-      <c r="T469" t="n">
-        <v>2</v>
-      </c>
-      <c r="U469" t="inlineStr">
-        <is>
-          <t>2486519</t>
-        </is>
-      </c>
-      <c r="V469" t="n">
-        <v>80</v>
-      </c>
-      <c r="W469" t="n">
-        <v>78.12</v>
-      </c>
-      <c r="X469" t="n">
-        <v>0.985663082437276</v>
-      </c>
-      <c r="Y469" t="n">
-        <v>72.12</v>
-      </c>
-      <c r="Z469" t="n">
-        <v>106.7665002773156</v>
-      </c>
-      <c r="AA469" t="n">
-        <v>0.964785335262904</v>
-      </c>
-      <c r="AB469" t="n">
-        <v>108.2251082251082</v>
-      </c>
-      <c r="AC469" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="AD469" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="AE469" t="n">
-        <v>0.5454545454545454</v>
-      </c>
-      <c r="AF469" t="n">
-        <v>-1.458607947792657</v>
-      </c>
-      <c r="AG469" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH469" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AI469" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B470" t="n">
-        <v>30</v>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="E470" t="n">
-        <v>200</v>
-      </c>
-      <c r="F470" t="n">
-        <v>75</v>
-      </c>
-      <c r="G470" t="n">
-        <v>20</v>
-      </c>
-      <c r="H470" t="n">
-        <v>38</v>
-      </c>
-      <c r="I470" t="n">
-        <v>10</v>
-      </c>
-      <c r="J470" t="n">
-        <v>29</v>
-      </c>
-      <c r="K470" t="n">
-        <v>5</v>
-      </c>
-      <c r="L470" t="n">
-        <v>16</v>
-      </c>
-      <c r="M470" t="n">
-        <v>10</v>
-      </c>
-      <c r="N470" t="n">
-        <v>26</v>
-      </c>
-      <c r="O470" t="n">
-        <v>15</v>
-      </c>
-      <c r="P470" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q470" t="n">
-        <v>12</v>
-      </c>
-      <c r="R470" t="n">
-        <v>15</v>
-      </c>
-      <c r="S470" t="n">
-        <v>20</v>
-      </c>
-      <c r="T470" t="n">
-        <v>0</v>
-      </c>
-      <c r="U470" t="inlineStr">
-        <is>
-          <t>2486524</t>
-        </is>
-      </c>
-      <c r="V470" t="n">
-        <v>74</v>
-      </c>
-      <c r="W470" t="n">
-        <v>86.03999999999999</v>
-      </c>
-      <c r="X470" t="n">
-        <v>0.8716875871687588</v>
-      </c>
-      <c r="Y470" t="n">
-        <v>76.03999999999999</v>
-      </c>
-      <c r="Z470" t="n">
-        <v>98.63229879011048</v>
-      </c>
-      <c r="AA470" t="n">
-        <v>0.828853046594982</v>
-      </c>
-      <c r="AB470" t="n">
-        <v>97.01101206082852</v>
-      </c>
-      <c r="AC470" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="AD470" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE470" t="n">
-        <v>0.4675324675324675</v>
-      </c>
-      <c r="AF470" t="n">
-        <v>1.621286729281962</v>
-      </c>
-      <c r="AG470" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AH470" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AI470" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B471" t="n">
-        <v>30</v>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="E471" t="n">
-        <v>200</v>
-      </c>
-      <c r="F471" t="n">
-        <v>74</v>
-      </c>
-      <c r="G471" t="n">
-        <v>9</v>
-      </c>
-      <c r="H471" t="n">
-        <v>23</v>
-      </c>
-      <c r="I471" t="n">
-        <v>13</v>
-      </c>
-      <c r="J471" t="n">
-        <v>39</v>
-      </c>
-      <c r="K471" t="n">
-        <v>17</v>
-      </c>
-      <c r="L471" t="n">
-        <v>22</v>
-      </c>
-      <c r="M471" t="n">
-        <v>8</v>
-      </c>
-      <c r="N471" t="n">
-        <v>25</v>
-      </c>
-      <c r="O471" t="n">
-        <v>12</v>
-      </c>
-      <c r="P471" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q471" t="n">
-        <v>9</v>
-      </c>
-      <c r="R471" t="n">
-        <v>23</v>
-      </c>
-      <c r="S471" t="n">
-        <v>21</v>
-      </c>
-      <c r="T471" t="n">
-        <v>1</v>
-      </c>
-      <c r="U471" t="inlineStr">
-        <is>
-          <t>2486525</t>
-        </is>
-      </c>
-      <c r="V471" t="n">
-        <v>82</v>
-      </c>
-      <c r="W471" t="n">
-        <v>80.68000000000001</v>
-      </c>
-      <c r="X471" t="n">
-        <v>0.9172037679722359</v>
-      </c>
-      <c r="Y471" t="n">
-        <v>72.68000000000001</v>
-      </c>
-      <c r="Z471" t="n">
-        <v>101.8161805173363</v>
-      </c>
-      <c r="AA471" t="n">
-        <v>0.9597378277153559</v>
-      </c>
-      <c r="AB471" t="n">
-        <v>108.695652173913</v>
-      </c>
-      <c r="AC471" t="n">
-        <v>0.2162162162162162</v>
-      </c>
-      <c r="AD471" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="AE471" t="n">
-        <v>0.4583333333333333</v>
-      </c>
-      <c r="AF471" t="n">
-        <v>-6.879471656576783</v>
-      </c>
-      <c r="AG471" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH471" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI471" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B472" t="n">
-        <v>30</v>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="E472" t="n">
-        <v>200</v>
-      </c>
-      <c r="F472" t="n">
-        <v>80</v>
-      </c>
-      <c r="G472" t="n">
-        <v>11</v>
-      </c>
-      <c r="H472" t="n">
-        <v>26</v>
-      </c>
-      <c r="I472" t="n">
-        <v>16</v>
-      </c>
-      <c r="J472" t="n">
-        <v>33</v>
-      </c>
-      <c r="K472" t="n">
-        <v>10</v>
-      </c>
-      <c r="L472" t="n">
-        <v>18</v>
-      </c>
-      <c r="M472" t="n">
-        <v>9</v>
-      </c>
-      <c r="N472" t="n">
-        <v>16</v>
-      </c>
-      <c r="O472" t="n">
-        <v>18</v>
-      </c>
-      <c r="P472" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q472" t="n">
-        <v>16</v>
-      </c>
-      <c r="R472" t="n">
-        <v>18</v>
-      </c>
-      <c r="S472" t="n">
-        <v>18</v>
-      </c>
-      <c r="T472" t="n">
-        <v>2</v>
-      </c>
-      <c r="U472" t="inlineStr">
-        <is>
-          <t>2486519</t>
-        </is>
-      </c>
-      <c r="V472" t="n">
-        <v>77</v>
-      </c>
-      <c r="W472" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="X472" t="n">
-        <v>0.964785335262904</v>
-      </c>
-      <c r="Y472" t="n">
-        <v>73.92</v>
-      </c>
-      <c r="Z472" t="n">
-        <v>108.2251082251082</v>
-      </c>
-      <c r="AA472" t="n">
-        <v>0.985663082437276</v>
-      </c>
-      <c r="AB472" t="n">
-        <v>106.7665002773156</v>
-      </c>
-      <c r="AC472" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="AD472" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="AE472" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="AF472" t="n">
-        <v>1.458607947792657</v>
-      </c>
-      <c r="AG472" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH472" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AI472" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B473" t="n">
-        <v>30</v>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="E473" t="n">
-        <v>200</v>
-      </c>
-      <c r="F473" t="n">
-        <v>67</v>
-      </c>
-      <c r="G473" t="n">
-        <v>15</v>
-      </c>
-      <c r="H473" t="n">
-        <v>28</v>
-      </c>
-      <c r="I473" t="n">
-        <v>8</v>
-      </c>
-      <c r="J473" t="n">
-        <v>36</v>
-      </c>
-      <c r="K473" t="n">
-        <v>13</v>
-      </c>
-      <c r="L473" t="n">
-        <v>22</v>
-      </c>
-      <c r="M473" t="n">
-        <v>11</v>
-      </c>
-      <c r="N473" t="n">
-        <v>22</v>
-      </c>
-      <c r="O473" t="n">
-        <v>12</v>
-      </c>
-      <c r="P473" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q473" t="n">
-        <v>15</v>
-      </c>
-      <c r="R473" t="n">
-        <v>26</v>
-      </c>
-      <c r="S473" t="n">
-        <v>24</v>
-      </c>
-      <c r="T473" t="n">
-        <v>2</v>
-      </c>
-      <c r="U473" t="inlineStr">
-        <is>
-          <t>2486520</t>
-        </is>
-      </c>
-      <c r="V473" t="n">
-        <v>72</v>
-      </c>
-      <c r="W473" t="n">
-        <v>88.68000000000001</v>
-      </c>
-      <c r="X473" t="n">
-        <v>0.7555254848894902</v>
-      </c>
-      <c r="Y473" t="n">
-        <v>77.68000000000001</v>
-      </c>
-      <c r="Z473" t="n">
-        <v>86.25128733264675</v>
-      </c>
-      <c r="AA473" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="AB473" t="n">
-        <v>98.36065573770492</v>
-      </c>
-      <c r="AC473" t="n">
-        <v>0.34375</v>
-      </c>
-      <c r="AD473" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AE473" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AF473" t="n">
-        <v>-12.10936840505816</v>
-      </c>
-      <c r="AG473" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH473" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI473" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B474" t="n">
-        <v>30</v>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="E474" t="n">
-        <v>200</v>
-      </c>
-      <c r="F474" t="n">
-        <v>82</v>
-      </c>
-      <c r="G474" t="n">
-        <v>18</v>
-      </c>
-      <c r="H474" t="n">
-        <v>36</v>
-      </c>
-      <c r="I474" t="n">
-        <v>9</v>
-      </c>
-      <c r="J474" t="n">
-        <v>25</v>
-      </c>
-      <c r="K474" t="n">
-        <v>19</v>
-      </c>
-      <c r="L474" t="n">
-        <v>26</v>
-      </c>
-      <c r="M474" t="n">
-        <v>10</v>
-      </c>
-      <c r="N474" t="n">
-        <v>29</v>
-      </c>
-      <c r="O474" t="n">
-        <v>16</v>
-      </c>
-      <c r="P474" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q474" t="n">
-        <v>13</v>
-      </c>
-      <c r="R474" t="n">
-        <v>21</v>
-      </c>
-      <c r="S474" t="n">
-        <v>23</v>
-      </c>
-      <c r="T474" t="n">
-        <v>2</v>
-      </c>
-      <c r="U474" t="inlineStr">
-        <is>
-          <t>2486525</t>
-        </is>
-      </c>
-      <c r="V474" t="n">
-        <v>74</v>
-      </c>
-      <c r="W474" t="n">
-        <v>85.44</v>
-      </c>
-      <c r="X474" t="n">
-        <v>0.9597378277153559</v>
-      </c>
-      <c r="Y474" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="Z474" t="n">
-        <v>108.695652173913</v>
-      </c>
-      <c r="AA474" t="n">
-        <v>0.9172037679722359</v>
-      </c>
-      <c r="AB474" t="n">
-        <v>101.8161805173363</v>
-      </c>
-      <c r="AC474" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="AD474" t="n">
-        <v>0.7837837837837838</v>
-      </c>
-      <c r="AE474" t="n">
-        <v>0.5416666666666666</v>
-      </c>
-      <c r="AF474" t="n">
-        <v>6.879471656576783</v>
-      </c>
-      <c r="AG474" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH474" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI474" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B475" t="n">
-        <v>30</v>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="E475" t="n">
-        <v>200</v>
-      </c>
-      <c r="F475" t="n">
-        <v>82</v>
-      </c>
-      <c r="G475" t="n">
-        <v>18</v>
-      </c>
-      <c r="H475" t="n">
-        <v>34</v>
-      </c>
-      <c r="I475" t="n">
-        <v>8</v>
-      </c>
-      <c r="J475" t="n">
-        <v>30</v>
-      </c>
-      <c r="K475" t="n">
-        <v>22</v>
-      </c>
-      <c r="L475" t="n">
-        <v>36</v>
-      </c>
-      <c r="M475" t="n">
-        <v>19</v>
-      </c>
-      <c r="N475" t="n">
-        <v>34</v>
-      </c>
-      <c r="O475" t="n">
-        <v>17</v>
-      </c>
-      <c r="P475" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q475" t="n">
-        <v>18</v>
-      </c>
-      <c r="R475" t="n">
-        <v>21</v>
-      </c>
-      <c r="S475" t="n">
-        <v>26</v>
-      </c>
-      <c r="T475" t="n">
-        <v>2</v>
-      </c>
-      <c r="U475" t="inlineStr">
-        <is>
-          <t>2486522</t>
-        </is>
-      </c>
-      <c r="V475" t="n">
-        <v>65</v>
-      </c>
-      <c r="W475" t="n">
-        <v>97.84</v>
-      </c>
-      <c r="X475" t="n">
-        <v>0.8381030253475061</v>
-      </c>
-      <c r="Y475" t="n">
-        <v>78.84</v>
-      </c>
-      <c r="Z475" t="n">
-        <v>104.0081177067478</v>
-      </c>
-      <c r="AA475" t="n">
-        <v>0.7705073494547179</v>
-      </c>
-      <c r="AB475" t="n">
-        <v>80.88601294176208</v>
-      </c>
-      <c r="AC475" t="n">
-        <v>0.5135135135135135</v>
-      </c>
-      <c r="AD475" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="AE475" t="n">
-        <v>0.7066666666666667</v>
-      </c>
-      <c r="AF475" t="n">
-        <v>23.12210476498576</v>
-      </c>
-      <c r="AG475" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AH475" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AI475" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B476" t="n">
-        <v>30</v>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="E476" t="n">
-        <v>200</v>
-      </c>
-      <c r="F476" t="n">
-        <v>74</v>
-      </c>
-      <c r="G476" t="n">
-        <v>16</v>
-      </c>
-      <c r="H476" t="n">
-        <v>32</v>
-      </c>
-      <c r="I476" t="n">
-        <v>11</v>
-      </c>
-      <c r="J476" t="n">
-        <v>39</v>
-      </c>
-      <c r="K476" t="n">
-        <v>9</v>
-      </c>
-      <c r="L476" t="n">
-        <v>12</v>
-      </c>
-      <c r="M476" t="n">
-        <v>13</v>
-      </c>
-      <c r="N476" t="n">
-        <v>28</v>
-      </c>
-      <c r="O476" t="n">
-        <v>14</v>
-      </c>
-      <c r="P476" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q476" t="n">
-        <v>13</v>
-      </c>
-      <c r="R476" t="n">
-        <v>20</v>
-      </c>
-      <c r="S476" t="n">
-        <v>15</v>
-      </c>
-      <c r="T476" t="n">
-        <v>3</v>
-      </c>
-      <c r="U476" t="inlineStr">
-        <is>
-          <t>2486524</t>
-        </is>
-      </c>
-      <c r="V476" t="n">
-        <v>75</v>
-      </c>
-      <c r="W476" t="n">
-        <v>89.28</v>
-      </c>
-      <c r="X476" t="n">
-        <v>0.828853046594982</v>
-      </c>
-      <c r="Y476" t="n">
-        <v>76.28</v>
-      </c>
-      <c r="Z476" t="n">
-        <v>97.01101206082852</v>
-      </c>
-      <c r="AA476" t="n">
-        <v>0.8716875871687588</v>
-      </c>
-      <c r="AB476" t="n">
-        <v>98.63229879011048</v>
-      </c>
-      <c r="AC476" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD476" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="AE476" t="n">
-        <v>0.5324675324675324</v>
-      </c>
-      <c r="AF476" t="n">
-        <v>-1.621286729281962</v>
-      </c>
-      <c r="AG476" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AH476" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AI476" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B477" t="n">
-        <v>30</v>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="E477" t="n">
-        <v>225</v>
-      </c>
-      <c r="F477" t="n">
-        <v>94</v>
-      </c>
-      <c r="G477" t="n">
-        <v>17</v>
-      </c>
-      <c r="H477" t="n">
-        <v>30</v>
-      </c>
-      <c r="I477" t="n">
-        <v>15</v>
-      </c>
-      <c r="J477" t="n">
-        <v>49</v>
-      </c>
-      <c r="K477" t="n">
-        <v>15</v>
-      </c>
-      <c r="L477" t="n">
-        <v>20</v>
-      </c>
-      <c r="M477" t="n">
-        <v>11</v>
-      </c>
-      <c r="N477" t="n">
-        <v>34</v>
-      </c>
-      <c r="O477" t="n">
-        <v>20</v>
-      </c>
-      <c r="P477" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q477" t="n">
-        <v>12</v>
-      </c>
-      <c r="R477" t="n">
-        <v>22</v>
-      </c>
-      <c r="S477" t="n">
-        <v>24</v>
-      </c>
-      <c r="T477" t="n">
-        <v>1</v>
-      </c>
-      <c r="U477" t="inlineStr">
-        <is>
-          <t>2486526</t>
-        </is>
-      </c>
-      <c r="V477" t="n">
-        <v>87</v>
-      </c>
-      <c r="W477" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="X477" t="n">
-        <v>0.9418837675350702</v>
-      </c>
-      <c r="Y477" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z477" t="n">
-        <v>105.8558558558559</v>
-      </c>
-      <c r="AA477" t="n">
-        <v>0.8855863192182409</v>
-      </c>
-      <c r="AB477" t="n">
-        <v>97.48991483639622</v>
-      </c>
-      <c r="AC477" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD477" t="n">
-        <v>0.7906976744186046</v>
-      </c>
-      <c r="AE477" t="n">
-        <v>0.5172413793103449</v>
-      </c>
-      <c r="AF477" t="n">
-        <v>8.36594101945964</v>
-      </c>
-      <c r="AG477" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AH477" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI477" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B478" t="n">
-        <v>30</v>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E478" t="n">
-        <v>200</v>
-      </c>
-      <c r="F478" t="n">
-        <v>94</v>
-      </c>
-      <c r="G478" t="n">
-        <v>27</v>
-      </c>
-      <c r="H478" t="n">
-        <v>41</v>
-      </c>
-      <c r="I478" t="n">
-        <v>8</v>
-      </c>
-      <c r="J478" t="n">
-        <v>19</v>
-      </c>
-      <c r="K478" t="n">
-        <v>16</v>
-      </c>
-      <c r="L478" t="n">
-        <v>25</v>
-      </c>
-      <c r="M478" t="n">
-        <v>9</v>
-      </c>
-      <c r="N478" t="n">
-        <v>26</v>
-      </c>
-      <c r="O478" t="n">
-        <v>21</v>
-      </c>
-      <c r="P478" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q478" t="n">
-        <v>10</v>
-      </c>
-      <c r="R478" t="n">
-        <v>16</v>
-      </c>
-      <c r="S478" t="n">
-        <v>23</v>
-      </c>
-      <c r="T478" t="n">
-        <v>1</v>
-      </c>
-      <c r="U478" t="inlineStr">
-        <is>
-          <t>2486521</t>
-        </is>
-      </c>
-      <c r="V478" t="n">
-        <v>57</v>
-      </c>
-      <c r="W478" t="n">
-        <v>81</v>
-      </c>
-      <c r="X478" t="n">
-        <v>1.160493827160494</v>
-      </c>
-      <c r="Y478" t="n">
-        <v>72</v>
-      </c>
-      <c r="Z478" t="n">
-        <v>130.5555555555555</v>
-      </c>
-      <c r="AA478" t="n">
-        <v>0.6702728127939793</v>
-      </c>
-      <c r="AB478" t="n">
-        <v>79.12270960577457</v>
-      </c>
-      <c r="AC478" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AD478" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE478" t="n">
-        <v>0.546875</v>
-      </c>
-      <c r="AF478" t="n">
-        <v>51.43284594978097</v>
-      </c>
-      <c r="AG478" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH478" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI478" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B479" t="n">
-        <v>30</v>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E479" t="n">
-        <v>200</v>
-      </c>
-      <c r="F479" t="n">
-        <v>75</v>
-      </c>
-      <c r="G479" t="n">
-        <v>23</v>
-      </c>
-      <c r="H479" t="n">
-        <v>37</v>
-      </c>
-      <c r="I479" t="n">
-        <v>4</v>
-      </c>
-      <c r="J479" t="n">
-        <v>20</v>
-      </c>
-      <c r="K479" t="n">
-        <v>17</v>
-      </c>
-      <c r="L479" t="n">
-        <v>27</v>
-      </c>
-      <c r="M479" t="n">
-        <v>10</v>
-      </c>
-      <c r="N479" t="n">
-        <v>25</v>
-      </c>
-      <c r="O479" t="n">
-        <v>17</v>
-      </c>
-      <c r="P479" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q479" t="n">
-        <v>17</v>
-      </c>
-      <c r="R479" t="n">
-        <v>21</v>
-      </c>
-      <c r="S479" t="n">
-        <v>20</v>
-      </c>
-      <c r="T479" t="n">
-        <v>2</v>
-      </c>
-      <c r="U479" t="inlineStr">
-        <is>
-          <t>2486523</t>
-        </is>
-      </c>
-      <c r="V479" t="n">
-        <v>69</v>
-      </c>
-      <c r="W479" t="n">
-        <v>85.88</v>
-      </c>
-      <c r="X479" t="n">
-        <v>0.8733115975780159</v>
-      </c>
-      <c r="Y479" t="n">
-        <v>75.88</v>
-      </c>
-      <c r="Z479" t="n">
-        <v>98.84027411702689</v>
-      </c>
-      <c r="AA479" t="n">
-        <v>0.7971349353049907</v>
-      </c>
-      <c r="AB479" t="n">
-        <v>90.12539184952978</v>
-      </c>
-      <c r="AC479" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="AD479" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="AE479" t="n">
-        <v>0.5737704918032787</v>
-      </c>
-      <c r="AF479" t="n">
-        <v>8.714882267497117</v>
-      </c>
-      <c r="AG479" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH479" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI479" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B480" t="n">
-        <v>30</v>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="E480" t="n">
-        <v>200</v>
-      </c>
-      <c r="F480" t="n">
-        <v>65</v>
-      </c>
-      <c r="G480" t="n">
-        <v>22</v>
-      </c>
-      <c r="H480" t="n">
-        <v>45</v>
-      </c>
-      <c r="I480" t="n">
-        <v>3</v>
-      </c>
-      <c r="J480" t="n">
-        <v>17</v>
-      </c>
-      <c r="K480" t="n">
-        <v>12</v>
-      </c>
-      <c r="L480" t="n">
-        <v>19</v>
-      </c>
-      <c r="M480" t="n">
-        <v>4</v>
-      </c>
-      <c r="N480" t="n">
-        <v>18</v>
-      </c>
-      <c r="O480" t="n">
-        <v>6</v>
-      </c>
-      <c r="P480" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q480" t="n">
-        <v>14</v>
-      </c>
-      <c r="R480" t="n">
-        <v>27</v>
-      </c>
-      <c r="S480" t="n">
-        <v>21</v>
-      </c>
-      <c r="T480" t="n">
-        <v>2</v>
-      </c>
-      <c r="U480" t="inlineStr">
-        <is>
-          <t>2486522</t>
-        </is>
-      </c>
-      <c r="V480" t="n">
-        <v>82</v>
-      </c>
-      <c r="W480" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="X480" t="n">
-        <v>0.7705073494547179</v>
-      </c>
-      <c r="Y480" t="n">
-        <v>80.36</v>
-      </c>
-      <c r="Z480" t="n">
-        <v>80.88601294176208</v>
-      </c>
-      <c r="AA480" t="n">
-        <v>0.8381030253475061</v>
-      </c>
-      <c r="AB480" t="n">
-        <v>104.0081177067478</v>
-      </c>
-      <c r="AC480" t="n">
-        <v>0.1052631578947368</v>
-      </c>
-      <c r="AD480" t="n">
-        <v>0.4864864864864865</v>
-      </c>
-      <c r="AE480" t="n">
-        <v>0.2933333333333333</v>
-      </c>
-      <c r="AF480" t="n">
-        <v>-23.12210476498576</v>
-      </c>
-      <c r="AG480" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AH480" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AI480" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B481" t="n">
-        <v>30</v>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="E481" t="n">
-        <v>200</v>
-      </c>
-      <c r="F481" t="n">
-        <v>72</v>
-      </c>
-      <c r="G481" t="n">
-        <v>15</v>
-      </c>
-      <c r="H481" t="n">
-        <v>24</v>
-      </c>
-      <c r="I481" t="n">
-        <v>7</v>
-      </c>
-      <c r="J481" t="n">
-        <v>28</v>
-      </c>
-      <c r="K481" t="n">
-        <v>21</v>
-      </c>
-      <c r="L481" t="n">
-        <v>30</v>
-      </c>
-      <c r="M481" t="n">
-        <v>6</v>
-      </c>
-      <c r="N481" t="n">
-        <v>21</v>
-      </c>
-      <c r="O481" t="n">
-        <v>11</v>
-      </c>
-      <c r="P481" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q481" t="n">
-        <v>14</v>
-      </c>
-      <c r="R481" t="n">
-        <v>24</v>
-      </c>
-      <c r="S481" t="n">
-        <v>26</v>
-      </c>
-      <c r="T481" t="n">
-        <v>2</v>
-      </c>
-      <c r="U481" t="inlineStr">
-        <is>
-          <t>2486520</t>
-        </is>
-      </c>
-      <c r="V481" t="n">
-        <v>67</v>
-      </c>
-      <c r="W481" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="X481" t="n">
-        <v>0.9090909090909091</v>
-      </c>
-      <c r="Y481" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="Z481" t="n">
-        <v>98.36065573770492</v>
-      </c>
-      <c r="AA481" t="n">
-        <v>0.7555254848894902</v>
-      </c>
-      <c r="AB481" t="n">
-        <v>86.25128733264675</v>
-      </c>
-      <c r="AC481" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="AD481" t="n">
-        <v>0.65625</v>
-      </c>
-      <c r="AE481" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AF481" t="n">
-        <v>12.10936840505816</v>
-      </c>
-      <c r="AG481" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH481" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI481" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B482" t="n">
-        <v>31</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="E482" t="n">
-        <v>200</v>
-      </c>
-      <c r="F482" t="n">
-        <v>89</v>
-      </c>
-      <c r="G482" t="n">
-        <v>20</v>
-      </c>
-      <c r="H482" t="n">
-        <v>34</v>
-      </c>
-      <c r="I482" t="n">
-        <v>14</v>
-      </c>
-      <c r="J482" t="n">
-        <v>36</v>
-      </c>
-      <c r="K482" t="n">
-        <v>7</v>
-      </c>
-      <c r="L482" t="n">
-        <v>14</v>
-      </c>
-      <c r="M482" t="n">
-        <v>15</v>
-      </c>
-      <c r="N482" t="n">
-        <v>24</v>
-      </c>
-      <c r="O482" t="n">
-        <v>23</v>
-      </c>
-      <c r="P482" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q482" t="n">
-        <v>9</v>
-      </c>
-      <c r="R482" t="n">
-        <v>18</v>
-      </c>
-      <c r="S482" t="n">
-        <v>19</v>
-      </c>
-      <c r="T482" t="n">
-        <v>0</v>
-      </c>
-      <c r="U482" t="inlineStr">
-        <is>
-          <t>2486535</t>
-        </is>
-      </c>
-      <c r="V482" t="n">
-        <v>74</v>
-      </c>
-      <c r="W482" t="n">
-        <v>85.16</v>
-      </c>
-      <c r="X482" t="n">
-        <v>1.045091592296853</v>
-      </c>
-      <c r="Y482" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="Z482" t="n">
-        <v>126.8529076396807</v>
-      </c>
-      <c r="AA482" t="n">
-        <v>0.9245377311344328</v>
-      </c>
-      <c r="AB482" t="n">
-        <v>99.94597514856835</v>
-      </c>
-      <c r="AC482" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AD482" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AE482" t="n">
-        <v>0.5909090909090909</v>
-      </c>
-      <c r="AF482" t="n">
-        <v>26.90693249111239</v>
-      </c>
-      <c r="AG482" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AH482" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI482" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B483" t="n">
-        <v>31</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="E483" t="n">
-        <v>200</v>
-      </c>
-      <c r="F483" t="n">
-        <v>78</v>
-      </c>
-      <c r="G483" t="n">
-        <v>19</v>
-      </c>
-      <c r="H483" t="n">
-        <v>45</v>
-      </c>
-      <c r="I483" t="n">
-        <v>8</v>
-      </c>
-      <c r="J483" t="n">
-        <v>22</v>
-      </c>
-      <c r="K483" t="n">
-        <v>16</v>
-      </c>
-      <c r="L483" t="n">
-        <v>19</v>
-      </c>
-      <c r="M483" t="n">
-        <v>12</v>
-      </c>
-      <c r="N483" t="n">
-        <v>29</v>
-      </c>
-      <c r="O483" t="n">
-        <v>15</v>
-      </c>
-      <c r="P483" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q483" t="n">
-        <v>16</v>
-      </c>
-      <c r="R483" t="n">
-        <v>21</v>
-      </c>
-      <c r="S483" t="n">
-        <v>20</v>
-      </c>
-      <c r="T483" t="n">
-        <v>2</v>
-      </c>
-      <c r="U483" t="inlineStr">
-        <is>
-          <t>2486533</t>
-        </is>
-      </c>
-      <c r="V483" t="n">
-        <v>64</v>
-      </c>
-      <c r="W483" t="n">
-        <v>91.36</v>
-      </c>
-      <c r="X483" t="n">
-        <v>0.8537653239929948</v>
-      </c>
-      <c r="Y483" t="n">
-        <v>79.36</v>
-      </c>
-      <c r="Z483" t="n">
-        <v>98.28629032258064</v>
-      </c>
-      <c r="AA483" t="n">
-        <v>0.7191011235955056</v>
-      </c>
-      <c r="AB483" t="n">
-        <v>81.01265822784811</v>
-      </c>
-      <c r="AC483" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-      <c r="AD483" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="AE483" t="n">
-        <v>0.5324675324675324</v>
-      </c>
-      <c r="AF483" t="n">
-        <v>17.27363209473253</v>
-      </c>
-      <c r="AG483" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AH483" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AI483" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B484" t="n">
-        <v>31</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="E484" t="n">
-        <v>200</v>
-      </c>
-      <c r="F484" t="n">
-        <v>90</v>
-      </c>
-      <c r="G484" t="n">
-        <v>22</v>
-      </c>
-      <c r="H484" t="n">
-        <v>36</v>
-      </c>
-      <c r="I484" t="n">
-        <v>10</v>
-      </c>
-      <c r="J484" t="n">
-        <v>25</v>
-      </c>
-      <c r="K484" t="n">
-        <v>16</v>
-      </c>
-      <c r="L484" t="n">
-        <v>26</v>
-      </c>
-      <c r="M484" t="n">
-        <v>13</v>
-      </c>
-      <c r="N484" t="n">
-        <v>24</v>
-      </c>
-      <c r="O484" t="n">
-        <v>20</v>
-      </c>
-      <c r="P484" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q484" t="n">
-        <v>14</v>
-      </c>
-      <c r="R484" t="n">
-        <v>24</v>
-      </c>
-      <c r="S484" t="n">
-        <v>25</v>
-      </c>
-      <c r="T484" t="n">
-        <v>2</v>
-      </c>
-      <c r="U484" t="inlineStr">
-        <is>
-          <t>2486534</t>
-        </is>
-      </c>
-      <c r="V484" t="n">
-        <v>93</v>
-      </c>
-      <c r="W484" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="X484" t="n">
-        <v>1.041184636742249</v>
-      </c>
-      <c r="Y484" t="n">
-        <v>73.44</v>
-      </c>
-      <c r="Z484" t="n">
-        <v>122.5490196078431</v>
-      </c>
-      <c r="AA484" t="n">
-        <v>1.085941148995796</v>
-      </c>
-      <c r="AB484" t="n">
-        <v>118.2604272634791</v>
-      </c>
-      <c r="AC484" t="n">
-        <v>0.4193548387096774</v>
-      </c>
-      <c r="AD484" t="n">
-        <v>0.7741935483870968</v>
-      </c>
-      <c r="AE484" t="n">
-        <v>0.5967741935483871</v>
-      </c>
-      <c r="AF484" t="n">
-        <v>4.288592344363991</v>
-      </c>
-      <c r="AG484" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH484" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI484" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B485" t="n">
-        <v>31</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="E485" t="n">
-        <v>200</v>
-      </c>
-      <c r="F485" t="n">
-        <v>63</v>
-      </c>
-      <c r="G485" t="n">
-        <v>15</v>
-      </c>
-      <c r="H485" t="n">
-        <v>42</v>
-      </c>
-      <c r="I485" t="n">
-        <v>8</v>
-      </c>
-      <c r="J485" t="n">
-        <v>23</v>
-      </c>
-      <c r="K485" t="n">
-        <v>9</v>
-      </c>
-      <c r="L485" t="n">
-        <v>14</v>
-      </c>
-      <c r="M485" t="n">
-        <v>10</v>
-      </c>
-      <c r="N485" t="n">
-        <v>19</v>
-      </c>
-      <c r="O485" t="n">
-        <v>15</v>
-      </c>
-      <c r="P485" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q485" t="n">
-        <v>9</v>
-      </c>
-      <c r="R485" t="n">
-        <v>18</v>
-      </c>
-      <c r="S485" t="n">
-        <v>17</v>
-      </c>
-      <c r="T485" t="n">
-        <v>1</v>
-      </c>
-      <c r="U485" t="inlineStr">
-        <is>
-          <t>2486529</t>
-        </is>
-      </c>
-      <c r="V485" t="n">
-        <v>73</v>
-      </c>
-      <c r="W485" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="X485" t="n">
-        <v>0.7859281437125749</v>
-      </c>
-      <c r="Y485" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="Z485" t="n">
-        <v>89.79475484606614</v>
-      </c>
-      <c r="AA485" t="n">
-        <v>0.9843581445523194</v>
-      </c>
-      <c r="AB485" t="n">
-        <v>110.3385731559855</v>
-      </c>
-      <c r="AC485" t="n">
-        <v>0.2702702702702703</v>
-      </c>
-      <c r="AD485" t="n">
-        <v>0.7037037037037037</v>
-      </c>
-      <c r="AE485" t="n">
-        <v>0.453125</v>
-      </c>
-      <c r="AF485" t="n">
-        <v>-20.54381830991936</v>
-      </c>
-      <c r="AG485" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH485" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AI485" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B486" t="n">
-        <v>31</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="E486" t="n">
-        <v>200</v>
-      </c>
-      <c r="F486" t="n">
-        <v>89</v>
-      </c>
-      <c r="G486" t="n">
-        <v>24</v>
-      </c>
-      <c r="H486" t="n">
-        <v>44</v>
-      </c>
-      <c r="I486" t="n">
-        <v>7</v>
-      </c>
-      <c r="J486" t="n">
-        <v>20</v>
-      </c>
-      <c r="K486" t="n">
-        <v>20</v>
-      </c>
-      <c r="L486" t="n">
-        <v>21</v>
-      </c>
-      <c r="M486" t="n">
-        <v>4</v>
-      </c>
-      <c r="N486" t="n">
-        <v>26</v>
-      </c>
-      <c r="O486" t="n">
-        <v>20</v>
-      </c>
-      <c r="P486" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q486" t="n">
-        <v>9</v>
-      </c>
-      <c r="R486" t="n">
-        <v>18</v>
-      </c>
-      <c r="S486" t="n">
-        <v>21</v>
-      </c>
-      <c r="T486" t="n">
-        <v>1</v>
-      </c>
-      <c r="U486" t="inlineStr">
-        <is>
-          <t>2486536</t>
-        </is>
-      </c>
-      <c r="V486" t="n">
-        <v>80</v>
-      </c>
-      <c r="W486" t="n">
-        <v>82.24000000000001</v>
-      </c>
-      <c r="X486" t="n">
-        <v>1.082198443579766</v>
-      </c>
-      <c r="Y486" t="n">
-        <v>78.24000000000001</v>
-      </c>
-      <c r="Z486" t="n">
-        <v>113.7525562372188</v>
-      </c>
-      <c r="AA486" t="n">
-        <v>0.9737098344693281</v>
-      </c>
-      <c r="AB486" t="n">
-        <v>103.6806635562468</v>
-      </c>
-      <c r="AC486" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="AD486" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="AE486" t="n">
-        <v>0.4918032786885246</v>
-      </c>
-      <c r="AF486" t="n">
-        <v>10.07189268097203</v>
-      </c>
-      <c r="AG486" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH486" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI486" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B487" t="n">
-        <v>31</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="E487" t="n">
-        <v>200</v>
-      </c>
-      <c r="F487" t="n">
-        <v>80</v>
-      </c>
-      <c r="G487" t="n">
-        <v>16</v>
-      </c>
-      <c r="H487" t="n">
-        <v>30</v>
-      </c>
-      <c r="I487" t="n">
-        <v>13</v>
-      </c>
-      <c r="J487" t="n">
-        <v>32</v>
-      </c>
-      <c r="K487" t="n">
-        <v>9</v>
-      </c>
-      <c r="L487" t="n">
-        <v>14</v>
-      </c>
-      <c r="M487" t="n">
-        <v>5</v>
-      </c>
-      <c r="N487" t="n">
-        <v>26</v>
-      </c>
-      <c r="O487" t="n">
-        <v>20</v>
-      </c>
-      <c r="P487" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q487" t="n">
-        <v>14</v>
-      </c>
-      <c r="R487" t="n">
-        <v>21</v>
-      </c>
-      <c r="S487" t="n">
-        <v>16</v>
-      </c>
-      <c r="T487" t="n">
-        <v>2</v>
-      </c>
-      <c r="U487" t="inlineStr">
-        <is>
-          <t>2486536</t>
-        </is>
-      </c>
-      <c r="V487" t="n">
-        <v>89</v>
-      </c>
-      <c r="W487" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="X487" t="n">
-        <v>0.9737098344693281</v>
-      </c>
-      <c r="Y487" t="n">
-        <v>77.16</v>
-      </c>
-      <c r="Z487" t="n">
-        <v>103.6806635562468</v>
-      </c>
-      <c r="AA487" t="n">
-        <v>1.082198443579766</v>
-      </c>
-      <c r="AB487" t="n">
-        <v>113.7525562372188</v>
-      </c>
-      <c r="AC487" t="n">
-        <v>0.1612903225806452</v>
-      </c>
-      <c r="AD487" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="AE487" t="n">
-        <v>0.5081967213114754</v>
-      </c>
-      <c r="AF487" t="n">
-        <v>-10.07189268097203</v>
-      </c>
-      <c r="AG487" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AH487" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AI487" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B488" t="n">
-        <v>31</v>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="E488" t="n">
-        <v>200</v>
-      </c>
-      <c r="F488" t="n">
-        <v>64</v>
-      </c>
-      <c r="G488" t="n">
-        <v>14</v>
-      </c>
-      <c r="H488" t="n">
-        <v>26</v>
-      </c>
-      <c r="I488" t="n">
-        <v>7</v>
-      </c>
-      <c r="J488" t="n">
-        <v>35</v>
-      </c>
-      <c r="K488" t="n">
-        <v>15</v>
-      </c>
-      <c r="L488" t="n">
-        <v>25</v>
-      </c>
-      <c r="M488" t="n">
-        <v>10</v>
-      </c>
-      <c r="N488" t="n">
-        <v>26</v>
-      </c>
-      <c r="O488" t="n">
-        <v>17</v>
-      </c>
-      <c r="P488" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q488" t="n">
-        <v>17</v>
-      </c>
-      <c r="R488" t="n">
-        <v>20</v>
-      </c>
-      <c r="S488" t="n">
-        <v>21</v>
-      </c>
-      <c r="T488" t="n">
-        <v>4</v>
-      </c>
-      <c r="U488" t="inlineStr">
-        <is>
-          <t>2486533</t>
-        </is>
-      </c>
-      <c r="V488" t="n">
-        <v>78</v>
-      </c>
-      <c r="W488" t="n">
-        <v>89</v>
-      </c>
-      <c r="X488" t="n">
-        <v>0.7191011235955056</v>
-      </c>
-      <c r="Y488" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z488" t="n">
-        <v>81.01265822784811</v>
-      </c>
-      <c r="AA488" t="n">
-        <v>0.8537653239929948</v>
-      </c>
-      <c r="AB488" t="n">
-        <v>98.28629032258064</v>
-      </c>
-      <c r="AC488" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="AD488" t="n">
-        <v>0.6842105263157895</v>
-      </c>
-      <c r="AE488" t="n">
-        <v>0.4675324675324675</v>
-      </c>
-      <c r="AF488" t="n">
-        <v>-17.27363209473253</v>
-      </c>
-      <c r="AG488" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AH488" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AI488" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B489" t="n">
-        <v>31</v>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="E489" t="n">
-        <v>225</v>
-      </c>
-      <c r="F489" t="n">
-        <v>99</v>
-      </c>
-      <c r="G489" t="n">
-        <v>18</v>
-      </c>
-      <c r="H489" t="n">
-        <v>36</v>
-      </c>
-      <c r="I489" t="n">
-        <v>16</v>
-      </c>
-      <c r="J489" t="n">
-        <v>35</v>
-      </c>
-      <c r="K489" t="n">
-        <v>15</v>
-      </c>
-      <c r="L489" t="n">
-        <v>20</v>
-      </c>
-      <c r="M489" t="n">
-        <v>3</v>
-      </c>
-      <c r="N489" t="n">
-        <v>24</v>
-      </c>
-      <c r="O489" t="n">
-        <v>15</v>
-      </c>
-      <c r="P489" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q489" t="n">
-        <v>12</v>
-      </c>
-      <c r="R489" t="n">
-        <v>21</v>
-      </c>
-      <c r="S489" t="n">
-        <v>19</v>
-      </c>
-      <c r="T489" t="n">
-        <v>1</v>
-      </c>
-      <c r="U489" t="inlineStr">
-        <is>
-          <t>2486530</t>
-        </is>
-      </c>
-      <c r="V489" t="n">
-        <v>96</v>
-      </c>
-      <c r="W489" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="X489" t="n">
-        <v>1.07843137254902</v>
-      </c>
-      <c r="Y489" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z489" t="n">
-        <v>111.4864864864865</v>
-      </c>
-      <c r="AA489" t="n">
-        <v>0.9696969696969697</v>
-      </c>
-      <c r="AB489" t="n">
-        <v>109.0909090909091</v>
-      </c>
-      <c r="AC489" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="AD489" t="n">
-        <v>0.6857142857142857</v>
-      </c>
-      <c r="AE489" t="n">
-        <v>0.4029850746268657</v>
-      </c>
-      <c r="AF489" t="n">
-        <v>2.395577395577391</v>
-      </c>
-      <c r="AG489" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AH489" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AI489" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B490" t="n">
-        <v>31</v>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="E490" t="n">
-        <v>200</v>
-      </c>
-      <c r="F490" t="n">
-        <v>72</v>
-      </c>
-      <c r="G490" t="n">
-        <v>15</v>
-      </c>
-      <c r="H490" t="n">
-        <v>35</v>
-      </c>
-      <c r="I490" t="n">
-        <v>10</v>
-      </c>
-      <c r="J490" t="n">
-        <v>27</v>
-      </c>
-      <c r="K490" t="n">
-        <v>12</v>
-      </c>
-      <c r="L490" t="n">
-        <v>17</v>
-      </c>
-      <c r="M490" t="n">
-        <v>8</v>
-      </c>
-      <c r="N490" t="n">
-        <v>20</v>
-      </c>
-      <c r="O490" t="n">
-        <v>13</v>
-      </c>
-      <c r="P490" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q490" t="n">
-        <v>9</v>
-      </c>
-      <c r="R490" t="n">
-        <v>27</v>
-      </c>
-      <c r="S490" t="n">
-        <v>22</v>
-      </c>
-      <c r="T490" t="n">
-        <v>2</v>
-      </c>
-      <c r="U490" t="inlineStr">
-        <is>
-          <t>2486531</t>
-        </is>
-      </c>
-      <c r="V490" t="n">
-        <v>81</v>
-      </c>
-      <c r="W490" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="X490" t="n">
-        <v>0.9174311926605504</v>
-      </c>
-      <c r="Y490" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="Z490" t="n">
-        <v>102.1566401816118</v>
-      </c>
-      <c r="AA490" t="n">
-        <v>0.9839650145772596</v>
-      </c>
-      <c r="AB490" t="n">
-        <v>113.5726303982053</v>
-      </c>
-      <c r="AC490" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="AD490" t="n">
-        <v>0.6451612903225806</v>
-      </c>
-      <c r="AE490" t="n">
-        <v>0.4307692307692308</v>
-      </c>
-      <c r="AF490" t="n">
-        <v>-11.41599021659347</v>
-      </c>
-      <c r="AG490" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AH490" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI490" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B491" t="n">
-        <v>31</v>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="E491" t="n">
-        <v>200</v>
-      </c>
-      <c r="F491" t="n">
-        <v>73</v>
-      </c>
-      <c r="G491" t="n">
-        <v>26</v>
-      </c>
-      <c r="H491" t="n">
-        <v>42</v>
-      </c>
-      <c r="I491" t="n">
-        <v>4</v>
-      </c>
-      <c r="J491" t="n">
-        <v>18</v>
-      </c>
-      <c r="K491" t="n">
-        <v>9</v>
-      </c>
-      <c r="L491" t="n">
-        <v>14</v>
-      </c>
-      <c r="M491" t="n">
-        <v>8</v>
-      </c>
-      <c r="N491" t="n">
-        <v>27</v>
-      </c>
-      <c r="O491" t="n">
-        <v>23</v>
-      </c>
-      <c r="P491" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q491" t="n">
-        <v>8</v>
-      </c>
-      <c r="R491" t="n">
-        <v>18</v>
-      </c>
-      <c r="S491" t="n">
-        <v>18</v>
-      </c>
-      <c r="T491" t="n">
-        <v>6</v>
-      </c>
-      <c r="U491" t="inlineStr">
-        <is>
-          <t>2486529</t>
-        </is>
-      </c>
-      <c r="V491" t="n">
-        <v>63</v>
-      </c>
-      <c r="W491" t="n">
-        <v>74.16</v>
-      </c>
-      <c r="X491" t="n">
-        <v>0.9843581445523194</v>
-      </c>
-      <c r="Y491" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="Z491" t="n">
-        <v>110.3385731559855</v>
-      </c>
-      <c r="AA491" t="n">
-        <v>0.7859281437125749</v>
-      </c>
-      <c r="AB491" t="n">
-        <v>89.79475484606614</v>
-      </c>
-      <c r="AC491" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="AD491" t="n">
-        <v>0.7297297297297297</v>
-      </c>
-      <c r="AE491" t="n">
-        <v>0.546875</v>
-      </c>
-      <c r="AF491" t="n">
-        <v>20.54381830991936</v>
-      </c>
-      <c r="AG491" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH491" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AI491" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B492" t="n">
-        <v>31</v>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="E492" t="n">
-        <v>200</v>
-      </c>
-      <c r="F492" t="n">
-        <v>81</v>
-      </c>
-      <c r="G492" t="n">
-        <v>12</v>
-      </c>
-      <c r="H492" t="n">
-        <v>31</v>
-      </c>
-      <c r="I492" t="n">
-        <v>12</v>
-      </c>
-      <c r="J492" t="n">
-        <v>31</v>
-      </c>
-      <c r="K492" t="n">
-        <v>21</v>
-      </c>
-      <c r="L492" t="n">
-        <v>28</v>
-      </c>
-      <c r="M492" t="n">
-        <v>11</v>
-      </c>
-      <c r="N492" t="n">
-        <v>26</v>
-      </c>
-      <c r="O492" t="n">
-        <v>21</v>
-      </c>
-      <c r="P492" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q492" t="n">
-        <v>8</v>
-      </c>
-      <c r="R492" t="n">
-        <v>22</v>
-      </c>
-      <c r="S492" t="n">
-        <v>27</v>
-      </c>
-      <c r="T492" t="n">
-        <v>3</v>
-      </c>
-      <c r="U492" t="inlineStr">
-        <is>
-          <t>2486531</t>
-        </is>
-      </c>
-      <c r="V492" t="n">
-        <v>72</v>
-      </c>
-      <c r="W492" t="n">
-        <v>82.31999999999999</v>
-      </c>
-      <c r="X492" t="n">
-        <v>0.9839650145772596</v>
-      </c>
-      <c r="Y492" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="Z492" t="n">
-        <v>113.5726303982053</v>
-      </c>
-      <c r="AA492" t="n">
-        <v>0.9174311926605504</v>
-      </c>
-      <c r="AB492" t="n">
-        <v>102.1566401816118</v>
-      </c>
-      <c r="AC492" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-      <c r="AD492" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="AE492" t="n">
-        <v>0.5692307692307692</v>
-      </c>
-      <c r="AF492" t="n">
-        <v>11.41599021659347</v>
-      </c>
-      <c r="AG492" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AH492" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI492" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B493" t="n">
-        <v>31</v>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="E493" t="n">
-        <v>200</v>
-      </c>
-      <c r="F493" t="n">
-        <v>73</v>
-      </c>
-      <c r="G493" t="n">
-        <v>14</v>
-      </c>
-      <c r="H493" t="n">
-        <v>26</v>
-      </c>
-      <c r="I493" t="n">
-        <v>10</v>
-      </c>
-      <c r="J493" t="n">
-        <v>34</v>
-      </c>
-      <c r="K493" t="n">
-        <v>15</v>
-      </c>
-      <c r="L493" t="n">
-        <v>20</v>
-      </c>
-      <c r="M493" t="n">
-        <v>11</v>
-      </c>
-      <c r="N493" t="n">
-        <v>26</v>
-      </c>
-      <c r="O493" t="n">
-        <v>10</v>
-      </c>
-      <c r="P493" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q493" t="n">
-        <v>15</v>
-      </c>
-      <c r="R493" t="n">
-        <v>17</v>
-      </c>
-      <c r="S493" t="n">
-        <v>21</v>
-      </c>
-      <c r="T493" t="n">
-        <v>0</v>
-      </c>
-      <c r="U493" t="inlineStr">
-        <is>
-          <t>2486532</t>
-        </is>
-      </c>
-      <c r="V493" t="n">
-        <v>86</v>
-      </c>
-      <c r="W493" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="X493" t="n">
-        <v>0.8711217183770883</v>
-      </c>
-      <c r="Y493" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="Z493" t="n">
-        <v>100.2747252747253</v>
-      </c>
-      <c r="AA493" t="n">
-        <v>1.072854291417166</v>
-      </c>
-      <c r="AB493" t="n">
-        <v>117.550574084199</v>
-      </c>
-      <c r="AC493" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="AD493" t="n">
-        <v>0.7878787878787878</v>
-      </c>
-      <c r="AE493" t="n">
-        <v>0.5362318840579711</v>
-      </c>
-      <c r="AF493" t="n">
-        <v>-17.27584880947374</v>
-      </c>
-      <c r="AG493" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AH493" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI493" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B494" t="n">
-        <v>31</v>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="E494" t="n">
-        <v>225</v>
-      </c>
-      <c r="F494" t="n">
-        <v>96</v>
-      </c>
-      <c r="G494" t="n">
-        <v>19</v>
-      </c>
-      <c r="H494" t="n">
-        <v>35</v>
-      </c>
-      <c r="I494" t="n">
-        <v>13</v>
-      </c>
-      <c r="J494" t="n">
-        <v>37</v>
-      </c>
-      <c r="K494" t="n">
-        <v>19</v>
-      </c>
-      <c r="L494" t="n">
-        <v>25</v>
-      </c>
-      <c r="M494" t="n">
-        <v>11</v>
-      </c>
-      <c r="N494" t="n">
-        <v>29</v>
-      </c>
-      <c r="O494" t="n">
-        <v>13</v>
-      </c>
-      <c r="P494" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q494" t="n">
-        <v>16</v>
-      </c>
-      <c r="R494" t="n">
-        <v>19</v>
-      </c>
-      <c r="S494" t="n">
-        <v>21</v>
-      </c>
-      <c r="T494" t="n">
-        <v>2</v>
-      </c>
-      <c r="U494" t="inlineStr">
-        <is>
-          <t>2486530</t>
-        </is>
-      </c>
-      <c r="V494" t="n">
-        <v>99</v>
-      </c>
-      <c r="W494" t="n">
-        <v>99</v>
-      </c>
-      <c r="X494" t="n">
-        <v>0.9696969696969697</v>
-      </c>
-      <c r="Y494" t="n">
-        <v>88</v>
-      </c>
-      <c r="Z494" t="n">
-        <v>109.0909090909091</v>
-      </c>
-      <c r="AA494" t="n">
-        <v>1.07843137254902</v>
-      </c>
-      <c r="AB494" t="n">
-        <v>111.4864864864865</v>
-      </c>
-      <c r="AC494" t="n">
-        <v>0.3142857142857143</v>
-      </c>
-      <c r="AD494" t="n">
-        <v>0.90625</v>
-      </c>
-      <c r="AE494" t="n">
-        <v>0.5970149253731343</v>
-      </c>
-      <c r="AF494" t="n">
-        <v>-2.395577395577391</v>
-      </c>
-      <c r="AG494" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AH494" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AI494" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B495" t="n">
-        <v>31</v>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="E495" t="n">
-        <v>200</v>
-      </c>
-      <c r="F495" t="n">
-        <v>86</v>
-      </c>
-      <c r="G495" t="n">
-        <v>18</v>
-      </c>
-      <c r="H495" t="n">
-        <v>33</v>
-      </c>
-      <c r="I495" t="n">
-        <v>13</v>
-      </c>
-      <c r="J495" t="n">
-        <v>33</v>
-      </c>
-      <c r="K495" t="n">
-        <v>11</v>
-      </c>
-      <c r="L495" t="n">
-        <v>14</v>
-      </c>
-      <c r="M495" t="n">
-        <v>7</v>
-      </c>
-      <c r="N495" t="n">
-        <v>25</v>
-      </c>
-      <c r="O495" t="n">
-        <v>20</v>
-      </c>
-      <c r="P495" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q495" t="n">
-        <v>8</v>
-      </c>
-      <c r="R495" t="n">
-        <v>21</v>
-      </c>
-      <c r="S495" t="n">
-        <v>17</v>
-      </c>
-      <c r="T495" t="n">
-        <v>2</v>
-      </c>
-      <c r="U495" t="inlineStr">
-        <is>
-          <t>2486532</t>
-        </is>
-      </c>
-      <c r="V495" t="n">
-        <v>73</v>
-      </c>
-      <c r="W495" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="X495" t="n">
-        <v>1.072854291417166</v>
-      </c>
-      <c r="Y495" t="n">
-        <v>73.16</v>
-      </c>
-      <c r="Z495" t="n">
-        <v>117.550574084199</v>
-      </c>
-      <c r="AA495" t="n">
-        <v>0.8711217183770883</v>
-      </c>
-      <c r="AB495" t="n">
-        <v>100.2747252747253</v>
-      </c>
-      <c r="AC495" t="n">
-        <v>0.2121212121212121</v>
-      </c>
-      <c r="AD495" t="n">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="AE495" t="n">
-        <v>0.463768115942029</v>
-      </c>
-      <c r="AF495" t="n">
-        <v>17.27584880947374</v>
-      </c>
-      <c r="AG495" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AH495" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AI495" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B496" t="n">
-        <v>31</v>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E496" t="n">
-        <v>200</v>
-      </c>
-      <c r="F496" t="n">
-        <v>74</v>
-      </c>
-      <c r="G496" t="n">
-        <v>24</v>
-      </c>
-      <c r="H496" t="n">
-        <v>43</v>
-      </c>
-      <c r="I496" t="n">
-        <v>5</v>
-      </c>
-      <c r="J496" t="n">
-        <v>18</v>
-      </c>
-      <c r="K496" t="n">
-        <v>11</v>
-      </c>
-      <c r="L496" t="n">
-        <v>16</v>
-      </c>
-      <c r="M496" t="n">
-        <v>6</v>
-      </c>
-      <c r="N496" t="n">
-        <v>21</v>
-      </c>
-      <c r="O496" t="n">
-        <v>16</v>
-      </c>
-      <c r="P496" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q496" t="n">
-        <v>12</v>
-      </c>
-      <c r="R496" t="n">
-        <v>19</v>
-      </c>
-      <c r="S496" t="n">
-        <v>18</v>
-      </c>
-      <c r="T496" t="n">
-        <v>4</v>
-      </c>
-      <c r="U496" t="inlineStr">
-        <is>
-          <t>2486535</t>
-        </is>
-      </c>
-      <c r="V496" t="n">
-        <v>89</v>
-      </c>
-      <c r="W496" t="n">
-        <v>80.03999999999999</v>
-      </c>
-      <c r="X496" t="n">
-        <v>0.9245377311344328</v>
-      </c>
-      <c r="Y496" t="n">
-        <v>74.03999999999999</v>
-      </c>
-      <c r="Z496" t="n">
-        <v>99.94597514856835</v>
-      </c>
-      <c r="AA496" t="n">
-        <v>1.045091592296853</v>
-      </c>
-      <c r="AB496" t="n">
-        <v>126.8529076396807</v>
-      </c>
-      <c r="AC496" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AD496" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="AE496" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="AF496" t="n">
-        <v>-26.90693249111239</v>
-      </c>
-      <c r="AG496" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AH496" t="inlineStr">
-        <is>
-          <t>ALIMERKA OVIEDO BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI496" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B497" t="n">
-        <v>31</v>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E497" t="n">
-        <v>200</v>
-      </c>
-      <c r="F497" t="n">
-        <v>93</v>
-      </c>
-      <c r="G497" t="n">
-        <v>13</v>
-      </c>
-      <c r="H497" t="n">
-        <v>35</v>
-      </c>
-      <c r="I497" t="n">
-        <v>13</v>
-      </c>
-      <c r="J497" t="n">
-        <v>25</v>
-      </c>
-      <c r="K497" t="n">
-        <v>28</v>
-      </c>
-      <c r="L497" t="n">
-        <v>31</v>
-      </c>
-      <c r="M497" t="n">
-        <v>7</v>
-      </c>
-      <c r="N497" t="n">
-        <v>18</v>
-      </c>
-      <c r="O497" t="n">
-        <v>21</v>
-      </c>
-      <c r="P497" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q497" t="n">
-        <v>12</v>
-      </c>
-      <c r="R497" t="n">
-        <v>25</v>
-      </c>
-      <c r="S497" t="n">
-        <v>24</v>
-      </c>
-      <c r="T497" t="n">
-        <v>3</v>
-      </c>
-      <c r="U497" t="inlineStr">
-        <is>
-          <t>2486534</t>
-        </is>
-      </c>
-      <c r="V497" t="n">
-        <v>90</v>
-      </c>
-      <c r="W497" t="n">
-        <v>85.64</v>
-      </c>
-      <c r="X497" t="n">
-        <v>1.085941148995796</v>
-      </c>
-      <c r="Y497" t="n">
-        <v>78.64</v>
-      </c>
-      <c r="Z497" t="n">
-        <v>118.2604272634791</v>
-      </c>
-      <c r="AA497" t="n">
-        <v>1.041184636742249</v>
-      </c>
-      <c r="AB497" t="n">
-        <v>122.5490196078431</v>
-      </c>
-      <c r="AC497" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="AD497" t="n">
-        <v>0.5806451612903226</v>
-      </c>
-      <c r="AE497" t="n">
-        <v>0.4032258064516129</v>
-      </c>
-      <c r="AF497" t="n">
-        <v>-4.288592344363991</v>
-      </c>
-      <c r="AG497" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AH497" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI497" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B498" t="n">
-        <v>32</v>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="E498" t="n">
-        <v>200</v>
-      </c>
-      <c r="F498" t="n">
-        <v>86</v>
-      </c>
-      <c r="G498" t="n">
-        <v>21</v>
-      </c>
-      <c r="H498" t="n">
-        <v>40</v>
-      </c>
-      <c r="I498" t="n">
-        <v>9</v>
-      </c>
-      <c r="J498" t="n">
-        <v>28</v>
-      </c>
-      <c r="K498" t="n">
-        <v>17</v>
-      </c>
-      <c r="L498" t="n">
-        <v>26</v>
-      </c>
-      <c r="M498" t="n">
-        <v>11</v>
-      </c>
-      <c r="N498" t="n">
-        <v>18</v>
-      </c>
-      <c r="O498" t="n">
-        <v>18</v>
-      </c>
-      <c r="P498" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q498" t="n">
-        <v>4</v>
-      </c>
-      <c r="R498" t="n">
-        <v>19</v>
-      </c>
-      <c r="S498" t="n">
-        <v>26</v>
-      </c>
-      <c r="T498" t="n">
-        <v>2</v>
-      </c>
-      <c r="U498" t="inlineStr">
-        <is>
-          <t>2486543</t>
-        </is>
-      </c>
-      <c r="V498" t="n">
-        <v>89</v>
-      </c>
-      <c r="W498" t="n">
-        <v>83.44</v>
-      </c>
-      <c r="X498" t="n">
-        <v>1.030680728667306</v>
-      </c>
-      <c r="Y498" t="n">
-        <v>72.44</v>
-      </c>
-      <c r="Z498" t="n">
-        <v>118.7189398122584</v>
-      </c>
-      <c r="AA498" t="n">
-        <v>1.155244029075805</v>
-      </c>
-      <c r="AB498" t="n">
-        <v>123.5424764019989</v>
-      </c>
-      <c r="AC498" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="AD498" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="AE498" t="n">
-        <v>0.5087719298245614</v>
-      </c>
-      <c r="AF498" t="n">
-        <v>-4.823536589740471</v>
-      </c>
-      <c r="AG498" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AH498" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI498" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B499" t="n">
-        <v>32</v>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="E499" t="n">
-        <v>200</v>
-      </c>
-      <c r="F499" t="n">
-        <v>70</v>
-      </c>
-      <c r="G499" t="n">
-        <v>18</v>
-      </c>
-      <c r="H499" t="n">
-        <v>34</v>
-      </c>
-      <c r="I499" t="n">
-        <v>5</v>
-      </c>
-      <c r="J499" t="n">
-        <v>23</v>
-      </c>
-      <c r="K499" t="n">
-        <v>19</v>
-      </c>
-      <c r="L499" t="n">
-        <v>30</v>
-      </c>
-      <c r="M499" t="n">
-        <v>10</v>
-      </c>
-      <c r="N499" t="n">
-        <v>23</v>
-      </c>
-      <c r="O499" t="n">
-        <v>11</v>
-      </c>
-      <c r="P499" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q499" t="n">
-        <v>9</v>
-      </c>
-      <c r="R499" t="n">
-        <v>27</v>
-      </c>
-      <c r="S499" t="n">
-        <v>28</v>
-      </c>
-      <c r="T499" t="n">
-        <v>2</v>
-      </c>
-      <c r="U499" t="inlineStr">
-        <is>
-          <t>2486537</t>
-        </is>
-      </c>
-      <c r="V499" t="n">
-        <v>73</v>
-      </c>
-      <c r="W499" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="X499" t="n">
-        <v>0.8838383838383838</v>
-      </c>
-      <c r="Y499" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="Z499" t="n">
-        <v>101.1560693641619</v>
-      </c>
-      <c r="AA499" t="n">
-        <v>0.9554973821989529</v>
-      </c>
-      <c r="AB499" t="n">
-        <v>106.7251461988304</v>
-      </c>
-      <c r="AC499" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="AD499" t="n">
-        <v>0.7419354838709677</v>
-      </c>
-      <c r="AE499" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF499" t="n">
-        <v>-5.56907683466855</v>
-      </c>
-      <c r="AG499" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH499" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI499" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B500" t="n">
-        <v>32</v>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="E500" t="n">
-        <v>200</v>
-      </c>
-      <c r="F500" t="n">
-        <v>70</v>
-      </c>
-      <c r="G500" t="n">
-        <v>13</v>
-      </c>
-      <c r="H500" t="n">
-        <v>34</v>
-      </c>
-      <c r="I500" t="n">
-        <v>11</v>
-      </c>
-      <c r="J500" t="n">
-        <v>30</v>
-      </c>
-      <c r="K500" t="n">
-        <v>11</v>
-      </c>
-      <c r="L500" t="n">
-        <v>21</v>
-      </c>
-      <c r="M500" t="n">
-        <v>11</v>
-      </c>
-      <c r="N500" t="n">
-        <v>25</v>
-      </c>
-      <c r="O500" t="n">
-        <v>15</v>
-      </c>
-      <c r="P500" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q500" t="n">
-        <v>10</v>
-      </c>
-      <c r="R500" t="n">
-        <v>16</v>
-      </c>
-      <c r="S500" t="n">
-        <v>20</v>
-      </c>
-      <c r="T500" t="n">
-        <v>1</v>
-      </c>
-      <c r="U500" t="inlineStr">
-        <is>
-          <t>2486542</t>
-        </is>
-      </c>
-      <c r="V500" t="n">
-        <v>92</v>
-      </c>
-      <c r="W500" t="n">
-        <v>83.24000000000001</v>
-      </c>
-      <c r="X500" t="n">
-        <v>0.8409418548774626</v>
-      </c>
-      <c r="Y500" t="n">
-        <v>72.24000000000001</v>
-      </c>
-      <c r="Z500" t="n">
-        <v>96.89922480620154</v>
-      </c>
-      <c r="AA500" t="n">
-        <v>1.108968177434908</v>
-      </c>
-      <c r="AB500" t="n">
-        <v>127.8488048916064</v>
-      </c>
-      <c r="AC500" t="n">
-        <v>0.2682926829268293</v>
-      </c>
-      <c r="AD500" t="n">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="AE500" t="n">
-        <v>0.4675324675324675</v>
-      </c>
-      <c r="AF500" t="n">
-        <v>-30.94958008540489</v>
-      </c>
-      <c r="AG500" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AH500" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AI500" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B501" t="n">
-        <v>32</v>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="E501" t="n">
-        <v>200</v>
-      </c>
-      <c r="F501" t="n">
-        <v>91</v>
-      </c>
-      <c r="G501" t="n">
-        <v>24</v>
-      </c>
-      <c r="H501" t="n">
-        <v>37</v>
-      </c>
-      <c r="I501" t="n">
-        <v>10</v>
-      </c>
-      <c r="J501" t="n">
-        <v>26</v>
-      </c>
-      <c r="K501" t="n">
-        <v>13</v>
-      </c>
-      <c r="L501" t="n">
-        <v>19</v>
-      </c>
-      <c r="M501" t="n">
-        <v>8</v>
-      </c>
-      <c r="N501" t="n">
-        <v>33</v>
-      </c>
-      <c r="O501" t="n">
-        <v>19</v>
-      </c>
-      <c r="P501" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q501" t="n">
-        <v>17</v>
-      </c>
-      <c r="R501" t="n">
-        <v>15</v>
-      </c>
-      <c r="S501" t="n">
-        <v>19</v>
-      </c>
-      <c r="T501" t="n">
-        <v>1</v>
-      </c>
-      <c r="U501" t="inlineStr">
-        <is>
-          <t>2486541</t>
-        </is>
-      </c>
-      <c r="V501" t="n">
-        <v>82</v>
-      </c>
-      <c r="W501" t="n">
-        <v>88.36</v>
-      </c>
-      <c r="X501" t="n">
-        <v>1.02987777274785</v>
-      </c>
-      <c r="Y501" t="n">
-        <v>80.36</v>
-      </c>
-      <c r="Z501" t="n">
-        <v>113.2404181184669</v>
-      </c>
-      <c r="AA501" t="n">
-        <v>0.9860509860509861</v>
-      </c>
-      <c r="AB501" t="n">
-        <v>104.9129989764586</v>
-      </c>
-      <c r="AC501" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="AD501" t="n">
-        <v>0.868421052631579</v>
-      </c>
-      <c r="AE501" t="n">
-        <v>0.6307692307692307</v>
-      </c>
-      <c r="AF501" t="n">
-        <v>8.327419142008353</v>
-      </c>
-      <c r="AG501" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH501" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AI501" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B502" t="n">
-        <v>32</v>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="E502" t="n">
-        <v>200</v>
-      </c>
-      <c r="F502" t="n">
-        <v>89</v>
-      </c>
-      <c r="G502" t="n">
-        <v>18</v>
-      </c>
-      <c r="H502" t="n">
-        <v>27</v>
-      </c>
-      <c r="I502" t="n">
-        <v>13</v>
-      </c>
-      <c r="J502" t="n">
-        <v>29</v>
-      </c>
-      <c r="K502" t="n">
-        <v>14</v>
-      </c>
-      <c r="L502" t="n">
-        <v>16</v>
-      </c>
-      <c r="M502" t="n">
-        <v>5</v>
-      </c>
-      <c r="N502" t="n">
-        <v>23</v>
-      </c>
-      <c r="O502" t="n">
-        <v>12</v>
-      </c>
-      <c r="P502" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q502" t="n">
-        <v>14</v>
-      </c>
-      <c r="R502" t="n">
-        <v>27</v>
-      </c>
-      <c r="S502" t="n">
-        <v>19</v>
-      </c>
-      <c r="T502" t="n">
-        <v>0</v>
-      </c>
-      <c r="U502" t="inlineStr">
-        <is>
-          <t>2486543</t>
-        </is>
-      </c>
-      <c r="V502" t="n">
-        <v>86</v>
-      </c>
-      <c r="W502" t="n">
-        <v>77.03999999999999</v>
-      </c>
-      <c r="X502" t="n">
-        <v>1.155244029075805</v>
-      </c>
-      <c r="Y502" t="n">
-        <v>72.03999999999999</v>
-      </c>
-      <c r="Z502" t="n">
-        <v>123.5424764019989</v>
-      </c>
-      <c r="AA502" t="n">
-        <v>1.030680728667306</v>
-      </c>
-      <c r="AB502" t="n">
-        <v>118.7189398122584</v>
-      </c>
-      <c r="AC502" t="n">
-        <v>0.2173913043478261</v>
-      </c>
-      <c r="AD502" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="AE502" t="n">
-        <v>0.4912280701754386</v>
-      </c>
-      <c r="AF502" t="n">
-        <v>4.823536589740471</v>
-      </c>
-      <c r="AG502" t="inlineStr">
-        <is>
-          <t>GRUPO ALEGA CANTABRIA</t>
-        </is>
-      </c>
-      <c r="AH502" t="inlineStr">
-        <is>
-          <t>CAJA RURAL CB ZAMORA</t>
-        </is>
-      </c>
-      <c r="AI502" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B503" t="n">
-        <v>32</v>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="E503" t="n">
-        <v>200</v>
-      </c>
-      <c r="F503" t="n">
-        <v>82</v>
-      </c>
-      <c r="G503" t="n">
-        <v>18</v>
-      </c>
-      <c r="H503" t="n">
-        <v>40</v>
-      </c>
-      <c r="I503" t="n">
-        <v>12</v>
-      </c>
-      <c r="J503" t="n">
-        <v>29</v>
-      </c>
-      <c r="K503" t="n">
-        <v>10</v>
-      </c>
-      <c r="L503" t="n">
-        <v>14</v>
-      </c>
-      <c r="M503" t="n">
-        <v>5</v>
-      </c>
-      <c r="N503" t="n">
-        <v>19</v>
-      </c>
-      <c r="O503" t="n">
-        <v>18</v>
-      </c>
-      <c r="P503" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q503" t="n">
-        <v>8</v>
-      </c>
-      <c r="R503" t="n">
-        <v>19</v>
-      </c>
-      <c r="S503" t="n">
-        <v>15</v>
-      </c>
-      <c r="T503" t="n">
-        <v>4</v>
-      </c>
-      <c r="U503" t="inlineStr">
-        <is>
-          <t>2486541</t>
-        </is>
-      </c>
-      <c r="V503" t="n">
-        <v>91</v>
-      </c>
-      <c r="W503" t="n">
-        <v>83.16</v>
-      </c>
-      <c r="X503" t="n">
-        <v>0.9860509860509861</v>
-      </c>
-      <c r="Y503" t="n">
-        <v>78.16</v>
-      </c>
-      <c r="Z503" t="n">
-        <v>104.9129989764586</v>
-      </c>
-      <c r="AA503" t="n">
-        <v>1.02987777274785</v>
-      </c>
-      <c r="AB503" t="n">
-        <v>113.2404181184669</v>
-      </c>
-      <c r="AC503" t="n">
-        <v>0.131578947368421</v>
-      </c>
-      <c r="AD503" t="n">
-        <v>0.7037037037037037</v>
-      </c>
-      <c r="AE503" t="n">
-        <v>0.3692307692307693</v>
-      </c>
-      <c r="AF503" t="n">
-        <v>-8.327419142008353</v>
-      </c>
-      <c r="AG503" t="inlineStr">
-        <is>
-          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
-        </is>
-      </c>
-      <c r="AH503" t="inlineStr">
-        <is>
-          <t>FLEXICAR FUENLABRADA</t>
-        </is>
-      </c>
-      <c r="AI503" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>32</v>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="E504" t="n">
-        <v>200</v>
-      </c>
-      <c r="F504" t="n">
-        <v>96</v>
-      </c>
-      <c r="G504" t="n">
-        <v>23</v>
-      </c>
-      <c r="H504" t="n">
-        <v>33</v>
-      </c>
-      <c r="I504" t="n">
-        <v>10</v>
-      </c>
-      <c r="J504" t="n">
-        <v>23</v>
-      </c>
-      <c r="K504" t="n">
-        <v>20</v>
-      </c>
-      <c r="L504" t="n">
-        <v>32</v>
-      </c>
-      <c r="M504" t="n">
-        <v>6</v>
-      </c>
-      <c r="N504" t="n">
-        <v>25</v>
-      </c>
-      <c r="O504" t="n">
-        <v>21</v>
-      </c>
-      <c r="P504" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q504" t="n">
-        <v>16</v>
-      </c>
-      <c r="R504" t="n">
-        <v>27</v>
-      </c>
-      <c r="S504" t="n">
-        <v>29</v>
-      </c>
-      <c r="T504" t="n">
-        <v>3</v>
-      </c>
-      <c r="U504" t="inlineStr">
-        <is>
-          <t>2486544</t>
-        </is>
-      </c>
-      <c r="V504" t="n">
-        <v>81</v>
-      </c>
-      <c r="W504" t="n">
-        <v>86.08</v>
-      </c>
-      <c r="X504" t="n">
-        <v>1.115241635687732</v>
-      </c>
-      <c r="Y504" t="n">
-        <v>80.08</v>
-      </c>
-      <c r="Z504" t="n">
-        <v>119.8801198801199</v>
-      </c>
-      <c r="AA504" t="n">
-        <v>0.8587786259541985</v>
-      </c>
-      <c r="AB504" t="n">
-        <v>99.60649286768323</v>
-      </c>
-      <c r="AC504" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="AD504" t="n">
-        <v>0.6578947368421053</v>
-      </c>
-      <c r="AE504" t="n">
-        <v>0.4769230769230769</v>
-      </c>
-      <c r="AF504" t="n">
-        <v>20.27362701243665</v>
-      </c>
-      <c r="AG504" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AH504" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI504" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B505" t="n">
-        <v>32</v>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E505" t="n">
-        <v>200</v>
-      </c>
-      <c r="F505" t="n">
-        <v>73</v>
-      </c>
-      <c r="G505" t="n">
-        <v>12</v>
-      </c>
-      <c r="H505" t="n">
-        <v>27</v>
-      </c>
-      <c r="I505" t="n">
-        <v>7</v>
-      </c>
-      <c r="J505" t="n">
-        <v>26</v>
-      </c>
-      <c r="K505" t="n">
-        <v>28</v>
-      </c>
-      <c r="L505" t="n">
-        <v>35</v>
-      </c>
-      <c r="M505" t="n">
-        <v>8</v>
-      </c>
-      <c r="N505" t="n">
-        <v>25</v>
-      </c>
-      <c r="O505" t="n">
-        <v>13</v>
-      </c>
-      <c r="P505" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q505" t="n">
-        <v>8</v>
-      </c>
-      <c r="R505" t="n">
-        <v>29</v>
-      </c>
-      <c r="S505" t="n">
-        <v>27</v>
-      </c>
-      <c r="T505" t="n">
-        <v>3</v>
-      </c>
-      <c r="U505" t="inlineStr">
-        <is>
-          <t>2486537</t>
-        </is>
-      </c>
-      <c r="V505" t="n">
-        <v>70</v>
-      </c>
-      <c r="W505" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="X505" t="n">
-        <v>0.9554973821989529</v>
-      </c>
-      <c r="Y505" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="Z505" t="n">
-        <v>106.7251461988304</v>
-      </c>
-      <c r="AA505" t="n">
-        <v>0.8838383838383838</v>
-      </c>
-      <c r="AB505" t="n">
-        <v>101.1560693641619</v>
-      </c>
-      <c r="AC505" t="n">
-        <v>0.2580645161290323</v>
-      </c>
-      <c r="AD505" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="AE505" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF505" t="n">
-        <v>5.56907683466855</v>
-      </c>
-      <c r="AG505" t="inlineStr">
-        <is>
-          <t>CLOUD.GAL OURENSE BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH505" t="inlineStr">
-        <is>
-          <t>HESTIA MENORCA</t>
-        </is>
-      </c>
-      <c r="AI505" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>32</v>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="E506" t="n">
-        <v>200</v>
-      </c>
-      <c r="F506" t="n">
-        <v>68</v>
-      </c>
-      <c r="G506" t="n">
-        <v>11</v>
-      </c>
-      <c r="H506" t="n">
-        <v>35</v>
-      </c>
-      <c r="I506" t="n">
-        <v>11</v>
-      </c>
-      <c r="J506" t="n">
-        <v>33</v>
-      </c>
-      <c r="K506" t="n">
-        <v>13</v>
-      </c>
-      <c r="L506" t="n">
-        <v>20</v>
-      </c>
-      <c r="M506" t="n">
-        <v>15</v>
-      </c>
-      <c r="N506" t="n">
-        <v>29</v>
-      </c>
-      <c r="O506" t="n">
-        <v>16</v>
-      </c>
-      <c r="P506" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q506" t="n">
-        <v>11</v>
-      </c>
-      <c r="R506" t="n">
-        <v>22</v>
-      </c>
-      <c r="S506" t="n">
-        <v>21</v>
-      </c>
-      <c r="T506" t="n">
-        <v>2</v>
-      </c>
-      <c r="U506" t="inlineStr">
-        <is>
-          <t>2486538</t>
-        </is>
-      </c>
-      <c r="V506" t="n">
-        <v>77</v>
-      </c>
-      <c r="W506" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="X506" t="n">
-        <v>0.7744874715261959</v>
-      </c>
-      <c r="Y506" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="Z506" t="n">
-        <v>93.40659340659342</v>
-      </c>
-      <c r="AA506" t="n">
-        <v>0.918854415274463</v>
-      </c>
-      <c r="AB506" t="n">
-        <v>104.3360433604336</v>
-      </c>
-      <c r="AC506" t="n">
-        <v>0.3488372093023256</v>
-      </c>
-      <c r="AD506" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="AE506" t="n">
-        <v>0.5365853658536586</v>
-      </c>
-      <c r="AF506" t="n">
-        <v>-10.92944995384019</v>
-      </c>
-      <c r="AG506" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH506" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI506" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B507" t="n">
-        <v>32</v>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="E507" t="n">
-        <v>200</v>
-      </c>
-      <c r="F507" t="n">
-        <v>81</v>
-      </c>
-      <c r="G507" t="n">
-        <v>20</v>
-      </c>
-      <c r="H507" t="n">
-        <v>35</v>
-      </c>
-      <c r="I507" t="n">
-        <v>10</v>
-      </c>
-      <c r="J507" t="n">
-        <v>25</v>
-      </c>
-      <c r="K507" t="n">
-        <v>11</v>
-      </c>
-      <c r="L507" t="n">
-        <v>17</v>
-      </c>
-      <c r="M507" t="n">
-        <v>4</v>
-      </c>
-      <c r="N507" t="n">
-        <v>24</v>
-      </c>
-      <c r="O507" t="n">
-        <v>29</v>
-      </c>
-      <c r="P507" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q507" t="n">
-        <v>11</v>
-      </c>
-      <c r="R507" t="n">
-        <v>17</v>
-      </c>
-      <c r="S507" t="n">
-        <v>20</v>
-      </c>
-      <c r="T507" t="n">
-        <v>3</v>
-      </c>
-      <c r="U507" t="inlineStr">
-        <is>
-          <t>2486539</t>
-        </is>
-      </c>
-      <c r="V507" t="n">
-        <v>92</v>
-      </c>
-      <c r="W507" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="X507" t="n">
-        <v>1.032110091743119</v>
-      </c>
-      <c r="Y507" t="n">
-        <v>74.48</v>
-      </c>
-      <c r="Z507" t="n">
-        <v>108.7540279269602</v>
-      </c>
-      <c r="AA507" t="n">
-        <v>0.9603340292275574</v>
-      </c>
-      <c r="AB507" t="n">
-        <v>113.8613861386139</v>
-      </c>
-      <c r="AC507" t="n">
-        <v>0.1379310344827586</v>
-      </c>
-      <c r="AD507" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="AE507" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="AF507" t="n">
-        <v>-5.107358211653619</v>
-      </c>
-      <c r="AG507" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH507" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI507" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B508" t="n">
-        <v>32</v>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="E508" t="n">
-        <v>200</v>
-      </c>
-      <c r="F508" t="n">
-        <v>92</v>
-      </c>
-      <c r="G508" t="n">
-        <v>24</v>
-      </c>
-      <c r="H508" t="n">
-        <v>51</v>
-      </c>
-      <c r="I508" t="n">
-        <v>10</v>
-      </c>
-      <c r="J508" t="n">
-        <v>27</v>
-      </c>
-      <c r="K508" t="n">
-        <v>14</v>
-      </c>
-      <c r="L508" t="n">
-        <v>20</v>
-      </c>
-      <c r="M508" t="n">
-        <v>15</v>
-      </c>
-      <c r="N508" t="n">
-        <v>25</v>
-      </c>
-      <c r="O508" t="n">
-        <v>22</v>
-      </c>
-      <c r="P508" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q508" t="n">
-        <v>9</v>
-      </c>
-      <c r="R508" t="n">
-        <v>20</v>
-      </c>
-      <c r="S508" t="n">
-        <v>17</v>
-      </c>
-      <c r="T508" t="n">
-        <v>1</v>
-      </c>
-      <c r="U508" t="inlineStr">
-        <is>
-          <t>2486539</t>
-        </is>
-      </c>
-      <c r="V508" t="n">
-        <v>81</v>
-      </c>
-      <c r="W508" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="X508" t="n">
-        <v>0.9603340292275574</v>
-      </c>
-      <c r="Y508" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="Z508" t="n">
-        <v>113.8613861386139</v>
-      </c>
-      <c r="AA508" t="n">
-        <v>1.032110091743119</v>
-      </c>
-      <c r="AB508" t="n">
-        <v>108.7540279269602</v>
-      </c>
-      <c r="AC508" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="AD508" t="n">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="AE508" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="AF508" t="n">
-        <v>5.107358211653619</v>
-      </c>
-      <c r="AG508" t="inlineStr">
-        <is>
-          <t>INVEREADY GIPUZKOA</t>
-        </is>
-      </c>
-      <c r="AH508" t="inlineStr">
-        <is>
-          <t>LEYMA CORUÑA</t>
-        </is>
-      </c>
-      <c r="AI508" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B509" t="n">
-        <v>32</v>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="E509" t="n">
-        <v>200</v>
-      </c>
-      <c r="F509" t="n">
-        <v>81</v>
-      </c>
-      <c r="G509" t="n">
-        <v>13</v>
-      </c>
-      <c r="H509" t="n">
-        <v>30</v>
-      </c>
-      <c r="I509" t="n">
-        <v>11</v>
-      </c>
-      <c r="J509" t="n">
-        <v>37</v>
-      </c>
-      <c r="K509" t="n">
-        <v>22</v>
-      </c>
-      <c r="L509" t="n">
-        <v>28</v>
-      </c>
-      <c r="M509" t="n">
-        <v>13</v>
-      </c>
-      <c r="N509" t="n">
-        <v>21</v>
-      </c>
-      <c r="O509" t="n">
-        <v>12</v>
-      </c>
-      <c r="P509" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q509" t="n">
-        <v>15</v>
-      </c>
-      <c r="R509" t="n">
-        <v>29</v>
-      </c>
-      <c r="S509" t="n">
-        <v>26</v>
-      </c>
-      <c r="T509" t="n">
-        <v>0</v>
-      </c>
-      <c r="U509" t="inlineStr">
-        <is>
-          <t>2486544</t>
-        </is>
-      </c>
-      <c r="V509" t="n">
-        <v>96</v>
-      </c>
-      <c r="W509" t="n">
-        <v>94.31999999999999</v>
-      </c>
-      <c r="X509" t="n">
-        <v>0.8587786259541985</v>
-      </c>
-      <c r="Y509" t="n">
-        <v>81.31999999999999</v>
-      </c>
-      <c r="Z509" t="n">
-        <v>99.60649286768323</v>
-      </c>
-      <c r="AA509" t="n">
-        <v>1.115241635687732</v>
-      </c>
-      <c r="AB509" t="n">
-        <v>119.8801198801199</v>
-      </c>
-      <c r="AC509" t="n">
-        <v>0.3421052631578947</v>
-      </c>
-      <c r="AD509" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="AE509" t="n">
-        <v>0.5230769230769231</v>
-      </c>
-      <c r="AF509" t="n">
-        <v>-20.27362701243665</v>
-      </c>
-      <c r="AG509" t="inlineStr">
-        <is>
-          <t>GRUPO URETA TIZONA BURGOS</t>
-        </is>
-      </c>
-      <c r="AH509" t="inlineStr">
-        <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
-        </is>
-      </c>
-      <c r="AI509" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B510" t="n">
-        <v>32</v>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="E510" t="n">
-        <v>200</v>
-      </c>
-      <c r="F510" t="n">
-        <v>89</v>
-      </c>
-      <c r="G510" t="n">
-        <v>17</v>
-      </c>
-      <c r="H510" t="n">
-        <v>30</v>
-      </c>
-      <c r="I510" t="n">
-        <v>13</v>
-      </c>
-      <c r="J510" t="n">
-        <v>35</v>
-      </c>
-      <c r="K510" t="n">
-        <v>16</v>
-      </c>
-      <c r="L510" t="n">
-        <v>20</v>
-      </c>
-      <c r="M510" t="n">
-        <v>14</v>
-      </c>
-      <c r="N510" t="n">
-        <v>20</v>
-      </c>
-      <c r="O510" t="n">
-        <v>14</v>
-      </c>
-      <c r="P510" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q510" t="n">
-        <v>9</v>
-      </c>
-      <c r="R510" t="n">
-        <v>23</v>
-      </c>
-      <c r="S510" t="n">
-        <v>22</v>
-      </c>
-      <c r="T510" t="n">
-        <v>2</v>
-      </c>
-      <c r="U510" t="inlineStr">
-        <is>
-          <t>2486540</t>
-        </is>
-      </c>
-      <c r="V510" t="n">
-        <v>79</v>
-      </c>
-      <c r="W510" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="X510" t="n">
-        <v>1.07487922705314</v>
-      </c>
-      <c r="Y510" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="Z510" t="n">
-        <v>129.3604651162791</v>
-      </c>
-      <c r="AA510" t="n">
-        <v>1.004067107269954</v>
-      </c>
-      <c r="AB510" t="n">
-        <v>108.695652173913</v>
-      </c>
-      <c r="AC510" t="n">
-        <v>0.4242424242424243</v>
-      </c>
-      <c r="AD510" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="AE510" t="n">
-        <v>0.576271186440678</v>
-      </c>
-      <c r="AF510" t="n">
-        <v>20.66481294236604</v>
-      </c>
-      <c r="AG510" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AH510" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI510" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B511" t="n">
-        <v>32</v>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="E511" t="n">
-        <v>200</v>
-      </c>
-      <c r="F511" t="n">
-        <v>79</v>
-      </c>
-      <c r="G511" t="n">
-        <v>15</v>
-      </c>
-      <c r="H511" t="n">
-        <v>23</v>
-      </c>
-      <c r="I511" t="n">
-        <v>11</v>
-      </c>
-      <c r="J511" t="n">
-        <v>30</v>
-      </c>
-      <c r="K511" t="n">
-        <v>16</v>
-      </c>
-      <c r="L511" t="n">
-        <v>22</v>
-      </c>
-      <c r="M511" t="n">
-        <v>6</v>
-      </c>
-      <c r="N511" t="n">
-        <v>19</v>
-      </c>
-      <c r="O511" t="n">
-        <v>23</v>
-      </c>
-      <c r="P511" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q511" t="n">
-        <v>16</v>
-      </c>
-      <c r="R511" t="n">
-        <v>22</v>
-      </c>
-      <c r="S511" t="n">
-        <v>22</v>
-      </c>
-      <c r="T511" t="n">
-        <v>0</v>
-      </c>
-      <c r="U511" t="inlineStr">
-        <is>
-          <t>2486540</t>
-        </is>
-      </c>
-      <c r="V511" t="n">
-        <v>89</v>
-      </c>
-      <c r="W511" t="n">
-        <v>78.68000000000001</v>
-      </c>
-      <c r="X511" t="n">
-        <v>1.004067107269954</v>
-      </c>
-      <c r="Y511" t="n">
-        <v>72.68000000000001</v>
-      </c>
-      <c r="Z511" t="n">
-        <v>108.695652173913</v>
-      </c>
-      <c r="AA511" t="n">
-        <v>1.07487922705314</v>
-      </c>
-      <c r="AB511" t="n">
-        <v>129.3604651162791</v>
-      </c>
-      <c r="AC511" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="AD511" t="n">
-        <v>0.5757575757575758</v>
-      </c>
-      <c r="AE511" t="n">
-        <v>0.423728813559322</v>
-      </c>
-      <c r="AF511" t="n">
-        <v>-20.66481294236604</v>
-      </c>
-      <c r="AG511" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="AH511" t="inlineStr">
-        <is>
-          <t>MONBUS OBRADOIRO</t>
-        </is>
-      </c>
-      <c r="AI511" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B512" t="n">
-        <v>32</v>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="E512" t="n">
-        <v>200</v>
-      </c>
-      <c r="F512" t="n">
-        <v>77</v>
-      </c>
-      <c r="G512" t="n">
-        <v>16</v>
-      </c>
-      <c r="H512" t="n">
-        <v>34</v>
-      </c>
-      <c r="I512" t="n">
-        <v>9</v>
-      </c>
-      <c r="J512" t="n">
-        <v>32</v>
-      </c>
-      <c r="K512" t="n">
-        <v>18</v>
-      </c>
-      <c r="L512" t="n">
-        <v>20</v>
-      </c>
-      <c r="M512" t="n">
-        <v>10</v>
-      </c>
-      <c r="N512" t="n">
-        <v>28</v>
-      </c>
-      <c r="O512" t="n">
-        <v>12</v>
-      </c>
-      <c r="P512" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q512" t="n">
-        <v>9</v>
-      </c>
-      <c r="R512" t="n">
-        <v>21</v>
-      </c>
-      <c r="S512" t="n">
-        <v>20</v>
-      </c>
-      <c r="T512" t="n">
-        <v>5</v>
-      </c>
-      <c r="U512" t="inlineStr">
-        <is>
-          <t>2486538</t>
-        </is>
-      </c>
-      <c r="V512" t="n">
-        <v>68</v>
-      </c>
-      <c r="W512" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="X512" t="n">
-        <v>0.918854415274463</v>
-      </c>
-      <c r="Y512" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="Z512" t="n">
-        <v>104.3360433604336</v>
-      </c>
-      <c r="AA512" t="n">
-        <v>0.7744874715261959</v>
-      </c>
-      <c r="AB512" t="n">
-        <v>93.40659340659342</v>
-      </c>
-      <c r="AC512" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="AD512" t="n">
-        <v>0.6511627906976745</v>
-      </c>
-      <c r="AE512" t="n">
-        <v>0.4634146341463415</v>
-      </c>
-      <c r="AF512" t="n">
-        <v>10.92944995384019</v>
-      </c>
-      <c r="AG512" t="inlineStr">
-        <is>
-          <t>HLA ALICANTE</t>
-        </is>
-      </c>
-      <c r="AH512" t="inlineStr">
-        <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
-        </is>
-      </c>
-      <c r="AI512" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>Liga Regular Único</t>
-        </is>
-      </c>
-      <c r="B513" t="n">
-        <v>32</v>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="E513" t="n">
-        <v>200</v>
-      </c>
-      <c r="F513" t="n">
-        <v>92</v>
-      </c>
-      <c r="G513" t="n">
-        <v>26</v>
-      </c>
-      <c r="H513" t="n">
-        <v>43</v>
-      </c>
-      <c r="I513" t="n">
-        <v>12</v>
-      </c>
-      <c r="J513" t="n">
-        <v>29</v>
-      </c>
-      <c r="K513" t="n">
-        <v>4</v>
-      </c>
-      <c r="L513" t="n">
-        <v>9</v>
-      </c>
-      <c r="M513" t="n">
-        <v>11</v>
-      </c>
-      <c r="N513" t="n">
-        <v>30</v>
-      </c>
-      <c r="O513" t="n">
-        <v>24</v>
-      </c>
-      <c r="P513" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q513" t="n">
-        <v>7</v>
-      </c>
-      <c r="R513" t="n">
-        <v>20</v>
-      </c>
-      <c r="S513" t="n">
-        <v>16</v>
-      </c>
-      <c r="T513" t="n">
-        <v>1</v>
-      </c>
-      <c r="U513" t="inlineStr">
-        <is>
-          <t>2486542</t>
-        </is>
-      </c>
-      <c r="V513" t="n">
-        <v>70</v>
-      </c>
-      <c r="W513" t="n">
-        <v>82.96000000000001</v>
-      </c>
-      <c r="X513" t="n">
-        <v>1.108968177434908</v>
-      </c>
-      <c r="Y513" t="n">
-        <v>71.96000000000001</v>
-      </c>
-      <c r="Z513" t="n">
-        <v>127.8488048916064</v>
-      </c>
-      <c r="AA513" t="n">
-        <v>0.8409418548774626</v>
-      </c>
-      <c r="AB513" t="n">
-        <v>96.89922480620154</v>
-      </c>
-      <c r="AC513" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="AD513" t="n">
-        <v>0.7317073170731707</v>
-      </c>
-      <c r="AE513" t="n">
-        <v>0.5324675324675324</v>
-      </c>
-      <c r="AF513" t="n">
-        <v>30.94958008540489</v>
-      </c>
-      <c r="AG513" t="inlineStr">
-        <is>
-          <t>FIBWI MALLORCA BASQUET PALMA</t>
-        </is>
-      </c>
-      <c r="AH513" t="inlineStr">
-        <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
-        </is>
-      </c>
-      <c r="AI513" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI433"/>
+  <dimension ref="A1:AI513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52010,6 +52010,9526 @@
         </is>
       </c>
       <c r="AI433" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>28</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>200</v>
+      </c>
+      <c r="F434" t="n">
+        <v>76</v>
+      </c>
+      <c r="G434" t="n">
+        <v>19</v>
+      </c>
+      <c r="H434" t="n">
+        <v>36</v>
+      </c>
+      <c r="I434" t="n">
+        <v>7</v>
+      </c>
+      <c r="J434" t="n">
+        <v>28</v>
+      </c>
+      <c r="K434" t="n">
+        <v>17</v>
+      </c>
+      <c r="L434" t="n">
+        <v>20</v>
+      </c>
+      <c r="M434" t="n">
+        <v>14</v>
+      </c>
+      <c r="N434" t="n">
+        <v>27</v>
+      </c>
+      <c r="O434" t="n">
+        <v>9</v>
+      </c>
+      <c r="P434" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>16</v>
+      </c>
+      <c r="R434" t="n">
+        <v>19</v>
+      </c>
+      <c r="S434" t="n">
+        <v>19</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V434" t="n">
+        <v>74</v>
+      </c>
+      <c r="W434" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="X434" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AC434" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AD434" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE434" t="n">
+        <v>0.5616438356164384</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>5.848584493085781</v>
+      </c>
+      <c r="AG434" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI434" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>28</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>200</v>
+      </c>
+      <c r="F435" t="n">
+        <v>80</v>
+      </c>
+      <c r="G435" t="n">
+        <v>22</v>
+      </c>
+      <c r="H435" t="n">
+        <v>43</v>
+      </c>
+      <c r="I435" t="n">
+        <v>6</v>
+      </c>
+      <c r="J435" t="n">
+        <v>18</v>
+      </c>
+      <c r="K435" t="n">
+        <v>18</v>
+      </c>
+      <c r="L435" t="n">
+        <v>26</v>
+      </c>
+      <c r="M435" t="n">
+        <v>7</v>
+      </c>
+      <c r="N435" t="n">
+        <v>25</v>
+      </c>
+      <c r="O435" t="n">
+        <v>17</v>
+      </c>
+      <c r="P435" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q435" t="n">
+        <v>13</v>
+      </c>
+      <c r="R435" t="n">
+        <v>21</v>
+      </c>
+      <c r="S435" t="n">
+        <v>22</v>
+      </c>
+      <c r="T435" t="n">
+        <v>1</v>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V435" t="n">
+        <v>79</v>
+      </c>
+      <c r="W435" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X435" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>0.5079365079365079</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>2.190903518046071</v>
+      </c>
+      <c r="AG435" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI435" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>28</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>200</v>
+      </c>
+      <c r="F436" t="n">
+        <v>56</v>
+      </c>
+      <c r="G436" t="n">
+        <v>12</v>
+      </c>
+      <c r="H436" t="n">
+        <v>47</v>
+      </c>
+      <c r="I436" t="n">
+        <v>5</v>
+      </c>
+      <c r="J436" t="n">
+        <v>17</v>
+      </c>
+      <c r="K436" t="n">
+        <v>17</v>
+      </c>
+      <c r="L436" t="n">
+        <v>27</v>
+      </c>
+      <c r="M436" t="n">
+        <v>15</v>
+      </c>
+      <c r="N436" t="n">
+        <v>26</v>
+      </c>
+      <c r="O436" t="n">
+        <v>10</v>
+      </c>
+      <c r="P436" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q436" t="n">
+        <v>11</v>
+      </c>
+      <c r="R436" t="n">
+        <v>25</v>
+      </c>
+      <c r="S436" t="n">
+        <v>24</v>
+      </c>
+      <c r="T436" t="n">
+        <v>3</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V436" t="n">
+        <v>72</v>
+      </c>
+      <c r="W436" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="X436" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>0.3061224489795918</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>0.4939759036144578</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>-19.86532566650253</v>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI436" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>28</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>200</v>
+      </c>
+      <c r="F437" t="n">
+        <v>79</v>
+      </c>
+      <c r="G437" t="n">
+        <v>21</v>
+      </c>
+      <c r="H437" t="n">
+        <v>35</v>
+      </c>
+      <c r="I437" t="n">
+        <v>8</v>
+      </c>
+      <c r="J437" t="n">
+        <v>31</v>
+      </c>
+      <c r="K437" t="n">
+        <v>13</v>
+      </c>
+      <c r="L437" t="n">
+        <v>14</v>
+      </c>
+      <c r="M437" t="n">
+        <v>7</v>
+      </c>
+      <c r="N437" t="n">
+        <v>24</v>
+      </c>
+      <c r="O437" t="n">
+        <v>19</v>
+      </c>
+      <c r="P437" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q437" t="n">
+        <v>14</v>
+      </c>
+      <c r="R437" t="n">
+        <v>22</v>
+      </c>
+      <c r="S437" t="n">
+        <v>21</v>
+      </c>
+      <c r="T437" t="n">
+        <v>6</v>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>2486507</t>
+        </is>
+      </c>
+      <c r="V437" t="n">
+        <v>80</v>
+      </c>
+      <c r="W437" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="X437" t="n">
+        <v>0.9168987929433612</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>79.16</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>99.79787771601819</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>0.9363295880149813</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>101.9887812340643</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>0.492063492063492</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>-2.190903518046071</v>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI437" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>28</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>200</v>
+      </c>
+      <c r="F438" t="n">
+        <v>79</v>
+      </c>
+      <c r="G438" t="n">
+        <v>18</v>
+      </c>
+      <c r="H438" t="n">
+        <v>38</v>
+      </c>
+      <c r="I438" t="n">
+        <v>6</v>
+      </c>
+      <c r="J438" t="n">
+        <v>23</v>
+      </c>
+      <c r="K438" t="n">
+        <v>25</v>
+      </c>
+      <c r="L438" t="n">
+        <v>29</v>
+      </c>
+      <c r="M438" t="n">
+        <v>7</v>
+      </c>
+      <c r="N438" t="n">
+        <v>22</v>
+      </c>
+      <c r="O438" t="n">
+        <v>18</v>
+      </c>
+      <c r="P438" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q438" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" t="n">
+        <v>20</v>
+      </c>
+      <c r="S438" t="n">
+        <v>23</v>
+      </c>
+      <c r="T438" t="n">
+        <v>1</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V438" t="n">
+        <v>88</v>
+      </c>
+      <c r="W438" t="n">
+        <v>83.75999999999999</v>
+      </c>
+      <c r="X438" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>0.4202898550724637</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>-15.23433761206408</v>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI438" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>28</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>200</v>
+      </c>
+      <c r="F439" t="n">
+        <v>84</v>
+      </c>
+      <c r="G439" t="n">
+        <v>17</v>
+      </c>
+      <c r="H439" t="n">
+        <v>35</v>
+      </c>
+      <c r="I439" t="n">
+        <v>12</v>
+      </c>
+      <c r="J439" t="n">
+        <v>26</v>
+      </c>
+      <c r="K439" t="n">
+        <v>14</v>
+      </c>
+      <c r="L439" t="n">
+        <v>17</v>
+      </c>
+      <c r="M439" t="n">
+        <v>8</v>
+      </c>
+      <c r="N439" t="n">
+        <v>17</v>
+      </c>
+      <c r="O439" t="n">
+        <v>21</v>
+      </c>
+      <c r="P439" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q439" t="n">
+        <v>12</v>
+      </c>
+      <c r="R439" t="n">
+        <v>24</v>
+      </c>
+      <c r="S439" t="n">
+        <v>18</v>
+      </c>
+      <c r="T439" t="n">
+        <v>0</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V439" t="n">
+        <v>90</v>
+      </c>
+      <c r="W439" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="X439" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>72.48</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>-7.191299433390824</v>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI439" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>28</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>200</v>
+      </c>
+      <c r="F440" t="n">
+        <v>70</v>
+      </c>
+      <c r="G440" t="n">
+        <v>19</v>
+      </c>
+      <c r="H440" t="n">
+        <v>34</v>
+      </c>
+      <c r="I440" t="n">
+        <v>7</v>
+      </c>
+      <c r="J440" t="n">
+        <v>28</v>
+      </c>
+      <c r="K440" t="n">
+        <v>11</v>
+      </c>
+      <c r="L440" t="n">
+        <v>17</v>
+      </c>
+      <c r="M440" t="n">
+        <v>14</v>
+      </c>
+      <c r="N440" t="n">
+        <v>15</v>
+      </c>
+      <c r="O440" t="n">
+        <v>15</v>
+      </c>
+      <c r="P440" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q440" t="n">
+        <v>13</v>
+      </c>
+      <c r="R440" t="n">
+        <v>23</v>
+      </c>
+      <c r="S440" t="n">
+        <v>21</v>
+      </c>
+      <c r="T440" t="n">
+        <v>3</v>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V440" t="n">
+        <v>88</v>
+      </c>
+      <c r="W440" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="X440" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>0.4915254237288136</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>-30.47036176904953</v>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI440" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>28</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>200</v>
+      </c>
+      <c r="F441" t="n">
+        <v>88</v>
+      </c>
+      <c r="G441" t="n">
+        <v>18</v>
+      </c>
+      <c r="H441" t="n">
+        <v>29</v>
+      </c>
+      <c r="I441" t="n">
+        <v>9</v>
+      </c>
+      <c r="J441" t="n">
+        <v>22</v>
+      </c>
+      <c r="K441" t="n">
+        <v>25</v>
+      </c>
+      <c r="L441" t="n">
+        <v>28</v>
+      </c>
+      <c r="M441" t="n">
+        <v>8</v>
+      </c>
+      <c r="N441" t="n">
+        <v>22</v>
+      </c>
+      <c r="O441" t="n">
+        <v>27</v>
+      </c>
+      <c r="P441" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q441" t="n">
+        <v>11</v>
+      </c>
+      <c r="R441" t="n">
+        <v>21</v>
+      </c>
+      <c r="S441" t="n">
+        <v>23</v>
+      </c>
+      <c r="T441" t="n">
+        <v>1</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>2486501</t>
+        </is>
+      </c>
+      <c r="V441" t="n">
+        <v>70</v>
+      </c>
+      <c r="W441" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="X441" t="n">
+        <v>1.184068891280947</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>66.31999999999999</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>132.6899879372738</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>0.8486905916585838</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>102.2196261682243</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>0.5084745762711864</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>30.47036176904953</v>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI441" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>28</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>200</v>
+      </c>
+      <c r="F442" t="n">
+        <v>74</v>
+      </c>
+      <c r="G442" t="n">
+        <v>17</v>
+      </c>
+      <c r="H442" t="n">
+        <v>44</v>
+      </c>
+      <c r="I442" t="n">
+        <v>10</v>
+      </c>
+      <c r="J442" t="n">
+        <v>23</v>
+      </c>
+      <c r="K442" t="n">
+        <v>10</v>
+      </c>
+      <c r="L442" t="n">
+        <v>12</v>
+      </c>
+      <c r="M442" t="n">
+        <v>8</v>
+      </c>
+      <c r="N442" t="n">
+        <v>24</v>
+      </c>
+      <c r="O442" t="n">
+        <v>10</v>
+      </c>
+      <c r="P442" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q442" t="n">
+        <v>13</v>
+      </c>
+      <c r="R442" t="n">
+        <v>20</v>
+      </c>
+      <c r="S442" t="n">
+        <v>19</v>
+      </c>
+      <c r="T442" t="n">
+        <v>2</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>2486505</t>
+        </is>
+      </c>
+      <c r="V442" t="n">
+        <v>76</v>
+      </c>
+      <c r="W442" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="X442" t="n">
+        <v>0.8677298311444652</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>95.75569358178053</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>0.8558558558558559</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>101.6042780748663</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>0.4383561643835616</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>-5.848584493085781</v>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI442" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>28</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>200</v>
+      </c>
+      <c r="F443" t="n">
+        <v>54</v>
+      </c>
+      <c r="G443" t="n">
+        <v>22</v>
+      </c>
+      <c r="H443" t="n">
+        <v>39</v>
+      </c>
+      <c r="I443" t="n">
+        <v>1</v>
+      </c>
+      <c r="J443" t="n">
+        <v>28</v>
+      </c>
+      <c r="K443" t="n">
+        <v>7</v>
+      </c>
+      <c r="L443" t="n">
+        <v>13</v>
+      </c>
+      <c r="M443" t="n">
+        <v>12</v>
+      </c>
+      <c r="N443" t="n">
+        <v>29</v>
+      </c>
+      <c r="O443" t="n">
+        <v>16</v>
+      </c>
+      <c r="P443" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q443" t="n">
+        <v>14</v>
+      </c>
+      <c r="R443" t="n">
+        <v>17</v>
+      </c>
+      <c r="S443" t="n">
+        <v>18</v>
+      </c>
+      <c r="T443" t="n">
+        <v>5</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V443" t="n">
+        <v>73</v>
+      </c>
+      <c r="W443" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="X443" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>-32.91751260421231</v>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI443" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>28</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>200</v>
+      </c>
+      <c r="F444" t="n">
+        <v>88</v>
+      </c>
+      <c r="G444" t="n">
+        <v>24</v>
+      </c>
+      <c r="H444" t="n">
+        <v>48</v>
+      </c>
+      <c r="I444" t="n">
+        <v>9</v>
+      </c>
+      <c r="J444" t="n">
+        <v>26</v>
+      </c>
+      <c r="K444" t="n">
+        <v>13</v>
+      </c>
+      <c r="L444" t="n">
+        <v>17</v>
+      </c>
+      <c r="M444" t="n">
+        <v>14</v>
+      </c>
+      <c r="N444" t="n">
+        <v>26</v>
+      </c>
+      <c r="O444" t="n">
+        <v>14</v>
+      </c>
+      <c r="P444" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q444" t="n">
+        <v>7</v>
+      </c>
+      <c r="R444" t="n">
+        <v>23</v>
+      </c>
+      <c r="S444" t="n">
+        <v>20</v>
+      </c>
+      <c r="T444" t="n">
+        <v>2</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>2486506</t>
+        </is>
+      </c>
+      <c r="V444" t="n">
+        <v>79</v>
+      </c>
+      <c r="W444" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="X444" t="n">
+        <v>0.9945750452079566</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>118.1525241675618</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>0.9431709646609361</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>102.9181865554977</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>0.5797101449275363</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>15.23433761206408</v>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI444" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>28</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>200</v>
+      </c>
+      <c r="F445" t="n">
+        <v>73</v>
+      </c>
+      <c r="G445" t="n">
+        <v>13</v>
+      </c>
+      <c r="H445" t="n">
+        <v>28</v>
+      </c>
+      <c r="I445" t="n">
+        <v>13</v>
+      </c>
+      <c r="J445" t="n">
+        <v>38</v>
+      </c>
+      <c r="K445" t="n">
+        <v>8</v>
+      </c>
+      <c r="L445" t="n">
+        <v>10</v>
+      </c>
+      <c r="M445" t="n">
+        <v>11</v>
+      </c>
+      <c r="N445" t="n">
+        <v>26</v>
+      </c>
+      <c r="O445" t="n">
+        <v>18</v>
+      </c>
+      <c r="P445" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q445" t="n">
+        <v>10</v>
+      </c>
+      <c r="R445" t="n">
+        <v>18</v>
+      </c>
+      <c r="S445" t="n">
+        <v>17</v>
+      </c>
+      <c r="T445" t="n">
+        <v>1</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>2486508</t>
+        </is>
+      </c>
+      <c r="V445" t="n">
+        <v>54</v>
+      </c>
+      <c r="W445" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="X445" t="n">
+        <v>0.907960199004975</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>105.1873198847262</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>0.6226937269372694</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>72.26980728051392</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>32.91751260421231</v>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI445" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>28</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>200</v>
+      </c>
+      <c r="F446" t="n">
+        <v>81</v>
+      </c>
+      <c r="G446" t="n">
+        <v>20</v>
+      </c>
+      <c r="H446" t="n">
+        <v>30</v>
+      </c>
+      <c r="I446" t="n">
+        <v>10</v>
+      </c>
+      <c r="J446" t="n">
+        <v>34</v>
+      </c>
+      <c r="K446" t="n">
+        <v>11</v>
+      </c>
+      <c r="L446" t="n">
+        <v>19</v>
+      </c>
+      <c r="M446" t="n">
+        <v>13</v>
+      </c>
+      <c r="N446" t="n">
+        <v>26</v>
+      </c>
+      <c r="O446" t="n">
+        <v>18</v>
+      </c>
+      <c r="P446" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>10</v>
+      </c>
+      <c r="R446" t="n">
+        <v>23</v>
+      </c>
+      <c r="S446" t="n">
+        <v>21</v>
+      </c>
+      <c r="T446" t="n">
+        <v>5</v>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V446" t="n">
+        <v>53</v>
+      </c>
+      <c r="W446" t="n">
+        <v>82.36</v>
+      </c>
+      <c r="X446" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>0.3939393939393939</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>47.48284374049891</v>
+      </c>
+      <c r="AG446" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI446" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>28</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>200</v>
+      </c>
+      <c r="F447" t="n">
+        <v>90</v>
+      </c>
+      <c r="G447" t="n">
+        <v>19</v>
+      </c>
+      <c r="H447" t="n">
+        <v>27</v>
+      </c>
+      <c r="I447" t="n">
+        <v>11</v>
+      </c>
+      <c r="J447" t="n">
+        <v>32</v>
+      </c>
+      <c r="K447" t="n">
+        <v>19</v>
+      </c>
+      <c r="L447" t="n">
+        <v>23</v>
+      </c>
+      <c r="M447" t="n">
+        <v>8</v>
+      </c>
+      <c r="N447" t="n">
+        <v>22</v>
+      </c>
+      <c r="O447" t="n">
+        <v>16</v>
+      </c>
+      <c r="P447" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>12</v>
+      </c>
+      <c r="R447" t="n">
+        <v>18</v>
+      </c>
+      <c r="S447" t="n">
+        <v>24</v>
+      </c>
+      <c r="T447" t="n">
+        <v>1</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>2486504</t>
+        </is>
+      </c>
+      <c r="V447" t="n">
+        <v>84</v>
+      </c>
+      <c r="W447" t="n">
+        <v>81.12</v>
+      </c>
+      <c r="X447" t="n">
+        <v>1.109467455621302</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>123.0853391684902</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>1.043737574552684</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>115.8940397350993</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>7.191299433390824</v>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI447" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>28</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>200</v>
+      </c>
+      <c r="F448" t="n">
+        <v>72</v>
+      </c>
+      <c r="G448" t="n">
+        <v>16</v>
+      </c>
+      <c r="H448" t="n">
+        <v>33</v>
+      </c>
+      <c r="I448" t="n">
+        <v>6</v>
+      </c>
+      <c r="J448" t="n">
+        <v>24</v>
+      </c>
+      <c r="K448" t="n">
+        <v>22</v>
+      </c>
+      <c r="L448" t="n">
+        <v>31</v>
+      </c>
+      <c r="M448" t="n">
+        <v>8</v>
+      </c>
+      <c r="N448" t="n">
+        <v>34</v>
+      </c>
+      <c r="O448" t="n">
+        <v>15</v>
+      </c>
+      <c r="P448" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>11</v>
+      </c>
+      <c r="R448" t="n">
+        <v>24</v>
+      </c>
+      <c r="S448" t="n">
+        <v>25</v>
+      </c>
+      <c r="T448" t="n">
+        <v>7</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>2486502</t>
+        </is>
+      </c>
+      <c r="V448" t="n">
+        <v>56</v>
+      </c>
+      <c r="W448" t="n">
+        <v>81.64</v>
+      </c>
+      <c r="X448" t="n">
+        <v>0.8819206271435571</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>97.77294948397611</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>0.6445672191528545</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>77.90762381747358</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>0.6938775510204082</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>0.5060240963855421</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>19.86532566650253</v>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI448" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>28</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>200</v>
+      </c>
+      <c r="F449" t="n">
+        <v>53</v>
+      </c>
+      <c r="G449" t="n">
+        <v>15</v>
+      </c>
+      <c r="H449" t="n">
+        <v>41</v>
+      </c>
+      <c r="I449" t="n">
+        <v>4</v>
+      </c>
+      <c r="J449" t="n">
+        <v>23</v>
+      </c>
+      <c r="K449" t="n">
+        <v>11</v>
+      </c>
+      <c r="L449" t="n">
+        <v>17</v>
+      </c>
+      <c r="M449" t="n">
+        <v>10</v>
+      </c>
+      <c r="N449" t="n">
+        <v>20</v>
+      </c>
+      <c r="O449" t="n">
+        <v>8</v>
+      </c>
+      <c r="P449" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>15</v>
+      </c>
+      <c r="R449" t="n">
+        <v>21</v>
+      </c>
+      <c r="S449" t="n">
+        <v>23</v>
+      </c>
+      <c r="T449" t="n">
+        <v>1</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>2486503</t>
+        </is>
+      </c>
+      <c r="V449" t="n">
+        <v>81</v>
+      </c>
+      <c r="W449" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="X449" t="n">
+        <v>0.6128584643848288</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>69.29916317991632</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>0.9834871296745993</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>116.7820069204152</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>-47.48284374049891</v>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI449" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>29</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>200</v>
+      </c>
+      <c r="F450" t="n">
+        <v>65</v>
+      </c>
+      <c r="G450" t="n">
+        <v>12</v>
+      </c>
+      <c r="H450" t="n">
+        <v>25</v>
+      </c>
+      <c r="I450" t="n">
+        <v>11</v>
+      </c>
+      <c r="J450" t="n">
+        <v>32</v>
+      </c>
+      <c r="K450" t="n">
+        <v>8</v>
+      </c>
+      <c r="L450" t="n">
+        <v>12</v>
+      </c>
+      <c r="M450" t="n">
+        <v>10</v>
+      </c>
+      <c r="N450" t="n">
+        <v>22</v>
+      </c>
+      <c r="O450" t="n">
+        <v>11</v>
+      </c>
+      <c r="P450" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>17</v>
+      </c>
+      <c r="R450" t="n">
+        <v>22</v>
+      </c>
+      <c r="S450" t="n">
+        <v>18</v>
+      </c>
+      <c r="T450" t="n">
+        <v>2</v>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="V450" t="n">
+        <v>73</v>
+      </c>
+      <c r="W450" t="n">
+        <v>79.28</v>
+      </c>
+      <c r="X450" t="n">
+        <v>0.8198789101917255</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>69.28</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>93.82217090069284</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>0.9292260692464358</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>100.606394707828</v>
+      </c>
+      <c r="AC450" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AD450" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>0.5245901639344263</v>
+      </c>
+      <c r="AF450" t="n">
+        <v>-6.784223807135163</v>
+      </c>
+      <c r="AG450" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI450" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>29</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>200</v>
+      </c>
+      <c r="F451" t="n">
+        <v>81</v>
+      </c>
+      <c r="G451" t="n">
+        <v>15</v>
+      </c>
+      <c r="H451" t="n">
+        <v>32</v>
+      </c>
+      <c r="I451" t="n">
+        <v>8</v>
+      </c>
+      <c r="J451" t="n">
+        <v>31</v>
+      </c>
+      <c r="K451" t="n">
+        <v>27</v>
+      </c>
+      <c r="L451" t="n">
+        <v>30</v>
+      </c>
+      <c r="M451" t="n">
+        <v>14</v>
+      </c>
+      <c r="N451" t="n">
+        <v>15</v>
+      </c>
+      <c r="O451" t="n">
+        <v>19</v>
+      </c>
+      <c r="P451" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q451" t="n">
+        <v>12</v>
+      </c>
+      <c r="R451" t="n">
+        <v>19</v>
+      </c>
+      <c r="S451" t="n">
+        <v>22</v>
+      </c>
+      <c r="T451" t="n">
+        <v>3</v>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="V451" t="n">
+        <v>79</v>
+      </c>
+      <c r="W451" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="X451" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>109.1644204851752</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>0.9748272458045411</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>108.1599123767799</v>
+      </c>
+      <c r="AC451" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="AD451" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF451" t="n">
+        <v>1.004508108395342</v>
+      </c>
+      <c r="AG451" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI451" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>29</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>200</v>
+      </c>
+      <c r="F452" t="n">
+        <v>67</v>
+      </c>
+      <c r="G452" t="n">
+        <v>17</v>
+      </c>
+      <c r="H452" t="n">
+        <v>41</v>
+      </c>
+      <c r="I452" t="n">
+        <v>7</v>
+      </c>
+      <c r="J452" t="n">
+        <v>27</v>
+      </c>
+      <c r="K452" t="n">
+        <v>12</v>
+      </c>
+      <c r="L452" t="n">
+        <v>20</v>
+      </c>
+      <c r="M452" t="n">
+        <v>19</v>
+      </c>
+      <c r="N452" t="n">
+        <v>21</v>
+      </c>
+      <c r="O452" t="n">
+        <v>13</v>
+      </c>
+      <c r="P452" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q452" t="n">
+        <v>13</v>
+      </c>
+      <c r="R452" t="n">
+        <v>27</v>
+      </c>
+      <c r="S452" t="n">
+        <v>19</v>
+      </c>
+      <c r="T452" t="n">
+        <v>1</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="V452" t="n">
+        <v>72</v>
+      </c>
+      <c r="W452" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="X452" t="n">
+        <v>0.7461024498886415</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>94.63276836158192</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>0.9370119729307652</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>104.5903544450901</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>0.4318181818181818</v>
+      </c>
+      <c r="AD452" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF452" t="n">
+        <v>-9.957586083508133</v>
+      </c>
+      <c r="AG452" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI452" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>29</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>200</v>
+      </c>
+      <c r="F453" t="n">
+        <v>79</v>
+      </c>
+      <c r="G453" t="n">
+        <v>16</v>
+      </c>
+      <c r="H453" t="n">
+        <v>26</v>
+      </c>
+      <c r="I453" t="n">
+        <v>12</v>
+      </c>
+      <c r="J453" t="n">
+        <v>32</v>
+      </c>
+      <c r="K453" t="n">
+        <v>11</v>
+      </c>
+      <c r="L453" t="n">
+        <v>16</v>
+      </c>
+      <c r="M453" t="n">
+        <v>8</v>
+      </c>
+      <c r="N453" t="n">
+        <v>20</v>
+      </c>
+      <c r="O453" t="n">
+        <v>22</v>
+      </c>
+      <c r="P453" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>16</v>
+      </c>
+      <c r="R453" t="n">
+        <v>22</v>
+      </c>
+      <c r="S453" t="n">
+        <v>19</v>
+      </c>
+      <c r="T453" t="n">
+        <v>1</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>2486518</t>
+        </is>
+      </c>
+      <c r="V453" t="n">
+        <v>81</v>
+      </c>
+      <c r="W453" t="n">
+        <v>81.03999999999999</v>
+      </c>
+      <c r="X453" t="n">
+        <v>0.9748272458045411</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>73.03999999999999</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>108.1599123767799</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>0.9183673469387755</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>109.1644204851752</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="AE453" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF453" t="n">
+        <v>-1.004508108395342</v>
+      </c>
+      <c r="AG453" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI453" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>29</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>200</v>
+      </c>
+      <c r="F454" t="n">
+        <v>73</v>
+      </c>
+      <c r="G454" t="n">
+        <v>21</v>
+      </c>
+      <c r="H454" t="n">
+        <v>38</v>
+      </c>
+      <c r="I454" t="n">
+        <v>4</v>
+      </c>
+      <c r="J454" t="n">
+        <v>17</v>
+      </c>
+      <c r="K454" t="n">
+        <v>19</v>
+      </c>
+      <c r="L454" t="n">
+        <v>24</v>
+      </c>
+      <c r="M454" t="n">
+        <v>6</v>
+      </c>
+      <c r="N454" t="n">
+        <v>23</v>
+      </c>
+      <c r="O454" t="n">
+        <v>14</v>
+      </c>
+      <c r="P454" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q454" t="n">
+        <v>13</v>
+      </c>
+      <c r="R454" t="n">
+        <v>19</v>
+      </c>
+      <c r="S454" t="n">
+        <v>22</v>
+      </c>
+      <c r="T454" t="n">
+        <v>4</v>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>2486516</t>
+        </is>
+      </c>
+      <c r="V454" t="n">
+        <v>65</v>
+      </c>
+      <c r="W454" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="X454" t="n">
+        <v>0.9292260692464358</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>100.606394707828</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>0.8198789101917255</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>93.82217090069284</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>0.4754098360655737</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>6.784223807135163</v>
+      </c>
+      <c r="AG454" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH454" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI454" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>29</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>200</v>
+      </c>
+      <c r="F455" t="n">
+        <v>72</v>
+      </c>
+      <c r="G455" t="n">
+        <v>10</v>
+      </c>
+      <c r="H455" t="n">
+        <v>24</v>
+      </c>
+      <c r="I455" t="n">
+        <v>7</v>
+      </c>
+      <c r="J455" t="n">
+        <v>24</v>
+      </c>
+      <c r="K455" t="n">
+        <v>31</v>
+      </c>
+      <c r="L455" t="n">
+        <v>36</v>
+      </c>
+      <c r="M455" t="n">
+        <v>8</v>
+      </c>
+      <c r="N455" t="n">
+        <v>25</v>
+      </c>
+      <c r="O455" t="n">
+        <v>16</v>
+      </c>
+      <c r="P455" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>13</v>
+      </c>
+      <c r="R455" t="n">
+        <v>19</v>
+      </c>
+      <c r="S455" t="n">
+        <v>27</v>
+      </c>
+      <c r="T455" t="n">
+        <v>0</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>2486515</t>
+        </is>
+      </c>
+      <c r="V455" t="n">
+        <v>67</v>
+      </c>
+      <c r="W455" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="X455" t="n">
+        <v>0.9370119729307652</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>104.5903544450901</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>0.7461024498886415</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>94.63276836158192</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>0.2758620689655172</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>0.5681818181818182</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>0.4520547945205479</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>9.957586083508133</v>
+      </c>
+      <c r="AG455" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI455" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>29</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>200</v>
+      </c>
+      <c r="F456" t="n">
+        <v>79</v>
+      </c>
+      <c r="G456" t="n">
+        <v>20</v>
+      </c>
+      <c r="H456" t="n">
+        <v>34</v>
+      </c>
+      <c r="I456" t="n">
+        <v>9</v>
+      </c>
+      <c r="J456" t="n">
+        <v>25</v>
+      </c>
+      <c r="K456" t="n">
+        <v>12</v>
+      </c>
+      <c r="L456" t="n">
+        <v>21</v>
+      </c>
+      <c r="M456" t="n">
+        <v>10</v>
+      </c>
+      <c r="N456" t="n">
+        <v>16</v>
+      </c>
+      <c r="O456" t="n">
+        <v>18</v>
+      </c>
+      <c r="P456" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>11</v>
+      </c>
+      <c r="R456" t="n">
+        <v>19</v>
+      </c>
+      <c r="S456" t="n">
+        <v>21</v>
+      </c>
+      <c r="T456" t="n">
+        <v>1</v>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="V456" t="n">
+        <v>83</v>
+      </c>
+      <c r="W456" t="n">
+        <v>79.24000000000001</v>
+      </c>
+      <c r="X456" t="n">
+        <v>0.9969712266532054</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>69.24000000000001</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>114.0958983246678</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>1.014669926650367</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>117.2316384180791</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>0.5925925925925926</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>0.456140350877193</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>-3.1357400934113</v>
+      </c>
+      <c r="AG456" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH456" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI456" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>29</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>200</v>
+      </c>
+      <c r="F457" t="n">
+        <v>76</v>
+      </c>
+      <c r="G457" t="n">
+        <v>13</v>
+      </c>
+      <c r="H457" t="n">
+        <v>30</v>
+      </c>
+      <c r="I457" t="n">
+        <v>9</v>
+      </c>
+      <c r="J457" t="n">
+        <v>35</v>
+      </c>
+      <c r="K457" t="n">
+        <v>23</v>
+      </c>
+      <c r="L457" t="n">
+        <v>26</v>
+      </c>
+      <c r="M457" t="n">
+        <v>13</v>
+      </c>
+      <c r="N457" t="n">
+        <v>12</v>
+      </c>
+      <c r="O457" t="n">
+        <v>12</v>
+      </c>
+      <c r="P457" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>12</v>
+      </c>
+      <c r="R457" t="n">
+        <v>22</v>
+      </c>
+      <c r="S457" t="n">
+        <v>23</v>
+      </c>
+      <c r="T457" t="n">
+        <v>1</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>2486512</t>
+        </is>
+      </c>
+      <c r="V457" t="n">
+        <v>96</v>
+      </c>
+      <c r="W457" t="n">
+        <v>88.44</v>
+      </c>
+      <c r="X457" t="n">
+        <v>0.8593396653098145</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>100.7423117709438</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>1.170731707317073</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>126.3157894736842</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>0.462962962962963</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>-25.5734777027404</v>
+      </c>
+      <c r="AG457" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI457" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>29</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>200</v>
+      </c>
+      <c r="F458" t="n">
+        <v>83</v>
+      </c>
+      <c r="G458" t="n">
+        <v>19</v>
+      </c>
+      <c r="H458" t="n">
+        <v>32</v>
+      </c>
+      <c r="I458" t="n">
+        <v>9</v>
+      </c>
+      <c r="J458" t="n">
+        <v>31</v>
+      </c>
+      <c r="K458" t="n">
+        <v>18</v>
+      </c>
+      <c r="L458" t="n">
+        <v>20</v>
+      </c>
+      <c r="M458" t="n">
+        <v>11</v>
+      </c>
+      <c r="N458" t="n">
+        <v>20</v>
+      </c>
+      <c r="O458" t="n">
+        <v>19</v>
+      </c>
+      <c r="P458" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>10</v>
+      </c>
+      <c r="R458" t="n">
+        <v>21</v>
+      </c>
+      <c r="S458" t="n">
+        <v>19</v>
+      </c>
+      <c r="T458" t="n">
+        <v>3</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>2486514</t>
+        </is>
+      </c>
+      <c r="V458" t="n">
+        <v>79</v>
+      </c>
+      <c r="W458" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="X458" t="n">
+        <v>1.014669926650367</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>117.2316384180791</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>0.9969712266532054</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>114.0958983246678</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>0.4074074074074074</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>0.543859649122807</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>3.1357400934113</v>
+      </c>
+      <c r="AG458" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI458" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>29</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>200</v>
+      </c>
+      <c r="F459" t="n">
+        <v>74</v>
+      </c>
+      <c r="G459" t="n">
+        <v>15</v>
+      </c>
+      <c r="H459" t="n">
+        <v>42</v>
+      </c>
+      <c r="I459" t="n">
+        <v>10</v>
+      </c>
+      <c r="J459" t="n">
+        <v>35</v>
+      </c>
+      <c r="K459" t="n">
+        <v>14</v>
+      </c>
+      <c r="L459" t="n">
+        <v>19</v>
+      </c>
+      <c r="M459" t="n">
+        <v>11</v>
+      </c>
+      <c r="N459" t="n">
+        <v>17</v>
+      </c>
+      <c r="O459" t="n">
+        <v>13</v>
+      </c>
+      <c r="P459" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>7</v>
+      </c>
+      <c r="R459" t="n">
+        <v>18</v>
+      </c>
+      <c r="S459" t="n">
+        <v>21</v>
+      </c>
+      <c r="T459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>2486510</t>
+        </is>
+      </c>
+      <c r="V459" t="n">
+        <v>87</v>
+      </c>
+      <c r="W459" t="n">
+        <v>92.36</v>
+      </c>
+      <c r="X459" t="n">
+        <v>0.8012126461671719</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>90.95378564405114</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>1.028368794326241</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>115.0793650793651</v>
+      </c>
+      <c r="AC459" t="n">
+        <v>0.2244897959183673</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AE459" t="n">
+        <v>0.3733333333333334</v>
+      </c>
+      <c r="AF459" t="n">
+        <v>-24.12557943531395</v>
+      </c>
+      <c r="AG459" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AI459" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>29</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>200</v>
+      </c>
+      <c r="F460" t="n">
+        <v>87</v>
+      </c>
+      <c r="G460" t="n">
+        <v>25</v>
+      </c>
+      <c r="H460" t="n">
+        <v>34</v>
+      </c>
+      <c r="I460" t="n">
+        <v>8</v>
+      </c>
+      <c r="J460" t="n">
+        <v>28</v>
+      </c>
+      <c r="K460" t="n">
+        <v>13</v>
+      </c>
+      <c r="L460" t="n">
+        <v>15</v>
+      </c>
+      <c r="M460" t="n">
+        <v>9</v>
+      </c>
+      <c r="N460" t="n">
+        <v>38</v>
+      </c>
+      <c r="O460" t="n">
+        <v>17</v>
+      </c>
+      <c r="P460" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>16</v>
+      </c>
+      <c r="R460" t="n">
+        <v>21</v>
+      </c>
+      <c r="S460" t="n">
+        <v>18</v>
+      </c>
+      <c r="T460" t="n">
+        <v>3</v>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>2486510</t>
+        </is>
+      </c>
+      <c r="V460" t="n">
+        <v>74</v>
+      </c>
+      <c r="W460" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="X460" t="n">
+        <v>1.028368794326241</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>115.0793650793651</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>0.8012126461671719</v>
+      </c>
+      <c r="AB460" t="n">
+        <v>90.95378564405114</v>
+      </c>
+      <c r="AC460" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="AD460" t="n">
+        <v>0.7755102040816326</v>
+      </c>
+      <c r="AE460" t="n">
+        <v>0.6266666666666667</v>
+      </c>
+      <c r="AF460" t="n">
+        <v>24.12557943531395</v>
+      </c>
+      <c r="AG460" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH460" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AI460" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>29</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>200</v>
+      </c>
+      <c r="F461" t="n">
+        <v>84</v>
+      </c>
+      <c r="G461" t="n">
+        <v>14</v>
+      </c>
+      <c r="H461" t="n">
+        <v>25</v>
+      </c>
+      <c r="I461" t="n">
+        <v>11</v>
+      </c>
+      <c r="J461" t="n">
+        <v>33</v>
+      </c>
+      <c r="K461" t="n">
+        <v>23</v>
+      </c>
+      <c r="L461" t="n">
+        <v>28</v>
+      </c>
+      <c r="M461" t="n">
+        <v>11</v>
+      </c>
+      <c r="N461" t="n">
+        <v>16</v>
+      </c>
+      <c r="O461" t="n">
+        <v>12</v>
+      </c>
+      <c r="P461" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>13</v>
+      </c>
+      <c r="R461" t="n">
+        <v>29</v>
+      </c>
+      <c r="S461" t="n">
+        <v>24</v>
+      </c>
+      <c r="T461" t="n">
+        <v>0</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="V461" t="n">
+        <v>92</v>
+      </c>
+      <c r="W461" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="X461" t="n">
+        <v>1.00816130580893</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>116.1504424778761</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>1.147704590818363</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>127.4944567627495</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>0.3793103448275862</v>
+      </c>
+      <c r="AD461" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE461" t="n">
+        <v>0.5094339622641509</v>
+      </c>
+      <c r="AF461" t="n">
+        <v>-11.34401428487334</v>
+      </c>
+      <c r="AG461" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI461" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>29</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>200</v>
+      </c>
+      <c r="F462" t="n">
+        <v>82</v>
+      </c>
+      <c r="G462" t="n">
+        <v>12</v>
+      </c>
+      <c r="H462" t="n">
+        <v>27</v>
+      </c>
+      <c r="I462" t="n">
+        <v>14</v>
+      </c>
+      <c r="J462" t="n">
+        <v>37</v>
+      </c>
+      <c r="K462" t="n">
+        <v>16</v>
+      </c>
+      <c r="L462" t="n">
+        <v>19</v>
+      </c>
+      <c r="M462" t="n">
+        <v>9</v>
+      </c>
+      <c r="N462" t="n">
+        <v>30</v>
+      </c>
+      <c r="O462" t="n">
+        <v>21</v>
+      </c>
+      <c r="P462" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>14</v>
+      </c>
+      <c r="R462" t="n">
+        <v>18</v>
+      </c>
+      <c r="S462" t="n">
+        <v>19</v>
+      </c>
+      <c r="T462" t="n">
+        <v>1</v>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="V462" t="n">
+        <v>75</v>
+      </c>
+      <c r="W462" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="X462" t="n">
+        <v>0.9495136637332098</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>77.36</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>105.9979317476732</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>0.8628624022089277</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>96.25256673511294</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>0.5064935064935064</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>9.745365012560285</v>
+      </c>
+      <c r="AG462" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH462" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI462" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>29</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>200</v>
+      </c>
+      <c r="F463" t="n">
+        <v>92</v>
+      </c>
+      <c r="G463" t="n">
+        <v>18</v>
+      </c>
+      <c r="H463" t="n">
+        <v>26</v>
+      </c>
+      <c r="I463" t="n">
+        <v>10</v>
+      </c>
+      <c r="J463" t="n">
+        <v>26</v>
+      </c>
+      <c r="K463" t="n">
+        <v>26</v>
+      </c>
+      <c r="L463" t="n">
+        <v>39</v>
+      </c>
+      <c r="M463" t="n">
+        <v>8</v>
+      </c>
+      <c r="N463" t="n">
+        <v>18</v>
+      </c>
+      <c r="O463" t="n">
+        <v>15</v>
+      </c>
+      <c r="P463" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>11</v>
+      </c>
+      <c r="R463" t="n">
+        <v>24</v>
+      </c>
+      <c r="S463" t="n">
+        <v>29</v>
+      </c>
+      <c r="T463" t="n">
+        <v>1</v>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>2486513</t>
+        </is>
+      </c>
+      <c r="V463" t="n">
+        <v>84</v>
+      </c>
+      <c r="W463" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X463" t="n">
+        <v>1.147704590818363</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>127.4944567627495</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>1.00816130580893</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>116.1504424778761</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD463" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="AE463" t="n">
+        <v>0.4905660377358491</v>
+      </c>
+      <c r="AF463" t="n">
+        <v>11.34401428487334</v>
+      </c>
+      <c r="AG463" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH463" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI463" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>29</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>200</v>
+      </c>
+      <c r="F464" t="n">
+        <v>96</v>
+      </c>
+      <c r="G464" t="n">
+        <v>17</v>
+      </c>
+      <c r="H464" t="n">
+        <v>24</v>
+      </c>
+      <c r="I464" t="n">
+        <v>14</v>
+      </c>
+      <c r="J464" t="n">
+        <v>28</v>
+      </c>
+      <c r="K464" t="n">
+        <v>20</v>
+      </c>
+      <c r="L464" t="n">
+        <v>25</v>
+      </c>
+      <c r="M464" t="n">
+        <v>6</v>
+      </c>
+      <c r="N464" t="n">
+        <v>23</v>
+      </c>
+      <c r="O464" t="n">
+        <v>13</v>
+      </c>
+      <c r="P464" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>19</v>
+      </c>
+      <c r="R464" t="n">
+        <v>23</v>
+      </c>
+      <c r="S464" t="n">
+        <v>22</v>
+      </c>
+      <c r="T464" t="n">
+        <v>2</v>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>2486512</t>
+        </is>
+      </c>
+      <c r="V464" t="n">
+        <v>76</v>
+      </c>
+      <c r="W464" t="n">
+        <v>82</v>
+      </c>
+      <c r="X464" t="n">
+        <v>1.170731707317073</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>126.3157894736842</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>0.8593396653098145</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>100.7423117709438</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD464" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AE464" t="n">
+        <v>0.5370370370370371</v>
+      </c>
+      <c r="AF464" t="n">
+        <v>25.5734777027404</v>
+      </c>
+      <c r="AG464" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH464" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI464" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>29</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>200</v>
+      </c>
+      <c r="F465" t="n">
+        <v>75</v>
+      </c>
+      <c r="G465" t="n">
+        <v>20</v>
+      </c>
+      <c r="H465" t="n">
+        <v>47</v>
+      </c>
+      <c r="I465" t="n">
+        <v>7</v>
+      </c>
+      <c r="J465" t="n">
+        <v>23</v>
+      </c>
+      <c r="K465" t="n">
+        <v>14</v>
+      </c>
+      <c r="L465" t="n">
+        <v>18</v>
+      </c>
+      <c r="M465" t="n">
+        <v>9</v>
+      </c>
+      <c r="N465" t="n">
+        <v>29</v>
+      </c>
+      <c r="O465" t="n">
+        <v>14</v>
+      </c>
+      <c r="P465" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>9</v>
+      </c>
+      <c r="R465" t="n">
+        <v>20</v>
+      </c>
+      <c r="S465" t="n">
+        <v>17</v>
+      </c>
+      <c r="T465" t="n">
+        <v>3</v>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>2486511</t>
+        </is>
+      </c>
+      <c r="V465" t="n">
+        <v>82</v>
+      </c>
+      <c r="W465" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="X465" t="n">
+        <v>0.8628624022089277</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>96.25256673511294</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>0.9495136637332098</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>105.9979317476732</v>
+      </c>
+      <c r="AC465" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AD465" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="AE465" t="n">
+        <v>0.4935064935064935</v>
+      </c>
+      <c r="AF465" t="n">
+        <v>-9.745365012560285</v>
+      </c>
+      <c r="AG465" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH465" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI465" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>30</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>200</v>
+      </c>
+      <c r="F466" t="n">
+        <v>69</v>
+      </c>
+      <c r="G466" t="n">
+        <v>11</v>
+      </c>
+      <c r="H466" t="n">
+        <v>28</v>
+      </c>
+      <c r="I466" t="n">
+        <v>9</v>
+      </c>
+      <c r="J466" t="n">
+        <v>32</v>
+      </c>
+      <c r="K466" t="n">
+        <v>20</v>
+      </c>
+      <c r="L466" t="n">
+        <v>24</v>
+      </c>
+      <c r="M466" t="n">
+        <v>10</v>
+      </c>
+      <c r="N466" t="n">
+        <v>16</v>
+      </c>
+      <c r="O466" t="n">
+        <v>16</v>
+      </c>
+      <c r="P466" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>16</v>
+      </c>
+      <c r="R466" t="n">
+        <v>20</v>
+      </c>
+      <c r="S466" t="n">
+        <v>20</v>
+      </c>
+      <c r="T466" t="n">
+        <v>0</v>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="V466" t="n">
+        <v>75</v>
+      </c>
+      <c r="W466" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="X466" t="n">
+        <v>0.7971349353049907</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>90.12539184952978</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>0.8733115975780159</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>98.84027411702689</v>
+      </c>
+      <c r="AC466" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD466" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="AE466" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="AF466" t="n">
+        <v>-8.714882267497117</v>
+      </c>
+      <c r="AG466" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH466" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI466" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>30</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>225</v>
+      </c>
+      <c r="F467" t="n">
+        <v>87</v>
+      </c>
+      <c r="G467" t="n">
+        <v>21</v>
+      </c>
+      <c r="H467" t="n">
+        <v>42</v>
+      </c>
+      <c r="I467" t="n">
+        <v>10</v>
+      </c>
+      <c r="J467" t="n">
+        <v>37</v>
+      </c>
+      <c r="K467" t="n">
+        <v>15</v>
+      </c>
+      <c r="L467" t="n">
+        <v>21</v>
+      </c>
+      <c r="M467" t="n">
+        <v>9</v>
+      </c>
+      <c r="N467" t="n">
+        <v>33</v>
+      </c>
+      <c r="O467" t="n">
+        <v>10</v>
+      </c>
+      <c r="P467" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>10</v>
+      </c>
+      <c r="R467" t="n">
+        <v>24</v>
+      </c>
+      <c r="S467" t="n">
+        <v>21</v>
+      </c>
+      <c r="T467" t="n">
+        <v>0</v>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="V467" t="n">
+        <v>94</v>
+      </c>
+      <c r="W467" t="n">
+        <v>98.24000000000001</v>
+      </c>
+      <c r="X467" t="n">
+        <v>0.8855863192182409</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>89.24000000000001</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>97.48991483639622</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>0.9418837675350702</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>105.8558558558559</v>
+      </c>
+      <c r="AC467" t="n">
+        <v>0.2093023255813954</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE467" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="AF467" t="n">
+        <v>-8.36594101945964</v>
+      </c>
+      <c r="AG467" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH467" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI467" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>30</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>200</v>
+      </c>
+      <c r="F468" t="n">
+        <v>57</v>
+      </c>
+      <c r="G468" t="n">
+        <v>16</v>
+      </c>
+      <c r="H468" t="n">
+        <v>43</v>
+      </c>
+      <c r="I468" t="n">
+        <v>4</v>
+      </c>
+      <c r="J468" t="n">
+        <v>22</v>
+      </c>
+      <c r="K468" t="n">
+        <v>13</v>
+      </c>
+      <c r="L468" t="n">
+        <v>16</v>
+      </c>
+      <c r="M468" t="n">
+        <v>13</v>
+      </c>
+      <c r="N468" t="n">
+        <v>16</v>
+      </c>
+      <c r="O468" t="n">
+        <v>14</v>
+      </c>
+      <c r="P468" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>13</v>
+      </c>
+      <c r="R468" t="n">
+        <v>24</v>
+      </c>
+      <c r="S468" t="n">
+        <v>16</v>
+      </c>
+      <c r="T468" t="n">
+        <v>2</v>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>2486521</t>
+        </is>
+      </c>
+      <c r="V468" t="n">
+        <v>94</v>
+      </c>
+      <c r="W468" t="n">
+        <v>85.03999999999999</v>
+      </c>
+      <c r="X468" t="n">
+        <v>0.6702728127939793</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>72.03999999999999</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>79.12270960577457</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>1.160493827160494</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>130.5555555555555</v>
+      </c>
+      <c r="AC468" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AE468" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="AF468" t="n">
+        <v>-51.43284594978097</v>
+      </c>
+      <c r="AG468" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH468" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI468" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>30</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>200</v>
+      </c>
+      <c r="F469" t="n">
+        <v>77</v>
+      </c>
+      <c r="G469" t="n">
+        <v>22</v>
+      </c>
+      <c r="H469" t="n">
+        <v>34</v>
+      </c>
+      <c r="I469" t="n">
+        <v>6</v>
+      </c>
+      <c r="J469" t="n">
+        <v>17</v>
+      </c>
+      <c r="K469" t="n">
+        <v>15</v>
+      </c>
+      <c r="L469" t="n">
+        <v>23</v>
+      </c>
+      <c r="M469" t="n">
+        <v>6</v>
+      </c>
+      <c r="N469" t="n">
+        <v>24</v>
+      </c>
+      <c r="O469" t="n">
+        <v>11</v>
+      </c>
+      <c r="P469" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>17</v>
+      </c>
+      <c r="R469" t="n">
+        <v>18</v>
+      </c>
+      <c r="S469" t="n">
+        <v>18</v>
+      </c>
+      <c r="T469" t="n">
+        <v>2</v>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="V469" t="n">
+        <v>80</v>
+      </c>
+      <c r="W469" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="X469" t="n">
+        <v>0.985663082437276</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>106.7665002773156</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>0.964785335262904</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>108.2251082251082</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE469" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF469" t="n">
+        <v>-1.458607947792657</v>
+      </c>
+      <c r="AG469" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH469" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI469" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>30</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>200</v>
+      </c>
+      <c r="F470" t="n">
+        <v>75</v>
+      </c>
+      <c r="G470" t="n">
+        <v>20</v>
+      </c>
+      <c r="H470" t="n">
+        <v>38</v>
+      </c>
+      <c r="I470" t="n">
+        <v>10</v>
+      </c>
+      <c r="J470" t="n">
+        <v>29</v>
+      </c>
+      <c r="K470" t="n">
+        <v>5</v>
+      </c>
+      <c r="L470" t="n">
+        <v>16</v>
+      </c>
+      <c r="M470" t="n">
+        <v>10</v>
+      </c>
+      <c r="N470" t="n">
+        <v>26</v>
+      </c>
+      <c r="O470" t="n">
+        <v>15</v>
+      </c>
+      <c r="P470" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>12</v>
+      </c>
+      <c r="R470" t="n">
+        <v>15</v>
+      </c>
+      <c r="S470" t="n">
+        <v>20</v>
+      </c>
+      <c r="T470" t="n">
+        <v>0</v>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="V470" t="n">
+        <v>74</v>
+      </c>
+      <c r="W470" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X470" t="n">
+        <v>0.8716875871687588</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>98.63229879011048</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>0.828853046594982</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>97.01101206082852</v>
+      </c>
+      <c r="AC470" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE470" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF470" t="n">
+        <v>1.621286729281962</v>
+      </c>
+      <c r="AG470" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH470" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI470" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>30</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>200</v>
+      </c>
+      <c r="F471" t="n">
+        <v>74</v>
+      </c>
+      <c r="G471" t="n">
+        <v>9</v>
+      </c>
+      <c r="H471" t="n">
+        <v>23</v>
+      </c>
+      <c r="I471" t="n">
+        <v>13</v>
+      </c>
+      <c r="J471" t="n">
+        <v>39</v>
+      </c>
+      <c r="K471" t="n">
+        <v>17</v>
+      </c>
+      <c r="L471" t="n">
+        <v>22</v>
+      </c>
+      <c r="M471" t="n">
+        <v>8</v>
+      </c>
+      <c r="N471" t="n">
+        <v>25</v>
+      </c>
+      <c r="O471" t="n">
+        <v>12</v>
+      </c>
+      <c r="P471" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>9</v>
+      </c>
+      <c r="R471" t="n">
+        <v>23</v>
+      </c>
+      <c r="S471" t="n">
+        <v>21</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1</v>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="V471" t="n">
+        <v>82</v>
+      </c>
+      <c r="W471" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="X471" t="n">
+        <v>0.9172037679722359</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>101.8161805173363</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>0.9597378277153559</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AC471" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE471" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="AF471" t="n">
+        <v>-6.879471656576783</v>
+      </c>
+      <c r="AG471" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH471" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI471" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>30</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>200</v>
+      </c>
+      <c r="F472" t="n">
+        <v>80</v>
+      </c>
+      <c r="G472" t="n">
+        <v>11</v>
+      </c>
+      <c r="H472" t="n">
+        <v>26</v>
+      </c>
+      <c r="I472" t="n">
+        <v>16</v>
+      </c>
+      <c r="J472" t="n">
+        <v>33</v>
+      </c>
+      <c r="K472" t="n">
+        <v>10</v>
+      </c>
+      <c r="L472" t="n">
+        <v>18</v>
+      </c>
+      <c r="M472" t="n">
+        <v>9</v>
+      </c>
+      <c r="N472" t="n">
+        <v>16</v>
+      </c>
+      <c r="O472" t="n">
+        <v>18</v>
+      </c>
+      <c r="P472" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>16</v>
+      </c>
+      <c r="R472" t="n">
+        <v>18</v>
+      </c>
+      <c r="S472" t="n">
+        <v>18</v>
+      </c>
+      <c r="T472" t="n">
+        <v>2</v>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>2486519</t>
+        </is>
+      </c>
+      <c r="V472" t="n">
+        <v>77</v>
+      </c>
+      <c r="W472" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="X472" t="n">
+        <v>0.964785335262904</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>108.2251082251082</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>0.985663082437276</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>106.7665002773156</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE472" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF472" t="n">
+        <v>1.458607947792657</v>
+      </c>
+      <c r="AG472" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH472" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI472" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>30</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>200</v>
+      </c>
+      <c r="F473" t="n">
+        <v>67</v>
+      </c>
+      <c r="G473" t="n">
+        <v>15</v>
+      </c>
+      <c r="H473" t="n">
+        <v>28</v>
+      </c>
+      <c r="I473" t="n">
+        <v>8</v>
+      </c>
+      <c r="J473" t="n">
+        <v>36</v>
+      </c>
+      <c r="K473" t="n">
+        <v>13</v>
+      </c>
+      <c r="L473" t="n">
+        <v>22</v>
+      </c>
+      <c r="M473" t="n">
+        <v>11</v>
+      </c>
+      <c r="N473" t="n">
+        <v>22</v>
+      </c>
+      <c r="O473" t="n">
+        <v>12</v>
+      </c>
+      <c r="P473" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q473" t="n">
+        <v>15</v>
+      </c>
+      <c r="R473" t="n">
+        <v>26</v>
+      </c>
+      <c r="S473" t="n">
+        <v>24</v>
+      </c>
+      <c r="T473" t="n">
+        <v>2</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="V473" t="n">
+        <v>72</v>
+      </c>
+      <c r="W473" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="X473" t="n">
+        <v>0.7555254848894902</v>
+      </c>
+      <c r="Y473" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="Z473" t="n">
+        <v>86.25128733264675</v>
+      </c>
+      <c r="AA473" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AB473" t="n">
+        <v>98.36065573770492</v>
+      </c>
+      <c r="AC473" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AD473" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE473" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AF473" t="n">
+        <v>-12.10936840505816</v>
+      </c>
+      <c r="AG473" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI473" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>30</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>200</v>
+      </c>
+      <c r="F474" t="n">
+        <v>82</v>
+      </c>
+      <c r="G474" t="n">
+        <v>18</v>
+      </c>
+      <c r="H474" t="n">
+        <v>36</v>
+      </c>
+      <c r="I474" t="n">
+        <v>9</v>
+      </c>
+      <c r="J474" t="n">
+        <v>25</v>
+      </c>
+      <c r="K474" t="n">
+        <v>19</v>
+      </c>
+      <c r="L474" t="n">
+        <v>26</v>
+      </c>
+      <c r="M474" t="n">
+        <v>10</v>
+      </c>
+      <c r="N474" t="n">
+        <v>29</v>
+      </c>
+      <c r="O474" t="n">
+        <v>16</v>
+      </c>
+      <c r="P474" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>13</v>
+      </c>
+      <c r="R474" t="n">
+        <v>21</v>
+      </c>
+      <c r="S474" t="n">
+        <v>23</v>
+      </c>
+      <c r="T474" t="n">
+        <v>2</v>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>2486525</t>
+        </is>
+      </c>
+      <c r="V474" t="n">
+        <v>74</v>
+      </c>
+      <c r="W474" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X474" t="n">
+        <v>0.9597378277153559</v>
+      </c>
+      <c r="Y474" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="Z474" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AA474" t="n">
+        <v>0.9172037679722359</v>
+      </c>
+      <c r="AB474" t="n">
+        <v>101.8161805173363</v>
+      </c>
+      <c r="AC474" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD474" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="AE474" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="AF474" t="n">
+        <v>6.879471656576783</v>
+      </c>
+      <c r="AG474" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH474" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI474" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>30</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>200</v>
+      </c>
+      <c r="F475" t="n">
+        <v>82</v>
+      </c>
+      <c r="G475" t="n">
+        <v>18</v>
+      </c>
+      <c r="H475" t="n">
+        <v>34</v>
+      </c>
+      <c r="I475" t="n">
+        <v>8</v>
+      </c>
+      <c r="J475" t="n">
+        <v>30</v>
+      </c>
+      <c r="K475" t="n">
+        <v>22</v>
+      </c>
+      <c r="L475" t="n">
+        <v>36</v>
+      </c>
+      <c r="M475" t="n">
+        <v>19</v>
+      </c>
+      <c r="N475" t="n">
+        <v>34</v>
+      </c>
+      <c r="O475" t="n">
+        <v>17</v>
+      </c>
+      <c r="P475" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q475" t="n">
+        <v>18</v>
+      </c>
+      <c r="R475" t="n">
+        <v>21</v>
+      </c>
+      <c r="S475" t="n">
+        <v>26</v>
+      </c>
+      <c r="T475" t="n">
+        <v>2</v>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>2486522</t>
+        </is>
+      </c>
+      <c r="V475" t="n">
+        <v>65</v>
+      </c>
+      <c r="W475" t="n">
+        <v>97.84</v>
+      </c>
+      <c r="X475" t="n">
+        <v>0.8381030253475061</v>
+      </c>
+      <c r="Y475" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="Z475" t="n">
+        <v>104.0081177067478</v>
+      </c>
+      <c r="AA475" t="n">
+        <v>0.7705073494547179</v>
+      </c>
+      <c r="AB475" t="n">
+        <v>80.88601294176208</v>
+      </c>
+      <c r="AC475" t="n">
+        <v>0.5135135135135135</v>
+      </c>
+      <c r="AD475" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AE475" t="n">
+        <v>0.7066666666666667</v>
+      </c>
+      <c r="AF475" t="n">
+        <v>23.12210476498576</v>
+      </c>
+      <c r="AG475" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH475" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AI475" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>30</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>200</v>
+      </c>
+      <c r="F476" t="n">
+        <v>74</v>
+      </c>
+      <c r="G476" t="n">
+        <v>16</v>
+      </c>
+      <c r="H476" t="n">
+        <v>32</v>
+      </c>
+      <c r="I476" t="n">
+        <v>11</v>
+      </c>
+      <c r="J476" t="n">
+        <v>39</v>
+      </c>
+      <c r="K476" t="n">
+        <v>9</v>
+      </c>
+      <c r="L476" t="n">
+        <v>12</v>
+      </c>
+      <c r="M476" t="n">
+        <v>13</v>
+      </c>
+      <c r="N476" t="n">
+        <v>28</v>
+      </c>
+      <c r="O476" t="n">
+        <v>14</v>
+      </c>
+      <c r="P476" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>13</v>
+      </c>
+      <c r="R476" t="n">
+        <v>20</v>
+      </c>
+      <c r="S476" t="n">
+        <v>15</v>
+      </c>
+      <c r="T476" t="n">
+        <v>3</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>2486524</t>
+        </is>
+      </c>
+      <c r="V476" t="n">
+        <v>75</v>
+      </c>
+      <c r="W476" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="X476" t="n">
+        <v>0.828853046594982</v>
+      </c>
+      <c r="Y476" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="Z476" t="n">
+        <v>97.01101206082852</v>
+      </c>
+      <c r="AA476" t="n">
+        <v>0.8716875871687588</v>
+      </c>
+      <c r="AB476" t="n">
+        <v>98.63229879011048</v>
+      </c>
+      <c r="AC476" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD476" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="AE476" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF476" t="n">
+        <v>-1.621286729281962</v>
+      </c>
+      <c r="AG476" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI476" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>30</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>225</v>
+      </c>
+      <c r="F477" t="n">
+        <v>94</v>
+      </c>
+      <c r="G477" t="n">
+        <v>17</v>
+      </c>
+      <c r="H477" t="n">
+        <v>30</v>
+      </c>
+      <c r="I477" t="n">
+        <v>15</v>
+      </c>
+      <c r="J477" t="n">
+        <v>49</v>
+      </c>
+      <c r="K477" t="n">
+        <v>15</v>
+      </c>
+      <c r="L477" t="n">
+        <v>20</v>
+      </c>
+      <c r="M477" t="n">
+        <v>11</v>
+      </c>
+      <c r="N477" t="n">
+        <v>34</v>
+      </c>
+      <c r="O477" t="n">
+        <v>20</v>
+      </c>
+      <c r="P477" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q477" t="n">
+        <v>12</v>
+      </c>
+      <c r="R477" t="n">
+        <v>22</v>
+      </c>
+      <c r="S477" t="n">
+        <v>24</v>
+      </c>
+      <c r="T477" t="n">
+        <v>1</v>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>2486526</t>
+        </is>
+      </c>
+      <c r="V477" t="n">
+        <v>87</v>
+      </c>
+      <c r="W477" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="X477" t="n">
+        <v>0.9418837675350702</v>
+      </c>
+      <c r="Y477" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z477" t="n">
+        <v>105.8558558558559</v>
+      </c>
+      <c r="AA477" t="n">
+        <v>0.8855863192182409</v>
+      </c>
+      <c r="AB477" t="n">
+        <v>97.48991483639622</v>
+      </c>
+      <c r="AC477" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD477" t="n">
+        <v>0.7906976744186046</v>
+      </c>
+      <c r="AE477" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="AF477" t="n">
+        <v>8.36594101945964</v>
+      </c>
+      <c r="AG477" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH477" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI477" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>30</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>200</v>
+      </c>
+      <c r="F478" t="n">
+        <v>94</v>
+      </c>
+      <c r="G478" t="n">
+        <v>27</v>
+      </c>
+      <c r="H478" t="n">
+        <v>41</v>
+      </c>
+      <c r="I478" t="n">
+        <v>8</v>
+      </c>
+      <c r="J478" t="n">
+        <v>19</v>
+      </c>
+      <c r="K478" t="n">
+        <v>16</v>
+      </c>
+      <c r="L478" t="n">
+        <v>25</v>
+      </c>
+      <c r="M478" t="n">
+        <v>9</v>
+      </c>
+      <c r="N478" t="n">
+        <v>26</v>
+      </c>
+      <c r="O478" t="n">
+        <v>21</v>
+      </c>
+      <c r="P478" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>10</v>
+      </c>
+      <c r="R478" t="n">
+        <v>16</v>
+      </c>
+      <c r="S478" t="n">
+        <v>23</v>
+      </c>
+      <c r="T478" t="n">
+        <v>1</v>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>2486521</t>
+        </is>
+      </c>
+      <c r="V478" t="n">
+        <v>57</v>
+      </c>
+      <c r="W478" t="n">
+        <v>81</v>
+      </c>
+      <c r="X478" t="n">
+        <v>1.160493827160494</v>
+      </c>
+      <c r="Y478" t="n">
+        <v>72</v>
+      </c>
+      <c r="Z478" t="n">
+        <v>130.5555555555555</v>
+      </c>
+      <c r="AA478" t="n">
+        <v>0.6702728127939793</v>
+      </c>
+      <c r="AB478" t="n">
+        <v>79.12270960577457</v>
+      </c>
+      <c r="AC478" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AD478" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE478" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="AF478" t="n">
+        <v>51.43284594978097</v>
+      </c>
+      <c r="AG478" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH478" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI478" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>30</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>200</v>
+      </c>
+      <c r="F479" t="n">
+        <v>75</v>
+      </c>
+      <c r="G479" t="n">
+        <v>23</v>
+      </c>
+      <c r="H479" t="n">
+        <v>37</v>
+      </c>
+      <c r="I479" t="n">
+        <v>4</v>
+      </c>
+      <c r="J479" t="n">
+        <v>20</v>
+      </c>
+      <c r="K479" t="n">
+        <v>17</v>
+      </c>
+      <c r="L479" t="n">
+        <v>27</v>
+      </c>
+      <c r="M479" t="n">
+        <v>10</v>
+      </c>
+      <c r="N479" t="n">
+        <v>25</v>
+      </c>
+      <c r="O479" t="n">
+        <v>17</v>
+      </c>
+      <c r="P479" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q479" t="n">
+        <v>17</v>
+      </c>
+      <c r="R479" t="n">
+        <v>21</v>
+      </c>
+      <c r="S479" t="n">
+        <v>20</v>
+      </c>
+      <c r="T479" t="n">
+        <v>2</v>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>2486523</t>
+        </is>
+      </c>
+      <c r="V479" t="n">
+        <v>69</v>
+      </c>
+      <c r="W479" t="n">
+        <v>85.88</v>
+      </c>
+      <c r="X479" t="n">
+        <v>0.8733115975780159</v>
+      </c>
+      <c r="Y479" t="n">
+        <v>75.88</v>
+      </c>
+      <c r="Z479" t="n">
+        <v>98.84027411702689</v>
+      </c>
+      <c r="AA479" t="n">
+        <v>0.7971349353049907</v>
+      </c>
+      <c r="AB479" t="n">
+        <v>90.12539184952978</v>
+      </c>
+      <c r="AC479" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="AD479" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE479" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="AF479" t="n">
+        <v>8.714882267497117</v>
+      </c>
+      <c r="AG479" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH479" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI479" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>30</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>200</v>
+      </c>
+      <c r="F480" t="n">
+        <v>65</v>
+      </c>
+      <c r="G480" t="n">
+        <v>22</v>
+      </c>
+      <c r="H480" t="n">
+        <v>45</v>
+      </c>
+      <c r="I480" t="n">
+        <v>3</v>
+      </c>
+      <c r="J480" t="n">
+        <v>17</v>
+      </c>
+      <c r="K480" t="n">
+        <v>12</v>
+      </c>
+      <c r="L480" t="n">
+        <v>19</v>
+      </c>
+      <c r="M480" t="n">
+        <v>4</v>
+      </c>
+      <c r="N480" t="n">
+        <v>18</v>
+      </c>
+      <c r="O480" t="n">
+        <v>6</v>
+      </c>
+      <c r="P480" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>14</v>
+      </c>
+      <c r="R480" t="n">
+        <v>27</v>
+      </c>
+      <c r="S480" t="n">
+        <v>21</v>
+      </c>
+      <c r="T480" t="n">
+        <v>2</v>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>2486522</t>
+        </is>
+      </c>
+      <c r="V480" t="n">
+        <v>82</v>
+      </c>
+      <c r="W480" t="n">
+        <v>84.36</v>
+      </c>
+      <c r="X480" t="n">
+        <v>0.7705073494547179</v>
+      </c>
+      <c r="Y480" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="Z480" t="n">
+        <v>80.88601294176208</v>
+      </c>
+      <c r="AA480" t="n">
+        <v>0.8381030253475061</v>
+      </c>
+      <c r="AB480" t="n">
+        <v>104.0081177067478</v>
+      </c>
+      <c r="AC480" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AD480" t="n">
+        <v>0.4864864864864865</v>
+      </c>
+      <c r="AE480" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="AF480" t="n">
+        <v>-23.12210476498576</v>
+      </c>
+      <c r="AG480" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH480" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AI480" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>30</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>200</v>
+      </c>
+      <c r="F481" t="n">
+        <v>72</v>
+      </c>
+      <c r="G481" t="n">
+        <v>15</v>
+      </c>
+      <c r="H481" t="n">
+        <v>24</v>
+      </c>
+      <c r="I481" t="n">
+        <v>7</v>
+      </c>
+      <c r="J481" t="n">
+        <v>28</v>
+      </c>
+      <c r="K481" t="n">
+        <v>21</v>
+      </c>
+      <c r="L481" t="n">
+        <v>30</v>
+      </c>
+      <c r="M481" t="n">
+        <v>6</v>
+      </c>
+      <c r="N481" t="n">
+        <v>21</v>
+      </c>
+      <c r="O481" t="n">
+        <v>11</v>
+      </c>
+      <c r="P481" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q481" t="n">
+        <v>14</v>
+      </c>
+      <c r="R481" t="n">
+        <v>24</v>
+      </c>
+      <c r="S481" t="n">
+        <v>26</v>
+      </c>
+      <c r="T481" t="n">
+        <v>2</v>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>2486520</t>
+        </is>
+      </c>
+      <c r="V481" t="n">
+        <v>67</v>
+      </c>
+      <c r="W481" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="X481" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="Y481" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="Z481" t="n">
+        <v>98.36065573770492</v>
+      </c>
+      <c r="AA481" t="n">
+        <v>0.7555254848894902</v>
+      </c>
+      <c r="AB481" t="n">
+        <v>86.25128733264675</v>
+      </c>
+      <c r="AC481" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD481" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AE481" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AF481" t="n">
+        <v>12.10936840505816</v>
+      </c>
+      <c r="AG481" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH481" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI481" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>31</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>200</v>
+      </c>
+      <c r="F482" t="n">
+        <v>89</v>
+      </c>
+      <c r="G482" t="n">
+        <v>20</v>
+      </c>
+      <c r="H482" t="n">
+        <v>34</v>
+      </c>
+      <c r="I482" t="n">
+        <v>14</v>
+      </c>
+      <c r="J482" t="n">
+        <v>36</v>
+      </c>
+      <c r="K482" t="n">
+        <v>7</v>
+      </c>
+      <c r="L482" t="n">
+        <v>14</v>
+      </c>
+      <c r="M482" t="n">
+        <v>15</v>
+      </c>
+      <c r="N482" t="n">
+        <v>24</v>
+      </c>
+      <c r="O482" t="n">
+        <v>23</v>
+      </c>
+      <c r="P482" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q482" t="n">
+        <v>9</v>
+      </c>
+      <c r="R482" t="n">
+        <v>18</v>
+      </c>
+      <c r="S482" t="n">
+        <v>19</v>
+      </c>
+      <c r="T482" t="n">
+        <v>0</v>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>2486535</t>
+        </is>
+      </c>
+      <c r="V482" t="n">
+        <v>74</v>
+      </c>
+      <c r="W482" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="X482" t="n">
+        <v>1.045091592296853</v>
+      </c>
+      <c r="Y482" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="Z482" t="n">
+        <v>126.8529076396807</v>
+      </c>
+      <c r="AA482" t="n">
+        <v>0.9245377311344328</v>
+      </c>
+      <c r="AB482" t="n">
+        <v>99.94597514856835</v>
+      </c>
+      <c r="AC482" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AD482" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AE482" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AF482" t="n">
+        <v>26.90693249111239</v>
+      </c>
+      <c r="AG482" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH482" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI482" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>31</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>200</v>
+      </c>
+      <c r="F483" t="n">
+        <v>78</v>
+      </c>
+      <c r="G483" t="n">
+        <v>19</v>
+      </c>
+      <c r="H483" t="n">
+        <v>45</v>
+      </c>
+      <c r="I483" t="n">
+        <v>8</v>
+      </c>
+      <c r="J483" t="n">
+        <v>22</v>
+      </c>
+      <c r="K483" t="n">
+        <v>16</v>
+      </c>
+      <c r="L483" t="n">
+        <v>19</v>
+      </c>
+      <c r="M483" t="n">
+        <v>12</v>
+      </c>
+      <c r="N483" t="n">
+        <v>29</v>
+      </c>
+      <c r="O483" t="n">
+        <v>15</v>
+      </c>
+      <c r="P483" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q483" t="n">
+        <v>16</v>
+      </c>
+      <c r="R483" t="n">
+        <v>21</v>
+      </c>
+      <c r="S483" t="n">
+        <v>20</v>
+      </c>
+      <c r="T483" t="n">
+        <v>2</v>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>2486533</t>
+        </is>
+      </c>
+      <c r="V483" t="n">
+        <v>64</v>
+      </c>
+      <c r="W483" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="X483" t="n">
+        <v>0.8537653239929948</v>
+      </c>
+      <c r="Y483" t="n">
+        <v>79.36</v>
+      </c>
+      <c r="Z483" t="n">
+        <v>98.28629032258064</v>
+      </c>
+      <c r="AA483" t="n">
+        <v>0.7191011235955056</v>
+      </c>
+      <c r="AB483" t="n">
+        <v>81.01265822784811</v>
+      </c>
+      <c r="AC483" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="AD483" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE483" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF483" t="n">
+        <v>17.27363209473253</v>
+      </c>
+      <c r="AG483" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH483" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI483" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>31</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>200</v>
+      </c>
+      <c r="F484" t="n">
+        <v>90</v>
+      </c>
+      <c r="G484" t="n">
+        <v>22</v>
+      </c>
+      <c r="H484" t="n">
+        <v>36</v>
+      </c>
+      <c r="I484" t="n">
+        <v>10</v>
+      </c>
+      <c r="J484" t="n">
+        <v>25</v>
+      </c>
+      <c r="K484" t="n">
+        <v>16</v>
+      </c>
+      <c r="L484" t="n">
+        <v>26</v>
+      </c>
+      <c r="M484" t="n">
+        <v>13</v>
+      </c>
+      <c r="N484" t="n">
+        <v>24</v>
+      </c>
+      <c r="O484" t="n">
+        <v>20</v>
+      </c>
+      <c r="P484" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q484" t="n">
+        <v>14</v>
+      </c>
+      <c r="R484" t="n">
+        <v>24</v>
+      </c>
+      <c r="S484" t="n">
+        <v>25</v>
+      </c>
+      <c r="T484" t="n">
+        <v>2</v>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="V484" t="n">
+        <v>93</v>
+      </c>
+      <c r="W484" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="X484" t="n">
+        <v>1.041184636742249</v>
+      </c>
+      <c r="Y484" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="Z484" t="n">
+        <v>122.5490196078431</v>
+      </c>
+      <c r="AA484" t="n">
+        <v>1.085941148995796</v>
+      </c>
+      <c r="AB484" t="n">
+        <v>118.2604272634791</v>
+      </c>
+      <c r="AC484" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="AD484" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AE484" t="n">
+        <v>0.5967741935483871</v>
+      </c>
+      <c r="AF484" t="n">
+        <v>4.288592344363991</v>
+      </c>
+      <c r="AG484" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH484" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI484" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>31</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>200</v>
+      </c>
+      <c r="F485" t="n">
+        <v>63</v>
+      </c>
+      <c r="G485" t="n">
+        <v>15</v>
+      </c>
+      <c r="H485" t="n">
+        <v>42</v>
+      </c>
+      <c r="I485" t="n">
+        <v>8</v>
+      </c>
+      <c r="J485" t="n">
+        <v>23</v>
+      </c>
+      <c r="K485" t="n">
+        <v>9</v>
+      </c>
+      <c r="L485" t="n">
+        <v>14</v>
+      </c>
+      <c r="M485" t="n">
+        <v>10</v>
+      </c>
+      <c r="N485" t="n">
+        <v>19</v>
+      </c>
+      <c r="O485" t="n">
+        <v>15</v>
+      </c>
+      <c r="P485" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q485" t="n">
+        <v>9</v>
+      </c>
+      <c r="R485" t="n">
+        <v>18</v>
+      </c>
+      <c r="S485" t="n">
+        <v>17</v>
+      </c>
+      <c r="T485" t="n">
+        <v>1</v>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="V485" t="n">
+        <v>73</v>
+      </c>
+      <c r="W485" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X485" t="n">
+        <v>0.7859281437125749</v>
+      </c>
+      <c r="Y485" t="n">
+        <v>70.16</v>
+      </c>
+      <c r="Z485" t="n">
+        <v>89.79475484606614</v>
+      </c>
+      <c r="AA485" t="n">
+        <v>0.9843581445523194</v>
+      </c>
+      <c r="AB485" t="n">
+        <v>110.3385731559855</v>
+      </c>
+      <c r="AC485" t="n">
+        <v>0.2702702702702703</v>
+      </c>
+      <c r="AD485" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="AE485" t="n">
+        <v>0.453125</v>
+      </c>
+      <c r="AF485" t="n">
+        <v>-20.54381830991936</v>
+      </c>
+      <c r="AG485" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH485" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI485" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>31</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>200</v>
+      </c>
+      <c r="F486" t="n">
+        <v>89</v>
+      </c>
+      <c r="G486" t="n">
+        <v>24</v>
+      </c>
+      <c r="H486" t="n">
+        <v>44</v>
+      </c>
+      <c r="I486" t="n">
+        <v>7</v>
+      </c>
+      <c r="J486" t="n">
+        <v>20</v>
+      </c>
+      <c r="K486" t="n">
+        <v>20</v>
+      </c>
+      <c r="L486" t="n">
+        <v>21</v>
+      </c>
+      <c r="M486" t="n">
+        <v>4</v>
+      </c>
+      <c r="N486" t="n">
+        <v>26</v>
+      </c>
+      <c r="O486" t="n">
+        <v>20</v>
+      </c>
+      <c r="P486" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q486" t="n">
+        <v>9</v>
+      </c>
+      <c r="R486" t="n">
+        <v>18</v>
+      </c>
+      <c r="S486" t="n">
+        <v>21</v>
+      </c>
+      <c r="T486" t="n">
+        <v>1</v>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="V486" t="n">
+        <v>80</v>
+      </c>
+      <c r="W486" t="n">
+        <v>82.24000000000001</v>
+      </c>
+      <c r="X486" t="n">
+        <v>1.082198443579766</v>
+      </c>
+      <c r="Y486" t="n">
+        <v>78.24000000000001</v>
+      </c>
+      <c r="Z486" t="n">
+        <v>113.7525562372188</v>
+      </c>
+      <c r="AA486" t="n">
+        <v>0.9737098344693281</v>
+      </c>
+      <c r="AB486" t="n">
+        <v>103.6806635562468</v>
+      </c>
+      <c r="AC486" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="AD486" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AE486" t="n">
+        <v>0.4918032786885246</v>
+      </c>
+      <c r="AF486" t="n">
+        <v>10.07189268097203</v>
+      </c>
+      <c r="AG486" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH486" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI486" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>31</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>200</v>
+      </c>
+      <c r="F487" t="n">
+        <v>80</v>
+      </c>
+      <c r="G487" t="n">
+        <v>16</v>
+      </c>
+      <c r="H487" t="n">
+        <v>30</v>
+      </c>
+      <c r="I487" t="n">
+        <v>13</v>
+      </c>
+      <c r="J487" t="n">
+        <v>32</v>
+      </c>
+      <c r="K487" t="n">
+        <v>9</v>
+      </c>
+      <c r="L487" t="n">
+        <v>14</v>
+      </c>
+      <c r="M487" t="n">
+        <v>5</v>
+      </c>
+      <c r="N487" t="n">
+        <v>26</v>
+      </c>
+      <c r="O487" t="n">
+        <v>20</v>
+      </c>
+      <c r="P487" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q487" t="n">
+        <v>14</v>
+      </c>
+      <c r="R487" t="n">
+        <v>21</v>
+      </c>
+      <c r="S487" t="n">
+        <v>16</v>
+      </c>
+      <c r="T487" t="n">
+        <v>2</v>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>2486536</t>
+        </is>
+      </c>
+      <c r="V487" t="n">
+        <v>89</v>
+      </c>
+      <c r="W487" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="X487" t="n">
+        <v>0.9737098344693281</v>
+      </c>
+      <c r="Y487" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="Z487" t="n">
+        <v>103.6806635562468</v>
+      </c>
+      <c r="AA487" t="n">
+        <v>1.082198443579766</v>
+      </c>
+      <c r="AB487" t="n">
+        <v>113.7525562372188</v>
+      </c>
+      <c r="AC487" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AD487" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AE487" t="n">
+        <v>0.5081967213114754</v>
+      </c>
+      <c r="AF487" t="n">
+        <v>-10.07189268097203</v>
+      </c>
+      <c r="AG487" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AH487" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AI487" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>31</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>200</v>
+      </c>
+      <c r="F488" t="n">
+        <v>64</v>
+      </c>
+      <c r="G488" t="n">
+        <v>14</v>
+      </c>
+      <c r="H488" t="n">
+        <v>26</v>
+      </c>
+      <c r="I488" t="n">
+        <v>7</v>
+      </c>
+      <c r="J488" t="n">
+        <v>35</v>
+      </c>
+      <c r="K488" t="n">
+        <v>15</v>
+      </c>
+      <c r="L488" t="n">
+        <v>25</v>
+      </c>
+      <c r="M488" t="n">
+        <v>10</v>
+      </c>
+      <c r="N488" t="n">
+        <v>26</v>
+      </c>
+      <c r="O488" t="n">
+        <v>17</v>
+      </c>
+      <c r="P488" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>17</v>
+      </c>
+      <c r="R488" t="n">
+        <v>20</v>
+      </c>
+      <c r="S488" t="n">
+        <v>21</v>
+      </c>
+      <c r="T488" t="n">
+        <v>4</v>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>2486533</t>
+        </is>
+      </c>
+      <c r="V488" t="n">
+        <v>78</v>
+      </c>
+      <c r="W488" t="n">
+        <v>89</v>
+      </c>
+      <c r="X488" t="n">
+        <v>0.7191011235955056</v>
+      </c>
+      <c r="Y488" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z488" t="n">
+        <v>81.01265822784811</v>
+      </c>
+      <c r="AA488" t="n">
+        <v>0.8537653239929948</v>
+      </c>
+      <c r="AB488" t="n">
+        <v>98.28629032258064</v>
+      </c>
+      <c r="AC488" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD488" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AE488" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF488" t="n">
+        <v>-17.27363209473253</v>
+      </c>
+      <c r="AG488" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AH488" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AI488" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>31</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>225</v>
+      </c>
+      <c r="F489" t="n">
+        <v>99</v>
+      </c>
+      <c r="G489" t="n">
+        <v>18</v>
+      </c>
+      <c r="H489" t="n">
+        <v>36</v>
+      </c>
+      <c r="I489" t="n">
+        <v>16</v>
+      </c>
+      <c r="J489" t="n">
+        <v>35</v>
+      </c>
+      <c r="K489" t="n">
+        <v>15</v>
+      </c>
+      <c r="L489" t="n">
+        <v>20</v>
+      </c>
+      <c r="M489" t="n">
+        <v>3</v>
+      </c>
+      <c r="N489" t="n">
+        <v>24</v>
+      </c>
+      <c r="O489" t="n">
+        <v>15</v>
+      </c>
+      <c r="P489" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>12</v>
+      </c>
+      <c r="R489" t="n">
+        <v>21</v>
+      </c>
+      <c r="S489" t="n">
+        <v>19</v>
+      </c>
+      <c r="T489" t="n">
+        <v>1</v>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="V489" t="n">
+        <v>96</v>
+      </c>
+      <c r="W489" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="X489" t="n">
+        <v>1.07843137254902</v>
+      </c>
+      <c r="Y489" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="Z489" t="n">
+        <v>111.4864864864865</v>
+      </c>
+      <c r="AA489" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="AB489" t="n">
+        <v>109.0909090909091</v>
+      </c>
+      <c r="AC489" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AD489" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AE489" t="n">
+        <v>0.4029850746268657</v>
+      </c>
+      <c r="AF489" t="n">
+        <v>2.395577395577391</v>
+      </c>
+      <c r="AG489" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH489" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI489" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>31</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>200</v>
+      </c>
+      <c r="F490" t="n">
+        <v>72</v>
+      </c>
+      <c r="G490" t="n">
+        <v>15</v>
+      </c>
+      <c r="H490" t="n">
+        <v>35</v>
+      </c>
+      <c r="I490" t="n">
+        <v>10</v>
+      </c>
+      <c r="J490" t="n">
+        <v>27</v>
+      </c>
+      <c r="K490" t="n">
+        <v>12</v>
+      </c>
+      <c r="L490" t="n">
+        <v>17</v>
+      </c>
+      <c r="M490" t="n">
+        <v>8</v>
+      </c>
+      <c r="N490" t="n">
+        <v>20</v>
+      </c>
+      <c r="O490" t="n">
+        <v>13</v>
+      </c>
+      <c r="P490" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>9</v>
+      </c>
+      <c r="R490" t="n">
+        <v>27</v>
+      </c>
+      <c r="S490" t="n">
+        <v>22</v>
+      </c>
+      <c r="T490" t="n">
+        <v>2</v>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>2486531</t>
+        </is>
+      </c>
+      <c r="V490" t="n">
+        <v>81</v>
+      </c>
+      <c r="W490" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="X490" t="n">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="Y490" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="Z490" t="n">
+        <v>102.1566401816118</v>
+      </c>
+      <c r="AA490" t="n">
+        <v>0.9839650145772596</v>
+      </c>
+      <c r="AB490" t="n">
+        <v>113.5726303982053</v>
+      </c>
+      <c r="AC490" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD490" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AE490" t="n">
+        <v>0.4307692307692308</v>
+      </c>
+      <c r="AF490" t="n">
+        <v>-11.41599021659347</v>
+      </c>
+      <c r="AG490" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH490" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI490" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>31</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>200</v>
+      </c>
+      <c r="F491" t="n">
+        <v>73</v>
+      </c>
+      <c r="G491" t="n">
+        <v>26</v>
+      </c>
+      <c r="H491" t="n">
+        <v>42</v>
+      </c>
+      <c r="I491" t="n">
+        <v>4</v>
+      </c>
+      <c r="J491" t="n">
+        <v>18</v>
+      </c>
+      <c r="K491" t="n">
+        <v>9</v>
+      </c>
+      <c r="L491" t="n">
+        <v>14</v>
+      </c>
+      <c r="M491" t="n">
+        <v>8</v>
+      </c>
+      <c r="N491" t="n">
+        <v>27</v>
+      </c>
+      <c r="O491" t="n">
+        <v>23</v>
+      </c>
+      <c r="P491" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>8</v>
+      </c>
+      <c r="R491" t="n">
+        <v>18</v>
+      </c>
+      <c r="S491" t="n">
+        <v>18</v>
+      </c>
+      <c r="T491" t="n">
+        <v>6</v>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>2486529</t>
+        </is>
+      </c>
+      <c r="V491" t="n">
+        <v>63</v>
+      </c>
+      <c r="W491" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="X491" t="n">
+        <v>0.9843581445523194</v>
+      </c>
+      <c r="Y491" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="Z491" t="n">
+        <v>110.3385731559855</v>
+      </c>
+      <c r="AA491" t="n">
+        <v>0.7859281437125749</v>
+      </c>
+      <c r="AB491" t="n">
+        <v>89.79475484606614</v>
+      </c>
+      <c r="AC491" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="AD491" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="AE491" t="n">
+        <v>0.546875</v>
+      </c>
+      <c r="AF491" t="n">
+        <v>20.54381830991936</v>
+      </c>
+      <c r="AG491" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH491" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AI491" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>31</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>200</v>
+      </c>
+      <c r="F492" t="n">
+        <v>81</v>
+      </c>
+      <c r="G492" t="n">
+        <v>12</v>
+      </c>
+      <c r="H492" t="n">
+        <v>31</v>
+      </c>
+      <c r="I492" t="n">
+        <v>12</v>
+      </c>
+      <c r="J492" t="n">
+        <v>31</v>
+      </c>
+      <c r="K492" t="n">
+        <v>21</v>
+      </c>
+      <c r="L492" t="n">
+        <v>28</v>
+      </c>
+      <c r="M492" t="n">
+        <v>11</v>
+      </c>
+      <c r="N492" t="n">
+        <v>26</v>
+      </c>
+      <c r="O492" t="n">
+        <v>21</v>
+      </c>
+      <c r="P492" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>8</v>
+      </c>
+      <c r="R492" t="n">
+        <v>22</v>
+      </c>
+      <c r="S492" t="n">
+        <v>27</v>
+      </c>
+      <c r="T492" t="n">
+        <v>3</v>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>2486531</t>
+        </is>
+      </c>
+      <c r="V492" t="n">
+        <v>72</v>
+      </c>
+      <c r="W492" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="X492" t="n">
+        <v>0.9839650145772596</v>
+      </c>
+      <c r="Y492" t="n">
+        <v>71.31999999999999</v>
+      </c>
+      <c r="Z492" t="n">
+        <v>113.5726303982053</v>
+      </c>
+      <c r="AA492" t="n">
+        <v>0.9174311926605504</v>
+      </c>
+      <c r="AB492" t="n">
+        <v>102.1566401816118</v>
+      </c>
+      <c r="AC492" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="AD492" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE492" t="n">
+        <v>0.5692307692307692</v>
+      </c>
+      <c r="AF492" t="n">
+        <v>11.41599021659347</v>
+      </c>
+      <c r="AG492" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AH492" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI492" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>31</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>200</v>
+      </c>
+      <c r="F493" t="n">
+        <v>73</v>
+      </c>
+      <c r="G493" t="n">
+        <v>14</v>
+      </c>
+      <c r="H493" t="n">
+        <v>26</v>
+      </c>
+      <c r="I493" t="n">
+        <v>10</v>
+      </c>
+      <c r="J493" t="n">
+        <v>34</v>
+      </c>
+      <c r="K493" t="n">
+        <v>15</v>
+      </c>
+      <c r="L493" t="n">
+        <v>20</v>
+      </c>
+      <c r="M493" t="n">
+        <v>11</v>
+      </c>
+      <c r="N493" t="n">
+        <v>26</v>
+      </c>
+      <c r="O493" t="n">
+        <v>10</v>
+      </c>
+      <c r="P493" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>15</v>
+      </c>
+      <c r="R493" t="n">
+        <v>17</v>
+      </c>
+      <c r="S493" t="n">
+        <v>21</v>
+      </c>
+      <c r="T493" t="n">
+        <v>0</v>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>2486532</t>
+        </is>
+      </c>
+      <c r="V493" t="n">
+        <v>86</v>
+      </c>
+      <c r="W493" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X493" t="n">
+        <v>0.8711217183770883</v>
+      </c>
+      <c r="Y493" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z493" t="n">
+        <v>100.2747252747253</v>
+      </c>
+      <c r="AA493" t="n">
+        <v>1.072854291417166</v>
+      </c>
+      <c r="AB493" t="n">
+        <v>117.550574084199</v>
+      </c>
+      <c r="AC493" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD493" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="AE493" t="n">
+        <v>0.5362318840579711</v>
+      </c>
+      <c r="AF493" t="n">
+        <v>-17.27584880947374</v>
+      </c>
+      <c r="AG493" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH493" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI493" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>31</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>225</v>
+      </c>
+      <c r="F494" t="n">
+        <v>96</v>
+      </c>
+      <c r="G494" t="n">
+        <v>19</v>
+      </c>
+      <c r="H494" t="n">
+        <v>35</v>
+      </c>
+      <c r="I494" t="n">
+        <v>13</v>
+      </c>
+      <c r="J494" t="n">
+        <v>37</v>
+      </c>
+      <c r="K494" t="n">
+        <v>19</v>
+      </c>
+      <c r="L494" t="n">
+        <v>25</v>
+      </c>
+      <c r="M494" t="n">
+        <v>11</v>
+      </c>
+      <c r="N494" t="n">
+        <v>29</v>
+      </c>
+      <c r="O494" t="n">
+        <v>13</v>
+      </c>
+      <c r="P494" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>16</v>
+      </c>
+      <c r="R494" t="n">
+        <v>19</v>
+      </c>
+      <c r="S494" t="n">
+        <v>21</v>
+      </c>
+      <c r="T494" t="n">
+        <v>2</v>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>2486530</t>
+        </is>
+      </c>
+      <c r="V494" t="n">
+        <v>99</v>
+      </c>
+      <c r="W494" t="n">
+        <v>99</v>
+      </c>
+      <c r="X494" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="Y494" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z494" t="n">
+        <v>109.0909090909091</v>
+      </c>
+      <c r="AA494" t="n">
+        <v>1.07843137254902</v>
+      </c>
+      <c r="AB494" t="n">
+        <v>111.4864864864865</v>
+      </c>
+      <c r="AC494" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="AD494" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="AE494" t="n">
+        <v>0.5970149253731343</v>
+      </c>
+      <c r="AF494" t="n">
+        <v>-2.395577395577391</v>
+      </c>
+      <c r="AG494" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AH494" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI494" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>31</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>200</v>
+      </c>
+      <c r="F495" t="n">
+        <v>86</v>
+      </c>
+      <c r="G495" t="n">
+        <v>18</v>
+      </c>
+      <c r="H495" t="n">
+        <v>33</v>
+      </c>
+      <c r="I495" t="n">
+        <v>13</v>
+      </c>
+      <c r="J495" t="n">
+        <v>33</v>
+      </c>
+      <c r="K495" t="n">
+        <v>11</v>
+      </c>
+      <c r="L495" t="n">
+        <v>14</v>
+      </c>
+      <c r="M495" t="n">
+        <v>7</v>
+      </c>
+      <c r="N495" t="n">
+        <v>25</v>
+      </c>
+      <c r="O495" t="n">
+        <v>20</v>
+      </c>
+      <c r="P495" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>8</v>
+      </c>
+      <c r="R495" t="n">
+        <v>21</v>
+      </c>
+      <c r="S495" t="n">
+        <v>17</v>
+      </c>
+      <c r="T495" t="n">
+        <v>2</v>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>2486532</t>
+        </is>
+      </c>
+      <c r="V495" t="n">
+        <v>73</v>
+      </c>
+      <c r="W495" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="X495" t="n">
+        <v>1.072854291417166</v>
+      </c>
+      <c r="Y495" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="Z495" t="n">
+        <v>117.550574084199</v>
+      </c>
+      <c r="AA495" t="n">
+        <v>0.8711217183770883</v>
+      </c>
+      <c r="AB495" t="n">
+        <v>100.2747252747253</v>
+      </c>
+      <c r="AC495" t="n">
+        <v>0.2121212121212121</v>
+      </c>
+      <c r="AD495" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE495" t="n">
+        <v>0.463768115942029</v>
+      </c>
+      <c r="AF495" t="n">
+        <v>17.27584880947374</v>
+      </c>
+      <c r="AG495" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH495" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AI495" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>31</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>200</v>
+      </c>
+      <c r="F496" t="n">
+        <v>74</v>
+      </c>
+      <c r="G496" t="n">
+        <v>24</v>
+      </c>
+      <c r="H496" t="n">
+        <v>43</v>
+      </c>
+      <c r="I496" t="n">
+        <v>5</v>
+      </c>
+      <c r="J496" t="n">
+        <v>18</v>
+      </c>
+      <c r="K496" t="n">
+        <v>11</v>
+      </c>
+      <c r="L496" t="n">
+        <v>16</v>
+      </c>
+      <c r="M496" t="n">
+        <v>6</v>
+      </c>
+      <c r="N496" t="n">
+        <v>21</v>
+      </c>
+      <c r="O496" t="n">
+        <v>16</v>
+      </c>
+      <c r="P496" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>12</v>
+      </c>
+      <c r="R496" t="n">
+        <v>19</v>
+      </c>
+      <c r="S496" t="n">
+        <v>18</v>
+      </c>
+      <c r="T496" t="n">
+        <v>4</v>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>2486535</t>
+        </is>
+      </c>
+      <c r="V496" t="n">
+        <v>89</v>
+      </c>
+      <c r="W496" t="n">
+        <v>80.03999999999999</v>
+      </c>
+      <c r="X496" t="n">
+        <v>0.9245377311344328</v>
+      </c>
+      <c r="Y496" t="n">
+        <v>74.03999999999999</v>
+      </c>
+      <c r="Z496" t="n">
+        <v>99.94597514856835</v>
+      </c>
+      <c r="AA496" t="n">
+        <v>1.045091592296853</v>
+      </c>
+      <c r="AB496" t="n">
+        <v>126.8529076396807</v>
+      </c>
+      <c r="AC496" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD496" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AE496" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="AF496" t="n">
+        <v>-26.90693249111239</v>
+      </c>
+      <c r="AG496" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AH496" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI496" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>31</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>200</v>
+      </c>
+      <c r="F497" t="n">
+        <v>93</v>
+      </c>
+      <c r="G497" t="n">
+        <v>13</v>
+      </c>
+      <c r="H497" t="n">
+        <v>35</v>
+      </c>
+      <c r="I497" t="n">
+        <v>13</v>
+      </c>
+      <c r="J497" t="n">
+        <v>25</v>
+      </c>
+      <c r="K497" t="n">
+        <v>28</v>
+      </c>
+      <c r="L497" t="n">
+        <v>31</v>
+      </c>
+      <c r="M497" t="n">
+        <v>7</v>
+      </c>
+      <c r="N497" t="n">
+        <v>18</v>
+      </c>
+      <c r="O497" t="n">
+        <v>21</v>
+      </c>
+      <c r="P497" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>12</v>
+      </c>
+      <c r="R497" t="n">
+        <v>25</v>
+      </c>
+      <c r="S497" t="n">
+        <v>24</v>
+      </c>
+      <c r="T497" t="n">
+        <v>3</v>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>2486534</t>
+        </is>
+      </c>
+      <c r="V497" t="n">
+        <v>90</v>
+      </c>
+      <c r="W497" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="X497" t="n">
+        <v>1.085941148995796</v>
+      </c>
+      <c r="Y497" t="n">
+        <v>78.64</v>
+      </c>
+      <c r="Z497" t="n">
+        <v>118.2604272634791</v>
+      </c>
+      <c r="AA497" t="n">
+        <v>1.041184636742249</v>
+      </c>
+      <c r="AB497" t="n">
+        <v>122.5490196078431</v>
+      </c>
+      <c r="AC497" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="AD497" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="AE497" t="n">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="AF497" t="n">
+        <v>-4.288592344363991</v>
+      </c>
+      <c r="AG497" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AH497" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI497" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>32</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>200</v>
+      </c>
+      <c r="F498" t="n">
+        <v>86</v>
+      </c>
+      <c r="G498" t="n">
+        <v>21</v>
+      </c>
+      <c r="H498" t="n">
+        <v>40</v>
+      </c>
+      <c r="I498" t="n">
+        <v>9</v>
+      </c>
+      <c r="J498" t="n">
+        <v>28</v>
+      </c>
+      <c r="K498" t="n">
+        <v>17</v>
+      </c>
+      <c r="L498" t="n">
+        <v>26</v>
+      </c>
+      <c r="M498" t="n">
+        <v>11</v>
+      </c>
+      <c r="N498" t="n">
+        <v>18</v>
+      </c>
+      <c r="O498" t="n">
+        <v>18</v>
+      </c>
+      <c r="P498" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>4</v>
+      </c>
+      <c r="R498" t="n">
+        <v>19</v>
+      </c>
+      <c r="S498" t="n">
+        <v>26</v>
+      </c>
+      <c r="T498" t="n">
+        <v>2</v>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="V498" t="n">
+        <v>89</v>
+      </c>
+      <c r="W498" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="X498" t="n">
+        <v>1.030680728667306</v>
+      </c>
+      <c r="Y498" t="n">
+        <v>72.44</v>
+      </c>
+      <c r="Z498" t="n">
+        <v>118.7189398122584</v>
+      </c>
+      <c r="AA498" t="n">
+        <v>1.155244029075805</v>
+      </c>
+      <c r="AB498" t="n">
+        <v>123.5424764019989</v>
+      </c>
+      <c r="AC498" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD498" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="AE498" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF498" t="n">
+        <v>-4.823536589740471</v>
+      </c>
+      <c r="AG498" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH498" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI498" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>32</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>200</v>
+      </c>
+      <c r="F499" t="n">
+        <v>70</v>
+      </c>
+      <c r="G499" t="n">
+        <v>18</v>
+      </c>
+      <c r="H499" t="n">
+        <v>34</v>
+      </c>
+      <c r="I499" t="n">
+        <v>5</v>
+      </c>
+      <c r="J499" t="n">
+        <v>23</v>
+      </c>
+      <c r="K499" t="n">
+        <v>19</v>
+      </c>
+      <c r="L499" t="n">
+        <v>30</v>
+      </c>
+      <c r="M499" t="n">
+        <v>10</v>
+      </c>
+      <c r="N499" t="n">
+        <v>23</v>
+      </c>
+      <c r="O499" t="n">
+        <v>11</v>
+      </c>
+      <c r="P499" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>9</v>
+      </c>
+      <c r="R499" t="n">
+        <v>27</v>
+      </c>
+      <c r="S499" t="n">
+        <v>28</v>
+      </c>
+      <c r="T499" t="n">
+        <v>2</v>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="V499" t="n">
+        <v>73</v>
+      </c>
+      <c r="W499" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="X499" t="n">
+        <v>0.8838383838383838</v>
+      </c>
+      <c r="Y499" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="Z499" t="n">
+        <v>101.1560693641619</v>
+      </c>
+      <c r="AA499" t="n">
+        <v>0.9554973821989529</v>
+      </c>
+      <c r="AB499" t="n">
+        <v>106.7251461988304</v>
+      </c>
+      <c r="AC499" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD499" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="AE499" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF499" t="n">
+        <v>-5.56907683466855</v>
+      </c>
+      <c r="AG499" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH499" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI499" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>32</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>200</v>
+      </c>
+      <c r="F500" t="n">
+        <v>70</v>
+      </c>
+      <c r="G500" t="n">
+        <v>13</v>
+      </c>
+      <c r="H500" t="n">
+        <v>34</v>
+      </c>
+      <c r="I500" t="n">
+        <v>11</v>
+      </c>
+      <c r="J500" t="n">
+        <v>30</v>
+      </c>
+      <c r="K500" t="n">
+        <v>11</v>
+      </c>
+      <c r="L500" t="n">
+        <v>21</v>
+      </c>
+      <c r="M500" t="n">
+        <v>11</v>
+      </c>
+      <c r="N500" t="n">
+        <v>25</v>
+      </c>
+      <c r="O500" t="n">
+        <v>15</v>
+      </c>
+      <c r="P500" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>10</v>
+      </c>
+      <c r="R500" t="n">
+        <v>16</v>
+      </c>
+      <c r="S500" t="n">
+        <v>20</v>
+      </c>
+      <c r="T500" t="n">
+        <v>1</v>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>2486542</t>
+        </is>
+      </c>
+      <c r="V500" t="n">
+        <v>92</v>
+      </c>
+      <c r="W500" t="n">
+        <v>83.24000000000001</v>
+      </c>
+      <c r="X500" t="n">
+        <v>0.8409418548774626</v>
+      </c>
+      <c r="Y500" t="n">
+        <v>72.24000000000001</v>
+      </c>
+      <c r="Z500" t="n">
+        <v>96.89922480620154</v>
+      </c>
+      <c r="AA500" t="n">
+        <v>1.108968177434908</v>
+      </c>
+      <c r="AB500" t="n">
+        <v>127.8488048916064</v>
+      </c>
+      <c r="AC500" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="AD500" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE500" t="n">
+        <v>0.4675324675324675</v>
+      </c>
+      <c r="AF500" t="n">
+        <v>-30.94958008540489</v>
+      </c>
+      <c r="AG500" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH500" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI500" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>32</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>200</v>
+      </c>
+      <c r="F501" t="n">
+        <v>91</v>
+      </c>
+      <c r="G501" t="n">
+        <v>24</v>
+      </c>
+      <c r="H501" t="n">
+        <v>37</v>
+      </c>
+      <c r="I501" t="n">
+        <v>10</v>
+      </c>
+      <c r="J501" t="n">
+        <v>26</v>
+      </c>
+      <c r="K501" t="n">
+        <v>13</v>
+      </c>
+      <c r="L501" t="n">
+        <v>19</v>
+      </c>
+      <c r="M501" t="n">
+        <v>8</v>
+      </c>
+      <c r="N501" t="n">
+        <v>33</v>
+      </c>
+      <c r="O501" t="n">
+        <v>19</v>
+      </c>
+      <c r="P501" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>17</v>
+      </c>
+      <c r="R501" t="n">
+        <v>15</v>
+      </c>
+      <c r="S501" t="n">
+        <v>19</v>
+      </c>
+      <c r="T501" t="n">
+        <v>1</v>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="V501" t="n">
+        <v>82</v>
+      </c>
+      <c r="W501" t="n">
+        <v>88.36</v>
+      </c>
+      <c r="X501" t="n">
+        <v>1.02987777274785</v>
+      </c>
+      <c r="Y501" t="n">
+        <v>80.36</v>
+      </c>
+      <c r="Z501" t="n">
+        <v>113.2404181184669</v>
+      </c>
+      <c r="AA501" t="n">
+        <v>0.9860509860509861</v>
+      </c>
+      <c r="AB501" t="n">
+        <v>104.9129989764586</v>
+      </c>
+      <c r="AC501" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="AD501" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="AE501" t="n">
+        <v>0.6307692307692307</v>
+      </c>
+      <c r="AF501" t="n">
+        <v>8.327419142008353</v>
+      </c>
+      <c r="AG501" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH501" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI501" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>32</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>200</v>
+      </c>
+      <c r="F502" t="n">
+        <v>89</v>
+      </c>
+      <c r="G502" t="n">
+        <v>18</v>
+      </c>
+      <c r="H502" t="n">
+        <v>27</v>
+      </c>
+      <c r="I502" t="n">
+        <v>13</v>
+      </c>
+      <c r="J502" t="n">
+        <v>29</v>
+      </c>
+      <c r="K502" t="n">
+        <v>14</v>
+      </c>
+      <c r="L502" t="n">
+        <v>16</v>
+      </c>
+      <c r="M502" t="n">
+        <v>5</v>
+      </c>
+      <c r="N502" t="n">
+        <v>23</v>
+      </c>
+      <c r="O502" t="n">
+        <v>12</v>
+      </c>
+      <c r="P502" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q502" t="n">
+        <v>14</v>
+      </c>
+      <c r="R502" t="n">
+        <v>27</v>
+      </c>
+      <c r="S502" t="n">
+        <v>19</v>
+      </c>
+      <c r="T502" t="n">
+        <v>0</v>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>2486543</t>
+        </is>
+      </c>
+      <c r="V502" t="n">
+        <v>86</v>
+      </c>
+      <c r="W502" t="n">
+        <v>77.03999999999999</v>
+      </c>
+      <c r="X502" t="n">
+        <v>1.155244029075805</v>
+      </c>
+      <c r="Y502" t="n">
+        <v>72.03999999999999</v>
+      </c>
+      <c r="Z502" t="n">
+        <v>123.5424764019989</v>
+      </c>
+      <c r="AA502" t="n">
+        <v>1.030680728667306</v>
+      </c>
+      <c r="AB502" t="n">
+        <v>118.7189398122584</v>
+      </c>
+      <c r="AC502" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="AD502" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE502" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF502" t="n">
+        <v>4.823536589740471</v>
+      </c>
+      <c r="AG502" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH502" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI502" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>32</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>200</v>
+      </c>
+      <c r="F503" t="n">
+        <v>82</v>
+      </c>
+      <c r="G503" t="n">
+        <v>18</v>
+      </c>
+      <c r="H503" t="n">
+        <v>40</v>
+      </c>
+      <c r="I503" t="n">
+        <v>12</v>
+      </c>
+      <c r="J503" t="n">
+        <v>29</v>
+      </c>
+      <c r="K503" t="n">
+        <v>10</v>
+      </c>
+      <c r="L503" t="n">
+        <v>14</v>
+      </c>
+      <c r="M503" t="n">
+        <v>5</v>
+      </c>
+      <c r="N503" t="n">
+        <v>19</v>
+      </c>
+      <c r="O503" t="n">
+        <v>18</v>
+      </c>
+      <c r="P503" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q503" t="n">
+        <v>8</v>
+      </c>
+      <c r="R503" t="n">
+        <v>19</v>
+      </c>
+      <c r="S503" t="n">
+        <v>15</v>
+      </c>
+      <c r="T503" t="n">
+        <v>4</v>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>2486541</t>
+        </is>
+      </c>
+      <c r="V503" t="n">
+        <v>91</v>
+      </c>
+      <c r="W503" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="X503" t="n">
+        <v>0.9860509860509861</v>
+      </c>
+      <c r="Y503" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="Z503" t="n">
+        <v>104.9129989764586</v>
+      </c>
+      <c r="AA503" t="n">
+        <v>1.02987777274785</v>
+      </c>
+      <c r="AB503" t="n">
+        <v>113.2404181184669</v>
+      </c>
+      <c r="AC503" t="n">
+        <v>0.131578947368421</v>
+      </c>
+      <c r="AD503" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="AE503" t="n">
+        <v>0.3692307692307693</v>
+      </c>
+      <c r="AF503" t="n">
+        <v>-8.327419142008353</v>
+      </c>
+      <c r="AG503" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH503" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI503" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>32</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>200</v>
+      </c>
+      <c r="F504" t="n">
+        <v>96</v>
+      </c>
+      <c r="G504" t="n">
+        <v>23</v>
+      </c>
+      <c r="H504" t="n">
+        <v>33</v>
+      </c>
+      <c r="I504" t="n">
+        <v>10</v>
+      </c>
+      <c r="J504" t="n">
+        <v>23</v>
+      </c>
+      <c r="K504" t="n">
+        <v>20</v>
+      </c>
+      <c r="L504" t="n">
+        <v>32</v>
+      </c>
+      <c r="M504" t="n">
+        <v>6</v>
+      </c>
+      <c r="N504" t="n">
+        <v>25</v>
+      </c>
+      <c r="O504" t="n">
+        <v>21</v>
+      </c>
+      <c r="P504" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q504" t="n">
+        <v>16</v>
+      </c>
+      <c r="R504" t="n">
+        <v>27</v>
+      </c>
+      <c r="S504" t="n">
+        <v>29</v>
+      </c>
+      <c r="T504" t="n">
+        <v>3</v>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="V504" t="n">
+        <v>81</v>
+      </c>
+      <c r="W504" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="X504" t="n">
+        <v>1.115241635687732</v>
+      </c>
+      <c r="Y504" t="n">
+        <v>80.08</v>
+      </c>
+      <c r="Z504" t="n">
+        <v>119.8801198801199</v>
+      </c>
+      <c r="AA504" t="n">
+        <v>0.8587786259541985</v>
+      </c>
+      <c r="AB504" t="n">
+        <v>99.60649286768323</v>
+      </c>
+      <c r="AC504" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="AD504" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AE504" t="n">
+        <v>0.4769230769230769</v>
+      </c>
+      <c r="AF504" t="n">
+        <v>20.27362701243665</v>
+      </c>
+      <c r="AG504" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH504" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI504" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>32</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>200</v>
+      </c>
+      <c r="F505" t="n">
+        <v>73</v>
+      </c>
+      <c r="G505" t="n">
+        <v>12</v>
+      </c>
+      <c r="H505" t="n">
+        <v>27</v>
+      </c>
+      <c r="I505" t="n">
+        <v>7</v>
+      </c>
+      <c r="J505" t="n">
+        <v>26</v>
+      </c>
+      <c r="K505" t="n">
+        <v>28</v>
+      </c>
+      <c r="L505" t="n">
+        <v>35</v>
+      </c>
+      <c r="M505" t="n">
+        <v>8</v>
+      </c>
+      <c r="N505" t="n">
+        <v>25</v>
+      </c>
+      <c r="O505" t="n">
+        <v>13</v>
+      </c>
+      <c r="P505" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q505" t="n">
+        <v>8</v>
+      </c>
+      <c r="R505" t="n">
+        <v>29</v>
+      </c>
+      <c r="S505" t="n">
+        <v>27</v>
+      </c>
+      <c r="T505" t="n">
+        <v>3</v>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>2486537</t>
+        </is>
+      </c>
+      <c r="V505" t="n">
+        <v>70</v>
+      </c>
+      <c r="W505" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="X505" t="n">
+        <v>0.9554973821989529</v>
+      </c>
+      <c r="Y505" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="Z505" t="n">
+        <v>106.7251461988304</v>
+      </c>
+      <c r="AA505" t="n">
+        <v>0.8838383838383838</v>
+      </c>
+      <c r="AB505" t="n">
+        <v>101.1560693641619</v>
+      </c>
+      <c r="AC505" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="AD505" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE505" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF505" t="n">
+        <v>5.56907683466855</v>
+      </c>
+      <c r="AG505" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH505" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI505" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>32</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>200</v>
+      </c>
+      <c r="F506" t="n">
+        <v>68</v>
+      </c>
+      <c r="G506" t="n">
+        <v>11</v>
+      </c>
+      <c r="H506" t="n">
+        <v>35</v>
+      </c>
+      <c r="I506" t="n">
+        <v>11</v>
+      </c>
+      <c r="J506" t="n">
+        <v>33</v>
+      </c>
+      <c r="K506" t="n">
+        <v>13</v>
+      </c>
+      <c r="L506" t="n">
+        <v>20</v>
+      </c>
+      <c r="M506" t="n">
+        <v>15</v>
+      </c>
+      <c r="N506" t="n">
+        <v>29</v>
+      </c>
+      <c r="O506" t="n">
+        <v>16</v>
+      </c>
+      <c r="P506" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q506" t="n">
+        <v>11</v>
+      </c>
+      <c r="R506" t="n">
+        <v>22</v>
+      </c>
+      <c r="S506" t="n">
+        <v>21</v>
+      </c>
+      <c r="T506" t="n">
+        <v>2</v>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="V506" t="n">
+        <v>77</v>
+      </c>
+      <c r="W506" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="X506" t="n">
+        <v>0.7744874715261959</v>
+      </c>
+      <c r="Y506" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z506" t="n">
+        <v>93.40659340659342</v>
+      </c>
+      <c r="AA506" t="n">
+        <v>0.918854415274463</v>
+      </c>
+      <c r="AB506" t="n">
+        <v>104.3360433604336</v>
+      </c>
+      <c r="AC506" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="AD506" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE506" t="n">
+        <v>0.5365853658536586</v>
+      </c>
+      <c r="AF506" t="n">
+        <v>-10.92944995384019</v>
+      </c>
+      <c r="AG506" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH506" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI506" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>32</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>200</v>
+      </c>
+      <c r="F507" t="n">
+        <v>81</v>
+      </c>
+      <c r="G507" t="n">
+        <v>20</v>
+      </c>
+      <c r="H507" t="n">
+        <v>35</v>
+      </c>
+      <c r="I507" t="n">
+        <v>10</v>
+      </c>
+      <c r="J507" t="n">
+        <v>25</v>
+      </c>
+      <c r="K507" t="n">
+        <v>11</v>
+      </c>
+      <c r="L507" t="n">
+        <v>17</v>
+      </c>
+      <c r="M507" t="n">
+        <v>4</v>
+      </c>
+      <c r="N507" t="n">
+        <v>24</v>
+      </c>
+      <c r="O507" t="n">
+        <v>29</v>
+      </c>
+      <c r="P507" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q507" t="n">
+        <v>11</v>
+      </c>
+      <c r="R507" t="n">
+        <v>17</v>
+      </c>
+      <c r="S507" t="n">
+        <v>20</v>
+      </c>
+      <c r="T507" t="n">
+        <v>3</v>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>2486539</t>
+        </is>
+      </c>
+      <c r="V507" t="n">
+        <v>92</v>
+      </c>
+      <c r="W507" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="X507" t="n">
+        <v>1.032110091743119</v>
+      </c>
+      <c r="Y507" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="Z507" t="n">
+        <v>108.7540279269602</v>
+      </c>
+      <c r="AA507" t="n">
+        <v>0.9603340292275574</v>
+      </c>
+      <c r="AB507" t="n">
+        <v>113.8613861386139</v>
+      </c>
+      <c r="AC507" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="AD507" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="AE507" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="AF507" t="n">
+        <v>-5.107358211653619</v>
+      </c>
+      <c r="AG507" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH507" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI507" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>32</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>200</v>
+      </c>
+      <c r="F508" t="n">
+        <v>92</v>
+      </c>
+      <c r="G508" t="n">
+        <v>24</v>
+      </c>
+      <c r="H508" t="n">
+        <v>51</v>
+      </c>
+      <c r="I508" t="n">
+        <v>10</v>
+      </c>
+      <c r="J508" t="n">
+        <v>27</v>
+      </c>
+      <c r="K508" t="n">
+        <v>14</v>
+      </c>
+      <c r="L508" t="n">
+        <v>20</v>
+      </c>
+      <c r="M508" t="n">
+        <v>15</v>
+      </c>
+      <c r="N508" t="n">
+        <v>25</v>
+      </c>
+      <c r="O508" t="n">
+        <v>22</v>
+      </c>
+      <c r="P508" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q508" t="n">
+        <v>9</v>
+      </c>
+      <c r="R508" t="n">
+        <v>20</v>
+      </c>
+      <c r="S508" t="n">
+        <v>17</v>
+      </c>
+      <c r="T508" t="n">
+        <v>1</v>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>2486539</t>
+        </is>
+      </c>
+      <c r="V508" t="n">
+        <v>81</v>
+      </c>
+      <c r="W508" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="X508" t="n">
+        <v>0.9603340292275574</v>
+      </c>
+      <c r="Y508" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="Z508" t="n">
+        <v>113.8613861386139</v>
+      </c>
+      <c r="AA508" t="n">
+        <v>1.032110091743119</v>
+      </c>
+      <c r="AB508" t="n">
+        <v>108.7540279269602</v>
+      </c>
+      <c r="AC508" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="AD508" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="AE508" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="AF508" t="n">
+        <v>5.107358211653619</v>
+      </c>
+      <c r="AG508" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH508" t="inlineStr">
+        <is>
+          <t>LEYMA CORUÑA</t>
+        </is>
+      </c>
+      <c r="AI508" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>32</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>200</v>
+      </c>
+      <c r="F509" t="n">
+        <v>81</v>
+      </c>
+      <c r="G509" t="n">
+        <v>13</v>
+      </c>
+      <c r="H509" t="n">
+        <v>30</v>
+      </c>
+      <c r="I509" t="n">
+        <v>11</v>
+      </c>
+      <c r="J509" t="n">
+        <v>37</v>
+      </c>
+      <c r="K509" t="n">
+        <v>22</v>
+      </c>
+      <c r="L509" t="n">
+        <v>28</v>
+      </c>
+      <c r="M509" t="n">
+        <v>13</v>
+      </c>
+      <c r="N509" t="n">
+        <v>21</v>
+      </c>
+      <c r="O509" t="n">
+        <v>12</v>
+      </c>
+      <c r="P509" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q509" t="n">
+        <v>15</v>
+      </c>
+      <c r="R509" t="n">
+        <v>29</v>
+      </c>
+      <c r="S509" t="n">
+        <v>26</v>
+      </c>
+      <c r="T509" t="n">
+        <v>0</v>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>2486544</t>
+        </is>
+      </c>
+      <c r="V509" t="n">
+        <v>96</v>
+      </c>
+      <c r="W509" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="X509" t="n">
+        <v>0.8587786259541985</v>
+      </c>
+      <c r="Y509" t="n">
+        <v>81.31999999999999</v>
+      </c>
+      <c r="Z509" t="n">
+        <v>99.60649286768323</v>
+      </c>
+      <c r="AA509" t="n">
+        <v>1.115241635687732</v>
+      </c>
+      <c r="AB509" t="n">
+        <v>119.8801198801199</v>
+      </c>
+      <c r="AC509" t="n">
+        <v>0.3421052631578947</v>
+      </c>
+      <c r="AD509" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AE509" t="n">
+        <v>0.5230769230769231</v>
+      </c>
+      <c r="AF509" t="n">
+        <v>-20.27362701243665</v>
+      </c>
+      <c r="AG509" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AH509" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AI509" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>32</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>200</v>
+      </c>
+      <c r="F510" t="n">
+        <v>89</v>
+      </c>
+      <c r="G510" t="n">
+        <v>17</v>
+      </c>
+      <c r="H510" t="n">
+        <v>30</v>
+      </c>
+      <c r="I510" t="n">
+        <v>13</v>
+      </c>
+      <c r="J510" t="n">
+        <v>35</v>
+      </c>
+      <c r="K510" t="n">
+        <v>16</v>
+      </c>
+      <c r="L510" t="n">
+        <v>20</v>
+      </c>
+      <c r="M510" t="n">
+        <v>14</v>
+      </c>
+      <c r="N510" t="n">
+        <v>20</v>
+      </c>
+      <c r="O510" t="n">
+        <v>14</v>
+      </c>
+      <c r="P510" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q510" t="n">
+        <v>9</v>
+      </c>
+      <c r="R510" t="n">
+        <v>23</v>
+      </c>
+      <c r="S510" t="n">
+        <v>22</v>
+      </c>
+      <c r="T510" t="n">
+        <v>2</v>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="V510" t="n">
+        <v>79</v>
+      </c>
+      <c r="W510" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="X510" t="n">
+        <v>1.07487922705314</v>
+      </c>
+      <c r="Y510" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="Z510" t="n">
+        <v>129.3604651162791</v>
+      </c>
+      <c r="AA510" t="n">
+        <v>1.004067107269954</v>
+      </c>
+      <c r="AB510" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AC510" t="n">
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="AD510" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AE510" t="n">
+        <v>0.576271186440678</v>
+      </c>
+      <c r="AF510" t="n">
+        <v>20.66481294236604</v>
+      </c>
+      <c r="AG510" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH510" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI510" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>32</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>200</v>
+      </c>
+      <c r="F511" t="n">
+        <v>79</v>
+      </c>
+      <c r="G511" t="n">
+        <v>15</v>
+      </c>
+      <c r="H511" t="n">
+        <v>23</v>
+      </c>
+      <c r="I511" t="n">
+        <v>11</v>
+      </c>
+      <c r="J511" t="n">
+        <v>30</v>
+      </c>
+      <c r="K511" t="n">
+        <v>16</v>
+      </c>
+      <c r="L511" t="n">
+        <v>22</v>
+      </c>
+      <c r="M511" t="n">
+        <v>6</v>
+      </c>
+      <c r="N511" t="n">
+        <v>19</v>
+      </c>
+      <c r="O511" t="n">
+        <v>23</v>
+      </c>
+      <c r="P511" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q511" t="n">
+        <v>16</v>
+      </c>
+      <c r="R511" t="n">
+        <v>22</v>
+      </c>
+      <c r="S511" t="n">
+        <v>22</v>
+      </c>
+      <c r="T511" t="n">
+        <v>0</v>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>2486540</t>
+        </is>
+      </c>
+      <c r="V511" t="n">
+        <v>89</v>
+      </c>
+      <c r="W511" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="X511" t="n">
+        <v>1.004067107269954</v>
+      </c>
+      <c r="Y511" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z511" t="n">
+        <v>108.695652173913</v>
+      </c>
+      <c r="AA511" t="n">
+        <v>1.07487922705314</v>
+      </c>
+      <c r="AB511" t="n">
+        <v>129.3604651162791</v>
+      </c>
+      <c r="AC511" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AD511" t="n">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="AE511" t="n">
+        <v>0.423728813559322</v>
+      </c>
+      <c r="AF511" t="n">
+        <v>-20.66481294236604</v>
+      </c>
+      <c r="AG511" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH511" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI511" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>32</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>200</v>
+      </c>
+      <c r="F512" t="n">
+        <v>77</v>
+      </c>
+      <c r="G512" t="n">
+        <v>16</v>
+      </c>
+      <c r="H512" t="n">
+        <v>34</v>
+      </c>
+      <c r="I512" t="n">
+        <v>9</v>
+      </c>
+      <c r="J512" t="n">
+        <v>32</v>
+      </c>
+      <c r="K512" t="n">
+        <v>18</v>
+      </c>
+      <c r="L512" t="n">
+        <v>20</v>
+      </c>
+      <c r="M512" t="n">
+        <v>10</v>
+      </c>
+      <c r="N512" t="n">
+        <v>28</v>
+      </c>
+      <c r="O512" t="n">
+        <v>12</v>
+      </c>
+      <c r="P512" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q512" t="n">
+        <v>9</v>
+      </c>
+      <c r="R512" t="n">
+        <v>21</v>
+      </c>
+      <c r="S512" t="n">
+        <v>20</v>
+      </c>
+      <c r="T512" t="n">
+        <v>5</v>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>2486538</t>
+        </is>
+      </c>
+      <c r="V512" t="n">
+        <v>68</v>
+      </c>
+      <c r="W512" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="X512" t="n">
+        <v>0.918854415274463</v>
+      </c>
+      <c r="Y512" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="Z512" t="n">
+        <v>104.3360433604336</v>
+      </c>
+      <c r="AA512" t="n">
+        <v>0.7744874715261959</v>
+      </c>
+      <c r="AB512" t="n">
+        <v>93.40659340659342</v>
+      </c>
+      <c r="AC512" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD512" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="AE512" t="n">
+        <v>0.4634146341463415</v>
+      </c>
+      <c r="AF512" t="n">
+        <v>10.92944995384019</v>
+      </c>
+      <c r="AG512" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH512" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI512" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>32</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>200</v>
+      </c>
+      <c r="F513" t="n">
+        <v>92</v>
+      </c>
+      <c r="G513" t="n">
+        <v>26</v>
+      </c>
+      <c r="H513" t="n">
+        <v>43</v>
+      </c>
+      <c r="I513" t="n">
+        <v>12</v>
+      </c>
+      <c r="J513" t="n">
+        <v>29</v>
+      </c>
+      <c r="K513" t="n">
+        <v>4</v>
+      </c>
+      <c r="L513" t="n">
+        <v>9</v>
+      </c>
+      <c r="M513" t="n">
+        <v>11</v>
+      </c>
+      <c r="N513" t="n">
+        <v>30</v>
+      </c>
+      <c r="O513" t="n">
+        <v>24</v>
+      </c>
+      <c r="P513" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q513" t="n">
+        <v>7</v>
+      </c>
+      <c r="R513" t="n">
+        <v>20</v>
+      </c>
+      <c r="S513" t="n">
+        <v>16</v>
+      </c>
+      <c r="T513" t="n">
+        <v>1</v>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>2486542</t>
+        </is>
+      </c>
+      <c r="V513" t="n">
+        <v>70</v>
+      </c>
+      <c r="W513" t="n">
+        <v>82.96000000000001</v>
+      </c>
+      <c r="X513" t="n">
+        <v>1.108968177434908</v>
+      </c>
+      <c r="Y513" t="n">
+        <v>71.96000000000001</v>
+      </c>
+      <c r="Z513" t="n">
+        <v>127.8488048916064</v>
+      </c>
+      <c r="AA513" t="n">
+        <v>0.8409418548774626</v>
+      </c>
+      <c r="AB513" t="n">
+        <v>96.89922480620154</v>
+      </c>
+      <c r="AC513" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD513" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="AE513" t="n">
+        <v>0.5324675324675324</v>
+      </c>
+      <c r="AF513" t="n">
+        <v>30.94958008540489</v>
+      </c>
+      <c r="AG513" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH513" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI513" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
+++ b/data/1FEB_25_26/players_25_26_1FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI529"/>
+  <dimension ref="A1:AI545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63435,6 +63435,1910 @@
       </c>
       <c r="AI529" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>34</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>200</v>
+      </c>
+      <c r="F530" t="n">
+        <v>74</v>
+      </c>
+      <c r="G530" t="n">
+        <v>14</v>
+      </c>
+      <c r="H530" t="n">
+        <v>28</v>
+      </c>
+      <c r="I530" t="n">
+        <v>10</v>
+      </c>
+      <c r="J530" t="n">
+        <v>37</v>
+      </c>
+      <c r="K530" t="n">
+        <v>16</v>
+      </c>
+      <c r="L530" t="n">
+        <v>19</v>
+      </c>
+      <c r="M530" t="n">
+        <v>8</v>
+      </c>
+      <c r="N530" t="n">
+        <v>27</v>
+      </c>
+      <c r="O530" t="n">
+        <v>13</v>
+      </c>
+      <c r="P530" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q530" t="n">
+        <v>5</v>
+      </c>
+      <c r="R530" t="n">
+        <v>17</v>
+      </c>
+      <c r="S530" t="n">
+        <v>22</v>
+      </c>
+      <c r="T530" t="n">
+        <v>0</v>
+      </c>
+      <c r="U530" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="V530" t="n">
+        <v>70</v>
+      </c>
+      <c r="W530" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="X530" t="n">
+        <v>0.9443593670239918</v>
+      </c>
+      <c r="Y530" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="Z530" t="n">
+        <v>105.1733939738488</v>
+      </c>
+      <c r="AA530" t="n">
+        <v>0.8892276422764228</v>
+      </c>
+      <c r="AB530" t="n">
+        <v>101.8626309662398</v>
+      </c>
+      <c r="AC530" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD530" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="AE530" t="n">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="AF530" t="n">
+        <v>3.310763007608955</v>
+      </c>
+      <c r="AG530" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH530" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI530" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>34</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>200</v>
+      </c>
+      <c r="F531" t="n">
+        <v>83</v>
+      </c>
+      <c r="G531" t="n">
+        <v>19</v>
+      </c>
+      <c r="H531" t="n">
+        <v>40</v>
+      </c>
+      <c r="I531" t="n">
+        <v>11</v>
+      </c>
+      <c r="J531" t="n">
+        <v>32</v>
+      </c>
+      <c r="K531" t="n">
+        <v>12</v>
+      </c>
+      <c r="L531" t="n">
+        <v>15</v>
+      </c>
+      <c r="M531" t="n">
+        <v>14</v>
+      </c>
+      <c r="N531" t="n">
+        <v>22</v>
+      </c>
+      <c r="O531" t="n">
+        <v>9</v>
+      </c>
+      <c r="P531" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q531" t="n">
+        <v>6</v>
+      </c>
+      <c r="R531" t="n">
+        <v>21</v>
+      </c>
+      <c r="S531" t="n">
+        <v>18</v>
+      </c>
+      <c r="T531" t="n">
+        <v>0</v>
+      </c>
+      <c r="U531" t="inlineStr">
+        <is>
+          <t>2486563</t>
+        </is>
+      </c>
+      <c r="V531" t="n">
+        <v>76</v>
+      </c>
+      <c r="W531" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="X531" t="n">
+        <v>0.9810874704491727</v>
+      </c>
+      <c r="Y531" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="Z531" t="n">
+        <v>117.5637393767705</v>
+      </c>
+      <c r="AA531" t="n">
+        <v>0.9753593429158111</v>
+      </c>
+      <c r="AB531" t="n">
+        <v>107.1630005640158</v>
+      </c>
+      <c r="AC531" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD531" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AE531" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AF531" t="n">
+        <v>10.40073881275475</v>
+      </c>
+      <c r="AG531" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH531" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI531" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>34</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>200</v>
+      </c>
+      <c r="F532" t="n">
+        <v>70</v>
+      </c>
+      <c r="G532" t="n">
+        <v>26</v>
+      </c>
+      <c r="H532" t="n">
+        <v>41</v>
+      </c>
+      <c r="I532" t="n">
+        <v>4</v>
+      </c>
+      <c r="J532" t="n">
+        <v>23</v>
+      </c>
+      <c r="K532" t="n">
+        <v>6</v>
+      </c>
+      <c r="L532" t="n">
+        <v>13</v>
+      </c>
+      <c r="M532" t="n">
+        <v>10</v>
+      </c>
+      <c r="N532" t="n">
+        <v>27</v>
+      </c>
+      <c r="O532" t="n">
+        <v>17</v>
+      </c>
+      <c r="P532" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q532" t="n">
+        <v>9</v>
+      </c>
+      <c r="R532" t="n">
+        <v>22</v>
+      </c>
+      <c r="S532" t="n">
+        <v>17</v>
+      </c>
+      <c r="T532" t="n">
+        <v>2</v>
+      </c>
+      <c r="U532" t="inlineStr">
+        <is>
+          <t>2486561</t>
+        </is>
+      </c>
+      <c r="V532" t="n">
+        <v>74</v>
+      </c>
+      <c r="W532" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="X532" t="n">
+        <v>0.8892276422764228</v>
+      </c>
+      <c r="Y532" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="Z532" t="n">
+        <v>101.8626309662398</v>
+      </c>
+      <c r="AA532" t="n">
+        <v>0.9443593670239918</v>
+      </c>
+      <c r="AB532" t="n">
+        <v>105.1733939738488</v>
+      </c>
+      <c r="AC532" t="n">
+        <v>0.2702702702702703</v>
+      </c>
+      <c r="AD532" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE532" t="n">
+        <v>0.5138888888888888</v>
+      </c>
+      <c r="AF532" t="n">
+        <v>-3.310763007608955</v>
+      </c>
+      <c r="AG532" t="inlineStr">
+        <is>
+          <t>ALIMERKA OVIEDO BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH532" t="inlineStr">
+        <is>
+          <t>CLOUD.GAL OURENSE BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI532" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>34</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>200</v>
+      </c>
+      <c r="F533" t="n">
+        <v>85</v>
+      </c>
+      <c r="G533" t="n">
+        <v>15</v>
+      </c>
+      <c r="H533" t="n">
+        <v>26</v>
+      </c>
+      <c r="I533" t="n">
+        <v>13</v>
+      </c>
+      <c r="J533" t="n">
+        <v>33</v>
+      </c>
+      <c r="K533" t="n">
+        <v>16</v>
+      </c>
+      <c r="L533" t="n">
+        <v>23</v>
+      </c>
+      <c r="M533" t="n">
+        <v>9</v>
+      </c>
+      <c r="N533" t="n">
+        <v>27</v>
+      </c>
+      <c r="O533" t="n">
+        <v>25</v>
+      </c>
+      <c r="P533" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q533" t="n">
+        <v>13</v>
+      </c>
+      <c r="R533" t="n">
+        <v>21</v>
+      </c>
+      <c r="S533" t="n">
+        <v>20</v>
+      </c>
+      <c r="T533" t="n">
+        <v>2</v>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>2486556</t>
+        </is>
+      </c>
+      <c r="V533" t="n">
+        <v>59</v>
+      </c>
+      <c r="W533" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="X533" t="n">
+        <v>1.035070628348758</v>
+      </c>
+      <c r="Y533" t="n">
+        <v>73.12</v>
+      </c>
+      <c r="Z533" t="n">
+        <v>116.2472647702407</v>
+      </c>
+      <c r="AA533" t="n">
+        <v>0.6602506714413607</v>
+      </c>
+      <c r="AB533" t="n">
+        <v>82.67937219730942</v>
+      </c>
+      <c r="AC533" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD533" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE533" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF533" t="n">
+        <v>33.56789257293127</v>
+      </c>
+      <c r="AG533" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH533" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI533" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>34</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>200</v>
+      </c>
+      <c r="F534" t="n">
+        <v>77</v>
+      </c>
+      <c r="G534" t="n">
+        <v>22</v>
+      </c>
+      <c r="H534" t="n">
+        <v>41</v>
+      </c>
+      <c r="I534" t="n">
+        <v>7</v>
+      </c>
+      <c r="J534" t="n">
+        <v>21</v>
+      </c>
+      <c r="K534" t="n">
+        <v>12</v>
+      </c>
+      <c r="L534" t="n">
+        <v>19</v>
+      </c>
+      <c r="M534" t="n">
+        <v>8</v>
+      </c>
+      <c r="N534" t="n">
+        <v>18</v>
+      </c>
+      <c r="O534" t="n">
+        <v>16</v>
+      </c>
+      <c r="P534" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q534" t="n">
+        <v>6</v>
+      </c>
+      <c r="R534" t="n">
+        <v>21</v>
+      </c>
+      <c r="S534" t="n">
+        <v>19</v>
+      </c>
+      <c r="T534" t="n">
+        <v>3</v>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="V534" t="n">
+        <v>70</v>
+      </c>
+      <c r="W534" t="n">
+        <v>76.36</v>
+      </c>
+      <c r="X534" t="n">
+        <v>1.008381351492928</v>
+      </c>
+      <c r="Y534" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="Z534" t="n">
+        <v>112.6389701579871</v>
+      </c>
+      <c r="AA534" t="n">
+        <v>0.8983572895277208</v>
+      </c>
+      <c r="AB534" t="n">
+        <v>106.1893203883495</v>
+      </c>
+      <c r="AC534" t="n">
+        <v>0.2580645161290323</v>
+      </c>
+      <c r="AD534" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE534" t="n">
+        <v>0.4262295081967213</v>
+      </c>
+      <c r="AF534" t="n">
+        <v>6.449649769637617</v>
+      </c>
+      <c r="AG534" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH534" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI534" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>34</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>200</v>
+      </c>
+      <c r="F535" t="n">
+        <v>70</v>
+      </c>
+      <c r="G535" t="n">
+        <v>18</v>
+      </c>
+      <c r="H535" t="n">
+        <v>30</v>
+      </c>
+      <c r="I535" t="n">
+        <v>8</v>
+      </c>
+      <c r="J535" t="n">
+        <v>34</v>
+      </c>
+      <c r="K535" t="n">
+        <v>10</v>
+      </c>
+      <c r="L535" t="n">
+        <v>16</v>
+      </c>
+      <c r="M535" t="n">
+        <v>10</v>
+      </c>
+      <c r="N535" t="n">
+        <v>15</v>
+      </c>
+      <c r="O535" t="n">
+        <v>10</v>
+      </c>
+      <c r="P535" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q535" t="n">
+        <v>12</v>
+      </c>
+      <c r="R535" t="n">
+        <v>21</v>
+      </c>
+      <c r="S535" t="n">
+        <v>19</v>
+      </c>
+      <c r="T535" t="n">
+        <v>1</v>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>2486562</t>
+        </is>
+      </c>
+      <c r="V535" t="n">
+        <v>100</v>
+      </c>
+      <c r="W535" t="n">
+        <v>83.03999999999999</v>
+      </c>
+      <c r="X535" t="n">
+        <v>0.8429672447013489</v>
+      </c>
+      <c r="Y535" t="n">
+        <v>73.03999999999999</v>
+      </c>
+      <c r="Z535" t="n">
+        <v>95.83789704271634</v>
+      </c>
+      <c r="AA535" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AB535" t="n">
+        <v>131.578947368421</v>
+      </c>
+      <c r="AC535" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AD535" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="AE535" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AF535" t="n">
+        <v>-35.74105032570471</v>
+      </c>
+      <c r="AG535" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH535" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI535" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>34</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>200</v>
+      </c>
+      <c r="F536" t="n">
+        <v>80</v>
+      </c>
+      <c r="G536" t="n">
+        <v>19</v>
+      </c>
+      <c r="H536" t="n">
+        <v>40</v>
+      </c>
+      <c r="I536" t="n">
+        <v>9</v>
+      </c>
+      <c r="J536" t="n">
+        <v>23</v>
+      </c>
+      <c r="K536" t="n">
+        <v>15</v>
+      </c>
+      <c r="L536" t="n">
+        <v>20</v>
+      </c>
+      <c r="M536" t="n">
+        <v>5</v>
+      </c>
+      <c r="N536" t="n">
+        <v>18</v>
+      </c>
+      <c r="O536" t="n">
+        <v>12</v>
+      </c>
+      <c r="P536" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q536" t="n">
+        <v>10</v>
+      </c>
+      <c r="R536" t="n">
+        <v>21</v>
+      </c>
+      <c r="S536" t="n">
+        <v>22</v>
+      </c>
+      <c r="T536" t="n">
+        <v>1</v>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>2486557</t>
+        </is>
+      </c>
+      <c r="V536" t="n">
+        <v>93</v>
+      </c>
+      <c r="W536" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="X536" t="n">
+        <v>0.9779951100244499</v>
+      </c>
+      <c r="Y536" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="Z536" t="n">
+        <v>104.1666666666667</v>
+      </c>
+      <c r="AA536" t="n">
+        <v>1.087973795039775</v>
+      </c>
+      <c r="AB536" t="n">
+        <v>121.6004184100418</v>
+      </c>
+      <c r="AC536" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AD536" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE536" t="n">
+        <v>0.3898305084745763</v>
+      </c>
+      <c r="AF536" t="n">
+        <v>-17.43375174337517</v>
+      </c>
+      <c r="AG536" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH536" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI536" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>34</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>200</v>
+      </c>
+      <c r="F537" t="n">
+        <v>93</v>
+      </c>
+      <c r="G537" t="n">
+        <v>27</v>
+      </c>
+      <c r="H537" t="n">
+        <v>40</v>
+      </c>
+      <c r="I537" t="n">
+        <v>10</v>
+      </c>
+      <c r="J537" t="n">
+        <v>22</v>
+      </c>
+      <c r="K537" t="n">
+        <v>9</v>
+      </c>
+      <c r="L537" t="n">
+        <v>17</v>
+      </c>
+      <c r="M537" t="n">
+        <v>9</v>
+      </c>
+      <c r="N537" t="n">
+        <v>27</v>
+      </c>
+      <c r="O537" t="n">
+        <v>21</v>
+      </c>
+      <c r="P537" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q537" t="n">
+        <v>16</v>
+      </c>
+      <c r="R537" t="n">
+        <v>22</v>
+      </c>
+      <c r="S537" t="n">
+        <v>21</v>
+      </c>
+      <c r="T537" t="n">
+        <v>5</v>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>2486557</t>
+        </is>
+      </c>
+      <c r="V537" t="n">
+        <v>80</v>
+      </c>
+      <c r="W537" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="X537" t="n">
+        <v>1.087973795039775</v>
+      </c>
+      <c r="Y537" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="Z537" t="n">
+        <v>121.6004184100418</v>
+      </c>
+      <c r="AA537" t="n">
+        <v>0.9779951100244499</v>
+      </c>
+      <c r="AB537" t="n">
+        <v>104.1666666666667</v>
+      </c>
+      <c r="AC537" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD537" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AE537" t="n">
+        <v>0.6101694915254238</v>
+      </c>
+      <c r="AF537" t="n">
+        <v>17.43375174337517</v>
+      </c>
+      <c r="AG537" t="inlineStr">
+        <is>
+          <t>GRUPO CAESA SEGUROS FC CARTAGENA CB</t>
+        </is>
+      </c>
+      <c r="AH537" t="inlineStr">
+        <is>
+          <t>GRUPO URETA TIZONA BURGOS</t>
+        </is>
+      </c>
+      <c r="AI537" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>34</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>200</v>
+      </c>
+      <c r="F538" t="n">
+        <v>102</v>
+      </c>
+      <c r="G538" t="n">
+        <v>18</v>
+      </c>
+      <c r="H538" t="n">
+        <v>36</v>
+      </c>
+      <c r="I538" t="n">
+        <v>20</v>
+      </c>
+      <c r="J538" t="n">
+        <v>41</v>
+      </c>
+      <c r="K538" t="n">
+        <v>6</v>
+      </c>
+      <c r="L538" t="n">
+        <v>9</v>
+      </c>
+      <c r="M538" t="n">
+        <v>14</v>
+      </c>
+      <c r="N538" t="n">
+        <v>25</v>
+      </c>
+      <c r="O538" t="n">
+        <v>25</v>
+      </c>
+      <c r="P538" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q538" t="n">
+        <v>11</v>
+      </c>
+      <c r="R538" t="n">
+        <v>27</v>
+      </c>
+      <c r="S538" t="n">
+        <v>12</v>
+      </c>
+      <c r="T538" t="n">
+        <v>2</v>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>2486555</t>
+        </is>
+      </c>
+      <c r="V538" t="n">
+        <v>72</v>
+      </c>
+      <c r="W538" t="n">
+        <v>91.96000000000001</v>
+      </c>
+      <c r="X538" t="n">
+        <v>1.109177903436277</v>
+      </c>
+      <c r="Y538" t="n">
+        <v>77.96000000000001</v>
+      </c>
+      <c r="Z538" t="n">
+        <v>130.8363263211903</v>
+      </c>
+      <c r="AA538" t="n">
+        <v>0.8174386920980926</v>
+      </c>
+      <c r="AB538" t="n">
+        <v>91.04704097116844</v>
+      </c>
+      <c r="AC538" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD538" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="AE538" t="n">
+        <v>0.5492957746478874</v>
+      </c>
+      <c r="AF538" t="n">
+        <v>39.7892853500219</v>
+      </c>
+      <c r="AG538" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH538" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI538" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>34</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>200</v>
+      </c>
+      <c r="F539" t="n">
+        <v>76</v>
+      </c>
+      <c r="G539" t="n">
+        <v>9</v>
+      </c>
+      <c r="H539" t="n">
+        <v>14</v>
+      </c>
+      <c r="I539" t="n">
+        <v>15</v>
+      </c>
+      <c r="J539" t="n">
+        <v>44</v>
+      </c>
+      <c r="K539" t="n">
+        <v>13</v>
+      </c>
+      <c r="L539" t="n">
+        <v>18</v>
+      </c>
+      <c r="M539" t="n">
+        <v>7</v>
+      </c>
+      <c r="N539" t="n">
+        <v>26</v>
+      </c>
+      <c r="O539" t="n">
+        <v>13</v>
+      </c>
+      <c r="P539" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q539" t="n">
+        <v>12</v>
+      </c>
+      <c r="R539" t="n">
+        <v>19</v>
+      </c>
+      <c r="S539" t="n">
+        <v>21</v>
+      </c>
+      <c r="T539" t="n">
+        <v>1</v>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>2486563</t>
+        </is>
+      </c>
+      <c r="V539" t="n">
+        <v>83</v>
+      </c>
+      <c r="W539" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="X539" t="n">
+        <v>0.9753593429158111</v>
+      </c>
+      <c r="Y539" t="n">
+        <v>70.92</v>
+      </c>
+      <c r="Z539" t="n">
+        <v>107.1630005640158</v>
+      </c>
+      <c r="AA539" t="n">
+        <v>0.9810874704491727</v>
+      </c>
+      <c r="AB539" t="n">
+        <v>117.5637393767705</v>
+      </c>
+      <c r="AC539" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AD539" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AE539" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="AF539" t="n">
+        <v>-10.40073881275475</v>
+      </c>
+      <c r="AG539" t="inlineStr">
+        <is>
+          <t>HLA ALICANTE</t>
+        </is>
+      </c>
+      <c r="AH539" t="inlineStr">
+        <is>
+          <t>CAJA RURAL CB ZAMORA</t>
+        </is>
+      </c>
+      <c r="AI539" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>34</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>200</v>
+      </c>
+      <c r="F540" t="n">
+        <v>68</v>
+      </c>
+      <c r="G540" t="n">
+        <v>11</v>
+      </c>
+      <c r="H540" t="n">
+        <v>24</v>
+      </c>
+      <c r="I540" t="n">
+        <v>9</v>
+      </c>
+      <c r="J540" t="n">
+        <v>25</v>
+      </c>
+      <c r="K540" t="n">
+        <v>19</v>
+      </c>
+      <c r="L540" t="n">
+        <v>23</v>
+      </c>
+      <c r="M540" t="n">
+        <v>4</v>
+      </c>
+      <c r="N540" t="n">
+        <v>24</v>
+      </c>
+      <c r="O540" t="n">
+        <v>15</v>
+      </c>
+      <c r="P540" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q540" t="n">
+        <v>17</v>
+      </c>
+      <c r="R540" t="n">
+        <v>16</v>
+      </c>
+      <c r="S540" t="n">
+        <v>22</v>
+      </c>
+      <c r="T540" t="n">
+        <v>1</v>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>2486559</t>
+        </is>
+      </c>
+      <c r="V540" t="n">
+        <v>85</v>
+      </c>
+      <c r="W540" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="X540" t="n">
+        <v>0.8933263268523384</v>
+      </c>
+      <c r="Y540" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="Z540" t="n">
+        <v>94.28729894620076</v>
+      </c>
+      <c r="AA540" t="n">
+        <v>0.9995296331138289</v>
+      </c>
+      <c r="AB540" t="n">
+        <v>111.7832719621252</v>
+      </c>
+      <c r="AC540" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AD540" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE540" t="n">
+        <v>0.4745762711864407</v>
+      </c>
+      <c r="AF540" t="n">
+        <v>-17.49597301592445</v>
+      </c>
+      <c r="AG540" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH540" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI540" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>34</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>200</v>
+      </c>
+      <c r="F541" t="n">
+        <v>72</v>
+      </c>
+      <c r="G541" t="n">
+        <v>11</v>
+      </c>
+      <c r="H541" t="n">
+        <v>32</v>
+      </c>
+      <c r="I541" t="n">
+        <v>8</v>
+      </c>
+      <c r="J541" t="n">
+        <v>22</v>
+      </c>
+      <c r="K541" t="n">
+        <v>26</v>
+      </c>
+      <c r="L541" t="n">
+        <v>32</v>
+      </c>
+      <c r="M541" t="n">
+        <v>9</v>
+      </c>
+      <c r="N541" t="n">
+        <v>23</v>
+      </c>
+      <c r="O541" t="n">
+        <v>13</v>
+      </c>
+      <c r="P541" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q541" t="n">
+        <v>20</v>
+      </c>
+      <c r="R541" t="n">
+        <v>12</v>
+      </c>
+      <c r="S541" t="n">
+        <v>26</v>
+      </c>
+      <c r="T541" t="n">
+        <v>0</v>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>2486555</t>
+        </is>
+      </c>
+      <c r="V541" t="n">
+        <v>102</v>
+      </c>
+      <c r="W541" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="X541" t="n">
+        <v>0.8174386920980926</v>
+      </c>
+      <c r="Y541" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="Z541" t="n">
+        <v>91.04704097116844</v>
+      </c>
+      <c r="AA541" t="n">
+        <v>1.109177903436277</v>
+      </c>
+      <c r="AB541" t="n">
+        <v>130.8363263211903</v>
+      </c>
+      <c r="AC541" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="AD541" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE541" t="n">
+        <v>0.4507042253521127</v>
+      </c>
+      <c r="AF541" t="n">
+        <v>-39.7892853500219</v>
+      </c>
+      <c r="AG541" t="inlineStr">
+        <is>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
+        </is>
+      </c>
+      <c r="AH541" t="inlineStr">
+        <is>
+          <t>HESTIA MENORCA</t>
+        </is>
+      </c>
+      <c r="AI541" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>34</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>200</v>
+      </c>
+      <c r="F542" t="n">
+        <v>85</v>
+      </c>
+      <c r="G542" t="n">
+        <v>24</v>
+      </c>
+      <c r="H542" t="n">
+        <v>42</v>
+      </c>
+      <c r="I542" t="n">
+        <v>8</v>
+      </c>
+      <c r="J542" t="n">
+        <v>28</v>
+      </c>
+      <c r="K542" t="n">
+        <v>13</v>
+      </c>
+      <c r="L542" t="n">
+        <v>16</v>
+      </c>
+      <c r="M542" t="n">
+        <v>9</v>
+      </c>
+      <c r="N542" t="n">
+        <v>22</v>
+      </c>
+      <c r="O542" t="n">
+        <v>14</v>
+      </c>
+      <c r="P542" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q542" t="n">
+        <v>8</v>
+      </c>
+      <c r="R542" t="n">
+        <v>22</v>
+      </c>
+      <c r="S542" t="n">
+        <v>16</v>
+      </c>
+      <c r="T542" t="n">
+        <v>4</v>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>2486559</t>
+        </is>
+      </c>
+      <c r="V542" t="n">
+        <v>68</v>
+      </c>
+      <c r="W542" t="n">
+        <v>85.03999999999999</v>
+      </c>
+      <c r="X542" t="n">
+        <v>0.9995296331138289</v>
+      </c>
+      <c r="Y542" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z542" t="n">
+        <v>111.7832719621252</v>
+      </c>
+      <c r="AA542" t="n">
+        <v>0.8933263268523384</v>
+      </c>
+      <c r="AB542" t="n">
+        <v>94.28729894620076</v>
+      </c>
+      <c r="AC542" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD542" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AE542" t="n">
+        <v>0.5254237288135594</v>
+      </c>
+      <c r="AF542" t="n">
+        <v>17.49597301592445</v>
+      </c>
+      <c r="AG542" t="inlineStr">
+        <is>
+          <t>INVEREADY GIPUZKOA</t>
+        </is>
+      </c>
+      <c r="AH542" t="inlineStr">
+        <is>
+          <t>MONBUS OBRADOIRO</t>
+        </is>
+      </c>
+      <c r="AI542" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>34</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>200</v>
+      </c>
+      <c r="F543" t="n">
+        <v>70</v>
+      </c>
+      <c r="G543" t="n">
+        <v>12</v>
+      </c>
+      <c r="H543" t="n">
+        <v>26</v>
+      </c>
+      <c r="I543" t="n">
+        <v>10</v>
+      </c>
+      <c r="J543" t="n">
+        <v>33</v>
+      </c>
+      <c r="K543" t="n">
+        <v>16</v>
+      </c>
+      <c r="L543" t="n">
+        <v>18</v>
+      </c>
+      <c r="M543" t="n">
+        <v>12</v>
+      </c>
+      <c r="N543" t="n">
+        <v>23</v>
+      </c>
+      <c r="O543" t="n">
+        <v>12</v>
+      </c>
+      <c r="P543" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q543" t="n">
+        <v>11</v>
+      </c>
+      <c r="R543" t="n">
+        <v>20</v>
+      </c>
+      <c r="S543" t="n">
+        <v>20</v>
+      </c>
+      <c r="T543" t="n">
+        <v>2</v>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>2486560</t>
+        </is>
+      </c>
+      <c r="V543" t="n">
+        <v>77</v>
+      </c>
+      <c r="W543" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="X543" t="n">
+        <v>0.8983572895277208</v>
+      </c>
+      <c r="Y543" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="Z543" t="n">
+        <v>106.1893203883495</v>
+      </c>
+      <c r="AA543" t="n">
+        <v>1.008381351492928</v>
+      </c>
+      <c r="AB543" t="n">
+        <v>112.6389701579871</v>
+      </c>
+      <c r="AC543" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD543" t="n">
+        <v>0.7419354838709677</v>
+      </c>
+      <c r="AE543" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+      <c r="AF543" t="n">
+        <v>-6.449649769637617</v>
+      </c>
+      <c r="AG543" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="AH543" t="inlineStr">
+        <is>
+          <t>FLEXICAR FUENLABRADA</t>
+        </is>
+      </c>
+      <c r="AI543" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>34</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>200</v>
+      </c>
+      <c r="F544" t="n">
+        <v>59</v>
+      </c>
+      <c r="G544" t="n">
+        <v>13</v>
+      </c>
+      <c r="H544" t="n">
+        <v>47</v>
+      </c>
+      <c r="I544" t="n">
+        <v>7</v>
+      </c>
+      <c r="J544" t="n">
+        <v>21</v>
+      </c>
+      <c r="K544" t="n">
+        <v>12</v>
+      </c>
+      <c r="L544" t="n">
+        <v>19</v>
+      </c>
+      <c r="M544" t="n">
+        <v>18</v>
+      </c>
+      <c r="N544" t="n">
+        <v>18</v>
+      </c>
+      <c r="O544" t="n">
+        <v>7</v>
+      </c>
+      <c r="P544" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q544" t="n">
+        <v>13</v>
+      </c>
+      <c r="R544" t="n">
+        <v>21</v>
+      </c>
+      <c r="S544" t="n">
+        <v>21</v>
+      </c>
+      <c r="T544" t="n">
+        <v>4</v>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>2486556</t>
+        </is>
+      </c>
+      <c r="V544" t="n">
+        <v>85</v>
+      </c>
+      <c r="W544" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="X544" t="n">
+        <v>0.6602506714413607</v>
+      </c>
+      <c r="Y544" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="Z544" t="n">
+        <v>82.67937219730942</v>
+      </c>
+      <c r="AA544" t="n">
+        <v>1.035070628348758</v>
+      </c>
+      <c r="AB544" t="n">
+        <v>116.2472647702407</v>
+      </c>
+      <c r="AC544" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD544" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE544" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF544" t="n">
+        <v>-33.56789257293127</v>
+      </c>
+      <c r="AG544" t="inlineStr">
+        <is>
+          <t>FIBWI MALLORCA BASQUET PALMA</t>
+        </is>
+      </c>
+      <c r="AH544" t="inlineStr">
+        <is>
+          <t>PALMER BASKET MALLORCA PALMA</t>
+        </is>
+      </c>
+      <c r="AI544" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Liga Regular Único</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>34</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>200</v>
+      </c>
+      <c r="F545" t="n">
+        <v>100</v>
+      </c>
+      <c r="G545" t="n">
+        <v>22</v>
+      </c>
+      <c r="H545" t="n">
+        <v>34</v>
+      </c>
+      <c r="I545" t="n">
+        <v>13</v>
+      </c>
+      <c r="J545" t="n">
+        <v>34</v>
+      </c>
+      <c r="K545" t="n">
+        <v>17</v>
+      </c>
+      <c r="L545" t="n">
+        <v>25</v>
+      </c>
+      <c r="M545" t="n">
+        <v>14</v>
+      </c>
+      <c r="N545" t="n">
+        <v>31</v>
+      </c>
+      <c r="O545" t="n">
+        <v>20</v>
+      </c>
+      <c r="P545" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q545" t="n">
+        <v>11</v>
+      </c>
+      <c r="R545" t="n">
+        <v>19</v>
+      </c>
+      <c r="S545" t="n">
+        <v>21</v>
+      </c>
+      <c r="T545" t="n">
+        <v>0</v>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>2486562</t>
+        </is>
+      </c>
+      <c r="V545" t="n">
+        <v>70</v>
+      </c>
+      <c r="W545" t="n">
+        <v>90</v>
+      </c>
+      <c r="X545" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="Y545" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z545" t="n">
+        <v>131.578947368421</v>
+      </c>
+      <c r="AA545" t="n">
+        <v>0.8429672447013489</v>
+      </c>
+      <c r="AB545" t="n">
+        <v>95.83789704271634</v>
+      </c>
+      <c r="AC545" t="n">
+        <v>0.4827586206896552</v>
+      </c>
+      <c r="AD545" t="n">
+        <v>0.7560975609756098</v>
+      </c>
+      <c r="AE545" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AF545" t="n">
+        <v>35.74105032570471</v>
+      </c>
+      <c r="AG545" t="inlineStr">
+        <is>
+          <t>GRUPO ALEGA CANTABRIA</t>
+        </is>
+      </c>
+      <c r="AH545" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="AI545" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
